--- a/csv processed/02 – products_cleaned.xlsx
+++ b/csv processed/02 – products_cleaned.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L52"/>
+  <dimension ref="A1:L53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,316 +493,316 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MACRO Photography Workshops Warwickshire - Various</t>
+          <t>Lightroom Courses for Beginners Photo Editing - Coventry</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Abstract and Macro Photography Workshop . Learn about camera settings, lens use, controlling DoF and composition. Various Dates in Warwickshire | Half DaySummaryLocation: WarwickshireDates: Macro Photography WorkshopsMacro Photography - Sun Aug 23rd - 10:30am - 12:30pmMacro Photography - Tue Sep 8th - 6:00pm - 8:00pmParticipants: Max 4Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: Digital Camera and Tripod, Zoom or Macro LensMacro Photography Workshop Event Details: Macro Photography and AbstractDescription: This Abstract and Macro Photography Workshop takes place at a Warwickshire location and is open to all levels and any camera. Macro is where ordinary surroundings become extraordinary — get close and a tree trunk, a piece of weathered stone or a patch of water reveals shapes, colours, tones and patterns most people walk straight past. The whole session is about learning to see them, and then photograph them with intention.The technical craft matters here — and we'll cover it properly — but it's the floor, not the point. Working around the area together, Alan guides you through the settings that give you control: getting sharp focus and using a macro lens or zoom, controlling depth of field to isolate your subject, and building a composition with real intention. From there the real work begins — training your eye to find the abstract within the ordinary, to read tone, shadow and highlight, and to treat colour as a harmony to compose with rather than a loud effect to chase. The aim is never the obvious close-up everyone takes, but an image that's considered and your own.It's a small group of no more than four, taught personally by an award-winning professional photographer, so every person gets real one-to-one guidance in the field — briefing and set-up, then shooting with reviews and tuition as you go. You'll leave with your own macro and abstract images, and a sharper, more intentional way of seeing detail, colour and light that changes how you photograph everything afterwards.</t>
+          <t>For those who want to implement the best workflow for image management and all the dos and don'ts of post-production with these Photo Editing Classes with LightroomAdobe Lightroom Classic Courses for Beginners - CoventryLocation: 45 Hathaway Road, Coventry, CV4 9HWDuration: 3 × 2hr evening classes (19:00–21:00)Participants: Max 3Start Dates:Lightroom Editing CourseCoventry 3 wks - Mon 7 Sep - 21 Sep 2026Coventry 3 wks - Thu 12 Nov - 26 Nov 2026Coventry 3 wks - Tue 12 Jan - 26 Jan 2027Coventry 3 wks - Thu 6 May - 20 May 2027Level: BeginnersDescription: A practical three-week evening course that takes you from a messy photo library and untouched RAW files to a finished, repeatable Lightroom Classic workflow — working on your own laptop throughout.Week 1 is about getting organised: catalogues, importing, collections, keywords and star ratings, so you can find and manage your photos for good rather than losing them across folders.Week 2 moves on to global adjustments — reading the histogram, then exposure, white balance, contrast, tone curves and sharpening — the core develop tools that do most of the work on any image.Week 3 covers local adjustments — graduated and radial filters, adjustment brushes and spot removal — and pulling it together into a consistent, repeatable style across your photos.With a maximum of three people, you get real hands-on help on your own screen whenever you hit a problem, plus course notes for each module and practical assignments to work on between sessions. Beginners welcome — no editing experience needed; just bring a laptop with Adobe Lightroom Classic installed and an active subscription.Equipment: You will need a laptop with Adobe Lightroom Classic subscription and the App installed. Alan will provide you with a training Lightroom Library with images and use that to explain and then demonstrate the various tools.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/25c550a3-a242-4303-a11b-367dd7055dbe/Abstract%2Band%2BMacro%2BPhotography%2BWorkshops%2B%25282%2529.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/fe40a5e1-7fa2-4057-982e-555479b97022/Lightroom+courses+-+photo+editing+course.png</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/abstract-and-macro-photography-workshops</t>
+          <t>https://www.alanranger.com/photography-services-near-me/lightroom-courses-for-beginners-coventry</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - half-day photo workshops, Macro &amp; Abstract</t>
+          <t>photography-classes, photography-courses, photo editing, lightroom</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8482281", "price": "65.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Sun Aug 23rd - 10:30am - 12:30pm"}, {"@type": "Offer", "sku": "SQ8660736", "price": "65.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Tue Sep 8th - 6:00pm - 8:00pm"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ7526725", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Coventry 3 wks - Mon 7 Sep - 21 Sep 2026"}, {"@type": "Offer", "sku": "SQ6831161", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Coventry 3 wks - Thu 12 Nov - 26 Nov 2026"}, {"@type": "Offer", "sku": "SQ1021857", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Coventry 3 wks - Tue 12 Jan - 26 Jan 2027"}, {"@type": "Offer", "sku": "SQ3349262", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Coventry 3 wks - Thu 6 May - 20 May 2027"}]</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H2" t="n">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="I2" t="n">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>SQ8482281, SQ8660736</t>
+          <t>SQ7526725, SQ6831161, SQ1021857, SQ3349262</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>SQ8482281</t>
+          <t>SQ7526725</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>course</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Annual Pick N Mix Subscription | Interest Free Payment Plan</t>
+          <t>RPS Courses - Independent RPS Mentoring for RPS Distinctions</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Make a one-off payment by bank transfer or through this to get 20% discount on events booked for 12 Months | Tailored Pick N Mix photography training plan</t>
+          <t>RPS Courses - Independant RPS Mentoring for RPS Distinctions - Start anytime, you select a package of Zoom sessions within twelve months at intervals to suit youDescription: Independent one-to-one RPS mentoring for your Licentiate (LRPS) or Associate (ARPS) distinction — online via Zoom, with a mentor who holds both distinctions himself and has a 100% pass rate to date. Most photographers who fall short don't fail on technique — they submit a collection of strong individual images rather than a planned, cohesive panel, and a panel is judged as a whole. That judgement — image selection, sequencing, the hanging plan and your Statement of Intent — is exactly what mentoring brings. We work in three stages: plan the panel, build and refine it, then test readiness before you submit. Sessions are flexible 1-hour Zoom slots — buy only what you need and book your dates later, across up to twelve months. Start fresh, or revise a panel that didn't pass first time.Format: One-to-one, online via Zoom — private and personal to you and your panel.Equipment Needed: Zoom App; free Dropbox account for sharing portfolios and updated images.Terms: A package of Zoom sessions must be used within 12 months of purchase or it is forfeited. You can extend the timeline or purchase additional sessions if needed.Method: Honest technical and creative critique with suggestions for improvement; advice on image selection, sequencing, the hanging plan and your Statement of Intent.Package Options: Choose Mon–Fri 9am–5pm daytime rates, or Mon–Sun 9am–9pm for evening and weekend flexibility.1 × 1hr — single session (fact-find &amp; review)4 × 1hr — 15% off (reset a failed panel)6 × 1hr — 20% off (from scratch, recommended)8 × 1hr — 25% off (extended panel build)12 × 1hr — 25% off (best value, full programme)More Details: about the RPS Mentoring Course</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/4c6bb1a6-8752-4aea-a250-484fb1acdf75/Photography+Payment+Plan.png</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707307452323-G3C2AIXAHRLLVB36VASA/RPS+Courses.jpg</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/annual-pick-n-mix-subscription</t>
+          <t>https://www.alanranger.com/photography-services-near-me/rps-mentoring-photography-course</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>photography-classes, photography-courses, photography-workshops</t>
+          <t>1-2-1-private-lessons, photography-classes, photography-courses, photography-tuition, rps</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ0754560", "price": "1200.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "1 x £1200 = £1200"}, {"@type": "Offer", "sku": "SQ7502565", "price": "1500.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "1 x £1500 = £1500"}, {"@type": "Offer", "sku": "SQ1485137", "price": "2000.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "1 x £2000 = £2000"}, {"@type": "Offer", "sku": "SQ7001156", "price": "2500.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "1 x £2500 = £2500"}, {"@type": "Offer", "sku": "SQ2612014", "price": "3000.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "1 x £3000 = £3000"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ7839038", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Mon- Fri 9am-5pm 1 x 1hr"}, {"@type": "Offer", "sku": "SQ3867813", "price": "170.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Mon- Fri 9am-5pm 4 x 1hr"}, {"@type": "Offer", "sku": "SQ8903198", "price": "240.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Mon- Fri 9am-5pm 6 x 1hr"}, {"@type": "Offer", "sku": "SQ4831915", "price": "300.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Mon- Fri 9am-5pm  8x 1hr"}, {"@type": "Offer", "sku": "SQ1077689", "price": "450.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Mon- Fri 9am-5pm 12 x 1hr"}, {"@type": "Offer", "sku": "SQ8233730", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Mon- Sun 9am-9pm 1 x 1hr"}, {"@type": "Offer", "sku": "SQ9139531", "price": "255.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Mon- Sun 9am-9pm 4 x 1hr"}, {"@type": "Offer", "sku": "SQ0776423", "price": "360.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Mon- Sun 9am-9pm 6 x 1hr"}, {"@type": "Offer", "sku": "SQ2385997", "price": "450.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Mon- Sun 9am-9pm 8 x 1hr"}, {"@type": "Offer", "sku": "SQ9440259", "price": "675.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Mon- Sun 9am-9pm 12 x 1hr"}]</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H3" t="n">
-        <v>1200</v>
+        <v>50</v>
       </c>
       <c r="I3" t="n">
-        <v>3000</v>
+        <v>675</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>SQ0754560, SQ7502565, SQ1485137, SQ7001156, SQ2612014</t>
+          <t>SQ7839038, SQ3867813, SQ8903198, SQ4831915, SQ1077689, SQ8233730, SQ9139531, SQ0776423, SQ2385997, SQ9440259</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>SQ0754560</t>
+          <t>SQ7839038</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>course</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BATSFORD Arboretum Autumn Photography Workshops 23 - 31 Oct</t>
+          <t>Professional Digital DSLR Camera Sensor Clean | Coventry</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Batsford Arboretum Photography Workshops in autumn. Enjoy the colour and expert photographic guidance | Half or One Day Sessions | Any Level and CameraSummaryLocation: Batsford Arboretum - GloucestershireDates: Fri 23 Oct – Sat 31 Oct 2026Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless CameraPhotography Workshop Event Batsford ArboretumDescription: For nearly fifteen years I've returned to Batsford Arboretum each autumn, and in that time I've come to know every corner of it — which spot works at which hour, where the light falls and the angles that turn one of Britain's finest tree collections into a photograph rather than a snapshot. This workshop is built on that knowledge. Open to all levels and any camera, it's a chance to photograph Batsford's autumn colour with someone who can put you in the right place at the right time, so you can spend your energy on the thing that actually matters: seeing.Because that's where this workshop really lives. We'll cover the technical setup — exposure, depth of field, the settings that give you control — but that's only the floor. The real work is learning to look: to compose with intention and move beyond the cliché shot everyone else comes home with, to find the close-up, the macro detail and the quiet abstract as readily as the wide vista, and above all to read light, texture and colour as a harmony rather than chasing the over-saturated "look how vivid this is" image. Colour handled with restraint and relationship will always outlast colour shouted.With small numbers and genuine one-to-one attention throughout, you'll have the time and space to slow down and work properly — and you can choose a half-day morning or afternoon session, or a full day in the colour. You'll leave not just with a set of strong autumn images, but with a way of seeing — light, texture and composition — that changes how you photograph colour, woodland and the natural world wherever you go next.Good to know: the workshop price includes entrance to the Arboretum. On the early morning session we have exclusive access before the gardens open to the public — the quiet best light of the day, with the place to ourselves. A grab-and-go breakfast is available from around 9:30am, and the café and outdoor snack bar are open through the day for lunch and refreshments, with toilets on site by the reception area.</t>
+          <t>Get a camera sensor clean in Coventry . Sensor checked and cleaned using professional equipment, swabs | Full Frame and Cropped Sensors | 24hr Turnaround</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1715155253660-I9BNV2CJV5TPWB56WH93/Batsford+Autumn+7.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1522495201980-KD6BKH54J01HJR93XXR6/photography-support-Services-1.png</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/batsford-arboretum-photography-workshops</t>
+          <t>https://www.alanranger.com/photography-services-near-me/camera-sensor-clean</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - half-day photo workshops, - one day photo workshops, Landscape, Woodlands, autumn</t>
+          <t>photography-services</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ0818501", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Fri 23  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7647904", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Fri 23 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9436105", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Fri 23 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1204772", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Sat 24  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9290465", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Sat 24 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7375084", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Sat 24 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0264308", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Sun 25 Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9938663", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Sun 25 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0693365", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Sun 25 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3442432", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Thu 29  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8197555", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Thu 29 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9853668", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Thu 29 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0732756", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Fri 30  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ6382131", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Fri 30 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ4533936", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Fri 30 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ4668363", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Sat 31  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5203247", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Sat 31 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1249736", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Sat 31 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ5650040", "price": "30.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29"}]</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>99</v>
+        <v>30</v>
       </c>
       <c r="I4" t="n">
-        <v>150</v>
+        <v>30</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>SQ0818501, SQ7647904, SQ9436105, SQ1204772, SQ9290465, SQ7375084, SQ0264308, SQ9938663, SQ0693365, SQ3442432, SQ8197555, SQ9853668, SQ0732756, SQ6382131, SQ4533936, SQ4668363, SQ5203247, SQ1249736</t>
+          <t>SQ5650040</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>SQ0818501</t>
+          <t>SQ5650040</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>product</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Beginners Photography Course | 3 Weekly Evening Classes</t>
+          <t>WARWICKSHIRE Woodland PHOTOGRAPHY WALKS - Monthly - 2hrs</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Beginners Photography Course CoventrySummary - Camera Courses For Beginners - Key InformationLocation: 45 Hathaway Road, Coventry, CV4 9HWDuration: 3 × 2hr evening classes (19:00–21:00)Participants: Max 4Start Dates: Beginners Photography Course3wks Wednesdays - Jul 1 - Jul 15 Coventry3wks Mondays - Jul 6 - Jul 20 Coventry3wks Thursdays - Sep 17 - Oct 1 Coventry3wks Tuesdays - Sep 22 - Oct 6 Coventry3wks Mondays - Oct 12 - Oct 26 Coventry3wks Wednesdays - Oct 14 - Oct 28 Coventry3wks Mondays - Nov 9 - Nov 23 Coventry3wks Tuesdays - Dec 1 - Dec 15 Coventry3wks Wednesdays - Jan 13 - Jan 27 Coventry3wks Thursdays - Jan 28 - Feb 11 CoventryLevel: Beginner and NoviceDescription:A practical three-week evening course that takes you from Auto to confident manual control, built around your own camera.Week 1 is about getting off Auto for good — the exposure modes, then aperture, shutter speed and ISO, and how they work together as the exposure triangle, with practical assignments to put it into practice.Week 2 goes deeper into getting the exposure right: manual exposure, metering, reading the histogram, exposure compensation, stops and dynamic range, and bracketing — followed by a review of your assignment work.Week 3 moves on to focusing and depth of field, white balance, JPEG vs RAW, and the foundations of composition, finishing with a final assignment review.With a maximum of four people, you get genuine attention and plenty of room to ask questions, and you'll leave with a printed course book covering every topic to revisit at home. Beginner and novice friendly — just bring a DSLR or mirrorless camera with manual modes.What You'll Learn: How to get off Auto and use manual exposure, aperture, shutter speed and ISO; how focus works; and the foundations of composition to make stronger, more deliberate photos.Includes: A printed course book covering every topic, so you can revisit it all afterwards.Equipment: A DSLR or mirrorless camera with manual exposure modes.</t>
+          <t>Informal woodland photography walks in and around Warwickshire Woodlands - All Levels and types of camera welcome - Length 2hrs. 9:30 am-11:30 amSummaryLocation: Various Warwickshire Woodlands2026 - 09:30 - 11:30Hay Woods - Solihull Fri Jan 2Tile Hill Nature Reserve Mon Feb 2Millisons Wood, Meriden -Sun May 3Piles Coppice, Coventry - Fri Oct 16Crackley Wood, Kenilworth - Fri Nov 6Hay Woods - Solihull Fri Dec 4Participants: Max 6Fitness: 1. EasyExperience Level: Novice to BeginnerEquipment Needed: Phone or Digital CameraPhotography Workshop Event Details: Woodland WalksDescription: This is a relaxed, informal woodland photography walk through the beautiful woodlands in and around Warwickshire — a regular monthly outing open to all levels and any camera. It's a gentle two hours among the trees with camera in hand, and it's as much about slowing down and reconnecting with nature as it is about photography: we walk, we observe, we take in the wood around us, and we make a photograph when something moves us to — or simply enjoy being there.My aim isn't to tell you what to shoot. It's to help you develop your own visual awareness, your photographic eye and your personal interpretation of what's in front of you. Woodland is one of the hardest subjects there is — chaotic, cluttered, endlessly busy — so the real work is learning to see: to simplify the scene, to find the quiet order and the light within the tangle, and to photograph the close-up, the intimate detail and the abstract as readily as the wider woodland view. I'm always on hand for the "how to" — the settings and the craft — but in service of what you feel drawn to express, not a shot list.The walks rotate through a lovely variety of local woodlands across the seasons — among them Crackley Wood, Hay Wood, Tile Hill Nature Reserve, Millisons Wood and Piles Coppice — so there's always something new to see. With no more than six of us it stays personal and unhurried, with one-to-one guidance whenever you want it. You'll come away with images that are genuinely your own — and a calmer, more intentional way of seeing that stays with you long after the walk.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/773443e9-940a-440b-9faa-14e22b8c4236/beginners+photography+classes+coventry.png</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707217364251-99ITJH38DI58S3G3YA47/Woodland+Photography+Walk.jpg</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/beginners-photography-course</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/woodland-photography-walk-warwickshire</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>photography-classes, photography-courses</t>
+          <t>All Photography Workshops, - half-day photo workshops, Woodlands</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ6482854", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "3wks Thursdays - Sep 17 - Oct 1 Coventry"}, {"@type": "Offer", "sku": "SQ1702168", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "3wks Tuesdays - Sep 22 - Oct 6 Coventry"}, {"@type": "Offer", "sku": "SQ6875626", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "3wks Mondays - Oct 12 - Oct 26 Coventry"}, {"@type": "Offer", "sku": "SQ8844762", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "3wks Wednesdays - Oct 14 - Oct 28 Coventry"}, {"@type": "Offer", "sku": "SQ5616379", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "3wks Mondays - Nov 9 - Nov 23 Coventry"}, {"@type": "Offer", "sku": "SQ3231903", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "3wks Tuesdays - Dec 1 - Dec 15 Coventry"}, {"@type": "Offer", "sku": "SQ5559634", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "3wks Wednesdays - Jan 13 - Jan 27 Coventry"}, {"@type": "Offer", "sku": "SQ0659870", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "3wks Thursdays - Jan 28 - Feb 11 Coventry"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ1654264", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Fri Jan 2 Hay Woods - Solihull"}, {"@type": "Offer", "sku": "SQ1288994", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Mon Feb 2 - Tile Hill Nature Reserve - Coventry"}, {"@type": "Offer", "sku": "SQ0063623", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Sun May 3 - Millisons Wood, Meriden"}, {"@type": "Offer", "sku": "SQ6524101", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Fri Oct 16 - Piles Coppice, Coventry"}, {"@type": "Offer", "sku": "SQ7078023", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Fri Nov 6 - Crackley Wood, Kenilworth"}, {"@type": "Offer", "sku": "SQ3819844", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Fri Dec 4 - Hay Wood - Lapworth"}]</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H5" t="n">
-        <v>150</v>
+        <v>15</v>
       </c>
       <c r="I5" t="n">
-        <v>150</v>
+        <v>15</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>SQ6482854, SQ1702168, SQ6875626, SQ8844762, SQ5616379, SQ3231903, SQ5559634, SQ0659870</t>
+          <t>SQ1654264, SQ1288994, SQ0063623, SQ6524101, SQ7078023, SQ3819844</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>SQ6482854</t>
+          <t>SQ1654264</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>course</t>
+          <t>event</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Beginners Portrait Photography Course - Coventry 11 Oct -25</t>
+          <t>4 x 2hr Private Photography Classes - Face to Face Coventry</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Beginners Portrait Photography Course Location: 17A Spon Street, Coventry, CV1 3BA (Pay &amp; Display, or Skydome Multi-Storey, 15 Croft Rd, CV1 3LD)Duration: 1-day course, 9am–5pm (approx 1hr lunch)Participants: Max 4Start Dates: Portrait Photography CourseSaturday 11 Oct 2025 - CoventryLevel: BeginnerDescription: A 1-day portrait photography course suitable for any amateur who wants to learn the fundamentals — lighting, exposure, camera settings and composition.Equipment: A DSLR or mirrorless camera with manual exposure modes, and a good understanding of the basics of exposure, aperture, shutter speed and ISO. Ideally a zoom lens (50mm+) or a 50mm prime.</t>
+          <t>4 × 2hr Private Photography Classes (Face to Face, Coventry)Summary - Private Photography Classes (Face to Face) - Key InformationLocation: Coventry (face to face)Format: Private 1-2-1 tuition, in personSessions: 4 × 2hr classes, scheduled to suit youAvailability: Mon–Fri, 9am–5pmValidity: Pay now, book dates later — you'll be sent a code to book your datesLevel: All levels, beginner to advancedDescription: A package of four private, face-to-face photography classes in Coventry — two hours each, tailored entirely to you and what you want to learn or improve.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/7d4f9092-b44c-4d74-b858-cc2bcf675b8b/portraits+class.png</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/17054018-4804-4c2d-ad29-c57cba809028/face+to+face+private+photography+classes.png</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/beginners-portrait-photography-course</t>
+          <t>https://www.alanranger.com/photography-services-near-me/four-private-photography-classes</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>photography-classes, photography-courses</t>
+          <t>1-2-1-private-lessons, photography-tuition</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ2592535", "price": "195.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ6583676", "price": "360.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "4 x 2hr sessions - weekday daytime", "priceSpecification": {"price": "360.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G6" t="n">
         <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>195</v>
+        <v>360</v>
       </c>
       <c r="I6" t="n">
-        <v>195</v>
+        <v>360</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>SQ2592535</t>
+          <t>SQ6583676</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>SQ2592535</t>
+          <t>SQ6583676</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>course</t>
+          <t>product</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BLUEBELL WOODLANDS Photography - Warks - 20 Apr - 30 Apr</t>
+          <t>BATSFORD Arboretum Autumn Photography Workshops 23 - 31 Oct</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bluebell woodlands photography workshop - Choose a sunrise or mid-morning 4hr bluebell photography shoot or both sessions at this private bluebell woodland with exclusive accessSummaryLocation: Warwickshire (Near Stratford Upon Avon)Dates (are subject to the timing of the bluebell flowering and their peek display - you will be contacted nearer the time to consider alt-dates, please pick your initial first date choice but be flexible if nearer the time it needs to change)Tue-20-Apr-27Wed-21-Apr-27Thu-22-Apr-27Fri-23-Apr-27Sat-24-Apr-27Sun-25-Apr-27Mon-26-Apr-27Tue-27-Apr-27Wed-28-Apr-27Thu-29-Apr-27Fri-30-Apr-274hrs - 5:45 am to 9:45 am or 10:30 am to 2:30 pmOR 1 day - 5:45 am to 2:30 pmBrunch between 9:45-10:30 (not included)Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details Bluebell WoodsDescription: This Bluebell Woodlands photography workshop gives you exclusive access to a private Warwickshire bluebell wood near Stratford-upon-Avon, open to all levels and any camera. For a few short weeks each spring the woodland floor turns into a sea of blue — and unlike the well-known public bluebell spots, this one is yours to photograph without the crowds, so you can slow right down and work the scene properly in soft woodland light, rather than grabbing the same shot everyone else takes.You choose how you shoot it. Pick a four-hour half-day session — sunrise (5:45am–9:45am) for soft, warm early light, or mid-morning (10:30am–2:30pm) for brighter colour — or book the full day (5:45am–2:30pm) to shoot both, with a brunch break in between (9:45–10:30, not included). Whichever you choose, the technical craft is the floor we build on — composition, depth of field, the settings that hold a carpet of blue in focus — but the real work is learning to see. Woodland is a beautifully chaotic subject, so we'll work on simplifying it into a frame with order and intention, on finding the intimate, close-up detail as readily as the wide woodland view, and on reading the soft spring light and the blue-and-green as a quiet harmony rather than chasing a loud, over-saturated bluebell cliché.It's a small group of no more than six, taught personally and pitched at exactly your level, with easy walks along the bluebell trails and one-to-one guidance throughout. Because bluebells wait for no one, dates flex to the flowering — you'll pick a first-choice date and I'll confirm the peak display nearer the time. You'll come away with a portfolio of atmospheric spring woodland images that feel like the place — and a calmer, more intentional way of seeing colour, light and detail that you can take anywhere.</t>
+          <t>Batsford Arboretum Photography Workshops in autumn. Enjoy the colour and expert photographic guidance | Half or One Day Sessions | Any Level and CameraSummaryLocation: Batsford Arboretum - GloucestershireDates: Fri 23 Oct – Sat 31 Oct 2026Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless CameraPhotography Workshop Event Batsford ArboretumDescription: For nearly fifteen years I've returned to Batsford Arboretum each autumn, and in that time I've come to know every corner of it — which spot works at which hour, where the light falls and the angles that turn one of Britain's finest tree collections into a photograph rather than a snapshot. This workshop is built on that knowledge. Open to all levels and any camera, it's a chance to photograph Batsford's autumn colour with someone who can put you in the right place at the right time, so you can spend your energy on the thing that actually matters: seeing.Because that's where this workshop really lives. We'll cover the technical setup — exposure, depth of field, the settings that give you control — but that's only the floor. The real work is learning to look: to compose with intention and move beyond the cliché shot everyone else comes home with, to find the close-up, the macro detail and the quiet abstract as readily as the wide vista, and above all to read light, texture and colour as a harmony rather than chasing the over-saturated "look how vivid this is" image. Colour handled with restraint and relationship will always outlast colour shouted.With small numbers and genuine one-to-one attention throughout, you'll have the time and space to slow down and work properly — and you can choose a half-day morning or afternoon session, or a full day in the colour. You'll leave not just with a set of strong autumn images, but with a way of seeing — light, texture and composition — that changes how you photograph colour, woodland and the natural world wherever you go next.Good to know: the workshop price includes entrance to the Arboretum. On the early morning session we have exclusive access before the gardens open to the public — the quiet best light of the day, with the place to ourselves. A grab-and-go breakfast is available from around 9:30am, and the café and outdoor snack bar are open through the day for lunch and refreshments, with toilets on site by the reception area.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707309659883-DPISYTNT0T584VPXCK39/bluebell+photography+workshops.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1715155253660-I9BNV2CJV5TPWB56WH93/Batsford+Autumn+7.jpg</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/bluebell-woodlands-photography-workshops</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/batsford-arboretum-photography-workshops</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>'- half-day photo work..., - one day photo workshops, Landscape, Woodlands, Flowering</t>
+          <t>All Photography Workshops, - half-day photo workshops, - one day photo workshops, Landscape, Woodlands, autumn</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8599409", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Tue 20 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7560082", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Tue 20 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7443277", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Tue 20 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8437523", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Wed 21 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8685603", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Wed 21 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1561078", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Wed 21 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1660230", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Thu 22 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1568285", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Thu 22 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5411810", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Thu 22 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5831738", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Fri 23 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3014350", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Fri 23 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5312475", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Fri 23 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1318075", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Sat 24 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8270632", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Sat 24 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ4260038", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Sat 24 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ6145280", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Sun 25 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2267773", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Sun 25 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2428415", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Sun 25 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ6117337", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Mon 26 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8500857", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Mon 26 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1516510", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Mon 26 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1102782", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Tue 27 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5885147", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Tue 27 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3102560", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Tue 27 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1465142", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Wed 28 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1264314", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Wed 28 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8706845", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Wed 28 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7100218", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Thu 29 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2446216", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Thu 29 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3086312", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Thu 29 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1353684", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Fri 30 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0574386", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Fri 30 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2004510", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Fri 30 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ0818501", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Fri 23  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7647904", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Fri 23 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9436105", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Fri 23 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1204772", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Sat 24  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9290465", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Sat 24 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7375084", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Sat 24 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0264308", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Sun 25 Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9938663", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Sun 25 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0693365", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Sun 25 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3442432", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Thu 29  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8197555", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Thu 29 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9853668", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Thu 29 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0732756", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Fri 30  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ6382131", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Fri 30 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ4533936", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Fri 30 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ4668363", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Sat 31  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5203247", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Sat 31 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1249736", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Sat 31 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="H7" t="n">
         <v>99</v>
@@ -812,12 +812,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>SQ8599409, SQ7560082, SQ7443277, SQ8437523, SQ8685603, SQ1561078, SQ1660230, SQ1568285, SQ5411810, SQ5831738, SQ3014350, SQ5312475, SQ1318075, SQ8270632, SQ4260038, SQ6145280, SQ2267773, SQ2428415, SQ6117337, SQ8500857, SQ1516510, SQ1102782, SQ5885147, SQ3102560, SQ1465142, SQ1264314, SQ8706845, SQ7100218, SQ2446216, SQ3086312, SQ1353684, SQ0574386, SQ2004510</t>
+          <t>SQ0818501, SQ7647904, SQ9436105, SQ1204772, SQ9290465, SQ7375084, SQ0264308, SQ9938663, SQ0693365, SQ3442432, SQ8197555, SQ9853668, SQ0732756, SQ6382131, SQ4533936, SQ4668363, SQ5203247, SQ1249736</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>SQ8599409</t>
+          <t>SQ0818501</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -829,51 +829,51 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Professional Digital DSLR Camera Sensor Clean | Coventry</t>
+          <t>Monthly Pick N Mix Subscription | Interest Free Payment Plan</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Get a camera sensor clean in Coventry . Sensor checked and cleaned using professional equipment, swabs | Full Frame and Cropped Sensors | 24hr Turnaround</t>
+          <t>Monthly Pick N Mix Subscription Package. 10% Discount on events/services for one year | Interest Free Payment Plan | Take events or lessons immediately |</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1522495201980-KD6BKH54J01HJR93XXR6/photography-support-Services-1.png</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/7c76925a-43b0-425c-995e-4f4e0190221c/Photography+Payment+Plan.png</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/camera-sensor-clean</t>
+          <t>https://www.alanranger.com/photography-services-near-me/monthly-pick-n-mix-subscription</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>photography-services</t>
+          <t>photography-classes, photography-courses, photography-workshops</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ5650040", "price": "30.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ3248242", "price": "42.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "12 x £42 = £500"}, {"@type": "Offer", "sku": "SQ3113323", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "12 x £50 = £600"}, {"@type": "Offer", "sku": "SQ4824271", "price": "60.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "12 x £60 = £720"}, {"@type": "Offer", "sku": "SQ5162846", "price": "65.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "12 x £65 = £780"}, {"@type": "Offer", "sku": "SQ0960457", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "12 x £75 = £900"}, {"@type": "Offer", "sku": "SQ6021981", "price": "85.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "12 x £85 = £1020"}, {"@type": "Offer", "sku": "SQ3596605", "price": "100.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "12 x £100 = £1200"}, {"@type": "Offer", "sku": "SQ2188035", "price": "120.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "12 x £120 = £1440"}, {"@type": "Offer", "sku": "SQ5970824", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "12 x £150 = £1800"}, {"@type": "Offer", "sku": "SQ0439157", "price": "175.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "12 x £175 = £2100"}, {"@type": "Offer", "sku": "SQ9583245", "price": "200.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "12 x £200 = £2400"}, {"@type": "Offer", "sku": "SQ9424558", "price": "250.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "12 x £250 = £3000"}]</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H8" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="I8" t="n">
-        <v>30</v>
+        <v>250</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>SQ5650040</t>
+          <t>SQ3248242, SQ3113323, SQ4824271, SQ5162846, SQ0960457, SQ6021981, SQ3596605, SQ2188035, SQ5970824, SQ0439157, SQ9583245, SQ9424558</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>SQ5650040</t>
+          <t>SQ3248242</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -885,51 +885,51 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Christmas Photography Seasonal Workshops - Warwickshire UK</t>
+          <t>BLUEBELL WOODLANDS Photography - Warks - 20 Apr - 30 Apr</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Christmas photography workshops. A Leisurely Christmas photography walk and photograph the countryside - Lapworth or the Christmas lights Stratford Upon Avon photography- Warwickshire - Expert Advice GivenSummaryLocation: WarwickshireDates: 2026 DatesThu 10 December 2026 - 18:45 - 20:30 - Stratford Upon Avon Evening ShootTue, 29 December 2026 - 1 day Christmas Photo Walk 09:00 15:00Break for pub lunch around 12:45 - Not includedParticipants: Max 6Fitness: 2. Easy-ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodChristmas Photography Workshop Event Details Christmas PhotowalkDescription: This Christmas Photography Workshop is the perfect way to escape the heat and fuss of the festive season — swap the wrapping paper for your camera, walk off a little of the overindulgence, and rediscover how much there is to photograph at the most atmospheric time of year. Open to all levels and any camera, it's a relaxed, sociable outing in Warwickshire with expert guidance throughout, and there's a choice of two very different sessions.Stratford-upon-Avon, evening: an after-dark shoot in the heart of the town, photographing the Christmas lights and festive atmosphere. It's a chance to work long exposure, reflections and the warm glow of the season — learning to control exposure in low light and compose a strong frame out of a busy, sparkling scene rather than settling for the obvious snapshot.Lapworth, daytime: the antidote to Christmas. Once the presents are unwrapped, the family politics have peaked and you've eaten your bodyweight in turkey, this leisurely day in the winter countryside is the tonic — a chance to breathe, clear your head and lose yourself in your photography for a few hours. We'll amble through frosty fields, bare woodland and quiet lanes reading the soft, low winter light, with a relaxed lunch in the middle of the day. The whole walk is under five miles at an easy, unhurried pace — gentle enough that the photography, the fresh air and the company are the whole point. The focus stays on seeing: composing with intention, working both intimate detail and wider vista, and reading light, texture and mood to make a picture that's truly yours.It's a small group of no more than six, taught personally and pitched at exactly your level, with one-to-one guidance in the field throughout. Whether you choose the festive lights of Stratford, the crisp countryside of Lapworth, or both, you'll come away with a set of atmospheric seasonal images — and a stronger eye for light, composition and winter colour that carries through long after the decorations come down. For the Lapworth day, a table is reserved in advance at a welcoming country pub, with a festive menu offering both lighter and full festive-meal options to suit every appetite. The lunch itself isn't included in the workshop fee, so you simply pay for what you choose on the day.</t>
+          <t>Bluebell woodlands photography workshop - Choose a sunrise or mid-morning 4hr bluebell photography shoot or both sessions at this private bluebell woodland with exclusive accessSummaryLocation: Warwickshire (Near Stratford Upon Avon)Dates (are subject to the timing of the bluebell flowering and their peek display - you will be contacted nearer the time to consider alt-dates, please pick your initial first date choice but be flexible if nearer the time it needs to change)Tue-20-Apr-27Wed-21-Apr-27Thu-22-Apr-27Fri-23-Apr-27Sat-24-Apr-27Sun-25-Apr-27Mon-26-Apr-27Tue-27-Apr-27Wed-28-Apr-27Thu-29-Apr-27Fri-30-Apr-274hrs - 5:45 am to 9:45 am or 10:30 am to 2:30 pmOR 1 day - 5:45 am to 2:30 pmBrunch between 9:45-10:30 (not included)Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details Bluebell WoodsDescription: This Bluebell Woodlands photography workshop gives you exclusive access to a private Warwickshire bluebell wood near Stratford-upon-Avon, open to all levels and any camera. For a few short weeks each spring the woodland floor turns into a sea of blue — and unlike the well-known public bluebell spots, this one is yours to photograph without the crowds, so you can slow right down and work the scene properly in soft woodland light, rather than grabbing the same shot everyone else takes.You choose how you shoot it. Pick a four-hour half-day session — sunrise (5:45am–9:45am) for soft, warm early light, or mid-morning (10:30am–2:30pm) for brighter colour — or book the full day (5:45am–2:30pm) to shoot both, with a brunch break in between (9:45–10:30, not included). Whichever you choose, the technical craft is the floor we build on — composition, depth of field, the settings that hold a carpet of blue in focus — but the real work is learning to see. Woodland is a beautifully chaotic subject, so we'll work on simplifying it into a frame with order and intention, on finding the intimate, close-up detail as readily as the wide woodland view, and on reading the soft spring light and the blue-and-green as a quiet harmony rather than chasing a loud, over-saturated bluebell cliché.It's a small group of no more than six, taught personally and pitched at exactly your level, with easy walks along the bluebell trails and one-to-one guidance throughout. Because bluebells wait for no one, dates flex to the flowering — you'll pick a first-choice date and I'll confirm the peak display nearer the time. You'll come away with a portfolio of atmospheric spring woodland images that feel like the place — and a calmer, more intentional way of seeing colour, light and detail that you can take anywhere.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1573822266360-1I7REB8B91RNZXW2PNKP/christmas-sparkle-photography-workshop.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707309659883-DPISYTNT0T584VPXCK39/bluebell+photography+workshops.jpg</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/christmas-photography-workshops</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/bluebell-woodlands-photography-workshops</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - half-day photo workshops, Landscape, Urban</t>
+          <t>'- half-day photo work..., - one day photo workshops, Landscape, Woodlands, Flowering</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8119747", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Thu 10 Dec 18:45- 20:30 - Stratford Upon Avon"}, {"@type": "Offer", "sku": "SQ6178610", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Tue 29 Dec 09:00 - 15:00 - Lapworth"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8599409", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Tue 20 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7560082", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Tue 20 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7443277", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Tue 20 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8437523", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Wed 21 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8685603", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Wed 21 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1561078", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Wed 21 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1660230", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Thu 22 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1568285", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Thu 22 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5411810", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Thu 22 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5831738", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Fri 23 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3014350", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Fri 23 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5312475", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Fri 23 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1318075", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Sat 24 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8270632", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Sat 24 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ4260038", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Sat 24 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ6145280", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Sun 25 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2267773", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Sun 25 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2428415", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Sun 25 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ6117337", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Mon 26 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8500857", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Mon 26 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1516510", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Mon 26 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1102782", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Tue 27 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5885147", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Tue 27 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3102560", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Tue 27 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1465142", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Wed 28 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1264314", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Wed 28 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8706845", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Wed 28 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7100218", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Thu 29 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2446216", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Thu 29 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3086312", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Thu 29 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1353684", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Fri 30 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0574386", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Fri 30 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2004510", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Fri 30 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="H9" t="n">
-        <v>50</v>
+        <v>99</v>
       </c>
       <c r="I9" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>SQ8119747, SQ6178610</t>
+          <t>SQ8599409, SQ7560082, SQ7443277, SQ8437523, SQ8685603, SQ1561078, SQ1660230, SQ1568285, SQ5411810, SQ5831738, SQ3014350, SQ5312475, SQ1318075, SQ8270632, SQ4260038, SQ6145280, SQ2267773, SQ2428415, SQ6117337, SQ8500857, SQ1516510, SQ1102782, SQ5885147, SQ3102560, SQ1465142, SQ1264314, SQ8706845, SQ7100218, SQ2446216, SQ3086312, SQ1353684, SQ0574386, SQ2004510</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>SQ8119747</t>
+          <t>SQ8599409</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -941,387 +941,387 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NORTHUMBERLAND Photography Workshops - Mar 18 - 21</t>
+          <t>Annual Pick N Mix Subscription | Interest Free Payment Plan</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Exciting 4 day residential Northumberland Landscape Photography Workshops - Coastline Photography visiting the iconic spots on the Northumbrian coastSummaryLocation: Northumberland, LowickDates:Thu 18 Mar, 13:00 - Sun 21st Mar, 13:00 2027 - 4 Days/3 NightsParticipants: Max 4Fitness: 2. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodNorthumberland Photography Workshops Event Details NorthumberlandDescription: This is a 4-day, 3-night residential Northumberland photography workshop along one of the most dramatic coastlines in Britain, open to all levels from beginner to advanced. Northumberland has more castles than any English county — over seventy — and on this coast the great ones meet the sea: Bamburgh rising from its rocky outcrop, Lindisfarne silhouetted against the North Sea, Dunstanburgh ringed by the black boulders of Embleton Beach. It's a coastline made for photographers who want history, drama and big coastal light in one trip.Based on the Northumberland coast, we spend four days chasing the best conditions across its finest locations — Bamburgh, Dunstanburgh, Lindisfarne, Beadnell, Craster and more — and because it's the east coast, you can shoot both sunrise and sunset from the same stretch of shore. The focus is on three things that define great coastal photography here: composing castles and shoreline into a strong frame, mastering long exposure to turn tide and sky into mood, and working the magical light of sunrise and sunset over the Farne Islands and empty beaches. Throughout, the emphasis isn't just on the famous castle view but on learning to see it — composing with intention, working intimate detail as readily as the grand vista, and reading light and weather as a harmony rather than chasing the obvious shot.With a maximum of just four photographers, this is genuinely personal tuition, planned each day around the tides, the light and the forecast, with a detailed location itinerary sent a few days ahead. Across four days you'll shoot empty beaches at first light, iconic castles and long-exposure seascapes — and come away with a portfolio of dramatic Northumbrian coastal images and a real command of long-exposure and coastal technique. An extra night's accommodation is available the day before if required — please request in advance, subject to hotel availability.</t>
+          <t>Make a one-off payment by bank transfer or through this to get 20% discount on events booked for 12 Months | Tailored Pick N Mix photography training plan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/eb76126f-7580-40f0-ac80-39b29897cdc7/Northumberland+-+March+2025+-+%2302.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/4c6bb1a6-8752-4aea-a250-484fb1acdf75/Photography+Payment+Plan.png</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/coastal-northumberland-photography-workshops</t>
+          <t>https://www.alanranger.com/photography-services-near-me/annual-pick-n-mix-subscription</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>coastal, All Photography Workshops, - weekend residential photo workshops</t>
+          <t>photography-classes, photography-courses, photography-workshops</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8540187", "price": "1095.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "priceSpecification": {"price": "1095.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ0754560", "price": "1200.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "1 x £1200 = £1200"}, {"@type": "Offer", "sku": "SQ7502565", "price": "1500.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "1 x £1500 = £1500"}, {"@type": "Offer", "sku": "SQ1485137", "price": "2000.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "1 x £2000 = £2000"}, {"@type": "Offer", "sku": "SQ7001156", "price": "2500.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "1 x £2500 = £2500"}, {"@type": "Offer", "sku": "SQ2612014", "price": "3000.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "1 x £3000 = £3000"}]</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H10" t="n">
-        <v>1095</v>
+        <v>1200</v>
       </c>
       <c r="I10" t="n">
-        <v>1095</v>
+        <v>3000</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>SQ8540187</t>
+          <t>SQ0754560, SQ7502565, SQ1485137, SQ7001156, SQ2612014</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>SQ8540187</t>
+          <t>SQ0754560</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>product</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DARTMOOR Photography Workshop - Landscapes - 2nd - 4th Apr</t>
+          <t>Quarterly Pick N Mix Subscription | Interest Free Payments</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Join me on this Landscape Dartmoor Photography Workshop - in the iconic woodlands, and landscape of Dartmoor TorsSummaryLocation: Dartmoor - South DevonDates: Fri 2nd - Sun 4th Apr 2027Participants: Max 4Fitness: 3. HardExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details DartmoorDescription: This is a 3-day, 2-night residential landscape photography workshop based around Dartmoor National Park in South Devon, open to all levels from beginner to advanced. Dartmoor is one of England's most atmospheric wild landscapes — a vast sweep of rugged open moor, dramatic granite tors, ancient stunted woodland and serene rivers running through hidden valleys — and across a weekend you'll learn to read and photograph this dramatic terrain in its ever-changing light.Over three days we range across the moor and its woodlands, working a variety of locations as the conditions dictate — from the sculptural granite tors and big moorland vistas to the mossy, otherworldly ancient woods and tumbling rivers. The focus is on three things that make a strong landscape image here: composing order from a wild, expansive scene, controlling exposure and depth of field across big tonal ranges, and timing your shoot to the moods of Dartmoor light, with optional sunrise and sunset shoots and evening picture reviews. Throughout, the emphasis isn't just on the grand vista but on learning to see it — composing with intention, working intimate detail as readily as the wide view, and reading light and weather as a harmony rather than chasing the obvious shot. Be prepared for some longer walks over rougher ground — this is a more demanding workshop that takes you to the moor's most rewarding spots.With a maximum of just four photographers, this is genuinely personal tuition — Alan plans each day around the season and the forecast, and sends a detailed location itinerary a few days ahead. Accommodation, breakfast and evening meals are included, so all you have to think about is your photography, and you'll come away with a varied portfolio of dramatic Dartmoor landscapes — moors, tors and ancient woodland — and the field craft to capture wild country anywhere. An extra night's accommodation is available the day before if required — please request in advance, subject to hotel availability.</t>
+          <t>Quarterly Pick N Mix Subscription Package. 15% Discount on events/services for one year | Interest Free Payment Plan | Take events or lessons immediately |</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707237329064-99H533NMXCONH5J276LM/dartmoor+photography+workshop.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/fbab50ee-2fe8-4fe9-8804-e691b883cf4b/Photography+Payment+Plan.png</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/dartmoor-photography-landscape-workshop</t>
+          <t>https://www.alanranger.com/photography-services-near-me/quarterly-pick-n-mix-subscription</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - weekend residential photo workshops, Landscape</t>
+          <t>photography-classes, photography-courses, photography-workshops</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ5540434", "price": "875.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ4217445", "price": "250.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "4 x £250 = £1000"}, {"@type": "Offer", "sku": "SQ6277577", "price": "300.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "4 x £300 = £1200"}, {"@type": "Offer", "sku": "SQ7788516", "price": "350.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "4 x £350 = £1400"}, {"@type": "Offer", "sku": "SQ5124608", "price": "400.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "4 x 400 = £1600"}, {"@type": "Offer", "sku": "SQ2657628", "price": "500.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "4 x £500 = £2000"}, {"@type": "Offer", "sku": "SQ2267503", "price": "750.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "4 x £750 = £3000"}]</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H11" t="n">
-        <v>875</v>
+        <v>250</v>
       </c>
       <c r="I11" t="n">
-        <v>875</v>
+        <v>750</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>SQ5540434</t>
+          <t>SQ4217445, SQ6277577, SQ7788516, SQ5124608, SQ2657628, SQ2267503</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>SQ5540434</t>
+          <t>SQ4217445</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>product</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DORSET Landscape Photography Workshop Purbeck 25 - 27 Sep</t>
+          <t>Beginners Photography Course | 3 Weekly Evening Classes</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Join me on this 3-day/2-night fantastic Dorset Photography workshop along the Jurassic coastline of Dorset - PurbeckSummary - Dorset Landscape PhotographyLocation: DorsetDates: Fri 2nd - Sun 4th Oct 2026 3 Days/2 Nights(Price includes B&amp;B and evening meal - Half Board)Participants: Max 4Fitness: 3. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details DorsetDescription: This is a 3-day, 2-night residential landscape photography workshop along the Jurassic Coast of Dorset, open to all levels from beginner to advanced. Dorset's Purbeck coastline is one of the UK's great seascape locations — a prehistoric, World Heritage shore of sculpted arches, sea stacks and folded cliffs, with the iconic Durdle Door and Lulworth Cove at its heart — and across a weekend you'll learn to photograph it in its best light.Based on the Purbeck coast, we work the area's finest locations — from Durdle Door, Man O'War and Lulworth Cove to Kimmeridge, Dancing Ledge, Mupe Bay and the ghost village of Tyneham. The focus is on three things that make a strong coastal image: composing rock, sea and sky into a balanced frame, using long exposure to turn the moving water into mood, and timing your shoot to the light and the tide. It's never prescriptive though — this varied coastline lends itself to any style, so whether you're drawn to classic seascapes, black and white or abstract, there's scope to follow your own creative vision; throughout, the emphasis is on learning to see, composing with intention and reading light and tone as a harmony rather than chasing the obvious shot. There are optional sunrise and sunset shoots and evenings for relaxed picture reviews.With a maximum of just four photographers, this is genuinely personal tuition — Alan plans each day around the tides, the season and the forecast, and sends a detailed location itinerary a few days ahead. B&amp;B accommodation and an evening meal are included, so all you have to think about for three days is your photography, and you'll come away with a portfolio of dramatic Jurassic Coast images and a real command of seascape and long-exposure technique. An extra night's accommodation is available the day before if required — please request in advance, subject to hotel availability.</t>
+          <t>Beginners Photography Course CoventrySummary - Camera Courses For Beginners - Key InformationLocation: 45 Hathaway Road, Coventry, CV4 9HWDuration: 3 × 2hr evening classes (19:00–21:00)Participants: Max 4Start Dates: Beginners Photography Course3wks Mondays - Oct 12 - Oct 26 Coventry3wks Wednesdays - Oct 14 - Oct 28 Coventry3wks Mondays - Nov 9 - Nov 23 Coventry3wks Tuesdays - Dec 1 - Dec 15 Coventry3wks Wednesdays - Jan 13 - Jan 27 Coventry3wks Thursdays - Jan 28 - Feb 11 Coventry3wks Tuesdays - Mar 2 - Mar 16 Coventry3wks Thursdays Apr 1 - Apr 15 Coventry3wks Wednesdays May 12 - May 26 Coventry3wks Mondays - Jun 7 - Jun 21 CoventryLevel: Beginner and NoviceDescription:A practical three-week evening course that takes you from Auto to confident manual control, built around your own camera.Week 1 is about getting off Auto for good — the exposure modes, then aperture, shutter speed and ISO, and how they work together as the exposure triangle, with practical assignments to put it into practice.Week 2 goes deeper into getting the exposure right: manual exposure, metering, reading the histogram, exposure compensation, stops and dynamic range, and bracketing — followed by a review of your assignment work.Week 3 moves on to focusing and depth of field, white balance, JPEG vs RAW, and the foundations of composition, finishing with a final assignment review.With a maximum of four people, you get genuine attention and plenty of room to ask questions, and you'll leave with a printed course book covering every topic to revisit at home. Beginner and novice friendly — just bring a DSLR or mirrorless camera with manual modes.What You'll Learn: How to get off Auto and use manual exposure, aperture, shutter speed and ISO; how focus works; and the foundations of composition to make stronger, more deliberate photos.Includes: A printed course book covering every topic, so you can revisit it all afterwards.Equipment: A DSLR or mirrorless camera with manual exposure modes.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714681245814-0QW8DK4XQ18FM0JLBXYN/Harry+Rocks+%2301+-+Mar+2024.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/773443e9-940a-440b-9faa-14e22b8c4236/beginners+photography+classes+coventry.png</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/dorset-landscape-photography-workshop</t>
+          <t>https://www.alanranger.com/photography-services-near-me/beginners-photography-course</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>coastal, All Photography Workshops, - weekend residential photo workshops</t>
+          <t>photography-classes, photography-courses</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ2754105", "price": "925.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ6875626", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "3wks Mondays - Oct 12 - Oct 26 Coventry"}, {"@type": "Offer", "sku": "SQ8844762", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "3wks Wednesdays - Oct 14 - Oct 28 Coventry"}, {"@type": "Offer", "sku": "SQ5616379", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "3wks Mondays - Nov 9 - Nov 23 Coventry"}, {"@type": "Offer", "sku": "SQ3231903", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "3wks Tuesdays - Dec 1 - Dec 15 Coventry"}, {"@type": "Offer", "sku": "SQ5559634", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "3wks Wednesdays - Jan 13 - Jan 27 Coventry"}, {"@type": "Offer", "sku": "SQ0659870", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "3wks Thursdays - Jan 28 - Feb 11 Coventry"}, {"@type": "Offer", "sku": "SQ0358019", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "3wks Tuesdays - Mar 2 - Mar 16 Coventry"}, {"@type": "Offer", "sku": "SQ0618983", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "3wks Thursdays  Apr 1 - Apr 15 Coventry"}, {"@type": "Offer", "sku": "SQ5714218", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "3wks Wednesdays May 12 - May 26 Coventry"}, {"@type": "Offer", "sku": "SQ7630533", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "3wks Mondays  - Jun 7  - Jun 21 Coventry"}]</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H12" t="n">
-        <v>925</v>
+        <v>150</v>
       </c>
       <c r="I12" t="n">
-        <v>925</v>
+        <v>150</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>SQ2754105</t>
+          <t>SQ6875626, SQ8844762, SQ5616379, SQ3231903, SQ5559634, SQ0659870, SQ0358019, SQ0618983, SQ5714218, SQ7630533</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>SQ2754105</t>
+          <t>SQ6875626</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>course</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EXMOOR Photography Workshop - Sat 8 - Sun 9 May 2027</t>
+          <t>Intermediates Intentions Photography Project Course</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Lynmouth - Exmoor Photography Workshop - Join me for this exciting and inspiring trip to explore and capture the stunning coastal landscapes and breathtaking natural beauty of North Devon.SummaryLocation: Lynmouth - ExmoorDates: Sat 8 10:30 - Sun 9 May 14:00 2027 2 Days/1 NightParticipants:Max 4 (1 Car, transport between locations included)Fitness: 1. Easy (5-15 min walks)Experience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodExmoor Photography Workshop Event DetailsLynmouthDescription: This is a 2-day, 1-night residential seascape photography workshop based at Lynmouth on the dramatic Exmoor coast of North Devon, open to all levels from beginner to advanced. Lynmouth is a photographer's paradise — where the East and West Lyn rivers meet the sea beneath towering cliffs, fringed by secluded bays, weathered rock formations and the quaint harbour village with its iconic Rhenish Tower. It's a compact, richly varied coastline that rewards a focused weekend of shooting.Over two days we work the area's finest coastal locations — from the secluded bays and rock formations around Lynmouth and the sweeping Valley of Rocks to Watersmeet, Heddon's Mouth and Porlock Weir. The focus is on three things that make a strong seascape: composing rock, water and sky into a balanced frame, using long exposure to turn the moving sea into mood, and timing your shoot to the light and the tide. Throughout, the emphasis isn't just on the grand view but on learning to see it — composing with intention, working intimate detail as readily as the wide vista, and reading light and tide as a harmony rather than chasing the obvious shot. The days follow the conditions — full days on location with tuition, an optional sunset shoot, and an optional sunrise, with evenings for relaxed picture reviews.With a maximum of just four photographers and transport between locations included, this is genuinely personal, hassle-free tuition — Alan plans each day around the tides, the season and the forecast, and sends a detailed location itinerary a few days ahead. Accommodation and breakfast are included, so all you have to think about is your photography, and you'll come away with a portfolio of dramatic Exmoor seascapes and the field craft to read light and tide on any coast. An extra night's accommodation is available the day before if required — please request in advance, subject to hotel availability.</t>
+          <t>Six-month photography project and showcase your images in a public exhibition in WarwickshireLocation: 45 Hathaway Road, Tile Hill Village, Coventry, CV4 9HWDuration: 6-month project, 6 classesParticipants: Max 4Level: IntermediateDescription: Embark on a six-month photography project and showcase your images in a public exhibition in Warwickshire — a course designed to develop your intentions, vision and a coherent body of work.Equipment: A DSLR or mirrorless camera with manual exposure modes.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714638630127-79B9OMJPFF60L8Q9VLJL/Timeless+Memories.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707220703945-94B0SK8PWUMOS78FTJMO/photography+project+-+intentions+photography+course.jpg</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/exmoor-photography-workshops-lynmouth</t>
+          <t>https://www.alanranger.com/photography-services-near-me/intermediates-intentions-photography-project-course</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>coastal, All Photography Workshops, - weekend residential photo workshops</t>
+          <t>photography-classes, photography-courses</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8057321", "price": "575.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9898707", "price": "400.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "priceSpecification": {"price": "400.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>575</v>
+        <v>400</v>
       </c>
       <c r="I13" t="n">
-        <v>575</v>
+        <v>400</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>SQ8057321</t>
+          <t>SQ9898707</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>SQ8057321</t>
+          <t>SQ9898707</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>course</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Fine Art Photography Prints - Canvas wrap-round - Multi Size</t>
+          <t>DEVON Landscape Photography  Workshops - Various Dates</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Fine Art Photography Prints - Canvas wrap-round creates a contemporary finish to your photo- available in seven sizes. Include in the image title when ordering</t>
+          <t>Hartland Quay - Landscape Photography Devon Workshop - Join me for this photo workshop to the best coastal and dramatic parts of Devon.SummaryLocation: North Devon - Hartland QuayDates:Thu 25th 12:30 - Sun 28th 12:30 Feb 2027 - 4 Days/3 NightsFri 3rd Sep - Sun 5th Sep 2027 - 3 Days/2 NightsParticipants: Max 4Fitness: 2. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera, Tripod and ND Filters (tripod and filters can be provided)Photography Workshop Event Details DevonDescription: This is a multi-day residential landscape photography workshop based at Hartland Quay on the dramatic North Devon coast, open to all levels from beginner to advanced. Hartland Quay is one of the UK's most spectacular seascape locations — long slithers of rock formations running out into a fierce Atlantic tide — and it's the perfect base for learning seascape photography on a coastline that rewards drama, patience and timing.Across the workshop you'll photograph the classic Hartland Quay views and range out along some of the finest coast in the South West — from Bude and Clovelly to Welcombe Bay, Saunton Sands and Woolacombe. The focus is on the craft of seascape photography: composing a strong coastal frame, mastering long exposure to turn moving water and sky into mood, and timing your shoot to the light and the tide. But the technical side is only the floor — the real work is learning to see, composing with intention and reading light and tide as a harmony rather than chasing the obvious shot, working the intimate detail as readily as the grand vista. Each day follows that rhythm — optional sunrise and sunset shoots when the light is best, full days in the field with tuition, and evening photo reviews and editing sessions to sharpen your eye.With a maximum of just four photographers, this is genuinely personal tuition, and because the whole coast is tide- and light-dependent, Alan plans each day around the forecast and sends a detailed location itinerary a few days ahead. Tripods and ND filters can be lent if you don't yet own them, accommodation and breakfast are included, and you'll come away with a portfolio of dramatic Devon seascapes and a real command of long-exposure coastal technique. An extra night's accommodation is available the day before if required — please request in advance, subject to hotel availability.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1572426141642-UH9GBUDOUFH8QMTUA0KA/cavas%2Bsizes.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714299365471-K36RWNIKFNGJ4C70UEXB/Atlantic+Force.jpg</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/fine-art-photography-prints-canvas</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/landscape-photography-devon-hartland-quay</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>print</t>
+          <t>coastal, All Photography Workshops, - weekend residential photo workshops</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ0105911", "price": "135.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "16x12 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ4206024", "price": "177.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "24x16 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ0781804", "price": "219.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "30x20 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ3982814", "price": "306.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "36x24 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ8209269", "price": "336.65", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "40x30 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ7901040", "price": "414.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "48x36 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ7260825", "price": "459.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "60x40 Canvas Wrap Round"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ3856406", "price": "950.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Thu 25th 12:30 - Sun 28th 12:30 Feb 2027 - 4 Days/3 Nights"}, {"@type": "Offer", "sku": "SQ2516659", "price": "775.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Fri 3rd Sep - Sun 5th Sep 2027 - 3 Days/2 Nights"}]</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>135.95</v>
+        <v>775</v>
       </c>
       <c r="I14" t="n">
-        <v>459.95</v>
+        <v>950</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>SQ0105911, SQ4206024, SQ0781804, SQ3982814, SQ8209269, SQ7901040, SQ7260825</t>
+          <t>SQ3856406, SQ2516659</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>SQ0105911</t>
+          <t>SQ3856406</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>event</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Fine Art Photography Prints - Unframed Prints - Multi Sizes</t>
+          <t>CHESTERTON WINDMILL Photography Workshops - Warwickshire</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Fine Art Photography Prints available in seven sizes. Giclee print on archival paper. Please include in the image title when ordering | Pro-Lab Printing</t>
+          <t>Chesterton windmill is one of Warwickshire's most famous landmarks. Join me in a sunset landscape photography workshop and learn about composition and lightSummaryLocation: Warwickshire - ChestertonDates:Mon 5th Oct 2026 - 17:30 - 19:45Tue 13th May 2027 - 18:15 - 20:15Mon 10th May 2027 - 18:30 - 20:30Mon 6th Sep 2027 - 18:00 - 20:00Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details ChestertonDescription: This sunset landscape photography workshop is an evening shoot at Chesterton Windmill, one of Warwickshire's most iconic landmarks, open to all levels and any camera. A striking 17th-century tower windmill on its arched stone legs, standing alone on a hilltop for nearly 350 years, it's one of the most photogenic structures in the county — and this workshop is built around capturing it in the golden light of sunset and the long-exposure drama of the hour that follows, in a way that's genuinely your own rather than the postcard everyone already has.The technical craft is the floor we build on — exposure, depth of field, and setting up long exposures to draw movement out of cloud and sky as dusk falls. But the real work is learning to see this familiar landmark freshly: composing the windmill with intention against the sky and the rolling countryside, finding the unexpected angle and the intimate detail as readily as the wide hilltop vista, and reading the warm, directional light of sunset as a harmony to compose with rather than just a pretty backdrop to point at. As the colour builds and fades, you'll learn to design a frame where the light, the land and the windmill all work together.It's a small group of no more than six, taught personally and pitched at exactly your level, so whether you're new to landscape photography or refining your technique, you get real one-to-one guidance in the field. You'll come away with a set of atmospheric images of this famous Warwickshire landmark — golden-hour silhouettes and long-exposure skies — and a sharper, more intentional way of seeing light and composition that lets you photograph any landmark at its best.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707240002916-MMJ7CA3MX9HLO60532BO/fine+art+photography+prints.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714682519866-NVMB6B7Q4F93DGOGPQIK/Moonlit+Chesterton.jpg</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/fine-art-photography-prints-unframed</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/photography-workshops-chesterton-windmill</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>print</t>
+          <t>All Photography Workshops, - half-day photo workshops, Landscape</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ4872440", "price": "50.57", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "16x12 Print"}, {"@type": "Offer", "sku": "SQ0453600", "price": "95.78", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "24x16 Print"}, {"@type": "Offer", "sku": "SQ7485354", "price": "138.86", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "30x20 Print"}, {"@type": "Offer", "sku": "SQ0167262", "price": "161.38", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "36x24 Print"}, {"@type": "Offer", "sku": "SQ1664775", "price": "217.23", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "40x30 Print"}, {"@type": "Offer", "sku": "SQ0377820", "price": "305.05", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "48x36 Print"}, {"@type": "Offer", "sku": "SQ8780582", "price": "416.85", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "60x40 Print"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ0796814", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Mon 5th Oct 2026 - 17:30 - 19:45", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9554270", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Tue 13th Apr 2027 - 18:15 - 20:15", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5307067", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Mon 10th May 2027 - 18:30 - 20:30", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3572999", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Mon 6th Sep 2027 - 18:00 - 20:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H15" t="n">
-        <v>50.57</v>
+        <v>50</v>
       </c>
       <c r="I15" t="n">
-        <v>416.85</v>
+        <v>50</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>SQ4872440, SQ0453600, SQ7485354, SQ0167262, SQ1664775, SQ0377820, SQ8780582</t>
+          <t>SQ0796814, SQ9554270, SQ5307067, SQ3572999</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>SQ4872440</t>
+          <t>SQ0796814</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>event</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Fireworks Photography Workshop | Long Exposure | Kenilworth</t>
+          <t>FAIRY GLEN and Fairy Falls Long Exposure Photography</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Fireworks Photography Workshop - Long exposure and fireworks. Learn about camera settings, exposure use and composition.SummaryLocation: KenilworthDates: TBCParticipants: Max 4Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: FireworksDescription: This Fireworks Photography Workshop is a one-off evening capturing one of the most exciting subjects in photography — a full fireworks display bursting over the floodlit ruins of Kenilworth Castle. Open to all levels and any camera, it's built around the Round Table's spectacular annual display, and the magical, fleeting moment when long exposure turns streaking light and exploding colour into a single dramatic image with the castle as its backdrop.Fireworks look chaotic but reward a calm, technical approach, and that's exactly what we'll work on. The focus is on three things that make the difference between a lucky snap and a controlled image: setting up for long exposure — shutter, aperture and the timing that lets you build a burst on the sensor — composing the frame so the castle and the sky work together rather than fighting, and reading the rhythm of the display to know when to open and close the shutter. You'll learn to anticipate rather than react, and to keep shooting cleanly when the sky is at its busiest.It's a small group of no more than four, taught personally and right beside you in the dark, so you get real one-to-one guidance exactly when the action is happening. Better still, we photograph from outside the castle walls, so there's no admission ticket to buy for the display. You'll come away with a set of dramatic fireworks images over a historic castle — and the long-exposure and timing skills to photograph fireworks, light trails and night scenes anywhere. (Please note this is an annual event with the date set by the organisers, so timing is confirmed each year nearer the display.)</t>
+          <t>A magical gorge on the River Conwy at Betws-y-Coed. Fairy Glen and Fairy Falls provide an opportunity to practise long exposure photography on the magic of this river. Fairy Glen Betws-y-Coed Long Exposure Photography WorkshopSummaryLocation: Wales - Betws-y-CoedDates:Sat 6th Mar 2027 - 10:00 - 13:30Fri 14th May 2027 - 10:00 - 13:30 + Option for Anglesey Weekend WorkshopSat 9th Oct 2027 - 10:00 - 13:30Participants: Max 4Fitness: 2. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details Fairy GlenDescription: This Fairy Glen long exposure photography workshop takes you into one of Wales' most magical locations — a serene, secluded gorge where the River Conwy tumbles through the woods at Betws-y-Coed — and is open to all levels and any camera. Flowing water through a wooded gorge is the perfect subject for long exposure, and this half-day workshop is about more than the silky-water effect: it's about learning to see this enchanting place and make images of it that are calm, considered and your own, rather than the same shot everyone takes.The long-exposure craft is the floor we build on — setting up your tripod and filters, and calculating the right exposure time for the effect you want — but the real work is composition and seeing. Working two great locations within a couple of miles of each other, you'll learn to find order among the rocks, water and woodland, to compose the intimate detail as readily as the wider gorge, and to read the soft, dappled light and the natural greens and browns of the glen as a quiet harmony rather than chasing a loud, over-processed look. The aim is a photograph with mood and restraint — moving water that feels like the place actually feels.With a maximum of just four photographers, this is genuinely personal tuition, with Alan guiding each person through observation, shot design, shooting and image reviews at both locations. You'll come away with a set of atmospheric long-exposure images of one of Snowdonia's hidden gems — and a stronger, more intentional way of seeing moving water and woodland that you can take anywhere.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1713518270092-GJSBASA0ZLL4NBMCK355/Kenilworth+Fireworks+2017+-+2.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707214813724-6QPD5O2XJNRQNOEIRBXO/Fairy+Glen+Betws-y-Coed+Photography+Workshop.jpg</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/fireworks-photography-workshop-kenilworth</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/long-exposure-photography-workshop-fairy-glen</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - half-day photo workshops</t>
+          <t>All Photography Workshops, - half-day photo workshops, Landscape</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ1182401", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9080164", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Sat 6th Mar 2027 - 10:00 - 13:30"}, {"@type": "Offer", "sku": "SQ6636860", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Fri 14th May 2027 - 10:00 - 13:30"}, {"@type": "Offer", "sku": "SQ8778402", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Sat 9th Oct 2027 - 10:00 - 13:30"}]</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H16" t="n">
-        <v>75</v>
+        <v>125</v>
       </c>
       <c r="I16" t="n">
-        <v>75</v>
+        <v>125</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>SQ1182401</t>
+          <t>SQ9080164, SQ6636860, SQ8778402</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>SQ1182401</t>
+          <t>SQ9080164</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1333,163 +1333,163 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>4 x 2hr Private Photography Classes - Face to Face Coventry</t>
+          <t>LAVENDER FIELD Photography Workshop - Glouc or Warks July</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>4 × 2hr Private Photography Classes (Face to Face, Coventry)Summary - Private Photography Classes (Face to Face) - Key InformationLocation: Coventry (face to face)Format: Private 1-2-1 tuition, in personSessions: 4 × 2hr classes, scheduled to suit youAvailability: Mon–Fri, 9am–5pmValidity: Pay now, book dates later — you'll be sent a code to book your datesLevel: All levels, beginner to advancedDescription: A package of four private, face-to-face photography classes in Coventry — two hours each, tailored entirely to you and what you want to learn or improve.</t>
+          <t>Join me in the Cotswolds, or Warwickshire for a spectacular lavender field landscape workshop . Photograph in the evening hours by arrangement of owners (date is subject to change or weather on the day) Price includes entry fee of £30 for either of the lavender farmsSummaryLocation: Snowshill - Gloucestershire or Bubbenhall · Warwickshire, Lavender FarmsDates:Sat 3rd Jul 2027 - 18:00 20:45Sat 10th Jul 2027 - 18:00 20:45Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and Tripod (tripod available to borrow)Photography Workshop Event Details LavenderDescription: This Lavender Photography Workshop is a magical evening among the lavender rows of the Cotswolds at Snowshill in Gloucestershire or depending on arrangements at Warwickshire Lavender Farm, Bubbenhall — open to all levels and any camera. Best of all, you'll photograph the fields after the farm has closed to the general public, so instead of working around coachloads of day-trippers you have the spectacular sea of purple and the wildflower areas largely to yourselves — making it far easier to slow down, see properly and compose clean shots as the light softens towards sunset and the colour comes alive.A field of lavender is seductive but deceptively hard — it's all too easy to come home with the loud, over-saturated purple shot everyone takes. The real work here is learning to see past that. The technical craft is the floor we build on — focusing and exposing accurately in fading light, and holding both shadow and highlight as the sun drops — but the focus is on composing with intention: finding order and a lead-in through the endless rows, working the intimate, abstract close-up of colour and texture as readily as the sweeping vista, and treating the purple, the green and the warm evening light as a harmony to balance rather than a colour to crank. The aim is a photograph with mood and restraint — one that feels like that quiet evening in the field.It's a small group of no more than six, taught personally and pitched at exactly your level, with one-to-one guidance throughout. With the crowds gone and the fields quiet, you'll have the space and time to really work your compositions — and you'll come away with a portfolio of vivid lavender images at their most atmospheric, plus a sharper, more intentional way of seeing colour, light and detail that you can take anywhere. This is a special after-hours session: the farm opens to us beyond its normal public hours so we can shoot from 5p/6pmm into the early sunset light 9/9:30pm, and your workshop fee includes that commercial after-hours access. Please note the dates and finish times are set by the lavender farm rather than by Alan, and may be subject to change with the season, flowering and weather as they do not extend the hours if rain is forecast on the day, so you need to be flexible and be able to swap to an alternative Saturday evening that the farm has extended hours. Usually the first 3 Saturdays of July.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/17054018-4804-4c2d-ad29-c57cba809028/face+to+face+private+photography+classes.png</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714572933715-EIVNF6O80HEJCSEU5D4U/lavender+sprint.jpg</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/four-private-photography-classes</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/photography-workshops-lavender-fields</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1-2-1-private-lessons, photography-classes, photography-tuition, photography-courses</t>
+          <t>All Photography Workshops, - half-day photo workshops, Flowering, Landscape</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ6583676", "price": "360.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "4 x 2hr sessions - weekday daytime", "priceSpecification": {"price": "360.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ6748367", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Sat 3rd Jul 2027 - 18:00 20:45"}, {"@type": "Offer", "sku": "SQ7542811", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Sat 10th Jul 2027 - 18:00 20:45"}]</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H17" t="n">
-        <v>360</v>
+        <v>150</v>
       </c>
       <c r="I17" t="n">
-        <v>360</v>
+        <v>150</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>SQ6583676</t>
+          <t>SQ6748367, SQ7542811</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>SQ6583676</t>
+          <t>SQ6748367</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>event</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Framed Fine Art Photography Prints - Multiple Sizes</t>
+          <t>Poppy Fields Photography Workshops | Worcestershire</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Fine Art Photography Prints - Giclee Framed Prints available in four sizes. Black frame with white mount. Please include in the image title when ordering</t>
+          <t>Poppy fields photography workshop - Choose a sunrise or sunset 2.5hrs photo workshop at amazing poppy fields in Worcestershire | Seasonal DependantSummaryLocation: WorcestershireDates: (dates are subject to change based on when the poppy fields flower in June)8th Jun 19:15 - 21:459th Jun 05:00 - 07:30Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: PoppiesDescription: There are few sights in the English summer to beat rolling Worcestershire hills washed red with wild poppies, and this Poppy Fields Photography Workshop is built to catch them at their fleeting best. Open to all levels and any camera, it runs as short, focused sessions at the golden hours of sunset and sunrise — the two times of day when low, warm light makes a field of poppies truly glow.A field of red is more seductive than it is easy, and the work is learning to turn it into a photograph rather than a snapshot. The focus is on three things: composing with intention to find order and a lead-in through a busy, repeating scene, controlling exposure and depth of field to decide what's sharp and what dissolves into colour, and reading light, texture and colour as a harmony — letting the reds sing without tipping into the over-saturated cliché. You'll work both the intimate, single-stem detail and the sweeping vista, and learn to see past the obvious shot everyone else takes.It's a small group of no more than six, taught personally and pitched at exactly your level, with one-to-one guidance in the field throughout. Whether you join the sunset session, the dawn one, or both, you'll come away with a portfolio of poppy-field images at their most atmospheric — and a stronger way of seeing colour, light and composition that carries into everything you photograph next. Please note that poppies bloom briefly and unpredictably each June, so both the exact dates and the field we use are confirmed at short notice once the flowering is at its best. A flexible approach is essential — but it's exactly what lets us photograph the poppies at their absolute peak.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707240165500-DB965TUR2FYMNEFPXS90/fine+art+photography+prints+-+framed.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714575407530-MBS3PUSXD9GGHA68754C/poppy+dawn.jpg</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/framed-fine-art-photography-prints</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/poppy-fields-photography-workshops</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>print</t>
+          <t>All Photography Workshops, - half-day photo workshops</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ6825544", "price": "133.85", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "16x12 Print (with Frame 20x16)"}, {"@type": "Offer", "sku": "SQ3786581", "price": "191.50", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "24x16 Print (with Frame 30x20)"}, {"@type": "Offer", "sku": "SQ1355351", "price": "267.43", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "30x20 Print (with Frame 40x30)"}, {"@type": "Offer", "sku": "SQ0156134", "price": "356.90", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "36x24 Print (with Frame 48x36)"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8740143", "price": "95.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Sat 8 Jun 19:15-21:45"}, {"@type": "Offer", "sku": "SQ7189877", "price": "95.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Sun 9 Jun 05:00-07:30"}]</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H18" t="n">
-        <v>133.85</v>
+        <v>95</v>
       </c>
       <c r="I18" t="n">
-        <v>356.9</v>
+        <v>95</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>SQ6825544, SQ3786581, SQ1355351, SQ0156134</t>
+          <t>SQ8740143, SQ7189877</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>SQ6825544</t>
+          <t>SQ8740143</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>event</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>The Art of GARDEN PHOTOGRAPHY  - Coventry -  May and July</t>
+          <t>BURNHAM ON SEA Long Exposure Photography Workshop 8 May</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Join us for an unforgettable journey into macro and abstract on this garden photography workshop. Secure your spot today and embark on a transformative learning experience in garden photography.SummaryLocation: Coventry - CV4Dates:Sun May 23rd 2027 - 15:00 - 17:00Sun Jul 11th 2027 - 15:00 - 17:00Participants: Max 4Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details Garden PhotographyDescription: This Garden Photography Workshop is an intimate afternoon in Alan's own private garden in Coventry — his personal creative studio, a space he knows intimately and tends with a photographer's eye — open to all levels and any camera. A garden is one of the richest and most overlooked subjects there is: get close and the flowers, foliage, structures and borders reveal endless macro, close-up and abstract images, and this relaxed half-day is all about learning to see them, then photograph them with intention.The technical craft is the floor we build on — getting sharp focus, using your lens for macro and close-up detail, and controlling exposure and depth of field — but the real work is learning to look. You'll be given four photography assignments with guidance notes that push you to experiment and vary your approach, from intimate macro to wider garden portraits, training your eye to find the abstract within the planting and to compose with real intention. Throughout, the emphasis is on reading colour, light and texture as a harmony — letting the flowers sing without tipping into the loud, over-saturated shot — so your images feel considered and your own, not the obvious bloom-in-the-middle snap. Image reviews and feedback on a large screen in the gazebo help you see what's working and why.Places are limited to just four, so this is genuinely personal tuition, with Alan on hand for settings, composition and one-to-one guidance the whole time — and tea, coffee and cake served throughout. You'll come away with your own portfolio of garden images, and a sharper, more intentional way of seeing detail, colour and light that changes how you photograph flowers and nature everywhere.</t>
+          <t>Seascape and Long Exposure Photography workshop at this iconic location in Somerset with the lighthouse at Burnham on SeaSummaryLocation: Somerset - Burnham On SeaDates: Sat 8th May 2027 - 18:30 - 21:00Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details BurnhamDescription: This Burnham on Sea long exposure photography workshop is an evening on the Somerset coast built around one of the most photogenic subjects in the country — the town's iconic nine-legged lighthouse, standing on stilts on the open beach. Open to all levels and any camera, it's about the art of long exposure: not just the silky-water effect, but learning to see this minimalist coast and make images of it that are calm, considered and your own, rather than the same shot everyone takes.The long-exposure craft is the floor we build on, and we'll cover it properly — setting up, calculating shutter times and using filters — before heading onto the beach to shoot on an incoming tide as the sun sets. But the real work is composition and seeing. As the light builds you'll learn to place the lighthouse with real intention in a clean, minimalist frame, to work the intimate detail of stilts, reflections and wet sand as readily as the wide seascape, and to read the soft, shifting colour of a coastal sunset as a harmony rather than chasing a loud, over-saturated sky. The aim is mood and restraint — an image that feels like the quiet of that beach at dusk.It's a small group of no more than six, taught personally and pitched at exactly your level, with Alan on hand throughout for settings, composition and one-to-one guidance in the field. Whether long exposure is new to you or you're refining your technique, you'll come away with a set of atmospheric sunset images of this famous Somerset landmark — and a sharper, more intentional way of seeing light, movement and mood that you can take to any coast.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1709974516534-UJBRDOK5RXR4QNLPTECD/_-677.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714573609279-RSKP2ELI51B1VY87SOCS/Burnham+Still.jpg</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/garden-photography-workshop</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/long-exposure-photography-workshops-burnham</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - half-day photo workshops, Flowering, Macro &amp; Abstract</t>
+          <t>coastal, All Photography Workshops, - half-day photo workshops</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ0939451", "price": "45.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Sun May 23rd 2027 - 15:00 - 17:00"}, {"@type": "Offer", "sku": "SQ3644687", "price": "45.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Sun Jul 11th 2027 - 15:00 - 17:00"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9466277", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29"}]</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>45</v>
+        <v>99</v>
       </c>
       <c r="I19" t="n">
-        <v>45</v>
+        <v>99</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>SQ0939451, SQ3644687</t>
+          <t>SQ9466277</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>SQ0939451</t>
+          <t>SQ9466277</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1501,168 +1501,168 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Intermediates Intentions Photography Project Course</t>
+          <t>LAKE DISTRICT Photography Workshops - Jan - Mar - Sep - Nov</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Six-month photography project and showcase your images in a public exhibition in WarwickshireLocation: 45 Hathaway Road, Tile Hill Village, Coventry, CV4 9HWDuration: 6-month project, 6 classesParticipants: Max 4Level: IntermediateDescription: Embark on a six-month photography project and showcase your images in a public exhibition in Warwickshire — a course designed to develop your intentions, vision and a coherent body of work.Equipment: A DSLR or mirrorless camera with manual exposure modes.</t>
+          <t>An exciting 3 day/2 night residential lake district photography workshop visiting some gorgeous spots around Cumbria. Runs every Jan, Mar, Sep, NovSummaryLocation: Cumbria - Lake DistrictDates:Fri 13 Nov - Sun 15 Nov - 3 Days/2 Nights 2026Fri 22 Jan - Sun 24 Jan - 3 Days/2 Nights 2027Fri 12 Mar - Sun 14 Mar - 3 Days/2 Nights 2027Fri 24 Sep - Sun 26 Sep - 3 Days/2 Nights 2027Extra night B&amp;B available for Thu - Contact me for details and booking separatelyParticipants: Max 4Fitness: 2. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details Lake DistrictDescription: This is a 3-day, 2-night residential Lake District photography workshop, based in the north lakes and open to all levels from beginner to advanced. The Lake District has been a favourite of landscape photographers for decades, and for good reason: nowhere else in England packs in such variety — mountains, tarns, ancient woodland, waterfalls and reflective lakes — and the changeable Cumbrian weather means it's never the same place twice. Misty mornings, atmospheric light, stormy skies and quiet reflections can all arrive within a single weekend.Over three days we shoot the iconic scenes at their best, basing ourselves in the north lakes and working two to three carefully chosen locations a day — from Derwent Water, Castlerigg and Ashness Bridge to the tarns and valleys of Langdale, Coniston and Buttermere. The rhythm follows the light: optional sunrise shoots, full days on location with tuition in the field, and optional sunset sessions, with evenings for relaxed picture reviews over a meal. Throughout, the emphasis isn't just on being at the famous viewpoint but on learning to see it — composing with intention, working intimate detail as readily as the grand vista, and reading light and weather as a harmony rather than chasing the obvious shot. You'll come away with a portfolio of dramatic Lakeland images and the field craft to read light and weather anywhere.With a maximum of just four photographers, this is genuinely personal tuition — Alan plans each day around the group, the season and the forecast, sends a detailed location itinerary a few days ahead, and adapts on the ground to chase the best conditions. Accommodation and breakfast are included, so you can switch off from the logistics and focus entirely on your photography for three days. Extra night B&amp;B available for Thursday — contact me for details and booking separately.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707220703945-94B0SK8PWUMOS78FTJMO/photography+project+-+intentions+photography+course.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714301696717-TME057MTL131H9UHU82H/Bassenthwaite+Rise.jpg</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/intermediates-intentions-photography-project-course</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/lake-district-photography-workshop</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>photography-classes, photography-courses</t>
+          <t>All Photography Workshops, - weekend residential photo workshops, Landscape</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9898707", "price": "400.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "priceSpecification": {"price": "400.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ5158309", "price": "1075.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Fri 13 Nov - 15 Nov - 3 Days 2026", "priceSpecification": {"price": "1075.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9016326", "price": "1075.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Fri 22 Jan - 24 Jan - 3 Days 2027"}, {"@type": "Offer", "sku": "SQ0142956", "price": "1125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Fri 12 Mar - 14 Mar - 3 Days 2027", "priceSpecification": {"price": "1125.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9100538", "price": "1075.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Fri 24 Sep - 26 Sep - 3 Days 2027", "priceSpecification": {"price": "1075.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H20" t="n">
-        <v>400</v>
+        <v>1075</v>
       </c>
       <c r="I20" t="n">
-        <v>400</v>
+        <v>1125</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>SQ9898707</t>
+          <t>SQ5158309, SQ9016326, SQ0142956, SQ9100538</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>SQ9898707</t>
+          <t>SQ5158309</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>course</t>
+          <t>event</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>KERRY - Southern Ireland Photography Workshop - Mar 2026</t>
+          <t>Fine Art Photography Prints - Canvas wrap-round - Multi Size</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Photograph amazing areas in South Kerry, Dingle, and Killarney National Park on this 5-day Ireland photography workshopSummaryLocation: Dingle and Killarney - Kerry Southern IrelandDates: Thu 5th - Mon 10th Mar 2026 - 5 Days/4 NightsParticipants: Max 4Fitness: 2. Easy-ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: DingleDescription: This is a 5-day, 4-night residential photography workshop in the south-west of Ireland — the longest and most immersive trip I run, based around Dingle and exploring some of the most beautiful country in Europe. Open to all levels and any camera, it takes in three extraordinary areas of County Kerry: the wild, sea-battered Dingle Peninsula, the dramatic coastline of South Kerry along the Skellig Ring, and the mountains, lakes and ancient woodland of Killarney National Park.The variety here is the gift and the challenge — mountains, lakes, waterfalls, woodland, coastline and rock formations, often within a single day — and five days gives us the time to do it justice. We'll cover the technical control you need, but the real focus is on learning to see: composing order and intention out of these vast, busy scenes, working close-up and intimate detail as readily as the grand vista, and reading light, weather and tide as a harmony rather than chasing the obvious postcard shot. Some stops are quick laybys to catch a fleeting moment; others we'll work slowly, waiting for the light and water to come good.With a maximum of just four photographers and five full days on the ground, this is genuinely personal tuition with the time to slow down and work properly — Alan plans each day around the season, the forecast and the tides, and sends a detailed itinerary ahead. You'll come away not just with a portfolio from one of Europe's great landscapes, but with a stronger way of seeing — light, composition and restraint — that will change how you photograph wherever you go next. An extra night's accommodation is available the day before if required — please request in advance, subject to hotel availability.</t>
+          <t>Fine Art Photography Prints - Canvas wrap-round creates a contemporary finish to your photo- available in seven sizes. Include in the image title when ordering</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1710060195646-WLFJL2H358FJD4GKV1CP/Coumeenoole+Strand+2.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1572426141642-UH9GBUDOUFH8QMTUA0KA/cavas%2Bsizes.jpg</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/ireland-photography-workshops-dingle</t>
+          <t>https://www.alanranger.com/photography-services-near-me/fine-art-photography-prints-canvas</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>coastal, All Photography Workshops, - weekend residential photo workshops</t>
+          <t>print</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ7419716", "price": "1595.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ0105911", "price": "135.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "16x12 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ4206024", "price": "177.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "24x16 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ0781804", "price": "219.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "30x20 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ3982814", "price": "306.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "36x24 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ8209269", "price": "336.65", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "40x30 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ7901040", "price": "414.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "48x36 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ7260825", "price": "459.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "60x40 Canvas Wrap Round"}]</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H21" t="n">
-        <v>1595</v>
+        <v>135.95</v>
       </c>
       <c r="I21" t="n">
-        <v>1595</v>
+        <v>459.95</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>SQ7419716</t>
+          <t>SQ0105911, SQ4206024, SQ0781804, SQ3982814, SQ8209269, SQ7901040, SQ7260825</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>SQ7419716</t>
+          <t>SQ0105911</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>product</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>LAKE DISTRICT Photography Workshops - Jan - Mar - Sep - Nov</t>
+          <t>Fine Art Photography Prints - Unframed Prints - Multi Sizes</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>An exciting 3 day/2 night residential lake district photography workshop visiting some gorgeous spots around Cumbria. Runs every Jan, Mar, Sep, NovSummaryLocation: Cumbria - Lake DistrictDates:Fri 18 Sep - Sun 20 Sep - 3 Days/2 Nights 2026Fri 13 Nov - Sun 15 Nov - 3 Days/2 Nights 2026Fri 22 Jan - Sun 24 Jan - 3 Days/2 Nights 2027Fri 12 Mar - Sun 14 Mar - 3 Days/2 Nights 2027Extra night B&amp;B available for Thu - Contact me for details and booking separatelyParticipants: Max 4Fitness: 2. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details Lake DistrictDescription: This is a 3-day, 2-night residential Lake District photography workshop, based in the north lakes and open to all levels from beginner to advanced. The Lake District has been a favourite of landscape photographers for decades, and for good reason: nowhere else in England packs in such variety — mountains, tarns, ancient woodland, waterfalls and reflective lakes — and the changeable Cumbrian weather means it's never the same place twice. Misty mornings, atmospheric light, stormy skies and quiet reflections can all arrive within a single weekend.Over three days we shoot the iconic scenes at their best, basing ourselves in the north lakes and working two to three carefully chosen locations a day — from Derwent Water, Castlerigg and Ashness Bridge to the tarns and valleys of Langdale, Coniston and Buttermere. The rhythm follows the light: optional sunrise shoots, full days on location with tuition in the field, and optional sunset sessions, with evenings for relaxed picture reviews over a meal. Throughout, the emphasis isn't just on being at the famous viewpoint but on learning to see it — composing with intention, working intimate detail as readily as the grand vista, and reading light and weather as a harmony rather than chasing the obvious shot. You'll come away with a portfolio of dramatic Lakeland images and the field craft to read light and weather anywhere.With a maximum of just four photographers, this is genuinely personal tuition — Alan plans each day around the group, the season and the forecast, sends a detailed location itinerary a few days ahead, and adapts on the ground to chase the best conditions. Accommodation and breakfast are included, so you can switch off from the logistics and focus entirely on your photography for three days. Extra night B&amp;B available for Thursday — contact me for details and booking separately.</t>
+          <t>Fine Art Photography Prints available in seven sizes. Giclee print on archival paper. Please include in the image title when ordering | Pro-Lab Printing</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714301696717-TME057MTL131H9UHU82H/Bassenthwaite+Rise.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707240002916-MMJ7CA3MX9HLO60532BO/fine+art+photography+prints.jpg</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/lake-district-photography-workshop</t>
+          <t>https://www.alanranger.com/photography-services-near-me/fine-art-photography-prints-unframed</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - weekend residential photo workshops, Landscape</t>
+          <t>print</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9100538", "price": "1075.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Fri 18 Sep - 20 Sep - 3 Days 2026", "priceSpecification": {"price": "1075.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5158309", "price": "1075.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Fri 13 Nov - 15 Nov - 3 Days 2026", "priceSpecification": {"price": "1075.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9016326", "price": "975.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Fri 22 Jan - 24 Jan - 3 Days 2027", "priceSpecification": {"price": "975.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0142956", "price": "1125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Fri 12 Mar - Sun 14 Mar - 3 Days/2 Nights 2027", "priceSpecification": {"price": "1125.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ4872440", "price": "50.57", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "16x12 Print"}, {"@type": "Offer", "sku": "SQ0453600", "price": "95.78", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "24x16 Print"}, {"@type": "Offer", "sku": "SQ7485354", "price": "138.86", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "30x20 Print"}, {"@type": "Offer", "sku": "SQ0167262", "price": "161.38", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "36x24 Print"}, {"@type": "Offer", "sku": "SQ1664775", "price": "217.23", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "40x30 Print"}, {"@type": "Offer", "sku": "SQ0377820", "price": "305.05", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "48x36 Print"}, {"@type": "Offer", "sku": "SQ8780582", "price": "416.85", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "60x40 Print"}]</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H22" t="n">
-        <v>975</v>
+        <v>50.57</v>
       </c>
       <c r="I22" t="n">
-        <v>1125</v>
+        <v>416.85</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>SQ9100538, SQ5158309, SQ9016326, SQ0142956</t>
+          <t>SQ4872440, SQ0453600, SQ7485354, SQ0167262, SQ1664775, SQ0377820, SQ8780582</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>SQ9100538</t>
+          <t>SQ4872440</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>product</t>
         </is>
       </c>
     </row>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ3794821", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Padley and Bolehill Sat 17th Oct  2026 09:30am - 4:00pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8457424", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Padley and Bolehill Sun 1st Nov  2026 09:30am - 4:00pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9037810", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Padley and Bolehill Sat 7th Nov  2026 09:30am - 4:00pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2363666", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Padley and Bolehill Sat 22nd May 2027 - 09:30 - 16:00", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ3794821", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Padley and Bolehill Sat 17th Oct  2026 09:30am - 4:00pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8457424", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Padley and Bolehill Sun 1st Nov  2026 09:30am - 4:00pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9037810", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Padley and Bolehill Sat 7th Nov  2026 09:30am - 4:00pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2363666", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Padley and Bolehill Sat 22nd May 2027 - 09:30 - 16:00", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -1725,107 +1725,107 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DEVON Landscape Photography  Workshops - Various Dates</t>
+          <t>Framed Fine Art Photography Prints - Multiple Sizes</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Hartland Quay - Landscape Photography Devon Workshop - Join me for this photo workshop to the best coastal and dramatic parts of Devon.SummaryLocation: North Devon - Hartland QuayDates:Fri 4th Sep - Sun 6th Sep 2026 - 3 Days/2 NightsThu 18th 12:30 - Sun 21st 12:30 Feb 2027 - 4 Days/3 NightsParticipants: Max 4Fitness: 2. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera, Tripod and ND Filters (tripod and filters can be provided)Photography Workshop Event Details DevonDescription: This is a multi-day residential landscape photography workshop based at Hartland Quay on the dramatic North Devon coast, open to all levels from beginner to advanced. Hartland Quay is one of the UK's most spectacular seascape locations — long slithers of rock formations running out into a fierce Atlantic tide — and it's the perfect base for learning seascape photography on a coastline that rewards drama, patience and timing.Across the workshop you'll photograph the classic Hartland Quay views and range out along some of the finest coast in the South West — from Bude and Clovelly to Welcombe Bay, Saunton Sands and Woolacombe. The focus is on the craft of seascape photography: composing a strong coastal frame, mastering long exposure to turn moving water and sky into mood, and timing your shoot to the light and the tide. But the technical side is only the floor — the real work is learning to see, composing with intention and reading light and tide as a harmony rather than chasing the obvious shot, working the intimate detail as readily as the grand vista. Each day follows that rhythm — optional sunrise and sunset shoots when the light is best, full days in the field with tuition, and evening photo reviews and editing sessions to sharpen your eye.With a maximum of just four photographers, this is genuinely personal tuition, and because the whole coast is tide- and light-dependent, Alan plans each day around the forecast and sends a detailed location itinerary a few days ahead. Tripods and ND filters can be lent if you don't yet own them, accommodation and breakfast are included, and you'll come away with a portfolio of dramatic Devon seascapes and a real command of long-exposure coastal technique. An extra night's accommodation is available the day before if required — please request in advance, subject to hotel availability.</t>
+          <t>Fine Art Photography Prints - Giclee Framed Prints available in four sizes. Black frame with white mount. Please include in the image title when ordering</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714299365471-K36RWNIKFNGJ4C70UEXB/Atlantic+Force.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707240165500-DB965TUR2FYMNEFPXS90/fine+art+photography+prints+-+framed.jpg</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/landscape-photography-devon-hartland-quay</t>
+          <t>https://www.alanranger.com/photography-services-near-me/framed-fine-art-photography-prints</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>coastal, All Photography Workshops, - weekend residential photo workshops</t>
+          <t>print</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ2516659", "price": "775.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Fri 4th Sep - Sun 6th Sep 2026 - 3 Days/2 Nights"}, {"@type": "Offer", "sku": "SQ3856406", "price": "950.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Thu 18th 12:30 - Sun 21st 12:30 Feb 2027 - 4 Days/3 Nights"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ6825544", "price": "133.85", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "16x12 Print (with Frame 20x16)"}, {"@type": "Offer", "sku": "SQ3786581", "price": "191.50", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "24x16 Print (with Frame 30x20)"}, {"@type": "Offer", "sku": "SQ1355351", "price": "267.43", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "30x20 Print (with Frame 40x30)"}, {"@type": "Offer", "sku": "SQ0156134", "price": "356.90", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "36x24 Print (with Frame 48x36)"}]</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H24" t="n">
-        <v>775</v>
+        <v>133.85</v>
       </c>
       <c r="I24" t="n">
-        <v>950</v>
+        <v>356.9</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>SQ2516659, SQ3856406</t>
+          <t>SQ6825544, SQ3786581, SQ1355351, SQ0156134</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>SQ2516659</t>
+          <t>SQ6825544</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>product</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SNOWDONIA Landscape Photography  - Sat 26 - Sun 27 Sep 2026</t>
+          <t>NORTHUMBERLAND Photography Workshops - Mar 18 - 21</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Join me on this landscape photography Snowdonia workshop in the iconic mountains, quarries and landscape of Snowdonia national park.Summary - Snowdonia Landscape photography workshopLocation:Wales - Snowdonia National ParkDates: Sat 26th - Sun 27th Sep 2026 - 2 Days/1 NightParticipants: Max 4 (1 Car, transport between locations included)Fitness: 2. Moderate (15-30 min walks)Experience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details SnowdoniaDescription: This is a 2-day, 1-night residential landscape photography workshop in Snowdonia National Park, North Wales — open to all levels from beginner to advanced. Home to the highest mountain ranges in England and Wales, Snowdonia is a landscape that will both inspire and challenge any photographer: rugged peaks and flowing rivers, serene lakes and ancient slate quarries, all within a compact corner of Wales that you'll learn to read and photograph in its ever-changing light.What makes Snowdonia so rewarding is its variety, and over two days we work three very different faces of it: the waterfalls and rivers that are perfect for long exposure, turning moving water to silk; the starker, striking world of the historic slate quarries and mining relics, where industry and mountain meet; and the majestic lakes, where still water mirrors the peaks for compelling, reflective compositions. Across all of it the focus stays on the same craft — composing order from a vast scene, controlling exposure across big tonal ranges, and timing your shoot to the light and weather that shift the mood from rugged to serene and back. And throughout, the emphasis isn't just on the grand vista but on learning to see it — working intimate detail as readily as the wide view, and reading light and colour as a harmony rather than chasing the obvious shot.With a maximum of just four photographers and transport between locations included, this is genuinely personal tuition — Alan plans each day around the season and the forecast, and sends a detailed location itinerary a few days ahead. Likely locations include the reflective waters of Llynnau Mymbyr beneath the Snowdon massif, the Capel Curig pinnacles, Swallow Falls and the hidden lake of Llyn Craftnant. Accommodation and breakfast are included, so all you have to think about is your photography — and you'll leave with a varied portfolio that captures both the drama and the stillness of this remarkable landscape. An extra night's accommodation is available the day before if required — please request in advance, subject to hotel availability.</t>
+          <t>Exciting 4 day residential Northumberland Landscape Photography Workshops - Coastline Photography visiting the iconic spots on the Northumbrian coastSummaryLocation: Northumberland, LowickDates:Thu 18 Mar, 13:00 - Sun 21st Mar, 13:00 2027 - 4 Days/3 NightsParticipants: Max 4Fitness: 2. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodNorthumberland Photography Workshops Event Details NorthumberlandDescription: This is a 4-day, 3-night residential Northumberland photography workshop along one of the most dramatic coastlines in Britain, open to all levels from beginner to advanced. Northumberland has more castles than any English county — over seventy — and on this coast the great ones meet the sea: Bamburgh rising from its rocky outcrop, Lindisfarne silhouetted against the North Sea, Dunstanburgh ringed by the black boulders of Embleton Beach. It's a coastline made for photographers who want history, drama and big coastal light in one trip.Based on the Northumberland coast, we spend four days chasing the best conditions across its finest locations — Bamburgh, Dunstanburgh, Lindisfarne, Beadnell, Craster and more — and because it's the east coast, you can shoot both sunrise and sunset from the same stretch of shore. The focus is on three things that define great coastal photography here: composing castles and shoreline into a strong frame, mastering long exposure to turn tide and sky into mood, and working the magical light of sunrise and sunset over the Farne Islands and empty beaches. Throughout, the emphasis isn't just on the famous castle view but on learning to see it — composing with intention, working intimate detail as readily as the grand vista, and reading light and weather as a harmony rather than chasing the obvious shot.With a maximum of just four photographers, this is genuinely personal tuition, planned each day around the tides, the light and the forecast, with a detailed location itinerary sent a few days ahead. Across four days you'll shoot empty beaches at first light, iconic castles and long-exposure seascapes — and come away with a portfolio of dramatic Northumbrian coastal images and a real command of long-exposure and coastal technique. An extra night's accommodation is available the day before if required — please request in advance, subject to hotel availability.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1711625824431-22D7V1RNKR8H2LBRW4Z9/Snowdonia+%2301+-+Oct+2023.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/eb76126f-7580-40f0-ac80-39b29897cdc7/Northumberland+-+March+2025+-+%2302.jpg</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/landscape-photography-snowdonia-workshops</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/coastal-northumberland-photography-workshops</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Landscape, - weekend residential photo workshops</t>
+          <t>coastal, All Photography Workshops, - weekend residential photo workshops</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ0548499", "price": "595.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8540187", "price": "1095.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "priceSpecification": {"price": "1095.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G25" t="n">
         <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>595</v>
+        <v>1095</v>
       </c>
       <c r="I25" t="n">
-        <v>595</v>
+        <v>1095</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>SQ0548499</t>
+          <t>SQ8540187</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>SQ0548499</t>
+          <t>SQ8540187</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1837,51 +1837,51 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>GOWER Landscape Photography Wales - 28 May - 30 May 2027</t>
+          <t>ANGLESEY Landscape Photography Workshop -  May 2027</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Stunning shorelines and beauty of South Wales and the Gower Peninsular. Max 3 places for this residential photography workshop - landscape photography walesSummaryLocation: South Wales - Gower PeninsularDates:Fri 28th May - Sun 30th May 2027 - 3 Days/2 NightsParticipants: Max 4Fitness: 3. HardExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodLandscape photography Wales Photography Workshop Event Details GowerDescription: This is a 3-day, 2-night residential landscape photography workshop on the Gower Peninsula in South Wales — the UK's very first Area of Outstanding Natural Beauty, and one of the finest stretches of coast for landscape photography in Wales. Open to all levels from beginner to advanced, it takes you along 19 miles of dramatic shoreline west of Swansea, where lofty limestone cliffs, golden sandy beaches and jagged rocky shores meet wild moorland, dunes and tranquil salt marshes.Over three days we work the peninsula's most iconic locations as the light and tides allow — from the sweeping expanse of Rhossili Bay and the dramatic outline of Worms Head to the wreck of the Helvetia and the snug cove of Pwll Du. The focus is on three things that make a strong coastal image: composing cliffs, beaches and rock forms into a balanced frame, mastering long exposure to draw movement out of sea and sky, and timing each shoot from dawn to dusk to catch the best light and tide. Throughout, the emphasis isn't just on the famous viewpoint but on learning to see it — composing with intention, working intimate detail as readily as the wide vista, and reading light and colour as a harmony rather than chasing the obvious shot. You'll photograph at sunrise and sunset, the richest hours on this coast, and return to locations in changing conditions to capture them at their best.With a small group taught personally, this is genuinely one-to-one tuition — Alan plans each day around the season, the forecast and the tide times, and sends a detailed location itinerary a few days ahead. Be prepared for some longer walks over cliff paths and rougher coastal ground to reach the best viewpoints. Accommodation and breakfast are included, so all you have to think about is your photography, and you'll come away with a varied portfolio of the Gower's iconic Welsh coastline — and the field craft to read light, tide and weather on any shore. An extra night's accommodation is available the day before if required — please request in advance, subject to hotel availability.</t>
+          <t>Join me for this exciting Anglesey landscape photography workshop, where we will shoot along the stunning coastline features to capture breathtaking vistas that showcase the natural beauty surrounding the shorelines and iconic lighthouses.Summary - Anglesey Photography WorkshopLocation: Wales - Anglesey IslandDates: Fri 14th May 15:00 - Sun 16th May 14:00, 2027Duration: 3 Days/2 NightsParticipants: Max 4 (1 Car, transport between locations included)Fitness: 2. Moderate (15-30 min walks)Experience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details Anglesey PhotographyDescription: This is a 3-day, 2-night residential landscape photography workshop on the iconic island of Anglesey, off the north-west coast of Wales, open to all levels from beginner to advanced. Anglesey's coastline is a photographer's dream — over 200 square miles ringed by sandy coves, working harbours, rocky headlands and three iconic lighthouses — and across a weekend you'll shoot it in the golden hours when its colour, light and sea views are at their most spectacular.We work the island's finest coastal locations — from Penmon Point's Trwyn Du Lighthouse and the Church in the Sea to South Stack, Llanddwyn Island and the strange, Martian-coloured landscape of Parys Mountain, once the world's largest copper mine. The focus is on three things that make a strong coastal landscape: composing sea, shore and sky into a balanced frame, working the golden-hour light at sunrise and sunset, and using long exposure to capture the movement of the Welsh sea. Throughout, the emphasis isn't just on the iconic view but on learning to see it — composing with intention, working intimate detail as readily as the wide vista, and reading colour and light as a harmony rather than chasing the obvious shot. The days follow the light — optional sunrise and sunset shoots, full days on location with tuition, and evenings for relaxed picture reviews.With a maximum of just four photographers and transport between locations included, this is genuinely personal, hassle-free tuition — Alan plans each day around the tides, the season and the forecast, and sends a detailed location itinerary a few days ahead. Accommodation and breakfast are included, so all you have to think about for three days is your photography, and you'll come away with a portfolio of dramatic Anglesey coastal images and the field craft to read light and sea anywhere. An extra night's accommodation is available the day before if required — please request in advance, subject to hotel availability.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1715702409761-590M3MJ45KYXBDH1KSM0/Gower+%2305+-+May+2024.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707225841274-TEMCPAEP5DHDVCBJP2RD/anglesey+photography+workshop.jpg</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/landscape-photography-wales-photo-workshop</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/landscape-photography-workshops-anglesey</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>coastal, All Photography Workshops, - weekend residential photo workshops</t>
+          <t>coastal, Landscape, - weekend residential photo workshops</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ5141863", "price": "825.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8503376", "price": "975.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29"}]</t>
         </is>
       </c>
       <c r="G26" t="n">
         <v>1</v>
       </c>
       <c r="H26" t="n">
-        <v>825</v>
+        <v>975</v>
       </c>
       <c r="I26" t="n">
-        <v>825</v>
+        <v>975</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>SQ5141863</t>
+          <t>SQ8503376</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>SQ5141863</t>
+          <t>SQ8503376</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -1893,51 +1893,51 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>NORFOLK Landscape Photography Workshop  - Coastal 20 - 22 Nov</t>
+          <t>NANT MILL Woodlands and Waterfalls Photo Workshop 7 Jun</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Landscape Photography Workshop Norfolk - Coastal Photography Based Nr CromerSummary - Norfolk Photography WorkshopLocation: North Norfolk Coast - Cromer AreaDates: Fri 20th, 09:30am - Sun 22nd Nov 2026, 14:00 - 3 Days/2 NightsParticipants: Max 4Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: NorfolkDescription: This is a 3-day, 2-night residential landscape photography workshop on the beautiful North Norfolk coast, based near Cromer — open to all levels from beginner to advanced. North Norfolk is one of the most varied and atmospheric stretches of coastline in England, and across a long weekend you'll photograph everything from classic seafronts and groynes to wild estuaries, windmills and big skies, learning to read and capture this ever-changing coastal landscape in its best light.There really is something for everyone here, and over three days we work a rich variety of locations as the light and tides allow — the seafronts and groynes at Overstrand and Cromer, the atmospheric estuaries of Morston Quay and Blakeney Harbour with their abandoned boats and twisting creeks, and the beach huts, windmills, sand dunes and flint-cottage charm of Blakeney village. The focus is on three things that make a strong coastal image: composing order from busy, expansive scenes, mastering long exposure to draw movement out of sea, sky and water, and timing each shoot to the tides and the soft coastal light. There's even an optional boat trip to see the seals along the way.With a maximum of just four photographers, this is genuinely personal tuition — Alan plans each day around the season, the forecast and the tide times, and sends a detailed location itinerary a few days ahead. Accommodation and breakfast are included, so all you have to think about is your photography, and you'll come away with a varied portfolio of the North Norfolk coast — seascapes, estuaries, windmills and beach huts — and the field craft to read light, tide and weather on any shore. An extra night's accommodation is available the day before if required — please request in advance, subject to hotel availability.</t>
+          <t>Long exposures photography on the river and waterfalls that run through this enchanting woodland, secluded Welsh valley at Nant MillSummaryLocation: Wales - Wrexham - Nant MillDates: Sat 7th June 202510:30 am to 2 pmParticipants: Max 6Fitness: 2. Easy-ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Nant MillDescription: This Nant Mill long exposure photography workshop takes you into a secluded Welsh valley near Wrexham, where a river and its waterfalls tumble through enchanting ancient woodland — open to all levels and any camera. Flowing water in a quiet, leafy gorge is the perfect subject for long exposure, and this half-day workshop is about more than the silky-water effect: it's about learning to see this beautiful, tucked-away place and make images of it that are calm, considered and your own, rather than the same shot everyone takes.The long-exposure craft is the floor we build on — setting up your tripod and filters, and calculating the right exposure time for the effect you want — but the real work is composition and seeing. Working the river, falls and woodland together, you'll learn to find order among the rocks, water and trees, to compose the intimate, close-up detail as readily as the wider valley view, and to read the soft, dappled light and the natural greens and browns of this ancient wood as a quiet harmony rather than chasing a loud, over-processed look. The aim is a photograph with mood and restraint — moving water that feels the way the place actually feels.It's a small group of no more than six, taught personally and pitched at exactly your level, so whether long exposure is new to you or you're refining your technique you get real one-to-one guidance in the field. You'll come away with a set of atmospheric long-exposure images of one of North Wales' hidden gems — and a stronger, more intentional way of seeing moving water and woodland that you can take anywhere.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/e301c931-8fdc-4ff0-bc78-618aea6241a1/Norfolk+Nov+2024+-+%2303.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/83fecb77-55e2-4a1b-b532-efa4213e832a/limbs.jpg</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/landscape-photography-workshop-norfolk</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/landscape-photography-workshops-nant-mill</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>coastal, All Photography Workshops, - weekend residential photo workshops</t>
+          <t>All Photography Workshops, - half-day photo workshops, Landscape, Woodlands</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8747213", "price": "1025.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "priceSpecification": {"price": "1025.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ4568959", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29"}]</t>
         </is>
       </c>
       <c r="G27" t="n">
         <v>1</v>
       </c>
       <c r="H27" t="n">
-        <v>1025</v>
+        <v>125</v>
       </c>
       <c r="I27" t="n">
-        <v>1025</v>
+        <v>125</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>SQ8747213</t>
+          <t>SQ4568959</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>SQ8747213</t>
+          <t>SQ4568959</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -1949,51 +1949,51 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ANGLESEY Landscape Photography Workshop -  May 2027</t>
+          <t>KERRY - Southern Ireland Photography Workshop - Mar 2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Join me for this exciting Anglesey landscape photography workshop, where we will shoot along the stunning coastline features to capture breathtaking vistas that showcase the natural beauty surrounding the shorelines and iconic lighthouses.Summary - Anglesey Photography WorkshopLocation: Wales - Anglesey IslandDates: Fri 14th May 15:00 - Sun 16th May 14:00, 2027Duration: 3 Days/2 NightsParticipants: Max 4 (1 Car, transport between locations included)Fitness: 2. Moderate (15-30 min walks)Experience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details Anglesey PhotographyDescription: This is a 3-day, 2-night residential landscape photography workshop on the iconic island of Anglesey, off the north-west coast of Wales, open to all levels from beginner to advanced. Anglesey's coastline is a photographer's dream — over 200 square miles ringed by sandy coves, working harbours, rocky headlands and three iconic lighthouses — and across a weekend you'll shoot it in the golden hours when its colour, light and sea views are at their most spectacular.We work the island's finest coastal locations — from Penmon Point's Trwyn Du Lighthouse and the Church in the Sea to South Stack, Llanddwyn Island and the strange, Martian-coloured landscape of Parys Mountain, once the world's largest copper mine. The focus is on three things that make a strong coastal landscape: composing sea, shore and sky into a balanced frame, working the golden-hour light at sunrise and sunset, and using long exposure to capture the movement of the Welsh sea. Throughout, the emphasis isn't just on the iconic view but on learning to see it — composing with intention, working intimate detail as readily as the wide vista, and reading colour and light as a harmony rather than chasing the obvious shot. The days follow the light — optional sunrise and sunset shoots, full days on location with tuition, and evenings for relaxed picture reviews.With a maximum of just four photographers and transport between locations included, this is genuinely personal, hassle-free tuition — Alan plans each day around the tides, the season and the forecast, and sends a detailed location itinerary a few days ahead. Accommodation and breakfast are included, so all you have to think about for three days is your photography, and you'll come away with a portfolio of dramatic Anglesey coastal images and the field craft to read light and sea anywhere. An extra night's accommodation is available the day before if required — please request in advance, subject to hotel availability.</t>
+          <t>Photograph amazing areas in South Kerry, Dingle, and Killarney National Park on this 5-day Ireland photography workshopSummaryLocation: Dingle and Killarney - Kerry Southern IrelandDates: Thu 5th - Mon 10th Mar 2026 - 5 Days/4 NightsParticipants: Max 4Fitness: 2. Easy-ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: DingleDescription: This is a 5-day, 4-night residential photography workshop in the south-west of Ireland — the longest and most immersive trip I run, based around Dingle and exploring some of the most beautiful country in Europe. Open to all levels and any camera, it takes in three extraordinary areas of County Kerry: the wild, sea-battered Dingle Peninsula, the dramatic coastline of South Kerry along the Skellig Ring, and the mountains, lakes and ancient woodland of Killarney National Park.The variety here is the gift and the challenge — mountains, lakes, waterfalls, woodland, coastline and rock formations, often within a single day — and five days gives us the time to do it justice. We'll cover the technical control you need, but the real focus is on learning to see: composing order and intention out of these vast, busy scenes, working close-up and intimate detail as readily as the grand vista, and reading light, weather and tide as a harmony rather than chasing the obvious postcard shot. Some stops are quick laybys to catch a fleeting moment; others we'll work slowly, waiting for the light and water to come good.With a maximum of just four photographers and five full days on the ground, this is genuinely personal tuition with the time to slow down and work properly — Alan plans each day around the season, the forecast and the tides, and sends a detailed itinerary ahead. You'll come away not just with a portfolio from one of Europe's great landscapes, but with a stronger way of seeing — light, composition and restraint — that will change how you photograph wherever you go next. An extra night's accommodation is available the day before if required — please request in advance, subject to hotel availability.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707225841274-TEMCPAEP5DHDVCBJP2RD/anglesey+photography+workshop.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1710060195646-WLFJL2H358FJD4GKV1CP/Coumeenoole+Strand+2.jpg</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/landscape-photography-workshops-anglesey</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/ireland-photography-workshops-dingle</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>coastal, Landscape, - weekend residential photo workshops</t>
+          <t>coastal, All Photography Workshops, - weekend residential photo workshops</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8503376", "price": "975.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ7419716", "price": "1595.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29"}]</t>
         </is>
       </c>
       <c r="G28" t="n">
         <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v>975</v>
+        <v>1595</v>
       </c>
       <c r="I28" t="n">
-        <v>975</v>
+        <v>1595</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>SQ8503376</t>
+          <t>SQ7419716</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>SQ8503376</t>
+          <t>SQ7419716</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2005,51 +2005,51 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>NANT MILL Woodlands and Waterfalls Photo Workshop 7 Jun</t>
+          <t>NORFOLK Landscape Photography Workshop  - Coastal 20 - 22 Nov</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Long exposures photography on the river and waterfalls that run through this enchanting woodland, secluded Welsh valley at Nant MillSummaryLocation: Wales - Wrexham - Nant MillDates: Sat 7th June 202510:30 am to 2 pmParticipants: Max 6Fitness: 2. Easy-ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Nant MillDescription: This Nant Mill long exposure photography workshop takes you into a secluded Welsh valley near Wrexham, where a river and its waterfalls tumble through enchanting ancient woodland — open to all levels and any camera. Flowing water in a quiet, leafy gorge is the perfect subject for long exposure, and this half-day workshop is about more than the silky-water effect: it's about learning to see this beautiful, tucked-away place and make images of it that are calm, considered and your own, rather than the same shot everyone takes.The long-exposure craft is the floor we build on — setting up your tripod and filters, and calculating the right exposure time for the effect you want — but the real work is composition and seeing. Working the river, falls and woodland together, you'll learn to find order among the rocks, water and trees, to compose the intimate, close-up detail as readily as the wider valley view, and to read the soft, dappled light and the natural greens and browns of this ancient wood as a quiet harmony rather than chasing a loud, over-processed look. The aim is a photograph with mood and restraint — moving water that feels the way the place actually feels.It's a small group of no more than six, taught personally and pitched at exactly your level, so whether long exposure is new to you or you're refining your technique you get real one-to-one guidance in the field. You'll come away with a set of atmospheric long-exposure images of one of North Wales' hidden gems — and a stronger, more intentional way of seeing moving water and woodland that you can take anywhere.</t>
+          <t>Landscape Photography Workshop Norfolk - Coastal Photography Based Nr CromerSummary - Norfolk Photography WorkshopLocation: North Norfolk Coast - Cromer AreaDates: Fri 20th, 09:30am - Sun 22nd Nov 2026, 14:00 - 3 Days/2 NightsParticipants: Max 4Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: NorfolkDescription: This is a 3-day, 2-night residential landscape photography workshop on the beautiful North Norfolk coast, based near Cromer — open to all levels from beginner to advanced. North Norfolk is one of the most varied and atmospheric stretches of coastline in England, and across a long weekend you'll photograph everything from classic seafronts and groynes to wild estuaries, windmills and big skies, learning to read and capture this ever-changing coastal landscape in its best light.There really is something for everyone here, and over three days we work a rich variety of locations as the light and tides allow — the seafronts and groynes at Overstrand and Cromer, the atmospheric estuaries of Morston Quay and Blakeney Harbour with their abandoned boats and twisting creeks, and the beach huts, windmills, sand dunes and flint-cottage charm of Blakeney village. The focus is on three things that make a strong coastal image: composing order from busy, expansive scenes, mastering long exposure to draw movement out of sea, sky and water, and timing each shoot to the tides and the soft coastal light. There's even an optional boat trip to see the seals along the way.With a maximum of just four photographers, this is genuinely personal tuition — Alan plans each day around the season, the forecast and the tide times, and sends a detailed location itinerary a few days ahead. Accommodation and breakfast are included, so all you have to think about is your photography, and you'll come away with a varied portfolio of the North Norfolk coast — seascapes, estuaries, windmills and beach huts — and the field craft to read light, tide and weather on any shore. An extra night's accommodation is available the day before if required — please request in advance, subject to hotel availability.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/83fecb77-55e2-4a1b-b532-efa4213e832a/limbs.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/e301c931-8fdc-4ff0-bc78-618aea6241a1/Norfolk+Nov+2024+-+%2303.jpg</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/landscape-photography-workshops-nant-mill</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/landscape-photography-workshop-norfolk</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - half-day photo workshops, Landscape, Woodlands</t>
+          <t>coastal, All Photography Workshops, - weekend residential photo workshops</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ4568959", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8747213", "price": "1025.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "priceSpecification": {"price": "1025.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G29" t="n">
         <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v>125</v>
+        <v>1025</v>
       </c>
       <c r="I29" t="n">
-        <v>125</v>
+        <v>1025</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>SQ4568959</t>
+          <t>SQ8747213</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>SQ4568959</t>
+          <t>SQ8747213</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2061,51 +2061,51 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Lightroom Courses for Beginners Photo Editing - Coventry</t>
+          <t>Beginners Portrait Photography Course - Coventry 11 Oct -25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>For those who want to implement the best workflow for image management and all the dos and don'ts of post-production with these Photo Editing Classes with LightroomAdobe Lightroom Classic Courses for Beginners - CoventryLocation: 45 Hathaway Road, Coventry, CV4 9HWDuration: 3 × 2hr evening classes (19:00–21:00)Participants: Max 3Start Dates:Lightroom Editing CourseCoventry 3 wks - Mon 7 Sep - 21 Sep 2026Coventry 3 wks - Thu 12 Nov - 26 Nov 2026Coventry 3 wks - Tue 12 Jan - 26 Jan 2027Coventry 3 wks - Thu 6 May - 20 May 2027Level: BeginnersDescription: A practical three-week evening course that takes you from a messy photo library and untouched RAW files to a finished, repeatable Lightroom Classic workflow — working on your own laptop throughout.Week 1 is about getting organised: catalogues, importing, collections, keywords and star ratings, so you can find and manage your photos for good rather than losing them across folders.Week 2 moves on to global adjustments — reading the histogram, then exposure, white balance, contrast, tone curves and sharpening — the core develop tools that do most of the work on any image.Week 3 covers local adjustments — graduated and radial filters, adjustment brushes and spot removal — and pulling it together into a consistent, repeatable style across your photos.With a maximum of three people, you get real hands-on help on your own screen whenever you hit a problem, plus course notes for each module and practical assignments to work on between sessions. Beginners welcome — no editing experience needed; just bring a laptop with Adobe Lightroom Classic installed and an active subscription.Equipment: You will need a laptop with Adobe Lightroom Classic subscription and the App installed. Alan will provide you with a training Lightroom Library with images and use that to explain and then demonstrate the various tools.</t>
+          <t>Beginners Portrait Photography Course Location: 17A Spon Street, Coventry, CV1 3BA (Pay &amp; Display, or Skydome Multi-Storey, 15 Croft Rd, CV1 3LD)Duration: 1-day course, 9am–5pm (approx 1hr lunch)Participants: Max 4Start Dates: Portrait Photography CourseSaturday 11 Oct 2025 - CoventryLevel: BeginnerDescription: A 1-day portrait photography course suitable for any amateur who wants to learn the fundamentals — lighting, exposure, camera settings and composition.Equipment: A DSLR or mirrorless camera with manual exposure modes, and a good understanding of the basics of exposure, aperture, shutter speed and ISO. Ideally a zoom lens (50mm+) or a 50mm prime.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/fe40a5e1-7fa2-4057-982e-555479b97022/Lightroom+courses+-+photo+editing+course.png</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/7d4f9092-b44c-4d74-b858-cc2bcf675b8b/portraits+class.png</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/lightroom-courses-for-beginners-coventry</t>
+          <t>https://www.alanranger.com/photography-services-near-me/beginners-portrait-photography-course</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>photography-classes, photography-courses, photo editing, lightroom</t>
+          <t>photography-classes, photography-courses</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ7526725", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Coventry 3 wks - Mon 7 Sep - 21 Sep 2026"}, {"@type": "Offer", "sku": "SQ6831161", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Coventry 3 wks - Thu 12 Nov - 26 Nov 2026"}, {"@type": "Offer", "sku": "SQ1021857", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Coventry 3 wks - Tue 12 Jan - 26 Jan 2027"}, {"@type": "Offer", "sku": "SQ3349262", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Coventry 3 wks - Thu 6 May - 20 May 2027"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ2592535", "price": "195.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29"}]</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H30" t="n">
-        <v>150</v>
+        <v>195</v>
       </c>
       <c r="I30" t="n">
-        <v>150</v>
+        <v>195</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>SQ7526725, SQ6831161, SQ1021857, SQ3349262</t>
+          <t>SQ2592535</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>SQ7526725</t>
+          <t>SQ2592535</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2117,51 +2117,51 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>KENILWORTH Sunset Long Exposure Photography Workshop</t>
+          <t>SUFFOLK Landscape Photography Workshops - 5th-7th Feb</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Sunset landscape long exposure photography workshop shoots around Kenilworth Castle - Warwickshire - Various Dates | Long Exposures | Open to all levels| Book TodaySummaryLocation: Warwickshire - KenilworthDates:Mon 11 May 2026 - 18:30 - 20:30Tue 1 Sep 2026 - 18:00 - 20:00Wed 23 Sep 2026 - 17:45 - 19:45Mon 22 Mar 2027 - 18:00 - 20:00Wed 14 Apr 2027 - 18:30 - 20:30Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details KenilworthDescription: This Long Exposure Photography Workshop is an evening shoot around the floodlit ruins of Kenilworth Castle in Warwickshire, open to all levels and any camera. Once one of England's mightiest fortresses and Robert Dudley's Elizabethan palace, the castle makes a dramatic subject against a darkening sky — and this workshop is built around the magic of long exposure at dusk, when the fading light, the castle's silhouette and a slow shutter combine to create atmospheric images that capture a sense of place, not just a record of a building.The long-exposure craft is the floor we build on, and we'll cover it properly: calculating exposure times for the movement and mood you want, focusing and exposing confidently in low light, and balancing ISO, shutter and aperture as the light drops. But the real work is learning to see. As the sky changes you'll compose the castle with intention — finding the frame beyond the obvious silhouette, working detail and texture as readily as the grand wide view, and reading the interplay of fading light, floodlight and deep shadow as a harmony rather than a problem to fight. The aim is an image with mood and restraint, where every element earns its place.It's a small group of no more than six, taught personally and pitched at exactly your level, so whether long exposure is new to you or you're refining your technique, you get real one-to-one guidance in the field. You'll come away with a set of atmospheric long-exposure images of one of England's most romantic castles — and a sharper, more intentional way of seeing light, movement and mood after dark anywhere.</t>
+          <t>Join us for an inspiring Suffolk landscape photography workshop, where you'll have the opportunity to create stunning long exposures during breathtaking sunrises and vibrant sunsets. We will explore picturesque quays, serene estuaries, intriguing piers, and tranquil marshes, all while capturing the beauty of charming beach huts and ancient woodlands. Emphasising artistic expression, we'll also delve into the world of black and white photography, allowing you to bring a classic touch to your coastal images.SummaryLocation: Suffolk - East Anglia / Southwold/Aldeburgh AreaDates: Fri 5th 09:30 - Sun 7th 14:30 Feb 2027 - 3 Days/2 NightsParticipants: Max 4 (1 Car, transport between locations included)Fitness: 2. Moderate (15-30 min walks)Experience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details SuffolkDescription: This is a 3-day, 2-night residential Suffolk landscape photography workshop based on the Southwold and Aldeburgh coast, open to all levels from beginner to advanced. The Suffolk coastline is one of England's most photogenic and most varied — wide shoreline vistas, big skies, and a wealth of subjects most coastlines can't match: weathered piers, painted beach huts, iconic sea-defence structures and the traditional sails of Herringfleet Windmill. It's a landscape that rewards photographers who slow down and learn to see it.The focus is on long exposure and the art of black and white photography — learning to compose a strong coastal frame, to use long exposures to smooth water and sky into mood, and to recognise when a scene works better in mono. It's about more than the technical craft, though: the real work is learning to see — composing with intention, working intimate detail as readily as the wide vista, and reading light and tone as a harmony rather than chasing the obvious shot. It's never prescriptive either: over three days and two to three locations a day — from Southwold and Walberswick to Dunwich, Orford and Aldeburgh — we work with whatever light and conditions the coast gives us, with early sunrise shoots, full days in the field with tuition, and evenings for relaxed picture reviews.With a maximum of just four photographers and transport between locations included, this is genuinely personal, hassle-free tuition — Alan plans each day around the group, the season, the tides and the forecast, and sends a detailed location itinerary a few days ahead. En-suite accommodation and breakfast are included, so all you have to think about for three days is your photography. You'll come away with a portfolio of atmospheric Suffolk coastal images and a real grasp of long exposure and black and white technique. An extra night is available the day before on request, ideal for those travelling from a distance — contact me to arrange.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1712472502735-OHOKCDKMCP1BAMQ0JQUA/kenilworth+defenses.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714667523305-2SEM1T5WD278HHO4HJIV/Southwold+Sunrise.jpg</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/long-exposure-photography-kenilworth</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/suffolk-landscape-photography-workshops</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - half-day photo workshops, Landscape</t>
+          <t>coastal, - weekend residential photo workshops</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9140400", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Tue 1 Sep 2026 - 18:00 - 20:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8220723", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Wed 23 Sep 2026 - 17:45 - 19:45", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0932604", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Mon 22 Mar 2027 - 18:00 - 20:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1178418", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Wed 14 Apr 2027 - 18:30 - 20:30", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ2176971", "price": "995.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "priceSpecification": {"price": "995.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H31" t="n">
-        <v>50</v>
+        <v>995</v>
       </c>
       <c r="I31" t="n">
-        <v>50</v>
+        <v>995</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>SQ9140400, SQ8220723, SQ0932604, SQ1178418</t>
+          <t>SQ2176971</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>SQ9140400</t>
+          <t>SQ2176971</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2173,51 +2173,51 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>FAIRY GLEN and Fairy Falls Long Exposure Photography</t>
+          <t>MACRO Photography Workshops Warwickshire - Various</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>A magical gorge on the River Conwy at Betws-y-Coed. Fairy Glen and Fairy Falls provide an opportunity to practise long exposure photography on the magic of this river. Fairy Glen Betws-y-Coed Long Exposure Photography WorkshopSummaryLocation: Wales - Betws-y-CoedDates:Sat 26th Sep 2026 - 10:00 - 13:30Sat 6th Mar 2027 - 10:00 - 13:30Fri 14th May 2027 - 10:00 - 13:30 + Option for Anglesey Weekend WorkshopParticipants: Max 4Fitness: 2. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details Fairy GlenDescription: This Fairy Glen long exposure photography workshop takes you into one of Wales' most magical locations — a serene, secluded gorge where the River Conwy tumbles through the woods at Betws-y-Coed — and is open to all levels and any camera. Flowing water through a wooded gorge is the perfect subject for long exposure, and this half-day workshop is about more than the silky-water effect: it's about learning to see this enchanting place and make images of it that are calm, considered and your own, rather than the same shot everyone takes.The long-exposure craft is the floor we build on — setting up your tripod and filters, and calculating the right exposure time for the effect you want — but the real work is composition and seeing. Working two great locations within a couple of miles of each other, you'll learn to find order among the rocks, water and woodland, to compose the intimate detail as readily as the wider gorge, and to read the soft, dappled light and the natural greens and browns of the glen as a quiet harmony rather than chasing a loud, over-processed look. The aim is a photograph with mood and restraint — moving water that feels like the place actually feels.With a maximum of just four photographers, this is genuinely personal tuition, with Alan guiding each person through observation, shot design, shooting and image reviews at both locations. You'll come away with a set of atmospheric long-exposure images of one of Snowdonia's hidden gems — and a stronger, more intentional way of seeing moving water and woodland that you can take anywhere.</t>
+          <t>Abstract and Macro Photography Workshop . Learn about camera settings, lens use, controlling DoF and composition. Various Dates in Warwickshire | Half DaySummaryLocation: WarwickshireDates: Macro Photography WorkshopsMacro Photography - Sun Nov 28th 2026 - 10:30am - 12:30pmMacro Photography - Sat May 1st 2027 - 11am - 1pmMacro Photography - Sun Sep 29th 2027 - 4:00pm - 6:00pmParticipants: Max 4Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: Digital Camera and Tripod, Zoom or Macro LensMacro Photography Workshop Event Details: Macro Photography and AbstractDescription: This Abstract and Macro Photography Workshop takes place at a Warwickshire location and is open to all levels and any camera. Macro is where ordinary surroundings become extraordinary — get close and a tree trunk, a piece of weathered stone or a patch of water reveals shapes, colours, tones and patterns most people walk straight past. The whole session is about learning to see them, and then photograph them with intention.The technical craft matters here — and we'll cover it properly — but it's the floor, not the point. Working around the area together, Alan guides you through the settings that give you control: getting sharp focus and using a macro lens or zoom, controlling depth of field to isolate your subject, and building a composition with real intention. From there the real work begins — training your eye to find the abstract within the ordinary, to read tone, shadow and highlight, and to treat colour as a harmony to compose with rather than a loud effect to chase. The aim is never the obvious close-up everyone takes, but an image that's considered and your own.It's a small group of no more than four, taught personally by an award-winning professional photographer, so every person gets real one-to-one guidance in the field — briefing and set-up, then shooting with reviews and tuition as you go. You'll leave with your own macro and abstract images, and a sharper, more intentional way of seeing detail, colour and light that changes how you photograph everything afterwards.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707214813724-6QPD5O2XJNRQNOEIRBXO/Fairy+Glen+Betws-y-Coed+Photography+Workshop.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/25c550a3-a242-4303-a11b-367dd7055dbe/Abstract%2Band%2BMacro%2BPhotography%2BWorkshops%2B%25282%2529.jpg</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/long-exposure-photography-workshop-fairy-glen</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/abstract-and-macro-photography-workshops</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - half-day photo workshops, Landscape</t>
+          <t>All Photography Workshops, - half-day photo workshops, Macro &amp; Abstract</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8778402", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Sat 26th Sep 2026 - 10:00 - 13:30"}, {"@type": "Offer", "sku": "SQ9080164", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Sat 6th Mar 2027 - 10:00 - 13:30"}, {"@type": "Offer", "sku": "SQ6636860", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Fri 14th May 2027 - 10:00 - 13:30"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9970442", "price": "65.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Sun Nov 28th 2026 - 10:30am - 12:30pm"}, {"@type": "Offer", "sku": "SQ2051466", "price": "65.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Sat May 1st 2027 - 11am - 1pm"}, {"@type": "Offer", "sku": "SQ8660736", "price": "65.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Sun Sep 29th 2027 - 4:00pm - 6:00pm"}]</t>
         </is>
       </c>
       <c r="G32" t="n">
         <v>3</v>
       </c>
       <c r="H32" t="n">
-        <v>125</v>
+        <v>65</v>
       </c>
       <c r="I32" t="n">
-        <v>125</v>
+        <v>65</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>SQ8778402, SQ9080164, SQ6636860</t>
+          <t>SQ9970442, SQ2051466, SQ8660736</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>SQ8778402</t>
+          <t>SQ9970442</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2229,51 +2229,51 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>BURNHAM ON SEA Long Exposure Photography Workshop 1 Aug</t>
+          <t>NORTH YORKSHIRE Landscape Photography Workshop - Jun 2027</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Seascape and Long Exposure Photography workshop at this iconic location in Somerset with the lighthouse at Burnham on SeaSummaryLocation: Somerset - Burnham On SeaDates: Sat 1st Aug 2026 - 18:45 - 21:30Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details BurnhamDescription: This Burnham on Sea long exposure photography workshop is an evening on the Somerset coast built around one of the most photogenic subjects in the country — the town's iconic nine-legged lighthouse, standing on stilts on the open beach. Open to all levels and any camera, it's about the art of long exposure: not just the silky-water effect, but learning to see this minimalist coast and make images of it that are calm, considered and your own, rather than the same shot everyone takes.The long-exposure craft is the floor we build on, and we'll cover it properly — setting up, calculating shutter times and using filters — before heading onto the beach to shoot on an incoming tide as the sun sets. But the real work is composition and seeing. As the light builds you'll learn to place the lighthouse with real intention in a clean, minimalist frame, to work the intimate detail of stilts, reflections and wet sand as readily as the wide seascape, and to read the soft, shifting colour of a coastal sunset as a harmony rather than chasing a loud, over-saturated sky. The aim is mood and restraint — an image that feels like the quiet of that beach at dusk.It's a small group of no more than six, taught personally and pitched at exactly your level, with Alan on hand throughout for settings, composition and one-to-one guidance in the field. Whether long exposure is new to you or you're refining your technique, you'll come away with a set of atmospheric sunset images of this famous Somerset landmark — and a sharper, more intentional way of seeing light, movement and mood that you can take to any coast.</t>
+          <t>An exciting 4-day residential Yorkshire Landscape Photography Workshop - visiting some of the iconic spots around the North Yorkshire Coast and MoorsSummary - Photography Workshops YorkshireLocation: North YorkshireDates:Thu 3 Jun - Sun 6 Jun 2027 - 4 Days/3 NightsParticipants: Max 3Fitness: 2. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event DetailsNorth YorkshireDescription: This is a 4-day, 3-night residential landscape photography workshop on the dramatic northeast coast of England, exploring the iconic coastline and moors of North Yorkshire — open to all levels from beginner to advanced. Based on the coast, you'll photograph some of the most atmospheric scenery in the country, from the tumbling fishing village of Staithes and the sweeping bay at Runswick to the harbour and abbey town of Whitby, with the wild North York Moors as a backdrop.Over four full days we work from sunrise to sunset to make the most of the best light, tides and empty beaches — far more time on location than a short workshop allows. The focus is on three things that make a strong coastal image: composing the rocks, headlands and shoreline into a balanced frame, mastering long exposure to draw out movement in the sea and sky, and timing each shoot to the tides and the golden light of dawn and dusk. Throughout, the emphasis isn't just on the postcard view but on learning to see it — composing with intention, working intimate detail as readily as the wide vista, and reading light and tide as a harmony rather than chasing the obvious shot. Across the four days you'll build a real working rhythm for coastal photography, returning to locations in different conditions to capture them at their very best.With a maximum of just three photographers, this is exceptionally personal tuition — Alan plans each day around the season, the forecast and the tide times, and sends a detailed location itinerary a few days ahead. Accommodation and breakfast are included, so all you have to think about is your photography, and you'll come away with a varied portfolio of iconic Yorkshire coast and moorland images — and the field craft to read light, tide and weather on any coastline. An extra night's accommodation is available the day before if required — please request in advance, subject to hotel availability.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714573609279-RSKP2ELI51B1VY87SOCS/Burnham+Still.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714649253879-9IH9C2DQR5W69WW1JK5P/Saltwick+Bay.jpg</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/long-exposure-photography-workshops-burnham</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/north-yorkshire-landscape-photography</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>coastal, All Photography Workshops, - half-day photo workshops</t>
+          <t>coastal, All Photography Workshops, - weekend residential photo workshops</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9466277", "price": "95.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9283225", "price": "1450.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "priceSpecification": {"price": "1450.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G33" t="n">
         <v>1</v>
       </c>
       <c r="H33" t="n">
-        <v>95</v>
+        <v>1450</v>
       </c>
       <c r="I33" t="n">
-        <v>95</v>
+        <v>1450</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>SQ9466277</t>
+          <t>SQ9283225</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>SQ9466277</t>
+          <t>SQ9283225</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2285,107 +2285,107 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Monthly Pick N Mix Subscription | Interest Free Payment Plan</t>
+          <t>Christmas Photography Seasonal Workshops - Warwickshire UK</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Monthly Pick N Mix Subscription Package. 10% Discount on events/services for one year | Interest Free Payment Plan | Take events or lessons immediately |</t>
+          <t>Christmas photography workshops. A Leisurely Christmas photography walk and photograph the countryside - Lapworth or the Christmas lights Stratford Upon Avon photography- Warwickshire - Expert Advice GivenSummaryLocation: WarwickshireDates: 2026 DatesThu 10 December 2026 - 18:45 - 20:30 - Stratford Upon Avon Evening ShootTue, 29 December 2026 - 1 day Christmas Photo Walk 09:00 15:00Break for pub lunch around 12:45 - Not includedParticipants: Max 6Fitness: 2. Easy-ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodChristmas Photography Workshop Event Details Christmas PhotowalkDescription: This Christmas Photography Workshop is the perfect way to escape the heat and fuss of the festive season — swap the wrapping paper for your camera, walk off a little of the overindulgence, and rediscover how much there is to photograph at the most atmospheric time of year. Open to all levels and any camera, it's a relaxed, sociable outing in Warwickshire with expert guidance throughout, and there's a choice of two very different sessions.Stratford-upon-Avon, evening: an after-dark shoot in the heart of the town, photographing the Christmas lights and festive atmosphere. It's a chance to work long exposure, reflections and the warm glow of the season — learning to control exposure in low light and compose a strong frame out of a busy, sparkling scene rather than settling for the obvious snapshot.Lapworth, daytime: the antidote to Christmas. Once the presents are unwrapped, the family politics have peaked and you've eaten your bodyweight in turkey, this leisurely day in the winter countryside is the tonic — a chance to breathe, clear your head and lose yourself in your photography for a few hours. We'll amble through frosty fields, bare woodland and quiet lanes reading the soft, low winter light, with a relaxed lunch in the middle of the day. The whole walk is under five miles at an easy, unhurried pace — gentle enough that the photography, the fresh air and the company are the whole point. The focus stays on seeing: composing with intention, working both intimate detail and wider vista, and reading light, texture and mood to make a picture that's truly yours.It's a small group of no more than six, taught personally and pitched at exactly your level, with one-to-one guidance in the field throughout. Whether you choose the festive lights of Stratford, the crisp countryside of Lapworth, or both, you'll come away with a set of atmospheric seasonal images — and a stronger eye for light, composition and winter colour that carries through long after the decorations come down. For the Lapworth day, a table is reserved in advance at a welcoming country pub, with a festive menu offering both lighter and full festive-meal options to suit every appetite. The lunch itself isn't included in the workshop fee, so you simply pay for what you choose on the day.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/7c76925a-43b0-425c-995e-4f4e0190221c/Photography+Payment+Plan.png</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1573822266360-1I7REB8B91RNZXW2PNKP/christmas-sparkle-photography-workshop.jpg</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/monthly-pick-n-mix-subscription</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/christmas-photography-workshops</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>photography-classes, photography-courses, photography-workshops</t>
+          <t>All Photography Workshops, - half-day photo workshops, Landscape, Urban</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ3248242", "price": "42.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "12 x £42 = £500"}, {"@type": "Offer", "sku": "SQ3113323", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "12 x £50 = £600"}, {"@type": "Offer", "sku": "SQ4824271", "price": "60.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "12 x £60 = £720"}, {"@type": "Offer", "sku": "SQ5162846", "price": "65.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "12 x £65 = £780"}, {"@type": "Offer", "sku": "SQ0960457", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "12 x £75 = £900"}, {"@type": "Offer", "sku": "SQ6021981", "price": "85.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "12 x £85 = £1020"}, {"@type": "Offer", "sku": "SQ3596605", "price": "100.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "12 x £100 = £1200"}, {"@type": "Offer", "sku": "SQ2188035", "price": "120.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "12 x £120 = £1440"}, {"@type": "Offer", "sku": "SQ5970824", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "12 x £150 = £1800"}, {"@type": "Offer", "sku": "SQ0439157", "price": "175.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "12 x £175 = £2100"}, {"@type": "Offer", "sku": "SQ9583245", "price": "200.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "12 x £200 = £2400"}, {"@type": "Offer", "sku": "SQ9424558", "price": "250.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "12 x £250 = £3000"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8119747", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Thu 10 Dec 18:45- 20:30 - Stratford Upon Avon"}, {"@type": "Offer", "sku": "SQ6178610", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Tue 29 Dec 09:00 - 15:00 - Lapworth"}]</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="H34" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="I34" t="n">
-        <v>250</v>
+        <v>125</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>SQ3248242, SQ3113323, SQ4824271, SQ5162846, SQ0960457, SQ6021981, SQ3596605, SQ2188035, SQ5970824, SQ0439157, SQ9583245, SQ9424558</t>
+          <t>SQ8119747, SQ6178610</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>SQ3248242</t>
+          <t>SQ8119747</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>event</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>NORTH YORKSHIRE Landscape Photography Workshop - Sep 2026</t>
+          <t>YORKSHIRE DALES Landscape  Photography Workshop - 16 - 18 Apr</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>An exciting 4-day residential Yorkshire Landscape Photography Workshop - visiting some of the iconic spots around the North Yorkshire Coast and MoorsSummary - Photography Workshops YorkshireLocation: North YorkshireDates:Thu 10 Sep - Sun 13 Sep 2026 - 4 Days/3 NightsParticipants: Max 3Fitness: 2. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details North YorkshireDescription: This is a 4-day, 3-night residential landscape photography workshop on the dramatic northeast coast of England, exploring the iconic coastline and moors of North Yorkshire — open to all levels from beginner to advanced. Based on the coast, you'll photograph some of the most atmospheric scenery in the country, from the tumbling fishing village of Staithes and the sweeping bay at Runswick to the harbour and abbey town of Whitby, with the wild North York Moors as a backdrop.Over four full days we work from sunrise to sunset to make the most of the best light, tides and empty beaches — far more time on location than a short workshop allows. The focus is on three things that make a strong coastal image: composing the rocks, headlands and shoreline into a balanced frame, mastering long exposure to draw out movement in the sea and sky, and timing each shoot to the tides and the golden light of dawn and dusk. Throughout, the emphasis isn't just on the postcard view but on learning to see it — composing with intention, working intimate detail as readily as the wide vista, and reading light and tide as a harmony rather than chasing the obvious shot. Across the four days you'll build a real working rhythm for coastal photography, returning to locations in different conditions to capture them at their very best.With a maximum of just three photographers, this is exceptionally personal tuition — Alan plans each day around the season, the forecast and the tide times, and sends a detailed location itinerary a few days ahead. Accommodation and breakfast are included, so all you have to think about is your photography, and you'll come away with a varied portfolio of iconic Yorkshire coast and moorland images — and the field craft to read light, tide and weather on any coastline. An extra night's accommodation is available the day before if required — please request in advance, subject to hotel availability.</t>
+          <t>Yorkshire Dales Photography Workshop - Join me for this fantastic landscape workshop on limestone pavements and waterfalls.SummaryLocation: Yorkshire DalesDates: Fri 16th - Sun 18th Apr 2027 - 3 Days/2 NightsParticipants: Max 4Fitness: 3. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details Yorkshire DalesDescription: This is a 3-day, 2-night residential landscape photography workshop in the Yorkshire Dales — one of England's most iconic and varied landscapes, open to all levels from beginner to advanced. From dramatic limestone pavements and amphitheatre cliffs to tumbling waterfalls, soaring viaducts and lone, wind-sculpted trees, the Dales pack an extraordinary range of subjects into one area, and over a long weekend you'll learn to read and photograph this moody, dramatic country in its best light.Across three days we work some of the Dales' most rewarding locations as the conditions and season allow — the natural amphitheatre of Malham Cove and the ravine at Gordale Scar, the waterfalls of Ingleton, Aysgarth and Janet's Foss, the sweeping arches of Ribblehead Viaduct, and the famous lone tree set on its bare limestone pavement. The focus is on three things that make a strong Dales image: composing rock, water and vista into a balanced frame, mastering long exposure to bring waterfalls and rivers to life, and timing each shoot — including early morning starts — to the dramatic light and weather these hills are known for. Throughout, the emphasis isn't just on the grand vista but on learning to see it — composing with intention, working intimate detail as readily as the wide view, and reading light and colour as a harmony rather than chasing the obvious shot.With a maximum of just four photographers, this is genuinely personal tuition — Alan plans each day around the season and the forecast, and sends a detailed location itinerary a few days ahead. Accommodation and breakfast are included, so all you have to think about is your photography, and you'll come away with a varied portfolio of the Yorkshire Dales — waterfalls, limestone pavements, viaducts and classic vistas — and the field craft to capture dramatic upland landscape anywhere. An extra night's accommodation is available the day before if required — please request in advance, subject to hotel availability.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714649253207-Y2XV1QZ3QPAVYS7CEE33/Flamborough+-+Temptation.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714659095505-TB874TXCA6ADNDFC82FX/Muker+%2302+-+July+2021.jpg</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/north-yorkshire-landscape-photography</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/yorkshire-dales-photography-workshops</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>coastal, All Photography Workshops, - weekend residential photo workshops</t>
+          <t>All Photography Workshops, - weekend residential photo workshops, Landscape</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9283225", "price": "1450.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "priceSpecification": {"price": "1450.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9211910", "price": "895.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29"}]</t>
         </is>
       </c>
       <c r="G35" t="n">
         <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>1450</v>
+        <v>895</v>
       </c>
       <c r="I35" t="n">
-        <v>1450</v>
+        <v>895</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>SQ9283225</t>
+          <t>SQ9211910</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>SQ9283225</t>
+          <t>SQ9211910</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2397,51 +2397,51 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>PEAK DISTRICT HEATHER Photography Workshops - 14-15 Aug</t>
+          <t>WALES Photography Workshop | Lake Vyrnwy 10-11 Oct</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Join me for the Peak District heather displays over this iconic landscape in August - 4hr Heather Peak District Photography Workshops | All levels welcomeSummaryLocation: Peak District - Derbyshire/Staffordshire2026 - Sat 15th Aug 18:15 21:15 - Derbyshire Surprise View2026 - Sun 16th Aug 05:45 08:45 - Staffordshire - The Roaches2027 - Sat 14th Aug 18:15 21:15 - Derbyshire Surprise View2027 - Sun 15th Aug 05:45 08:45 - Staffordshire - The RoachesParticipants: Max 6Fitness: 3. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details HeathersDescription: Every August the moors of the Peak District turn a spectacular purple as the heather comes into bloom, and this Peak District Heather Photography Workshop is your chance to capture that fleeting display at its very best — open to all levels and any camera. Run as short, focused sessions at the magic hours of sunrise and sunset, it pairs one of Britain's most iconic landscapes with its richest seasonal colour, and the low golden light that makes heather and gritstone glow.You can join either of two sessions, or both: a sunset shoot at Surprise View above Hathersage in Derbyshire — one of the finest viewpoints in the Peak, with sweeping heather foregrounds, the Mother Cap stone and famously dark skies — or a sunrise shoot among the dramatic gritstone of The Roaches, Hen Cloud and Ramshaw Rocks in Staffordshire, weathered into extraordinary shapes above a sea of purple moorland.A blaze of purple is more seductive than it is easy, and the real work is learning to see past the obvious. The technical craft is the floor we build on — controlling exposure to hold rich colour and a dramatic sky, and working quickly in the brief light of dawn and dusk — but the focus is on composing with intention: balancing the heather and the gritstone rock forms into a frame with order, working the intimate detail of bloom and weathered stone as readily as the wide moorland vista, and treating the purple, the gold and the low light as a harmony rather than a colour to crank. We shoot two to three locations each session as conditions allow, and the aim throughout is an image with mood and restraint — one that feels like that moor at first or last light.It's a small group of no more than six, taught personally and pitched at exactly your level, with one-to-one guidance in the field throughout. Whether you take the sunset, the sunrise or make a weekend of both, you'll come away with a portfolio of the Peak District's heather at its peak — and a sharper, more intentional way of seeing colour, light and landscape that you can take anywhere. If you're booking both sessions, please arrange your own overnight accommodation near The Roaches for the early sunrise shoot. Please also note this is a seasonal workshop tied to the heather bloom, so exact dates may shift slightly with the season.</t>
+          <t>Join me for this fantastic Wales photography workshop of woodlands, lakes and waterfalls in Mid-WalesLocation: Wales - Dee ValleyDates: Sat 10th - Sun 11th Oct 2026 - 2 Days/1 NightParticipants: Max 4Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodWales Photography Workshop Event Details Lake VyrnwyDescription: This is a 2-day, 1-night residential Wales photography workshop based in the valleys of Mid-Wales, open to all levels from beginner to advanced. It's built around two of the country's most rewarding landscape locations — Pistyll Rhaeadr, an enchanting waterfall in the Berwyn Mountains and, at 240ft, Britain's tallest single-drop fall, and the tranquil 11-mile shoreline of Lake Vyrnwy — giving you woodlands, water, mountains and one of the seven wonders of Wales in a single weekend.Over two days we work both locations at their best. At Pistyll Rhaeadr you'll photograph the three-stage falls from the viewing platform and bridge, then drop down to water level among the slate beds and mini-falls for intimate compositions; around Lake Vyrnwy we take a leisurely circuit of the reservoir, stopping at quiet bays and outlets and walking the river to the waterfall at the valley head. The focus is on three things that make moving water and big Welsh landscape work: composing a strong frame from a busy natural scene, mastering long exposure to turn falling water into silk, and reading the light and weather that give these valleys their mood. Throughout, the emphasis isn't just on the famous waterfall but on learning to see it — working intimate detail as readily as the wide vista, and treating light and colour as a harmony rather than chasing the obvious shot.With a maximum of just four photographers, this is genuinely personal tuition — Alan plans each day around the season and the forecast, and sends a detailed location itinerary a few days ahead. Accommodation and breakfast are included, so all you have to think about is your photography, and you'll come away with a varied portfolio of Welsh waterfalls, lakes and valleys — and a real command of long-exposure water technique. An extra night's accommodation is available the day before if required — please request in advance, subject to hotel availability.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1685361335026-KNDKR6D00CTPUASRDWDV/Surprise%2BView%2B2.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714636535694-5SWM865PVWA9MMT8LCQB/Dawn+at+Lake+Vyrnwy_.jpg</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/peak-district-heather-photography-workshop</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/wales-photography-workshop-pistyll-rhaeadr</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - half-day photo workshops, Landscape, Flowering</t>
+          <t>All Photography Workshops, - weekend residential photo workshops, Landscape</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ1994489", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Sat 15 Aug 2026 - Hathersage 18:15 - 21:15", "priceSpecification": {"price": "125.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1389945", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Sun 16 Aug 2026 - The Roaches &amp; Ramshaw 05:45 - 08:45", "priceSpecification": {"price": "125.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5395624", "price": "200.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Both sessions - 15 and 16 Aug - sunset and sunrise"}, {"@type": "Offer", "sku": "SQ7900435", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "2027 - Sat 14th Aug 18:15 21:15 - Derbyshire Surprise View"}, {"@type": "Offer", "sku": "SQ4225053", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "2027 - Sun 15 Aug - The Roaches &amp; Ramshaw 05:45 - 08:45"}, {"@type": "Offer", "sku": "SQ8702063", "price": "200.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Both sessions - 14 and 15 Aug - sunset and sunrise"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ5697158", "price": "695.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29"}]</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H36" t="n">
-        <v>125</v>
+        <v>695</v>
       </c>
       <c r="I36" t="n">
-        <v>200</v>
+        <v>695</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>SQ1994489, SQ1389945, SQ5395624, SQ7900435, SQ4225053, SQ8702063</t>
+          <t>SQ5697158</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>SQ1994489</t>
+          <t>SQ5697158</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2453,51 +2453,51 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CHESTERTON WINDMILL Photography Workshops - Warwickshire</t>
+          <t>DORSET Landscape Photography Workshop Purbeck 9 Apr</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Chesterton windmill is one of Warwickshire's most famous landmarks. Join me in a sunset landscape photography workshop and learn about composition and lightSummaryLocation: Warwickshire - ChestertonDates:Wed 16th Sep 2026 - 18:00 - 20:30Mon 5th Oct 2026 - 17:30 - 20:00Tue 13th May 2027 - 18:15 - 20:15Mon 10th May 2027 - 18:30 - 20:30Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details ChestertonDescription: This sunset landscape photography workshop is an evening shoot at Chesterton Windmill, one of Warwickshire's most iconic landmarks, open to all levels and any camera. A striking 17th-century tower windmill on its arched stone legs, standing alone on a hilltop for nearly 350 years, it's one of the most photogenic structures in the county — and this workshop is built around capturing it in the golden light of sunset and the long-exposure drama of the hour that follows, in a way that's genuinely your own rather than the postcard everyone already has.The technical craft is the floor we build on — exposure, depth of field, and setting up long exposures to draw movement out of cloud and sky as dusk falls. But the real work is learning to see this familiar landmark freshly: composing the windmill with intention against the sky and the rolling countryside, finding the unexpected angle and the intimate detail as readily as the wide hilltop vista, and reading the warm, directional light of sunset as a harmony to compose with rather than just a pretty backdrop to point at. As the colour builds and fades, you'll learn to design a frame where the light, the land and the windmill all work together.It's a small group of no more than six, taught personally and pitched at exactly your level, so whether you're new to landscape photography or refining your technique, you get real one-to-one guidance in the field. You'll come away with a set of atmospheric images of this famous Warwickshire landmark — golden-hour silhouettes and long-exposure skies — and a sharper, more intentional way of seeing light and composition that lets you photograph any landmark at its best.</t>
+          <t>Join me on this 3-day/2-night fantastic Dorset Photography workshop along the Jurassic coastline of Dorset - PurbeckSummary - Dorset Landscape PhotographyLocation: DorsetDates: Fri 9th - Sun 11th Apr 2027 3 Days/2 Nights(Price includes B&amp;B and evening meal - Half Board)Participants: Max 4Fitness: 3. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details DorsetDescription: This is a 3-day, 2-night residential landscape photography workshop along the Jurassic Coast of Dorset, open to all levels from beginner to advanced. Dorset's Purbeck coastline is one of the UK's great seascape locations — a prehistoric, World Heritage shore of sculpted arches, sea stacks and folded cliffs, with the iconic Durdle Door and Lulworth Cove at its heart — and across a weekend you'll learn to photograph it in its best light.Based on the Purbeck coast, we work the area's finest locations — from Durdle Door, Man O'War and Lulworth Cove to Kimmeridge, Dancing Ledge, Mupe Bay and the ghost village of Tyneham. The focus is on three things that make a strong coastal image: composing rock, sea and sky into a balanced frame, using long exposure to turn the moving water into mood, and timing your shoot to the light and the tide. It's never prescriptive though — this varied coastline lends itself to any style, so whether you're drawn to classic seascapes, black and white or abstract, there's scope to follow your own creative vision; throughout, the emphasis is on learning to see, composing with intention and reading light and tone as a harmony rather than chasing the obvious shot. There are optional sunrise and sunset shoots and evenings for relaxed picture reviews.With a maximum of just four photographers, this is genuinely personal tuition — Alan plans each day around the tides, the season and the forecast, and sends a detailed location itinerary a few days ahead. B&amp;B accommodation and an evening meal are included, so all you have to think about for three days is your photography, and you'll come away with a portfolio of dramatic Jurassic Coast images and a real command of seascape and long-exposure technique. An extra night's accommodation is available the day before if required — please request in advance, subject to hotel availability.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714682519866-NVMB6B7Q4F93DGOGPQIK/Moonlit+Chesterton.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714681245814-0QW8DK4XQ18FM0JLBXYN/Harry+Rocks+%2301+-+Mar+2024.jpg</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/photography-workshops-chesterton-windmill</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/dorset-landscape-photography-workshop</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - half-day photo workshops, Landscape</t>
+          <t>coastal, All Photography Workshops, - weekend residential photo workshops</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ3572999", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Wed 16th Sep 2026 - 18:00 - 20:30", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0796814", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Mon 5th Oct 2026 - 17:30 - 20:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9554270", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Tue 13th Apr 2027 - 18:15 - 20:15", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5307067", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Mon 10th May 2027 - 18:30 - 20:30", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ2754105", "price": "925.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29"}]</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H37" t="n">
-        <v>50</v>
+        <v>925</v>
       </c>
       <c r="I37" t="n">
-        <v>50</v>
+        <v>925</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>SQ3572999, SQ0796814, SQ9554270, SQ5307067</t>
+          <t>SQ2754105</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>SQ3572999</t>
+          <t>SQ2754105</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2509,51 +2509,51 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>LAVENDER FIELD Photography Workshop - Glouc or Warks July</t>
+          <t>URBAN ARCHITECTURE Photography Workshops - Coventry 9 Sep</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Join me in the Cotswolds, or Warwickshire for a spectacular lavender field landscape workshop . Photograph in the evening hours by arrangement of owners (date is subject to change or weather on the day) Price includes entry fee of £30 for either of the lavender farmsSummaryLocation: Snowshill - Gloucestershire or Bubbenhall · Warwickshire, Lavender FarmsDates:Sat 3rd Jul 2027 - 18:00 20:45Sat 10th Jul 2027 - 18:00 20:45Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and Tripod (tripod available to borrow)Photography Workshop Event Details LavenderDescription: This Lavender Photography Workshop is a magical evening among the lavender rows of the Cotswolds at Snowshill in Gloucestershire or depending on arrangements at Warwickshire Lavender Farm, Bubbenhall — open to all levels and any camera. Best of all, you'll photograph the fields after the farm has closed to the general public, so instead of working around coachloads of day-trippers you have the spectacular sea of purple and the wildflower areas largely to yourselves — making it far easier to slow down, see properly and compose clean shots as the light softens towards sunset and the colour comes alive.A field of lavender is seductive but deceptively hard — it's all too easy to come home with the loud, over-saturated purple shot everyone takes. The real work here is learning to see past that. The technical craft is the floor we build on — focusing and exposing accurately in fading light, and holding both shadow and highlight as the sun drops — but the focus is on composing with intention: finding order and a lead-in through the endless rows, working the intimate, abstract close-up of colour and texture as readily as the sweeping vista, and treating the purple, the green and the warm evening light as a harmony to balance rather than a colour to crank. The aim is a photograph with mood and restraint — one that feels like that quiet evening in the field.It's a small group of no more than six, taught personally and pitched at exactly your level, with one-to-one guidance throughout. With the crowds gone and the fields quiet, you'll have the space and time to really work your compositions — and you'll come away with a portfolio of vivid lavender images at their most atmospheric, plus a sharper, more intentional way of seeing colour, light and detail that you can take anywhere. This is a special after-hours session: the farm opens to us beyond its normal public hours so we can shoot from 5p/6pmm into the early sunset light 9/9:30pm, and your workshop fee includes that commercial after-hours access. Please note the dates and finish times are set by the lavender farm rather than by Alan, and may be subject to change with the season, flowering and weather as they do not extend the hours if rain is forecast on the day, so you need to be flexible and be able to swap to an alternative Saturday evening that the farm has extended hours. Usually the first 3 Saturdays of July.</t>
+          <t>We will walk around several historic parts of Coventry in this 2.5hr Urban Architecture Photography Workshop, photographing buildings and ruins.SummaryLocation: Coventry City CentreDates: Mon 13 Sep 2027 - 18:15-20:15Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Street PhotographyDescription: This Urban Architecture Photography workshop is an evening walk through the historic heart of Coventry — once UK City of Culture — open to all levels and any camera. Cities transform after dark: artificial light, deep shadow and the last colour in the sky turn ordinary buildings and ruins into something dramatic, and this 2.5-hour workshop is built around learning to see and design photographs at night, in the tricky low light most people find hardest to shoot.Confident technique in the dark is the floor we build on — and we'll cover it: focusing and exposing accurately in low light, and setting up long exposures to capture movement and mood. But the real work is learning to see the city as a photographer. Walking together through old and new architectural corners — including the cathedral area and its ruins — you'll learn to compose with form, line, texture and contrast, to read the interplay of artificial light and shadow as a harmony rather than a problem, and to find the considered, intentional frame instead of the obvious postcard of a landmark. Old against new, light against dark, detail against sweep — it's about designing an image, not just recording a building.It's a small group of no more than six, taught personally and pitched at exactly your level, so whether you're new to night photography or refining your eye you get real one-to-one guidance in the field. You'll come away with a set of atmospheric urban and architectural images — long exposures, abstracts, dramatic skies — and a sharper, more intentional way of seeing that lets you photograph any city after dark.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714572933715-EIVNF6O80HEJCSEU5D4U/lavender+sprint.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1658913526628-KD8S5Y2CTOHVVBBJMAYJ/Coventry+3.jpg</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/photography-workshops-lavender-fields</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/urban-architecture-photography-workshops-coventry</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - half-day photo workshops, Flowering, Landscape</t>
+          <t>All Photography Workshops, - half-day photo workshops, Urban</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ6748367", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Sat 3rd Jul 2027 - 18:00 20:45"}, {"@type": "Offer", "sku": "SQ7542811", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Sat 10th Jul 2027 - 18:00 20:45"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ4066377", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H38" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="I38" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>SQ6748367, SQ7542811</t>
+          <t>SQ4066377</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>SQ6748367</t>
+          <t>SQ4066377</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2565,51 +2565,51 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Poppy Fields Photography Workshops | Worcestershire</t>
+          <t>KENILWORTH Sunset Long Exposure Photography Workshop</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Poppy fields photography workshop - Choose a sunrise or sunset 2.5hrs photo workshop at amazing poppy fields in Worcestershire | Seasonal DependantSummaryLocation: WorcestershireDates: (dates are subject to change based on when the poppy fields flower in June)8th Jun 19:15 - 21:459th Jun 05:00 - 07:30Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: PoppiesDescription: There are few sights in the English summer to beat rolling Worcestershire hills washed red with wild poppies, and this Poppy Fields Photography Workshop is built to catch them at their fleeting best. Open to all levels and any camera, it runs as short, focused sessions at the golden hours of sunset and sunrise — the two times of day when low, warm light makes a field of poppies truly glow.A field of red is more seductive than it is easy, and the work is learning to turn it into a photograph rather than a snapshot. The focus is on three things: composing with intention to find order and a lead-in through a busy, repeating scene, controlling exposure and depth of field to decide what's sharp and what dissolves into colour, and reading light, texture and colour as a harmony — letting the reds sing without tipping into the over-saturated cliché. You'll work both the intimate, single-stem detail and the sweeping vista, and learn to see past the obvious shot everyone else takes.It's a small group of no more than six, taught personally and pitched at exactly your level, with one-to-one guidance in the field throughout. Whether you join the sunset session, the dawn one, or both, you'll come away with a portfolio of poppy-field images at their most atmospheric — and a stronger way of seeing colour, light and composition that carries into everything you photograph next. Please note that poppies bloom briefly and unpredictably each June, so both the exact dates and the field we use are confirmed at short notice once the flowering is at its best. A flexible approach is essential — but it's exactly what lets us photograph the poppies at their absolute peak.</t>
+          <t>Sunset landscape long exposure photography workshop shoots around Kenilworth Castle - Warwickshire - Various Dates | Long Exposures | Open to all levels| Book TodaySummaryLocation: Warwickshire - KenilworthDates:Mon 22 Mar 2027 - 18:00 - 20:00Wed 14 Apr 2027 - 18:30 - 20:30Wed 5 May 2027 - 18:00 - 20:00Wed 22 Sep 2027 - 17:45 - 19:45Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: KenilworthDescription: This Long Exposure Photography Workshop is an evening shoot around the floodlit ruins of Kenilworth Castle in Warwickshire, open to all levels and any camera. Once one of England's mightiest fortresses and Robert Dudley's Elizabethan palace, the castle makes a dramatic subject against a darkening sky — and this workshop is built around the magic of long exposure at dusk, when the fading light, the castle's silhouette and a slow shutter combine to create atmospheric images that capture a sense of place, not just a record of a building.The long-exposure craft is the floor we build on, and we'll cover it properly: calculating exposure times for the movement and mood you want, focusing and exposing confidently in low light, and balancing ISO, shutter and aperture as the light drops. But the real work is learning to see. As the sky changes you'll compose the castle with intention — finding the frame beyond the obvious silhouette, working detail and texture as readily as the grand wide view, and reading the interplay of fading light, floodlight and deep shadow as a harmony rather than a problem to fight. The aim is an image with mood and restraint, where every element earns its place.It's a small group of no more than six, taught personally and pitched at exactly your level, so whether long exposure is new to you or you're refining your technique, you get real one-to-one guidance in the field. You'll come away with a set of atmospheric long-exposure images of one of England's most romantic castles — and a sharper, more intentional way of seeing light, movement and mood after dark anywhere.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714575407530-MBS3PUSXD9GGHA68754C/poppy+dawn.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1712472502735-OHOKCDKMCP1BAMQ0JQUA/kenilworth+defenses.jpg</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/poppy-fields-photography-workshops</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/long-exposure-photography-kenilworth</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - half-day photo workshops</t>
+          <t>All Photography Workshops, - half-day photo workshops, Landscape</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8740143", "price": "95.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Sat 8 Jun 19:15-21:45"}, {"@type": "Offer", "sku": "SQ7189877", "price": "95.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Sun 9 Jun 05:00-07:30"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ0932604", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Mon 22 Mar 2027 - 18:00 - 20:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1178418", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Wed 14 Apr 2027 - 18:30 - 20:30", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9140400", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Wed 5 May 2027 - 18:00 - 20:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8220723", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Wed 22 Sep 2027 - 17:45 - 19:45", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H39" t="n">
-        <v>95</v>
+        <v>50</v>
       </c>
       <c r="I39" t="n">
-        <v>95</v>
+        <v>50</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>SQ8740143, SQ7189877</t>
+          <t>SQ0932604, SQ1178418, SQ9140400, SQ8220723</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>SQ8740143</t>
+          <t>SQ0932604</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2621,219 +2621,219 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Online Photography Classes 121 - Zoom - Package Options</t>
+          <t>SNOWDONIA Landscape Photography  - Sat 6 - Sun 7 Mar 2027</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Private Online Photography Classes (Zoom)Summary - Private Online Photography Classes - Key InformationFormat: Online 1-2-1 via Zoom (free to use)Sessions: Single 1hr lesson, or discounted packages of 4, 6, 8 or 12 hoursAvailability: Standard Mon–Fri, 9am–5pm or Premium - Mon-Sun 9am -9pmValidity: Pay now, book dates later — use within 12 months of purchaseLevel: All levels, beginner to advancedDescription: Private online photography classes tailored to your needs — tuition and support on any aspect of photography, with no other students, so the time you pay for is dedicated entirely to your own style and pace.Equipment: Anything you want to learn or improve on. Sessions run over Zoom, with notes provided; submit images for detailed feedback between lessons.</t>
+          <t>Join me on this landscape photography Snowdonia workshop in the iconic mountains, quarries and landscape of Snowdonia national park.Summary - Snowdonia Landscape photography workshopLocation:Wales - Snowdonia National ParkDates: Sat 6th - Sun 7th Mar 2027 - 2 Days/1 NightParticipants: Max 4 (1 Car, transport between locations included)Fitness: 2. Moderate (15-30 min walks)Experience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details SnowdoniaDescription: This is a 2-day, 1-night residential landscape photography workshop in Snowdonia National Park, North Wales — open to all levels from beginner to advanced. Home to the highest mountain ranges in England and Wales, Snowdonia is a landscape that will both inspire and challenge any photographer: rugged peaks and flowing rivers, serene lakes and ancient slate quarries, all within a compact corner of Wales that you'll learn to read and photograph in its ever-changing light.What makes Snowdonia so rewarding is its variety, and over two days we work three very different faces of it: the waterfalls and rivers that are perfect for long exposure, turning moving water to silk; the starker, striking world of the historic slate quarries and mining relics, where industry and mountain meet; and the majestic lakes, where still water mirrors the peaks for compelling, reflective compositions. Across all of it the focus stays on the same craft — composing order from a vast scene, controlling exposure across big tonal ranges, and timing your shoot to the light and weather that shift the mood from rugged to serene and back. And throughout, the emphasis isn't just on the grand vista but on learning to see it — working intimate detail as readily as the wide view, and reading light and colour as a harmony rather than chasing the obvious shot.With a maximum of just four photographers and transport between locations included, this is genuinely personal tuition — Alan plans each day around the season and the forecast, and sends a detailed location itinerary a few days ahead. Likely locations include the reflective waters of Llynnau Mymbyr beneath the Snowdon massif, the Capel Curig pinnacles, Swallow Falls and the hidden lake of Llyn Craftnant. Accommodation and breakfast are included, so all you have to think about is your photography — and you'll leave with a varied portfolio that captures both the drama and the stillness of this remarkable landscape. An extra night's accommodation is available the day before if required — please request in advance, subject to hotel availability.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/4ac49e77-bfdc-435d-bf46-d82bda3bec91/online+photography+lessons.png</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1711625824431-22D7V1RNKR8H2LBRW4Z9/Snowdonia+%2301+-+Oct+2023.jpg</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/private-online-photography-classes-zoom</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/landscape-photography-snowdonia-workshops</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1-2-1-private-lessons, photography-classes, photography-tuition</t>
+          <t>Landscape, - weekend residential photo workshops</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ1461156", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Zoom Standard (Weekdays 9-5) - 1 x 1hr - Pay as you go    £50"}, {"@type": "Offer", "sku": "SQ5568703", "price": "170.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Zoom Standard (Weekdays 9-5) - 4 x 1hr (15% Off)          £170"}, {"@type": "Offer", "sku": "SQ6341100", "price": "240.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Zoom Standard (Weekdays 9-5) - 6 x 1hr (20% Off)          £240"}, {"@type": "Offer", "sku": "SQ2281758", "price": "300.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Zoom Standard (Weekdays 9-5) - 8 x 1hr (25% Off)          £300"}, {"@type": "Offer", "sku": "SQ2043258", "price": "450.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Zoom Standard (Weekdays 9-5) - 12 x 1hr (25% Off)         £450"}, {"@type": "Offer", "sku": "SQ6476466", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Zoom Premium (Eve/Weekend 9-9) - 1 x 1hr - Pay as you go  £75"}, {"@type": "Offer", "sku": "SQ4036849", "price": "255.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Zoom Premium (Eve/Weekend 9-9) - 4 x 1hr (15% Off)        £255"}, {"@type": "Offer", "sku": "SQ6369047", "price": "360.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Zoom Premium (Eve/Weekend 9-9) - 6 x 1hr (20% Off)        £360"}, {"@type": "Offer", "sku": "SQ7040572", "price": "450.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Zoom Premium (Eve/Weekend 9-9) - 8 x 1hr (25% Off)        £450"}, {"@type": "Offer", "sku": "SQ6714463", "price": "675.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Zoom Premium (Eve/Weekend 9-9) - 12 x 1hr (25% Off)       £675"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ0548499", "price": "595.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29"}]</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H40" t="n">
-        <v>50</v>
+        <v>595</v>
       </c>
       <c r="I40" t="n">
-        <v>675</v>
+        <v>595</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>SQ1461156, SQ5568703, SQ6341100, SQ2281758, SQ2043258, SQ6476466, SQ4036849, SQ6369047, SQ7040572, SQ6714463</t>
+          <t>SQ0548499</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>SQ1461156</t>
+          <t>SQ0548499</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>event</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Quarterly Pick N Mix Subscription | Interest Free Payments</t>
+          <t>The Art of GARDEN PHOTOGRAPHY  - Coventry -  May and July</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Quarterly Pick N Mix Subscription Package. 15% Discount on events/services for one year | Interest Free Payment Plan | Take events or lessons immediately |</t>
+          <t>Join us for an unforgettable journey into macro and abstract on this garden photography workshop. Secure your spot today and embark on a transformative learning experience in garden photography.SummaryLocation: Coventry - CV4Dates:Sun May 23rd 2027 - 15:00 - 17:00Sun Jul 11th 2027 - 15:00 - 17:00Participants: Max 4Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details Garden PhotographyDescription: This Garden Photography Workshop is an intimate afternoon in Alan's own private garden in Coventry — his personal creative studio, a space he knows intimately and tends with a photographer's eye — open to all levels and any camera. A garden is one of the richest and most overlooked subjects there is: get close and the flowers, foliage, structures and borders reveal endless macro, close-up and abstract images, and this relaxed half-day is all about learning to see them, then photograph them with intention.The technical craft is the floor we build on — getting sharp focus, using your lens for macro and close-up detail, and controlling exposure and depth of field — but the real work is learning to look. You'll be given four photography assignments with guidance notes that push you to experiment and vary your approach, from intimate macro to wider garden portraits, training your eye to find the abstract within the planting and to compose with real intention. Throughout, the emphasis is on reading colour, light and texture as a harmony — letting the flowers sing without tipping into the loud, over-saturated shot — so your images feel considered and your own, not the obvious bloom-in-the-middle snap. Image reviews and feedback on a large screen in the gazebo help you see what's working and why.Places are limited to just four, so this is genuinely personal tuition, with Alan on hand for settings, composition and one-to-one guidance the whole time — and tea, coffee and cake served throughout. You'll come away with your own portfolio of garden images, and a sharper, more intentional way of seeing detail, colour and light that changes how you photograph flowers and nature everywhere.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/fbab50ee-2fe8-4fe9-8804-e691b883cf4b/Photography+Payment+Plan.png</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1709974516534-UJBRDOK5RXR4QNLPTECD/_-677.jpg</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/quarterly-pick-n-mix-subscription</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/garden-photography-workshop</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>photography-classes, photography-courses, photography-workshops</t>
+          <t>All Photography Workshops, - half-day photo workshops, Flowering, Macro &amp; Abstract</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ4217445", "price": "250.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "4 x £250 = £1000"}, {"@type": "Offer", "sku": "SQ6277577", "price": "300.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "4 x £300 = £1200"}, {"@type": "Offer", "sku": "SQ7788516", "price": "350.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "4 x £350 = £1400"}, {"@type": "Offer", "sku": "SQ5124608", "price": "400.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "4 x 400 = £1600"}, {"@type": "Offer", "sku": "SQ2657628", "price": "500.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "4 x £500 = £2000"}, {"@type": "Offer", "sku": "SQ2267503", "price": "750.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "4 x £750 = £3000"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ0939451", "price": "45.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Sun May 23rd 2027 - 15:00 - 17:00"}, {"@type": "Offer", "sku": "SQ3644687", "price": "45.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Sun Jul 11th 2027 - 15:00 - 17:00"}]</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H41" t="n">
-        <v>250</v>
+        <v>45</v>
       </c>
       <c r="I41" t="n">
-        <v>750</v>
+        <v>45</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>SQ4217445, SQ6277577, SQ7788516, SQ5124608, SQ2657628, SQ2267503</t>
+          <t>SQ0939451, SQ3644687</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>SQ4217445</t>
+          <t>SQ0939451</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>event</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>RPS Courses - Independent RPS Mentoring for RPS Distinctions</t>
+          <t>GOWER Landscape Photography Wales - 28 May - 30 May 2027</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>RPS Courses - Independant RPS Mentoring for RPS Distinctions - Start anytime, you select a package of Zoom sessions within twelve months at intervals to suit youDescription: Independent one-to-one RPS mentoring for your Licentiate (LRPS) or Associate (ARPS) distinction — online via Zoom, with a mentor who holds both distinctions himself and has a 100% pass rate to date. Most photographers who fall short don't fail on technique — they submit a collection of strong individual images rather than a planned, cohesive panel, and a panel is judged as a whole. That judgement — image selection, sequencing, the hanging plan and your Statement of Intent — is exactly what mentoring brings. We work in three stages: plan the panel, build and refine it, then test readiness before you submit. Sessions are flexible 1-hour Zoom slots — buy only what you need and book your dates later, across up to twelve months. Start fresh, or revise a panel that didn't pass first time.Format: One-to-one, online via Zoom — private and personal to you and your panel.Equipment Needed: Zoom App; free Dropbox account for sharing portfolios and updated images.Terms: A package of Zoom sessions must be used within 12 months of purchase or it is forfeited. You can extend the timeline or purchase additional sessions if needed.Method: Honest technical and creative critique with suggestions for improvement; advice on image selection, sequencing, the hanging plan and your Statement of Intent.Package Options: Choose Mon–Fri 9am–5pm daytime rates, or Mon–Sun 9am–9pm for evening and weekend flexibility.1 × 1hr — single session (fact-find &amp; review)4 × 1hr — 15% off (reset a failed panel)6 × 1hr — 20% off (from scratch, recommended)8 × 1hr — 25% off (extended panel build)12 × 1hr — 25% off (best value, full programme)More Details: about the RPS Mentoring Course</t>
+          <t>Stunning shorelines and beauty of South Wales and the Gower Peninsular. Max 3 places for this residential photography workshop - landscape photography walesSummaryLocation: South Wales - Gower PeninsularDates:Fri 28th May - Sun 30th May 2027 - 3 Days/2 NightsParticipants: Max 4Fitness: 3. HardExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodLandscape photography Wales Photography Workshop Event Details GowerDescription: This is a 3-day, 2-night residential landscape photography workshop on the Gower Peninsula in South Wales — the UK's very first Area of Outstanding Natural Beauty, and one of the finest stretches of coast for landscape photography in Wales. Open to all levels from beginner to advanced, it takes you along 19 miles of dramatic shoreline west of Swansea, where lofty limestone cliffs, golden sandy beaches and jagged rocky shores meet wild moorland, dunes and tranquil salt marshes.Over three days we work the peninsula's most iconic locations as the light and tides allow — from the sweeping expanse of Rhossili Bay and the dramatic outline of Worms Head to the wreck of the Helvetia and the snug cove of Pwll Du. The focus is on three things that make a strong coastal image: composing cliffs, beaches and rock forms into a balanced frame, mastering long exposure to draw movement out of sea and sky, and timing each shoot from dawn to dusk to catch the best light and tide. Throughout, the emphasis isn't just on the famous viewpoint but on learning to see it — composing with intention, working intimate detail as readily as the wide vista, and reading light and colour as a harmony rather than chasing the obvious shot. You'll photograph at sunrise and sunset, the richest hours on this coast, and return to locations in changing conditions to capture them at their best.With a small group taught personally, this is genuinely one-to-one tuition — Alan plans each day around the season, the forecast and the tide times, and sends a detailed location itinerary a few days ahead. Be prepared for some longer walks over cliff paths and rougher coastal ground to reach the best viewpoints. Accommodation and breakfast are included, so all you have to think about is your photography, and you'll come away with a varied portfolio of the Gower's iconic Welsh coastline — and the field craft to read light, tide and weather on any shore. An extra night's accommodation is available the day before if required — please request in advance, subject to hotel availability.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707307452323-G3C2AIXAHRLLVB36VASA/RPS+Courses.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1715702409761-590M3MJ45KYXBDH1KSM0/Gower+%2305+-+May+2024.jpg</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/rps-mentoring-photography-course</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/landscape-photography-wales-photo-workshop</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1-2-1-private-lessons, photography-classes, photography-courses, photography-tuition, rps</t>
+          <t>coastal, All Photography Workshops, - weekend residential photo workshops</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ7839038", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Mon- Fri 9am-5pm 1 x 1hr"}, {"@type": "Offer", "sku": "SQ3867813", "price": "170.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Mon- Fri 9am-5pm 4 x 1hr"}, {"@type": "Offer", "sku": "SQ8903198", "price": "240.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Mon- Fri 9am-5pm 6 x 1hr"}, {"@type": "Offer", "sku": "SQ4831915", "price": "300.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Mon- Fri 9am-5pm  8x 1hr"}, {"@type": "Offer", "sku": "SQ1077689", "price": "450.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Mon- Fri 9am-5pm 12 x 1hr"}, {"@type": "Offer", "sku": "SQ8233730", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Mon- Sun 9am-9pm 1 x 1hr"}, {"@type": "Offer", "sku": "SQ9139531", "price": "255.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Mon- Sun 9am-9pm 4 x 1hr"}, {"@type": "Offer", "sku": "SQ0776423", "price": "360.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Mon- Sun 9am-9pm 6 x 1hr"}, {"@type": "Offer", "sku": "SQ2385997", "price": "450.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Mon- Sun 9am-9pm 8 x 1hr"}, {"@type": "Offer", "sku": "SQ9440259", "price": "675.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Mon- Sun 9am-9pm 12 x 1hr"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ5141863", "price": "825.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29"}]</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H42" t="n">
-        <v>50</v>
+        <v>825</v>
       </c>
       <c r="I42" t="n">
-        <v>675</v>
+        <v>825</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>SQ7839038, SQ3867813, SQ8903198, SQ4831915, SQ1077689, SQ8233730, SQ9139531, SQ0776423, SQ2385997, SQ9440259</t>
+          <t>SQ5141863</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>SQ7839038</t>
+          <t>SQ5141863</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>course</t>
+          <t>event</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>The Secret of WOODLAND PHOTOGRAPHY- 1-Day Jan, Apr, Aug, Oct</t>
+          <t>Fireworks Photography Workshop | Long Exposure | Kenilworth</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Simplifying Woodland Photography | Unlocking the Secrets to Capturing the Beauty of woods | Three sessions - Theory - Practical - Editing in one daySummaryLocation: Coventry - CV4 9HWDates: - 10:00 - 16:00Sun 2nd Aug - SummerSun 18th Oct - AutumnSun 10th Jan - WinterSun 11th Apr - SpringParticipants: Max 3Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: Digital Camera and TripodPhotography Workshop Event Details: Woodland Photography MasterclassDescription: The Secrets of Woodland Photography is a 1-Day Masterclass in Coventry, open to all levels and any camera. Woodland is the hardest subject there is — chaotic, cluttered, endlessly busy — which is exactly why it's the best place to learn to see. Most people come away with the tangled, cliché shot; this day is about learning to find the order, the light and the quiet beauty hidden within the chaos, and to make woodland images that are calm, intentional and your own.The technical setup matters, but it's only the floor we build on. Rather than a typical walk-and-shoot, the day runs as three connected sessions — theory, practical and editing — so we can go deeper than settings. We start with the thinking behind a strong woodland image and the craft that delivers it: simplifying a busy scene, using light and shadow, choosing what to include and what to leave out. Then you put it into practice on a woodland walk, working the close-up, the macro detail and the abstract as readily as the wider view — reading texture and colour as a harmony, not chasing the loud, over-saturated shot. Finally we review your images together and finish on the editing that brings the quiet colours of the forest to life without shouting.The day runs from Alan's home, which offers three things most workshops can't: instant access to woodland straight from the garden, a comfortable covered and heated space for the presentations and image reviews, and a large screen to study your shots on — so the day works whatever the weather. You'll leave not just with a set of woodland images, but with a way of seeing — light, simplicity and restraint — that changes how you photograph trees, nature and detail wherever you go next.</t>
+          <t>Fireworks Photography Workshop - Long exposure and fireworks. Learn about camera settings, exposure use and composition.SummaryLocation: KenilworthDates: TBCParticipants: Max 4Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: FireworksDescription: This Fireworks Photography Workshop is a one-off evening capturing one of the most exciting subjects in photography — a full fireworks display bursting over the floodlit ruins of Kenilworth Castle. Open to all levels and any camera, it's built around the Round Table's spectacular annual display, and the magical, fleeting moment when long exposure turns streaking light and exploding colour into a single dramatic image with the castle as its backdrop.Fireworks look chaotic but reward a calm, technical approach, and that's exactly what we'll work on. The focus is on three things that make the difference between a lucky snap and a controlled image: setting up for long exposure — shutter, aperture and the timing that lets you build a burst on the sensor — composing the frame so the castle and the sky work together rather than fighting, and reading the rhythm of the display to know when to open and close the shutter. You'll learn to anticipate rather than react, and to keep shooting cleanly when the sky is at its busiest.It's a small group of no more than four, taught personally and right beside you in the dark, so you get real one-to-one guidance exactly when the action is happening. Better still, we photograph from outside the castle walls, so there's no admission ticket to buy for the display. You'll come away with a set of dramatic fireworks images over a historic castle — and the long-exposure and timing skills to photograph fireworks, light trails and night scenes anywhere. (Please note this is an annual event with the date set by the organisers, so timing is confirmed each year nearer the display.)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714646680135-9EB3PR57B78W9NMZ09JI/Plant+Hill+Woods+%2310+-+Jan+2022.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1713518270092-GJSBASA0ZLL4NBMCK355/Kenilworth+Fireworks+2017+-+2.jpg</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/secrets-of-woodland-photography-workshop</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/fireworks-photography-workshop-kenilworth</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - one day photo workshops, Macro &amp; Abstract, Woodlands</t>
+          <t>All Photography Workshops, - half-day photo workshops</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ4914997", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Sun 2nd Aug 2026 - 10am - 4pm"}, {"@type": "Offer", "sku": "SQ4894934", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Sun 18th Oct 2026 - 10am - 4pm"}, {"@type": "Offer", "sku": "SQ2827052", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Sun 10 Jan 2027 - 10am - 4pm"}, {"@type": "Offer", "sku": "SQ0512761", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Sun 11th Apr 2027 - 10am - 4pm"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ1182401", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29"}]</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H43" t="n">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="I43" t="n">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>SQ4914997, SQ4894934, SQ2827052, SQ0512761</t>
+          <t>SQ1182401</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>SQ4914997</t>
+          <t>SQ1182401</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -2845,51 +2845,51 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SEZINCOTE Garden Photography Workshop - Gloucs 29 May</t>
+          <t>EXMOOR Photography Workshop - Sat 12 - Sun 13 Jun 2027</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Macro and abstract Garden photography workshop. Camera settings, controlling DoF and composition at this Mughal Indian palace in the Cotswolds.SummaryLocation: Moreton on Marsh (Sezincote) - GloucestershireDates: Thu 29th May 2026 - 11:00 - 13:30Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details Garden PhotographyDescription: This Sezincote Garden Photography Workshop takes you into one of the most extraordinary gardens in the Cotswolds — the grounds of a Mughal Indian palace, complete with copper dome and minarets, set in the gentle hills of Gloucestershire and open to all levels and any camera. Few gardens offer a photographer this much: a water garden of seven pools, waterfalls and a grotto, a temple to the Hindu sun god Surya, and a curving Orangery framing a Persian Garden of Paradise — all waiting to be explored through your lens.A setting this rich is a wonderful place to slow down and learn to see. The technical craft is the floor we build on — sharp focus, controlling depth of field to isolate a subject, the settings that give you control — but the real work is composition and intention. Working through the estate's grounds together, you'll learn to find a strong frame within a busy, ornate scene, to work the intimate macro and close-up detail as readily as the wide views of pools, temple and dome, and to read the light and the colour as a harmony rather than chasing the loud, obvious shot. The aim is always an image that's considered and your own, not just a record of a remarkable place.It's a small group of no more than six, taught personally and pitched at exactly your level, with Alan on hand throughout for camera settings, composition and one-to-one guidance, plus image reviews to spark ideas and inspiration on the day. You'll come away with a portfolio of images from one of England's most unusual gardens — and a sharper, more intentional way of seeing detail, composition and light in any garden you photograph. Please note the workshop fee does not include the entrance fee to Sezincote garden and house, which is payable separately on the day.</t>
+          <t>Lynmouth - Exmoor Photography Workshop - Join me for this exciting and inspiring trip to explore and capture the stunning coastal landscapes and breathtaking natural beauty of North Devon.SummaryLocation: Lynmouth - ExmoorDates: Sat 12 10:30 - Sun 13 Jun 14:00 2027 2 Days/1 NightParticipants:Max 4 (1 Car, transport between locations included)Fitness: 1. Easy (5-15 min walks)Experience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodExmoor Photography Workshop Event DetailsLynmouthDescription: This is a 2-day, 1-night residential seascape photography workshop based at Lynmouth on the dramatic Exmoor coast of North Devon, open to all levels from beginner to advanced. Lynmouth is a photographer's paradise — where the East and West Lyn rivers meet the sea beneath towering cliffs, fringed by secluded bays, weathered rock formations and the quaint harbour village with its iconic Rhenish Tower. It's a compact, richly varied coastline that rewards a focused weekend of shooting.Over two days we work the area's finest coastal locations — from the secluded bays and rock formations around Lynmouth and the sweeping Valley of Rocks to Watersmeet, Heddon's Mouth and Porlock Weir. The focus is on three things that make a strong seascape: composing rock, water and sky into a balanced frame, using long exposure to turn the moving sea into mood, and timing your shoot to the light and the tide. Throughout, the emphasis isn't just on the grand view but on learning to see it — composing with intention, working intimate detail as readily as the wide vista, and reading light and tide as a harmony rather than chasing the obvious shot. The days follow the conditions — full days on location with tuition, an optional sunset shoot, and an optional sunrise, with evenings for relaxed picture reviews.With a maximum of just four photographers and transport between locations included, this is genuinely personal, hassle-free tuition — Alan plans each day around the tides, the season and the forecast, and sends a detailed location itinerary a few days ahead. Accommodation and breakfast are included, so all you have to think about is your photography, and you'll come away with a portfolio of dramatic Exmoor seascapes and the field craft to read light and tide on any coast. An extra night's accommodation is available the day before if required — please request in advance, subject to hotel availability.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1715077805264-XJYPE427XFHYBMW7L4TL/_.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714638630127-79B9OMJPFF60L8Q9VLJL/Timeless+Memories.jpg</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/sezincote-garden-photography-workshop</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/exmoor-photography-workshops-lynmouth</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - half-day photo workshops, Flowering, Macro &amp; Abstract</t>
+          <t>coastal, All Photography Workshops, - weekend residential photo workshops</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9859986", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8057321", "price": "575.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29"}]</t>
         </is>
       </c>
       <c r="G44" t="n">
         <v>1</v>
       </c>
       <c r="H44" t="n">
-        <v>50</v>
+        <v>575</v>
       </c>
       <c r="I44" t="n">
-        <v>50</v>
+        <v>575</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>SQ9859986</t>
+          <t>SQ8057321</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>SQ9859986</t>
+          <t>SQ8057321</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -2901,51 +2901,51 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SUFFOLK Landscape Photography Workshops - 5th-7th Feb</t>
+          <t>SEZINCOTE Garden Photography Workshop - Gloucs 29 May</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Join us for an inspiring Suffolk landscape photography workshop, where you'll have the opportunity to create stunning long exposures during breathtaking sunrises and vibrant sunsets. We will explore picturesque quays, serene estuaries, intriguing piers, and tranquil marshes, all while capturing the beauty of charming beach huts and ancient woodlands. Emphasising artistic expression, we'll also delve into the world of black and white photography, allowing you to bring a classic touch to your coastal images.SummaryLocation: Suffolk - East Anglia / Southwold/Aldeburgh AreaDates: Fri 5th 09:30 - Sun 7th 14:30 Feb 2027 - 3 Days/2 NightsParticipants: Max 4 (1 Car, transport between locations included)Fitness: 2. Moderate (15-30 min walks)Experience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details SuffolkDescription: This is a 3-day, 2-night residential Suffolk landscape photography workshop based on the Southwold and Aldeburgh coast, open to all levels from beginner to advanced. The Suffolk coastline is one of England's most photogenic and most varied — wide shoreline vistas, big skies, and a wealth of subjects most coastlines can't match: weathered piers, painted beach huts, iconic sea-defence structures and the traditional sails of Herringfleet Windmill. It's a landscape that rewards photographers who slow down and learn to see it.The focus is on long exposure and the art of black and white photography — learning to compose a strong coastal frame, to use long exposures to smooth water and sky into mood, and to recognise when a scene works better in mono. It's about more than the technical craft, though: the real work is learning to see — composing with intention, working intimate detail as readily as the wide vista, and reading light and tone as a harmony rather than chasing the obvious shot. It's never prescriptive either: over three days and two to three locations a day — from Southwold and Walberswick to Dunwich, Orford and Aldeburgh — we work with whatever light and conditions the coast gives us, with early sunrise shoots, full days in the field with tuition, and evenings for relaxed picture reviews.With a maximum of just four photographers and transport between locations included, this is genuinely personal, hassle-free tuition — Alan plans each day around the group, the season, the tides and the forecast, and sends a detailed location itinerary a few days ahead. En-suite accommodation and breakfast are included, so all you have to think about for three days is your photography. You'll come away with a portfolio of atmospheric Suffolk coastal images and a real grasp of long exposure and black and white technique. An extra night is available the day before on request, ideal for those travelling from a distance — contact me to arrange.</t>
+          <t>Macro and abstract Garden photography workshop. Camera settings, controlling DoF and composition at this Mughal Indian palace in the Cotswolds.SummaryLocation: Moreton on Marsh (Sezincote) - GloucestershireDates: Thu 29th May 2026 - 11:00 - 13:30Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details Garden PhotographyDescription: This Sezincote Garden Photography Workshop takes you into one of the most extraordinary gardens in the Cotswolds — the grounds of a Mughal Indian palace, complete with copper dome and minarets, set in the gentle hills of Gloucestershire and open to all levels and any camera. Few gardens offer a photographer this much: a water garden of seven pools, waterfalls and a grotto, a temple to the Hindu sun god Surya, and a curving Orangery framing a Persian Garden of Paradise — all waiting to be explored through your lens.A setting this rich is a wonderful place to slow down and learn to see. The technical craft is the floor we build on — sharp focus, controlling depth of field to isolate a subject, the settings that give you control — but the real work is composition and intention. Working through the estate's grounds together, you'll learn to find a strong frame within a busy, ornate scene, to work the intimate macro and close-up detail as readily as the wide views of pools, temple and dome, and to read the light and the colour as a harmony rather than chasing the loud, obvious shot. The aim is always an image that's considered and your own, not just a record of a remarkable place.It's a small group of no more than six, taught personally and pitched at exactly your level, with Alan on hand throughout for camera settings, composition and one-to-one guidance, plus image reviews to spark ideas and inspiration on the day. You'll come away with a portfolio of images from one of England's most unusual gardens — and a sharper, more intentional way of seeing detail, composition and light in any garden you photograph. Please note the workshop fee does not include the entrance fee to Sezincote garden and house, which is payable separately on the day.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714667523305-2SEM1T5WD278HHO4HJIV/Southwold+Sunrise.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1715077805264-XJYPE427XFHYBMW7L4TL/_.jpg</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/suffolk-landscape-photography-workshops</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/sezincote-garden-photography-workshop</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>coastal, - weekend residential photo workshops</t>
+          <t>All Photography Workshops, - half-day photo workshops, Flowering, Macro &amp; Abstract</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ2176971", "price": "995.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "priceSpecification": {"price": "995.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9859986", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G45" t="n">
         <v>1</v>
       </c>
       <c r="H45" t="n">
-        <v>995</v>
+        <v>50</v>
       </c>
       <c r="I45" t="n">
-        <v>995</v>
+        <v>50</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>SQ2176971</t>
+          <t>SQ9859986</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>SQ2176971</t>
+          <t>SQ9859986</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -2957,51 +2957,51 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>URBAN ARCHITECTURE Photography Workshops - Coventry 9 Sep</t>
+          <t>PEAK DISTRICT HEATHER Photography Workshops - 14-15 Aug</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>We will walk around several historic parts of Coventry in this 2.5hr Urban Architecture Photography Workshop, photographing buildings and ruins.SummaryLocation: Coventry City CentreDates: Wed 9 Sep 2026 - 18:15-20:15Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Street PhotographyDescription: This Urban Architecture Photography workshop is an evening walk through the historic heart of Coventry — once UK City of Culture — open to all levels and any camera. Cities transform after dark: artificial light, deep shadow and the last colour in the sky turn ordinary buildings and ruins into something dramatic, and this 2.5-hour workshop is built around learning to see and design photographs at night, in the tricky low light most people find hardest to shoot.Confident technique in the dark is the floor we build on — and we'll cover it: focusing and exposing accurately in low light, and setting up long exposures to capture movement and mood. But the real work is learning to see the city as a photographer. Walking together through old and new architectural corners — including the cathedral area and its ruins — you'll learn to compose with form, line, texture and contrast, to read the interplay of artificial light and shadow as a harmony rather than a problem, and to find the considered, intentional frame instead of the obvious postcard of a landmark. Old against new, light against dark, detail against sweep — it's about designing an image, not just recording a building.It's a small group of no more than six, taught personally and pitched at exactly your level, so whether you're new to night photography or refining your eye you get real one-to-one guidance in the field. You'll come away with a set of atmospheric urban and architectural images — long exposures, abstracts, dramatic skies — and a sharper, more intentional way of seeing that lets you photograph any city after dark.</t>
+          <t>Join me for the Peak District heather displays over this iconic landscape in August - 4hr Heather Peak District Photography Workshops | All levels welcomeSummaryLocation: Peak District - Derbyshire/Staffordshire2026 - Sat 15th Aug 18:15 21:15 - Derbyshire Surprise View2026 - Sun 16th Aug 05:45 08:45 - Staffordshire - The Roaches2027 - Sat 14th Aug 18:15 21:15 - Derbyshire Surprise View2027 - Sun 15th Aug 05:45 08:45 - Staffordshire - The RoachesParticipants: Max 6Fitness: 3. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details HeathersDescription: Every August the moors of the Peak District turn a spectacular purple as the heather comes into bloom, and this Peak District Heather Photography Workshop is your chance to capture that fleeting display at its very best — open to all levels and any camera. Run as short, focused sessions at the magic hours of sunrise and sunset, it pairs one of Britain's most iconic landscapes with its richest seasonal colour, and the low golden light that makes heather and gritstone glow.You can join either of two sessions, or both: a sunset shoot at Surprise View above Hathersage in Derbyshire — one of the finest viewpoints in the Peak, with sweeping heather foregrounds, the Mother Cap stone and famously dark skies — or a sunrise shoot among the dramatic gritstone of The Roaches, Hen Cloud and Ramshaw Rocks in Staffordshire, weathered into extraordinary shapes above a sea of purple moorland.A blaze of purple is more seductive than it is easy, and the real work is learning to see past the obvious. The technical craft is the floor we build on — controlling exposure to hold rich colour and a dramatic sky, and working quickly in the brief light of dawn and dusk — but the focus is on composing with intention: balancing the heather and the gritstone rock forms into a frame with order, working the intimate detail of bloom and weathered stone as readily as the wide moorland vista, and treating the purple, the gold and the low light as a harmony rather than a colour to crank. We shoot two to three locations each session as conditions allow, and the aim throughout is an image with mood and restraint — one that feels like that moor at first or last light.It's a small group of no more than six, taught personally and pitched at exactly your level, with one-to-one guidance in the field throughout. Whether you take the sunset, the sunrise or make a weekend of both, you'll come away with a portfolio of the Peak District's heather at its peak — and a sharper, more intentional way of seeing colour, light and landscape that you can take anywhere. If you're booking both sessions, please arrange your own overnight accommodation near The Roaches for the early sunrise shoot. Please also note this is a seasonal workshop tied to the heather bloom, so exact dates may shift slightly with the season.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1658913526124-UHAZAOPDEELSFKC627FT/Coventry+1.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1685361335026-KNDKR6D00CTPUASRDWDV/Surprise%2BView%2B2.jpg</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/urban-architecture-photography-workshops-coventry</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/peak-district-heather-photography-workshop</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - half-day photo workshops, Urban</t>
+          <t>All Photography Workshops, - half-day photo workshops, Landscape, Flowering</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ4066377", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ1994489", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Sat 15 Aug 2026 - Hathersage 18:15 - 21:15", "priceSpecification": {"price": "125.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1389945", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Sun 16 Aug 2026 - The Roaches &amp; Ramshaw 05:45 - 08:45", "priceSpecification": {"price": "125.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5395624", "price": "200.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Both sessions - 15 and 16 Aug - sunset and sunrise"}, {"@type": "Offer", "sku": "SQ7900435", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "2027 - Sat 14th Aug 18:15 21:15 - Derbyshire Surprise View"}, {"@type": "Offer", "sku": "SQ4225053", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "2027 - Sun 15 Aug - The Roaches &amp; Ramshaw 05:45 - 08:45"}, {"@type": "Offer", "sku": "SQ8702063", "price": "200.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Both sessions - 14 and 15 Aug - sunset and sunrise"}]</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H46" t="n">
-        <v>50</v>
+        <v>125</v>
       </c>
       <c r="I46" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>SQ4066377</t>
+          <t>SQ1994489, SQ1389945, SQ5395624, SQ7900435, SQ4225053, SQ8702063</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>SQ4066377</t>
+          <t>SQ1994489</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3013,51 +3013,51 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>WALES Photography Workshop | Lake Vyrnwy 10-11 Oct</t>
+          <t>The Secret of WOODLAND PHOTOGRAPHY- 1-Day Jan, Apr, Aug, Oct</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Join me for this fantastic Wales photography workshop of woodlands, lakes and waterfalls in Mid-WalesLocation: Wales - Dee ValleyDates: Sat 10th - Sun 11th Oct 2026 - 2 Days/1 NightParticipants: Max 4Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodWales Photography Workshop Event Details Lake VyrnwyDescription: This is a 2-day, 1-night residential Wales photography workshop based in the valleys of Mid-Wales, open to all levels from beginner to advanced. It's built around two of the country's most rewarding landscape locations — Pistyll Rhaeadr, an enchanting waterfall in the Berwyn Mountains and, at 240ft, Britain's tallest single-drop fall, and the tranquil 11-mile shoreline of Lake Vyrnwy — giving you woodlands, water, mountains and one of the seven wonders of Wales in a single weekend.Over two days we work both locations at their best. At Pistyll Rhaeadr you'll photograph the three-stage falls from the viewing platform and bridge, then drop down to water level among the slate beds and mini-falls for intimate compositions; around Lake Vyrnwy we take a leisurely circuit of the reservoir, stopping at quiet bays and outlets and walking the river to the waterfall at the valley head. The focus is on three things that make moving water and big Welsh landscape work: composing a strong frame from a busy natural scene, mastering long exposure to turn falling water into silk, and reading the light and weather that give these valleys their mood. Throughout, the emphasis isn't just on the famous waterfall but on learning to see it — working intimate detail as readily as the wide vista, and treating light and colour as a harmony rather than chasing the obvious shot.With a maximum of just four photographers, this is genuinely personal tuition — Alan plans each day around the season and the forecast, and sends a detailed location itinerary a few days ahead. Accommodation and breakfast are included, so all you have to think about is your photography, and you'll come away with a varied portfolio of Welsh waterfalls, lakes and valleys — and a real command of long-exposure water technique. An extra night's accommodation is available the day before if required — please request in advance, subject to hotel availability.</t>
+          <t>Simplifying Woodland Photography | Unlocking the Secrets to Capturing the Beauty of woods | Three sessions - Theory - Practical - Editing in one daySummaryLocation: Coventry - CV4 9HWDates: - 10:00 - 16:00Sun 18th Oct - AutumnSun 10th Jan - Winter 2027Sun 2nd May - Spring 2027Sun 1st Aug - Summer 2027Participants: Max 3Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: Digital Camera and TripodPhotography Workshop Event Details: Woodland Photography MasterclassDescription: The Secrets of Woodland Photography is a 1-Day Masterclass in Coventry, open to all levels and any camera. Woodland is the hardest subject there is — chaotic, cluttered, endlessly busy — which is exactly why it's the best place to learn to see. Most people come away with the tangled, cliché shot; this day is about learning to find the order, the light and the quiet beauty hidden within the chaos, and to make woodland images that are calm, intentional and your own.The technical setup matters, but it's only the floor we build on. Rather than a typical walk-and-shoot, the day runs as three connected sessions — theory, practical and editing — so we can go deeper than settings. We start with the thinking behind a strong woodland image and the craft that delivers it: simplifying a busy scene, using light and shadow, choosing what to include and what to leave out. Then you put it into practice on a woodland walk, working the close-up, the macro detail and the abstract as readily as the wider view — reading texture and colour as a harmony, not chasing the loud, over-saturated shot. Finally we review your images together and finish on the editing that brings the quiet colours of the forest to life without shouting.The day runs from Alan's home, which offers three things most workshops can't: instant access to woodland straight from the garden, a comfortable covered and heated space for the presentations and image reviews, and a large screen to study your shots on — so the day works whatever the weather. You'll leave not just with a set of woodland images, but with a way of seeing — light, simplicity and restraint — that changes how you photograph trees, nature and detail wherever you go next.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714636535694-5SWM865PVWA9MMT8LCQB/Dawn+at+Lake+Vyrnwy_.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714646680135-9EB3PR57B78W9NMZ09JI/Plant+Hill+Woods+%2310+-+Jan+2022.jpg</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/wales-photography-workshop-pistyll-rhaeadr</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/secrets-of-woodland-photography-workshop</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - weekend residential photo workshops, Landscape</t>
+          <t>All Photography Workshops, - one day photo workshops, Macro &amp; Abstract, Woodlands</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ5697158", "price": "695.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ4894934", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Sun 18th Oct 2026 - 10am - 4pm"}, {"@type": "Offer", "sku": "SQ2827052", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Sun 10 Jan 2027 - 10am - 4pm"}, {"@type": "Offer", "sku": "SQ0512761", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Sun 2nd May 2027 - 10am - 4pm"}, {"@type": "Offer", "sku": "SQ4914997", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Sun 1st Aug 2027 - 10am - 4pm"}]</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H47" t="n">
-        <v>695</v>
+        <v>150</v>
       </c>
       <c r="I47" t="n">
-        <v>695</v>
+        <v>150</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>SQ5697158</t>
+          <t>SQ4894934, SQ2827052, SQ0512761, SQ4914997</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>SQ5697158</t>
+          <t>SQ4894934</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3069,51 +3069,51 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>WARWICKSHIRE Woodland PHOTOGRAPHY WALKS - Monthly - 2hrs</t>
+          <t>DARTMOOR Photography Workshop - Landscapes - 2nd - 4th Apr</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Informal woodland photography walks in and around Warwickshire Woodlands - All Levels and types of camera welcome - Length 2hrs. 9:30 am-11:30 amSummaryLocation: Various Warwickshire Woodlands2026 - 09:30 - 11:30Hay Woods - Solihull Fri Jan 2Tile Hill Nature Reserve Mon Feb 2Millisons Wood, Meriden -Sun May 3Piles Coppice, Coventry - Fri Oct 16Crackley Wood, Kenilworth - Fri Nov 6Hay Woods - Solihull Fri Dec 4Participants: Max 6Fitness: 1. EasyExperience Level: Novice to BeginnerEquipment Needed: Phone or Digital CameraPhotography Workshop Event Details: Woodland WalksDescription: This is a relaxed, informal woodland photography walk through the beautiful woodlands in and around Warwickshire — a regular monthly outing open to all levels and any camera. It's a gentle two hours among the trees with camera in hand, and it's as much about slowing down and reconnecting with nature as it is about photography: we walk, we observe, we take in the wood around us, and we make a photograph when something moves us to — or simply enjoy being there.My aim isn't to tell you what to shoot. It's to help you develop your own visual awareness, your photographic eye and your personal interpretation of what's in front of you. Woodland is one of the hardest subjects there is — chaotic, cluttered, endlessly busy — so the real work is learning to see: to simplify the scene, to find the quiet order and the light within the tangle, and to photograph the close-up, the intimate detail and the abstract as readily as the wider woodland view. I'm always on hand for the "how to" — the settings and the craft — but in service of what you feel drawn to express, not a shot list.The walks rotate through a lovely variety of local woodlands across the seasons — among them Crackley Wood, Hay Wood, Tile Hill Nature Reserve, Millisons Wood and Piles Coppice — so there's always something new to see. With no more than six of us it stays personal and unhurried, with one-to-one guidance whenever you want it. You'll come away with images that are genuinely your own — and a calmer, more intentional way of seeing that stays with you long after the walk.</t>
+          <t>Join me on this Landscape Dartmoor Photography Workshop - in the iconic woodlands, and landscape of Dartmoor TorsSummaryLocation: Dartmoor - South DevonDates: Fri 2nd - Sun 4th Apr 2027Participants: Max 4Fitness: 3. HardExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details DartmoorDescription: This is a 3-day, 2-night residential landscape photography workshop based around Dartmoor National Park in South Devon, open to all levels from beginner to advanced. Dartmoor is one of England's most atmospheric wild landscapes — a vast sweep of rugged open moor, dramatic granite tors, ancient stunted woodland and serene rivers running through hidden valleys — and across a weekend you'll learn to read and photograph this dramatic terrain in its ever-changing light.Over three days we range across the moor and its woodlands, working a variety of locations as the conditions dictate — from the sculptural granite tors and big moorland vistas to the mossy, otherworldly ancient woods and tumbling rivers. The focus is on three things that make a strong landscape image here: composing order from a wild, expansive scene, controlling exposure and depth of field across big tonal ranges, and timing your shoot to the moods of Dartmoor light, with optional sunrise and sunset shoots and evening picture reviews. Throughout, the emphasis isn't just on the grand vista but on learning to see it — composing with intention, working intimate detail as readily as the wide view, and reading light and weather as a harmony rather than chasing the obvious shot. Be prepared for some longer walks over rougher ground — this is a more demanding workshop that takes you to the moor's most rewarding spots.With a maximum of just four photographers, this is genuinely personal tuition — Alan plans each day around the season and the forecast, and sends a detailed location itinerary a few days ahead. Accommodation, breakfast and evening meals are included, so all you have to think about is your photography, and you'll come away with a varied portfolio of dramatic Dartmoor landscapes — moors, tors and ancient woodland — and the field craft to capture wild country anywhere. An extra night's accommodation is available the day before if required — please request in advance, subject to hotel availability.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707217364251-99ITJH38DI58S3G3YA47/Woodland+Photography+Walk.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707237329064-99H533NMXCONH5J276LM/dartmoor+photography+workshop.jpg</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/woodland-photography-walk-warwickshire</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/dartmoor-photography-landscape-workshop</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - half-day photo workshops, Woodlands</t>
+          <t>All Photography Workshops, - weekend residential photo workshops, Landscape</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ1654264", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Fri Jan 2 Hay Woods - Solihull"}, {"@type": "Offer", "sku": "SQ1288994", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Mon Feb 2 - Tile Hill Nature Reserve - Coventry"}, {"@type": "Offer", "sku": "SQ0063623", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Sun May 3 - Millisons Wood, Meriden"}, {"@type": "Offer", "sku": "SQ6524101", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Fri Oct 16 - Piles Coppice, Coventry"}, {"@type": "Offer", "sku": "SQ7078023", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Fri Nov 6 - Crackley Wood, Kenilworth"}, {"@type": "Offer", "sku": "SQ3819844", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Fri Dec 4 - Hay Wood - Lapworth"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ5540434", "price": "875.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29"}]</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H48" t="n">
-        <v>15</v>
+        <v>875</v>
       </c>
       <c r="I48" t="n">
-        <v>15</v>
+        <v>875</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>SQ1654264, SQ1288994, SQ0063623, SQ6524101, SQ7078023, SQ3819844</t>
+          <t>SQ5540434</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>SQ1654264</t>
+          <t>SQ5540434</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3125,107 +3125,107 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>YORKSHIRE DALES Landscape  Photography Workshop - 16 - 18 Apr</t>
+          <t>Online Photography Classes 121 - Zoom - Package Options</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Yorkshire Dales Photography Workshop - Join me for this fantastic landscape workshop on limestone pavements and waterfalls.SummaryLocation: Yorkshire DalesDates: Fri 16th - Sun 18th Apr 2027 - 3 Days/2 NightsParticipants: Max 4Fitness: 3. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details Yorkshire DalesDescription: This is a 3-day, 2-night residential landscape photography workshop in the Yorkshire Dales — one of England's most iconic and varied landscapes, open to all levels from beginner to advanced. From dramatic limestone pavements and amphitheatre cliffs to tumbling waterfalls, soaring viaducts and lone, wind-sculpted trees, the Dales pack an extraordinary range of subjects into one area, and over a long weekend you'll learn to read and photograph this moody, dramatic country in its best light.Across three days we work some of the Dales' most rewarding locations as the conditions and season allow — the natural amphitheatre of Malham Cove and the ravine at Gordale Scar, the waterfalls of Ingleton, Aysgarth and Janet's Foss, the sweeping arches of Ribblehead Viaduct, and the famous lone tree set on its bare limestone pavement. The focus is on three things that make a strong Dales image: composing rock, water and vista into a balanced frame, mastering long exposure to bring waterfalls and rivers to life, and timing each shoot — including early morning starts — to the dramatic light and weather these hills are known for. Throughout, the emphasis isn't just on the grand vista but on learning to see it — composing with intention, working intimate detail as readily as the wide view, and reading light and colour as a harmony rather than chasing the obvious shot.With a maximum of just four photographers, this is genuinely personal tuition — Alan plans each day around the season and the forecast, and sends a detailed location itinerary a few days ahead. Accommodation and breakfast are included, so all you have to think about is your photography, and you'll come away with a varied portfolio of the Yorkshire Dales — waterfalls, limestone pavements, viaducts and classic vistas — and the field craft to capture dramatic upland landscape anywhere. An extra night's accommodation is available the day before if required — please request in advance, subject to hotel availability.</t>
+          <t>Private Online Photography Classes (Zoom)Summary - Private Online Photography Classes - Key InformationFormat: Online 1-2-1 via Zoom (free to use)Sessions: Single 1hr lesson, or discounted packages of 4, 6, 8 or 12 hoursAvailability: Standard Mon–Fri, 9am–5pm or Premium - Mon-Sun 9am -9pmValidity: Pay now, book dates later — use within 12 months of purchaseLevel: All levels, beginner to advancedDescription: Private online photography classes tailored to your needs — tuition and support on any aspect of photography, with no other students, so the time you pay for is dedicated entirely to your own style and pace.Equipment: Anything you want to learn or improve on. Sessions run over Zoom, with notes provided; submit images for detailed feedback between lessons.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714659095505-TB874TXCA6ADNDFC82FX/Muker+%2302+-+July+2021.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/4ac49e77-bfdc-435d-bf46-d82bda3bec91/online+photography+lessons.png</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/yorkshire-dales-photography-workshops</t>
+          <t>https://www.alanranger.com/photography-services-near-me/private-online-photography-classes-zoom</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - weekend residential photo workshops, Landscape</t>
+          <t>1-2-1-private-lessons, photography-tuition</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9211910", "price": "895.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ1461156", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Zoom Standard (Weekdays 9-5) - 1 x 1hr - Pay as you go    £50"}, {"@type": "Offer", "sku": "SQ5568703", "price": "170.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Zoom Standard (Weekdays 9-5) - 4 x 1hr (15% Off)          £170"}, {"@type": "Offer", "sku": "SQ6341100", "price": "240.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Zoom Standard (Weekdays 9-5) - 6 x 1hr (20% Off)          £240"}, {"@type": "Offer", "sku": "SQ2281758", "price": "300.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Zoom Standard (Weekdays 9-5) - 8 x 1hr (25% Off)          £300"}, {"@type": "Offer", "sku": "SQ2043258", "price": "450.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Zoom Standard (Weekdays 9-5) - 12 x 1hr (25% Off)         £450"}, {"@type": "Offer", "sku": "SQ6476466", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Zoom Premium (Eve/Weekend 9-9) - 1 x 1hr - Pay as you go  £75"}, {"@type": "Offer", "sku": "SQ4036849", "price": "255.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Zoom Premium (Eve/Weekend 9-9) - 4 x 1hr (15% Off)        £255"}, {"@type": "Offer", "sku": "SQ6369047", "price": "360.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Zoom Premium (Eve/Weekend 9-9) - 6 x 1hr (20% Off)        £360"}, {"@type": "Offer", "sku": "SQ7040572", "price": "450.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Zoom Premium (Eve/Weekend 9-9) - 8 x 1hr (25% Off)        £450"}, {"@type": "Offer", "sku": "SQ6714463", "price": "675.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Zoom Premium (Eve/Weekend 9-9) - 12 x 1hr (25% Off)       £675"}]</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H49" t="n">
-        <v>895</v>
+        <v>50</v>
       </c>
       <c r="I49" t="n">
-        <v>895</v>
+        <v>675</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>SQ9211910</t>
+          <t>SQ1461156, SQ5568703, SQ6341100, SQ2281758, SQ2043258, SQ6476466, SQ4036849, SQ6369047, SQ7040572, SQ6714463</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>SQ9211910</t>
+          <t>SQ1461156</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>product</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Photography Gift Vouchers | Digital eCard | Email Delivery</t>
+          <t>1 x 2hr Private Photography Classes - Face to Face Coventry</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Photography Gift Vouchers | Digital eCard | Email Delivery</t>
+          <t>1 × 2hr Private Photography Classes (Face to Face, Coventry)Summary - Private Photography Classes (Face to Face) - Key InformationLocation: Coventry (face to face)Format: Private 1-2-1 tuition, in personSessions: 1 × 2hr classes, scheduled to suit youAvailability: Mon–Fri, 9am–5pmValidity: Pay now, book dates later — you'll be sent a code to book your datesLevel: All levels, beginner to advancedDescription: A package of four private, face-to-face photography classes in Coventry — two hours each, tailored entirely to you and what you want to learn or improve.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1556527290185-GZJ3ZPC3M7AU34BFFVOE/photography-gift-vouchers.png</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/17054018-4804-4c2d-ad29-c57cba809028/face+to+face+private+photography+classes.png</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/photography-gift-vouchers</t>
+          <t>https://www.alanranger.com/photography-services-near-me/2hr-private-photography-classes-2hr</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>online;1-2-1-private-lessons;gift-voucher;photography-classes;photography-courses;photography-services;photography-tuition;photography-workshops, photography-gift-vouchers;photography-presents</t>
+          <t>1-2-1-private-lessons, photography-classes, photography-tuition, photography-courses</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SUP-PHOTOGRAPHY-GIFT-VOUCHERS-DIGITA", "price": "5.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Photography Gift Vouchers | Digital eCard | Email Delivery"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ5440373", "price": "120.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29"}]</t>
         </is>
       </c>
       <c r="G50" t="n">
         <v>1</v>
       </c>
       <c r="H50" t="n">
-        <v>5</v>
+        <v>120</v>
       </c>
       <c r="I50" t="n">
-        <v>5</v>
+        <v>120</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>SUP-PHOTOGRAPHY-GIFT-VOUCHERS-DIGITA</t>
+          <t>SQ5440373</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>SUP-PHOTOGRAPHY-GIFT-VOUCHERS-DIGITA</t>
+          <t>SQ5440373</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3237,88 +3237,88 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Professional Black and White Photography Course | Coventry</t>
+          <t>Photography Gift Vouchers | Digital eCard | Email Delivery</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Professional Black and White Photography Course | Coventry</t>
+          <t>Photography Gift Vouchers | Digital eCard | Email Delivery</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1721724334692-7KPD0E90A6E4YZMAR324/black+and+white+photography+course+.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1556527290185-GZJ3ZPC3M7AU34BFFVOE/photography-gift-vouchers.png</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/black-and-white-photography-course</t>
+          <t>https://www.alanranger.com/photography-services-near-me/photography-gift-vouchers</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>photography-courses, beginners-photography-course</t>
+          <t>online;1-2-1-private-lessons;gift-voucher;photography-services;photography-tuition, photography-gift-vouchers;photography-presents</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SUP-PROFESSIONAL-BLACK-AND-WHITE-PHO", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Professional Black and White Photography Course | Coventry"}]</t>
+          <t>[{"@type": "Offer", "sku": "SUP-PHOTOGRAPHY-GIFT-VOUCHERS-DIGITA", "price": "5.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Photography Gift Vouchers | Digital eCard | Email Delivery"}]</t>
         </is>
       </c>
       <c r="G51" t="n">
         <v>1</v>
       </c>
       <c r="H51" t="n">
-        <v>150</v>
+        <v>5</v>
       </c>
       <c r="I51" t="n">
-        <v>150</v>
+        <v>5</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>SUP-PROFESSIONAL-BLACK-AND-WHITE-PHO</t>
+          <t>SUP-PHOTOGRAPHY-GIFT-VOUCHERS-DIGITA</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>SUP-PROFESSIONAL-BLACK-AND-WHITE-PHO</t>
+          <t>SUP-PHOTOGRAPHY-GIFT-VOUCHERS-DIGITA</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>course</t>
+          <t>product</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Photography Masterclasses-Learn and improve your photography</t>
+          <t>Professional Black and White Photography Course | Coventry</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Photography Masterclasses-Learn and improve your photography</t>
+          <t>Professional Black and White Photography Course | Coventry</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1675588273356-8MVS4YXJTH3Y5PRQ36N7/photography-tuition-Package-2.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1721724334692-7KPD0E90A6E4YZMAR324/black+and+white+photography+course+.jpg</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/photography-masterclasses-coventry</t>
+          <t>https://www.alanranger.com/photography-services-near-me/black-and-white-photography-course</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>photography-classes;photography-courses;photography-tuition, coventry</t>
+          <t>photography-courses, beginners-photography-course</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SUP-PHOTOGRAPHY-MASTERCLASSES-LEARN-", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Photography Masterclasses-Learn and improve your photography"}]</t>
+          <t>[{"@type": "Offer", "sku": "SUP-PROFESSIONAL-BLACK-AND-WHITE-PHO", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Professional Black and White Photography Course | Coventry"}]</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -3332,15 +3332,71 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
+          <t>SUP-PROFESSIONAL-BLACK-AND-WHITE-PHO</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>SUP-PROFESSIONAL-BLACK-AND-WHITE-PHO</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>course</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Photography Masterclasses-Learn and improve your photography</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Photography Masterclasses-Learn and improve your photography</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1675588273356-8MVS4YXJTH3Y5PRQ36N7/photography-tuition-Package-2.jpg</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>https://www.alanranger.com/photography-services-near-me/photography-masterclasses-coventry</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>photography-classes;photography-courses;photography-tuition, coventry</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>[{"@type": "Offer", "sku": "SUP-PHOTOGRAPHY-MASTERCLASSES-LEARN-", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Photography Masterclasses-Learn and improve your photography"}]</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>1</v>
+      </c>
+      <c r="H53" t="n">
+        <v>150</v>
+      </c>
+      <c r="I53" t="n">
+        <v>150</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
           <t>SUP-PHOTOGRAPHY-MASTERCLASSES-LEARN-</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="K53" t="inlineStr">
         <is>
           <t>SUP-PHOTOGRAPHY-MASTERCLASSES-LEARN-</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t>product</t>
         </is>

--- a/csv processed/02 – products_cleaned.xlsx
+++ b/csv processed/02 – products_cleaned.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L53"/>
+  <dimension ref="A1:L55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3402,6 +3402,118 @@
         </is>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Photography Mentor Online — Monthly Mentoring</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Online photography mentoring with monthly assignments, a personal Lightroom review of your images and 30 practice packs. £20/month, cancel anytime.</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/0ddfe780-871c-4d90-a207-82f053d68ce0/monthly+mentoring+assigments.png</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>https://www.alanranger.com/photography-mentoring-online-assignments</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>photography-mentoring, online-mentoring</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>[{"@type": "Offer", "sku": "SQ-MENTOR-MONTHLY", "price": "20.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-06", "priceValidUntil": "2027-10-06", "name": "Foundation Plus \u2014 Monthly Mentoring \u00a320/mo"}]</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>1</v>
+      </c>
+      <c r="H54" t="n">
+        <v>20</v>
+      </c>
+      <c r="I54" t="n">
+        <v>20</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>SQ-MENTOR-MONTHLY</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>SQ-MENTOR-MONTHLY</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Free Online Photography Course</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Free online photography course from the Alan Ranger photography academy. 60 modules covering camera settings, gear, composition, genres and practical exercises. 14-day free trial; £79/year membership.</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/72b72191-5a88-45c1-85cc-db9f7e0032b7/FREE+online+photography+course</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>https://www.alanranger.com/free-online-photography-course</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>photography-academy, online-course</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>[{"@type": "Offer", "sku": "SQ-ACADEMY-ANNUAL", "price": "79.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-06", "priceValidUntil": "2027-10-06", "name": "Alan Ranger Academy \u2014 Annual Membership \u00a379/yr"}]</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>1</v>
+      </c>
+      <c r="H55" t="n">
+        <v>79</v>
+      </c>
+      <c r="I55" t="n">
+        <v>79</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>SQ-ACADEMY-ANNUAL</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>SQ-ACADEMY-ANNUAL</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/csv processed/02 – products_cleaned.xlsx
+++ b/csv processed/02 – products_cleaned.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L55"/>
+  <dimension ref="A1:N55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,6 +489,16 @@
           <t>schema_type</t>
         </is>
       </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>exclude_from_manifest</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>manual_paste_page</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -545,6 +555,12 @@
           <t>course</t>
         </is>
       </c>
+      <c r="M2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N2" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -601,6 +617,12 @@
           <t>course</t>
         </is>
       </c>
+      <c r="M3" t="b">
+        <v>0</v>
+      </c>
+      <c r="N3" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -657,6 +679,12 @@
           <t>product</t>
         </is>
       </c>
+      <c r="M4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N4" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -713,6 +741,12 @@
           <t>event</t>
         </is>
       </c>
+      <c r="M5" t="b">
+        <v>0</v>
+      </c>
+      <c r="N5" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -769,6 +803,12 @@
           <t>product</t>
         </is>
       </c>
+      <c r="M6" t="b">
+        <v>0</v>
+      </c>
+      <c r="N6" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -825,6 +865,12 @@
           <t>event</t>
         </is>
       </c>
+      <c r="M7" t="b">
+        <v>0</v>
+      </c>
+      <c r="N7" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -881,6 +927,12 @@
           <t>product</t>
         </is>
       </c>
+      <c r="M8" t="b">
+        <v>0</v>
+      </c>
+      <c r="N8" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -937,6 +989,12 @@
           <t>event</t>
         </is>
       </c>
+      <c r="M9" t="b">
+        <v>0</v>
+      </c>
+      <c r="N9" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -993,6 +1051,12 @@
           <t>product</t>
         </is>
       </c>
+      <c r="M10" t="b">
+        <v>0</v>
+      </c>
+      <c r="N10" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1049,6 +1113,12 @@
           <t>product</t>
         </is>
       </c>
+      <c r="M11" t="b">
+        <v>0</v>
+      </c>
+      <c r="N11" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1105,6 +1175,12 @@
           <t>course</t>
         </is>
       </c>
+      <c r="M12" t="b">
+        <v>0</v>
+      </c>
+      <c r="N12" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1161,6 +1237,12 @@
           <t>course</t>
         </is>
       </c>
+      <c r="M13" t="b">
+        <v>0</v>
+      </c>
+      <c r="N13" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1217,6 +1299,12 @@
           <t>event</t>
         </is>
       </c>
+      <c r="M14" t="b">
+        <v>0</v>
+      </c>
+      <c r="N14" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1273,6 +1361,12 @@
           <t>event</t>
         </is>
       </c>
+      <c r="M15" t="b">
+        <v>0</v>
+      </c>
+      <c r="N15" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1329,6 +1423,12 @@
           <t>event</t>
         </is>
       </c>
+      <c r="M16" t="b">
+        <v>0</v>
+      </c>
+      <c r="N16" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1385,6 +1485,12 @@
           <t>event</t>
         </is>
       </c>
+      <c r="M17" t="b">
+        <v>0</v>
+      </c>
+      <c r="N17" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1441,6 +1547,12 @@
           <t>event</t>
         </is>
       </c>
+      <c r="M18" t="b">
+        <v>0</v>
+      </c>
+      <c r="N18" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1497,6 +1609,12 @@
           <t>event</t>
         </is>
       </c>
+      <c r="M19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N19" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1553,6 +1671,12 @@
           <t>event</t>
         </is>
       </c>
+      <c r="M20" t="b">
+        <v>0</v>
+      </c>
+      <c r="N20" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1609,6 +1733,12 @@
           <t>product</t>
         </is>
       </c>
+      <c r="M21" t="b">
+        <v>0</v>
+      </c>
+      <c r="N21" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1665,6 +1795,12 @@
           <t>product</t>
         </is>
       </c>
+      <c r="M22" t="b">
+        <v>0</v>
+      </c>
+      <c r="N22" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1721,6 +1857,12 @@
           <t>event</t>
         </is>
       </c>
+      <c r="M23" t="b">
+        <v>0</v>
+      </c>
+      <c r="N23" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1777,6 +1919,12 @@
           <t>product</t>
         </is>
       </c>
+      <c r="M24" t="b">
+        <v>0</v>
+      </c>
+      <c r="N24" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1833,6 +1981,12 @@
           <t>event</t>
         </is>
       </c>
+      <c r="M25" t="b">
+        <v>0</v>
+      </c>
+      <c r="N25" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1889,6 +2043,12 @@
           <t>event</t>
         </is>
       </c>
+      <c r="M26" t="b">
+        <v>0</v>
+      </c>
+      <c r="N26" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1945,6 +2105,12 @@
           <t>event</t>
         </is>
       </c>
+      <c r="M27" t="b">
+        <v>0</v>
+      </c>
+      <c r="N27" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2001,6 +2167,12 @@
           <t>event</t>
         </is>
       </c>
+      <c r="M28" t="b">
+        <v>0</v>
+      </c>
+      <c r="N28" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2057,6 +2229,12 @@
           <t>event</t>
         </is>
       </c>
+      <c r="M29" t="b">
+        <v>0</v>
+      </c>
+      <c r="N29" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2113,6 +2291,12 @@
           <t>course</t>
         </is>
       </c>
+      <c r="M30" t="b">
+        <v>0</v>
+      </c>
+      <c r="N30" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2169,6 +2353,12 @@
           <t>event</t>
         </is>
       </c>
+      <c r="M31" t="b">
+        <v>0</v>
+      </c>
+      <c r="N31" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2225,6 +2415,12 @@
           <t>event</t>
         </is>
       </c>
+      <c r="M32" t="b">
+        <v>0</v>
+      </c>
+      <c r="N32" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2281,6 +2477,12 @@
           <t>event</t>
         </is>
       </c>
+      <c r="M33" t="b">
+        <v>0</v>
+      </c>
+      <c r="N33" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2337,6 +2539,12 @@
           <t>event</t>
         </is>
       </c>
+      <c r="M34" t="b">
+        <v>0</v>
+      </c>
+      <c r="N34" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2393,6 +2601,12 @@
           <t>event</t>
         </is>
       </c>
+      <c r="M35" t="b">
+        <v>0</v>
+      </c>
+      <c r="N35" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2449,6 +2663,12 @@
           <t>event</t>
         </is>
       </c>
+      <c r="M36" t="b">
+        <v>0</v>
+      </c>
+      <c r="N36" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2505,6 +2725,12 @@
           <t>event</t>
         </is>
       </c>
+      <c r="M37" t="b">
+        <v>0</v>
+      </c>
+      <c r="N37" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2561,6 +2787,12 @@
           <t>event</t>
         </is>
       </c>
+      <c r="M38" t="b">
+        <v>0</v>
+      </c>
+      <c r="N38" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2617,6 +2849,12 @@
           <t>event</t>
         </is>
       </c>
+      <c r="M39" t="b">
+        <v>0</v>
+      </c>
+      <c r="N39" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2673,6 +2911,12 @@
           <t>event</t>
         </is>
       </c>
+      <c r="M40" t="b">
+        <v>0</v>
+      </c>
+      <c r="N40" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2729,6 +2973,12 @@
           <t>event</t>
         </is>
       </c>
+      <c r="M41" t="b">
+        <v>0</v>
+      </c>
+      <c r="N41" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2785,6 +3035,12 @@
           <t>event</t>
         </is>
       </c>
+      <c r="M42" t="b">
+        <v>0</v>
+      </c>
+      <c r="N42" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2841,6 +3097,12 @@
           <t>event</t>
         </is>
       </c>
+      <c r="M43" t="b">
+        <v>0</v>
+      </c>
+      <c r="N43" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2897,6 +3159,12 @@
           <t>event</t>
         </is>
       </c>
+      <c r="M44" t="b">
+        <v>0</v>
+      </c>
+      <c r="N44" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2953,6 +3221,12 @@
           <t>event</t>
         </is>
       </c>
+      <c r="M45" t="b">
+        <v>0</v>
+      </c>
+      <c r="N45" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3009,6 +3283,12 @@
           <t>event</t>
         </is>
       </c>
+      <c r="M46" t="b">
+        <v>0</v>
+      </c>
+      <c r="N46" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3065,6 +3345,12 @@
           <t>event</t>
         </is>
       </c>
+      <c r="M47" t="b">
+        <v>0</v>
+      </c>
+      <c r="N47" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3121,6 +3407,12 @@
           <t>event</t>
         </is>
       </c>
+      <c r="M48" t="b">
+        <v>0</v>
+      </c>
+      <c r="N48" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3177,6 +3469,12 @@
           <t>product</t>
         </is>
       </c>
+      <c r="M49" t="b">
+        <v>0</v>
+      </c>
+      <c r="N49" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3233,6 +3531,12 @@
           <t>product</t>
         </is>
       </c>
+      <c r="M50" t="b">
+        <v>1</v>
+      </c>
+      <c r="N50" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3289,6 +3593,12 @@
           <t>product</t>
         </is>
       </c>
+      <c r="M51" t="b">
+        <v>0</v>
+      </c>
+      <c r="N51" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3345,6 +3655,12 @@
           <t>course</t>
         </is>
       </c>
+      <c r="M52" t="b">
+        <v>0</v>
+      </c>
+      <c r="N52" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3401,6 +3717,12 @@
           <t>product</t>
         </is>
       </c>
+      <c r="M53" t="b">
+        <v>0</v>
+      </c>
+      <c r="N53" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3457,6 +3779,12 @@
           <t>product</t>
         </is>
       </c>
+      <c r="M54" t="b">
+        <v>1</v>
+      </c>
+      <c r="N54" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3512,6 +3840,12 @@
         <is>
           <t>product</t>
         </is>
+      </c>
+      <c r="M55" t="b">
+        <v>0</v>
+      </c>
+      <c r="N55" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/csv processed/02 – products_cleaned.xlsx
+++ b/csv processed/02 – products_cleaned.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N55"/>
+  <dimension ref="A1:L38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,356 +489,316 @@
           <t>schema_type</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>exclude_from_manifest</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>manual_paste_page</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Lightroom Courses for Beginners Photo Editing - Coventry</t>
+          <t>MACRO Photography Workshops Warwickshire - Various</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>For those who want to implement the best workflow for image management and all the dos and don'ts of post-production with these Photo Editing Classes with LightroomAdobe Lightroom Classic Courses for Beginners - CoventryLocation: 45 Hathaway Road, Coventry, CV4 9HWDuration: 3 × 2hr evening classes (19:00–21:00)Participants: Max 3Start Dates:Lightroom Editing CourseCoventry 3 wks - Mon 7 Sep - 21 Sep 2026Coventry 3 wks - Thu 12 Nov - 26 Nov 2026Coventry 3 wks - Tue 12 Jan - 26 Jan 2027Coventry 3 wks - Thu 6 May - 20 May 2027Level: BeginnersDescription: A practical three-week evening course that takes you from a messy photo library and untouched RAW files to a finished, repeatable Lightroom Classic workflow — working on your own laptop throughout.Week 1 is about getting organised: catalogues, importing, collections, keywords and star ratings, so you can find and manage your photos for good rather than losing them across folders.Week 2 moves on to global adjustments — reading the histogram, then exposure, white balance, contrast, tone curves and sharpening — the core develop tools that do most of the work on any image.Week 3 covers local adjustments — graduated and radial filters, adjustment brushes and spot removal — and pulling it together into a consistent, repeatable style across your photos.With a maximum of three people, you get real hands-on help on your own screen whenever you hit a problem, plus course notes for each module and practical assignments to work on between sessions. Beginners welcome — no editing experience needed; just bring a laptop with Adobe Lightroom Classic installed and an active subscription.Equipment: You will need a laptop with Adobe Lightroom Classic subscription and the App installed. Alan will provide you with a training Lightroom Library with images and use that to explain and then demonstrate the various tools.</t>
+          <t>Abstract and Macro Photography Workshop . Learn about camera settings, lens use, controlling DoF and composition. Various Dates in Warwickshire | Half DaySummaryLocation: WarwickshireDates: Macro Photography WorkshopsMacro Photography - Sun Nov 28th 2026 - 10:30am - 12:30pmMacro Photography - Sat May 1st 2027 - 11am - 1pmMacro Photography - Sun Sep 29th 2027 - 4:00pm - 6:00pmParticipants: Max 4Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: Digital Camera and Tripod, Zoom or Macro LensMacro Photography Workshop Event Details: Macro Photography and AbstractDescription: This Abstract and Macro Photography Workshop takes place at a Warwickshire location and is open to all levels and any camera. Macro is where ordinary surroundings become extraordinary — get close and a tree trunk, a piece of weathered stone or a patch of water reveals shapes, colours, tones and patterns most people walk straight past. The whole session is about learning to see them, and then photograph them with intention.The technical craft matters here — and we'll cover it properly — but it's the floor, not the point. Working around the area together, Alan guides you through the settings that give you control: getting sharp focus and using a macro lens or zoom, controlling depth of field to isolate your subject, and building a composition with real intention. From there the real work begins — training your eye to find the abstract within the ordinary, to read tone, shadow and highlight, and to treat colour as a harmony to compose with rather than a loud effect to chase. The aim is never the obvious close-up everyone takes, but an image that's considered and your own.It's a small group of no more than four, taught personally by an award-winning professional photographer, so every person gets real one-to-one guidance in the field — briefing and set-up, then shooting with reviews and tuition as you go. You'll leave with your own macro and abstract images, and a sharper, more intentional way of seeing detail, colour and light that changes how you photograph everything afterwards.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/fe40a5e1-7fa2-4057-982e-555479b97022/Lightroom+courses+-+photo+editing+course.png</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/25c550a3-a242-4303-a11b-367dd7055dbe/Abstract%2Band%2BMacro%2BPhotography%2BWorkshops%2B%25282%2529.jpg</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/lightroom-courses-for-beginners-coventry</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/abstract-and-macro-photography-workshops</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>photography-classes, photography-courses, photo editing, lightroom</t>
+          <t>All Photography Workshops, - half-day photo workshops, Macro &amp; Abstract</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ7526725", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Coventry 3 wks - Mon 7 Sep - 21 Sep 2026"}, {"@type": "Offer", "sku": "SQ6831161", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Coventry 3 wks - Thu 12 Nov - 26 Nov 2026"}, {"@type": "Offer", "sku": "SQ1021857", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Coventry 3 wks - Tue 12 Jan - 26 Jan 2027"}, {"@type": "Offer", "sku": "SQ3349262", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Coventry 3 wks - Thu 6 May - 20 May 2027"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9970442", "price": "65.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Sun Nov 28th 2026 - 10:30am - 12:30pm"}, {"@type": "Offer", "sku": "SQ2051466", "price": "65.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Sat May 1st 2027 - 11am - 1pm"}, {"@type": "Offer", "sku": "SQ8660736", "price": "65.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Sun Sep 29th 2027 - 4:00pm - 6:00pm"}]</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H2" t="n">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="I2" t="n">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>SQ7526725, SQ6831161, SQ1021857, SQ3349262</t>
+          <t>SQ9970442, SQ2051466, SQ8660736</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>SQ7526725</t>
+          <t>SQ9970442</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>course</t>
-        </is>
-      </c>
-      <c r="M2" t="b">
-        <v>0</v>
-      </c>
-      <c r="N2" t="b">
-        <v>0</v>
+          <t>event</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>RPS Courses - Independent RPS Mentoring for RPS Distinctions</t>
+          <t>Annual Pick N Mix Subscription | £1,200 Up-Front, 15% Off</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>RPS Courses - Independant RPS Mentoring for RPS Distinctions - Start anytime, you select a package of Zoom sessions within twelve months at intervals to suit youDescription: Independent one-to-one RPS mentoring for your Licentiate (LRPS) or Associate (ARPS) distinction — online via Zoom, with a mentor who holds both distinctions himself and has a 100% pass rate to date. Most photographers who fall short don't fail on technique — they submit a collection of strong individual images rather than a planned, cohesive panel, and a panel is judged as a whole. That judgement — image selection, sequencing, the hanging plan and your Statement of Intent — is exactly what mentoring brings. We work in three stages: plan the panel, build and refine it, then test readiness before you submit. Sessions are flexible 1-hour Zoom slots — buy only what you need and book your dates later, across up to twelve months. Start fresh, or revise a panel that didn't pass first time.Format: One-to-one, online via Zoom — private and personal to you and your panel.Equipment Needed: Zoom App; free Dropbox account for sharing portfolios and updated images.Terms: A package of Zoom sessions must be used within 12 months of purchase or it is forfeited. You can extend the timeline or purchase additional sessions if needed.Method: Honest technical and creative critique with suggestions for improvement; advice on image selection, sequencing, the hanging plan and your Statement of Intent.Package Options: Choose Mon–Fri 9am–5pm daytime rates, or Mon–Sun 9am–9pm for evening and weekend flexibility.1 × 1hr — single session (fact-find &amp; review)4 × 1hr — 15% off (reset a failed panel)6 × 1hr — 20% off (from scratch, recommended)8 × 1hr — 25% off (extended panel build)12 × 1hr — 25% off (best value, full programme)More Details: about the RPS Mentoring Course</t>
+          <t>Annual Pick N Mix Subscription: pay once up-front, from £1,200, for your first year of photography development. 15% off courses, workshops and 1-to-1s, 4 one-hour quarterly 1-2-1 reviews and free Photography Academy membership for 12 months</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707307452323-G3C2AIXAHRLLVB36VASA/RPS+Courses.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/4c6bb1a6-8752-4aea-a250-484fb1acdf75/Photography+Payment+Plan.png</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/rps-mentoring-photography-course</t>
+          <t>https://www.alanranger.com/photography-services-near-me/annual-pick-n-mix-subscription</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1-2-1-private-lessons, photography-classes, photography-courses, photography-tuition, rps</t>
+          <t>photography-classes, photography-courses, photography-workshops</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ7839038", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Mon- Fri 9am-5pm 1 x 1hr"}, {"@type": "Offer", "sku": "SQ3867813", "price": "170.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Mon- Fri 9am-5pm 4 x 1hr"}, {"@type": "Offer", "sku": "SQ8903198", "price": "240.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Mon- Fri 9am-5pm 6 x 1hr"}, {"@type": "Offer", "sku": "SQ4831915", "price": "300.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Mon- Fri 9am-5pm  8x 1hr"}, {"@type": "Offer", "sku": "SQ1077689", "price": "450.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Mon- Fri 9am-5pm 12 x 1hr"}, {"@type": "Offer", "sku": "SQ8233730", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Mon- Sun 9am-9pm 1 x 1hr"}, {"@type": "Offer", "sku": "SQ9139531", "price": "255.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Mon- Sun 9am-9pm 4 x 1hr"}, {"@type": "Offer", "sku": "SQ0776423", "price": "360.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Mon- Sun 9am-9pm 6 x 1hr"}, {"@type": "Offer", "sku": "SQ2385997", "price": "450.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Mon- Sun 9am-9pm 8 x 1hr"}, {"@type": "Offer", "sku": "SQ9440259", "price": "675.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Mon- Sun 9am-9pm 12 x 1hr"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ0754560", "price": "1200.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "1 x £1200 = £1200"}, {"@type": "Offer", "sku": "SQ7502565", "price": "1500.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "1 x £1500 = £1500"}, {"@type": "Offer", "sku": "SQ1485137", "price": "2000.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "1 x £2000 = £2000"}, {"@type": "Offer", "sku": "SQ7001156", "price": "2500.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "1 x £2500 = £2500"}]</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H3" t="n">
-        <v>50</v>
+        <v>1200</v>
       </c>
       <c r="I3" t="n">
-        <v>675</v>
+        <v>2500</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>SQ7839038, SQ3867813, SQ8903198, SQ4831915, SQ1077689, SQ8233730, SQ9139531, SQ0776423, SQ2385997, SQ9440259</t>
+          <t>SQ0754560, SQ7502565, SQ1485137, SQ7001156</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>SQ7839038</t>
+          <t>SQ0754560</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>course</t>
-        </is>
-      </c>
-      <c r="M3" t="b">
-        <v>0</v>
-      </c>
-      <c r="N3" t="b">
-        <v>0</v>
+          <t>product</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Professional Digital DSLR Camera Sensor Clean | Coventry</t>
+          <t>BATSFORD Arboretum Autumn Photography Workshops 23 - 29 Oct</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Get a camera sensor clean in Coventry . Sensor checked and cleaned using professional equipment, swabs | Full Frame and Cropped Sensors | 24hr Turnaround</t>
+          <t>Batsford Arboretum Photography Workshops in autumn. Enjoy the colour and expert photographic guidance | Half or One Day Sessions | Any Level and CameraSummaryLocation: Batsford Arboretum - GloucestershireDates: Fri 23 Oct –Thu 29 2026Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless CameraPhotography Workshop Event Batsford ArboretumDescription: For nearly fifteen years I've returned to Batsford Arboretum each autumn, and in that time I've come to know every corner of it — which spot works at which hour, where the light falls and the angles that turn one of Britain's finest tree collections into a photograph rather than a snapshot. This workshop is built on that knowledge. Open to all levels and any camera, it's a chance to photograph Batsford's autumn colour with someone who can put you in the right place at the right time, so you can spend your energy on the thing that actually matters: seeing.Because that's where this workshop really lives. We'll cover the technical setup — exposure, depth of field, the settings that give you control — but that's only the floor. The real work is learning to look: to compose with intention and move beyond the cliché shot everyone else comes home with, to find the close-up, the macro detail and the quiet abstract as readily as the wide vista, and above all to read light, texture and colour as a harmony rather than chasing the over-saturated "look how vivid this is" image. Colour handled with restraint and relationship will always outlast colour shouted.With small numbers and genuine one-to-one attention throughout, you'll have the time and space to slow down and work properly — and you can choose a half-day morning or afternoon session, or a full day in the colour. You'll leave not just with a set of strong autumn images, but with a way of seeing — light, texture and composition — that changes how you photograph colour, woodland and the natural world wherever you go next.Good to know: the workshop price includes entrance to the Arboretum. On the early morning session we have exclusive access before the gardens open to the public — the quiet best light of the day, with the place to ourselves. A grab-and-go breakfast is available from around 9:30am, and the café and outdoor snack bar are open through the day for lunch and refreshments, with toilets on site by the reception area.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1522495201980-KD6BKH54J01HJR93XXR6/photography-support-Services-1.png</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1715155253660-I9BNV2CJV5TPWB56WH93/Batsford+Autumn+7.jpg</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/camera-sensor-clean</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/batsford-arboretum-photography-workshops</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>photography-services</t>
+          <t>All Photography Workshops, - half-day photo workshops, - one day photo workshops, Landscape, Woodlands, autumn</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ5650040", "price": "30.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ0818501", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Fri 23  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7647904", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Fri 23 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9436105", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Fri 23 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1204772", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Sat 24  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9290465", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Sat 24 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7375084", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Sat 24 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0264308", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Sun 25 Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9938663", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Sun 25 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0693365", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Sun 25 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3442432", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Thu 29  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8197555", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Thu 29 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9853668", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Thu 29 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H4" t="n">
-        <v>30</v>
+        <v>99</v>
       </c>
       <c r="I4" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>SQ5650040</t>
+          <t>SQ0818501, SQ7647904, SQ9436105, SQ1204772, SQ9290465, SQ7375084, SQ0264308, SQ9938663, SQ0693365, SQ3442432, SQ8197555, SQ9853668</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>SQ5650040</t>
+          <t>SQ0818501</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="M4" t="b">
-        <v>0</v>
-      </c>
-      <c r="N4" t="b">
-        <v>0</v>
+          <t>event</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>WARWICKSHIRE Woodland PHOTOGRAPHY WALKS - Monthly - 2hrs</t>
+          <t>Beginners Photography Course | 3 Weekly Evening Classes</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Informal woodland photography walks in and around Warwickshire Woodlands - All Levels and types of camera welcome - Length 2hrs. 9:30 am-11:30 amSummaryLocation: Various Warwickshire Woodlands2026 - 09:30 - 11:30Hay Woods - Solihull Fri Jan 2Tile Hill Nature Reserve Mon Feb 2Millisons Wood, Meriden -Sun May 3Piles Coppice, Coventry - Fri Oct 16Crackley Wood, Kenilworth - Fri Nov 6Hay Woods - Solihull Fri Dec 4Participants: Max 6Fitness: 1. EasyExperience Level: Novice to BeginnerEquipment Needed: Phone or Digital CameraPhotography Workshop Event Details: Woodland WalksDescription: This is a relaxed, informal woodland photography walk through the beautiful woodlands in and around Warwickshire — a regular monthly outing open to all levels and any camera. It's a gentle two hours among the trees with camera in hand, and it's as much about slowing down and reconnecting with nature as it is about photography: we walk, we observe, we take in the wood around us, and we make a photograph when something moves us to — or simply enjoy being there.My aim isn't to tell you what to shoot. It's to help you develop your own visual awareness, your photographic eye and your personal interpretation of what's in front of you. Woodland is one of the hardest subjects there is — chaotic, cluttered, endlessly busy — so the real work is learning to see: to simplify the scene, to find the quiet order and the light within the tangle, and to photograph the close-up, the intimate detail and the abstract as readily as the wider woodland view. I'm always on hand for the "how to" — the settings and the craft — but in service of what you feel drawn to express, not a shot list.The walks rotate through a lovely variety of local woodlands across the seasons — among them Crackley Wood, Hay Wood, Tile Hill Nature Reserve, Millisons Wood and Piles Coppice — so there's always something new to see. With no more than six of us it stays personal and unhurried, with one-to-one guidance whenever you want it. You'll come away with images that are genuinely your own — and a calmer, more intentional way of seeing that stays with you long after the walk.</t>
+          <t>Beginners Photography Course CoventrySummary - Camera Courses For Beginners - Key InformationLocation: 45 Hathaway Road, Coventry, CV4 9HWDuration: 3 × 2hr evening classes (19:00–21:00)Participants: Max 4Start Dates: Beginners Photography Course3wks Mondays - Nov 9 - Nov 23 Coventry3wks Tuesdays - Dec 1 - Dec 15 Coventry3wks Wednesdays - Jan 13 - Jan 27 Coventry3wks Thursdays - Jan 28 - Feb 11 Coventry3wks Tuesdays - Mar 2 - Mar 16 Coventry3wks Thursdays Apr 1 - Apr 15 Coventry3wks Wednesdays May 12 - May 26 Coventry3wks Mondays - Jun 7 - Jun 21 CoventryLevel: Beginner and NoviceDescription:A practical three-week evening course that takes you from Auto to confident manual control, built around your own camera.Week 1 is about getting off Auto for good — the exposure modes, then aperture, shutter speed and ISO, and how they work together as the exposure triangle, with practical assignments to put it into practice.Week 2 goes deeper into getting the exposure right: manual exposure, metering, reading the histogram, exposure compensation, stops and dynamic range, and bracketing — followed by a review of your assignment work.Week 3 moves on to focusing and depth of field, white balance, JPEG vs RAW, and the foundations of composition, finishing with a final assignment review.With a maximum of four people, you get genuine attention and plenty of room to ask questions, and you'll leave with a printed course book covering every topic to revisit at home. Beginner and novice friendly — just bring a DSLR or mirrorless camera with manual modes.What You'll Learn: How to get off Auto and use manual exposure, aperture, shutter speed and ISO; how focus works; and the foundations of composition to make stronger, more deliberate photos.Includes: A printed course book covering every topic, so you can revisit it all afterwards.Equipment: A DSLR or mirrorless camera with manual exposure modes.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707217364251-99ITJH38DI58S3G3YA47/Woodland+Photography+Walk.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/773443e9-940a-440b-9faa-14e22b8c4236/beginners+photography+classes+coventry.png</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/woodland-photography-walk-warwickshire</t>
+          <t>https://www.alanranger.com/photography-services-near-me/beginners-photography-course</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - half-day photo workshops, Woodlands</t>
+          <t>photography-classes, photography-courses</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ1654264", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Fri Jan 2 Hay Woods - Solihull"}, {"@type": "Offer", "sku": "SQ1288994", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Mon Feb 2 - Tile Hill Nature Reserve - Coventry"}, {"@type": "Offer", "sku": "SQ0063623", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Sun May 3 - Millisons Wood, Meriden"}, {"@type": "Offer", "sku": "SQ6524101", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Fri Oct 16 - Piles Coppice, Coventry"}, {"@type": "Offer", "sku": "SQ7078023", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Fri Nov 6 - Crackley Wood, Kenilworth"}, {"@type": "Offer", "sku": "SQ3819844", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Fri Dec 4 - Hay Wood - Lapworth"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ5616379", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "3wks Mondays - Nov 9 - Nov 23 Coventry"}, {"@type": "Offer", "sku": "SQ3231903", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "3wks Tuesdays - Dec 1 - Dec 15 Coventry"}, {"@type": "Offer", "sku": "SQ5559634", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "3wks Wednesdays - Jan 13 - Jan 27 Coventry"}, {"@type": "Offer", "sku": "SQ0659870", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "3wks Thursdays - Jan 28 - Feb 11 Coventry"}, {"@type": "Offer", "sku": "SQ0358019", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "3wks Tuesdays - Mar 2 - Mar 16 Coventry"}, {"@type": "Offer", "sku": "SQ0618983", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "3wks Thursdays  Apr 1 - Apr 15 Coventry"}, {"@type": "Offer", "sku": "SQ5714218", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "3wks Wednesdays May 12 - May 26 Coventry"}, {"@type": "Offer", "sku": "SQ7630533", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "3wks Mondays  - Jun 7  - Jun 21 Coventry"}]</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H5" t="n">
-        <v>15</v>
+        <v>150</v>
       </c>
       <c r="I5" t="n">
-        <v>15</v>
+        <v>150</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>SQ1654264, SQ1288994, SQ0063623, SQ6524101, SQ7078023, SQ3819844</t>
+          <t>SQ5616379, SQ3231903, SQ5559634, SQ0659870, SQ0358019, SQ0618983, SQ5714218, SQ7630533</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>SQ1654264</t>
+          <t>SQ5616379</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>event</t>
-        </is>
-      </c>
-      <c r="M5" t="b">
-        <v>0</v>
-      </c>
-      <c r="N5" t="b">
-        <v>0</v>
+          <t>course</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>4 x 2hr Private Photography Classes - Face to Face Coventry</t>
+          <t>Beginners Portrait Photography Course - Coventry 11 Oct -25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4 × 2hr Private Photography Classes (Face to Face, Coventry)Summary - Private Photography Classes (Face to Face) - Key InformationLocation: Coventry (face to face)Format: Private 1-2-1 tuition, in personSessions: 4 × 2hr classes, scheduled to suit youAvailability: Mon–Fri, 9am–5pmValidity: Pay now, book dates later — you'll be sent a code to book your datesLevel: All levels, beginner to advancedDescription: A package of four private, face-to-face photography classes in Coventry — two hours each, tailored entirely to you and what you want to learn or improve.</t>
+          <t>Beginners Portrait Photography Course Location: 17A Spon Street, Coventry, CV1 3BA (Pay &amp; Display, or Skydome Multi-Storey, 15 Croft Rd, CV1 3LD)Duration: 1-day course, 9am–5pm (approx 1hr lunch)Participants: Max 4Start Dates: Portrait Photography CourseSaturday 11 Oct 2025 - CoventryLevel: BeginnerDescription: A 1-day portrait photography course suitable for any amateur who wants to learn the fundamentals — lighting, exposure, camera settings and composition.Equipment: A DSLR or mirrorless camera with manual exposure modes, and a good understanding of the basics of exposure, aperture, shutter speed and ISO. Ideally a zoom lens (50mm+) or a 50mm prime.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/17054018-4804-4c2d-ad29-c57cba809028/face+to+face+private+photography+classes.png</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/7d4f9092-b44c-4d74-b858-cc2bcf675b8b/portraits+class.png</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/four-private-photography-classes</t>
+          <t>https://www.alanranger.com/photography-services-near-me/beginners-portrait-photography-course</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1-2-1-private-lessons, photography-tuition</t>
+          <t>photography-classes, photography-courses</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ6583676", "price": "360.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "4 x 2hr sessions - weekday daytime", "priceSpecification": {"price": "360.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ2592535", "price": "195.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12"}]</t>
         </is>
       </c>
       <c r="G6" t="n">
         <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>360</v>
+        <v>195</v>
       </c>
       <c r="I6" t="n">
-        <v>360</v>
+        <v>195</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>SQ6583676</t>
+          <t>SQ2592535</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>SQ6583676</t>
+          <t>SQ2592535</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="M6" t="b">
-        <v>0</v>
-      </c>
-      <c r="N6" t="b">
-        <v>0</v>
+          <t>course</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BATSFORD Arboretum Autumn Photography Workshops 23 - 31 Oct</t>
+          <t>BLUEBELL WOODLANDS Photography - Warks - 20 Apr - 29 Apr</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Batsford Arboretum Photography Workshops in autumn. Enjoy the colour and expert photographic guidance | Half or One Day Sessions | Any Level and CameraSummaryLocation: Batsford Arboretum - GloucestershireDates: Fri 23 Oct – Sat 31 Oct 2026Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless CameraPhotography Workshop Event Batsford ArboretumDescription: For nearly fifteen years I've returned to Batsford Arboretum each autumn, and in that time I've come to know every corner of it — which spot works at which hour, where the light falls and the angles that turn one of Britain's finest tree collections into a photograph rather than a snapshot. This workshop is built on that knowledge. Open to all levels and any camera, it's a chance to photograph Batsford's autumn colour with someone who can put you in the right place at the right time, so you can spend your energy on the thing that actually matters: seeing.Because that's where this workshop really lives. We'll cover the technical setup — exposure, depth of field, the settings that give you control — but that's only the floor. The real work is learning to look: to compose with intention and move beyond the cliché shot everyone else comes home with, to find the close-up, the macro detail and the quiet abstract as readily as the wide vista, and above all to read light, texture and colour as a harmony rather than chasing the over-saturated "look how vivid this is" image. Colour handled with restraint and relationship will always outlast colour shouted.With small numbers and genuine one-to-one attention throughout, you'll have the time and space to slow down and work properly — and you can choose a half-day morning or afternoon session, or a full day in the colour. You'll leave not just with a set of strong autumn images, but with a way of seeing — light, texture and composition — that changes how you photograph colour, woodland and the natural world wherever you go next.Good to know: the workshop price includes entrance to the Arboretum. On the early morning session we have exclusive access before the gardens open to the public — the quiet best light of the day, with the place to ourselves. A grab-and-go breakfast is available from around 9:30am, and the café and outdoor snack bar are open through the day for lunch and refreshments, with toilets on site by the reception area.</t>
+          <t>Bluebell woodlands photography workshop - Choose a sunrise or mid-morning 4hr bluebell photography shoot or both sessions at this private bluebell woodland with exclusive accessSummaryLocation: Warwickshire (Near Stratford Upon Avon)Dates (are subject to the timing of the bluebell flowering and their peek display - you will be contacted nearer the time to consider alt-dates, please pick your initial first date choice but be flexible if nearer the time it needs to change)Tue-20-Apr-27Thu-22-Apr-27Sat-24-Apr-27Sun-25-Apr-27Tue-27-Apr-27Thu-29-Apr-274hrs - 5:45 am to 9:45 am or 10:30 am to 2:30 pmOR 1 day - 5:45 am to 2:30 pmBrunch between 9:45-10:30 (not included)Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details Bluebell WoodsDescription: This Bluebell Woodlands photography workshop gives you exclusive access to a private Warwickshire bluebell wood near Stratford-upon-Avon, open to all levels and any camera. For a few short weeks each spring the woodland floor turns into a sea of blue — and unlike the well-known public bluebell spots, this one is yours to photograph without the crowds, so you can slow right down and work the scene properly in soft woodland light, rather than grabbing the same shot everyone else takes.You choose how you shoot it. Pick a four-hour half-day session — sunrise (5:45am–9:45am) for soft, warm early light, or mid-morning (10:30am–2:30pm) for brighter colour — or book the full day (5:45am–2:30pm) to shoot both, with a brunch break in between (9:45–10:30, not included). Whichever you choose, the technical craft is the floor we build on — composition, depth of field, the settings that hold a carpet of blue in focus — but the real work is learning to see. Woodland is a beautifully chaotic subject, so we'll work on simplifying it into a frame with order and intention, on finding the intimate, close-up detail as readily as the wide woodland view, and on reading the soft spring light and the blue-and-green as a quiet harmony rather than chasing a loud, over-saturated bluebell cliché.It's a small group of no more than six, taught personally and pitched at exactly your level, with easy walks along the bluebell trails and one-to-one guidance throughout. Because bluebells wait for no one, dates flex to the flowering — you'll pick a first-choice date and I'll confirm the peak display nearer the time. You'll come away with a portfolio of atmospheric spring woodland images that feel like the place — and a calmer, more intentional way of seeing colour, light and detail that you can take anywhere.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1715155253660-I9BNV2CJV5TPWB56WH93/Batsford+Autumn+7.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707309659883-DPISYTNT0T584VPXCK39/bluebell+photography+workshops.jpg</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/batsford-arboretum-photography-workshops</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/bluebell-woodlands-photography-workshops</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - half-day photo workshops, - one day photo workshops, Landscape, Woodlands, autumn</t>
+          <t>'- half-day photo work..., - one day photo workshops, Landscape, Woodlands, Flowering</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ0818501", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Fri 23  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7647904", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Fri 23 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9436105", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Fri 23 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1204772", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Sat 24  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9290465", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Sat 24 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7375084", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Sat 24 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0264308", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Sun 25 Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9938663", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Sun 25 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0693365", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Sun 25 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3442432", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Thu 29  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8197555", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Thu 29 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9853668", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Thu 29 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0732756", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Fri 30  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ6382131", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Fri 30 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ4533936", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Fri 30 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ4668363", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Sat 31  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5203247", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Sat 31 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1249736", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Sat 31 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8599409", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Tue 20 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7560082", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Tue 20 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7443277", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Tue 20 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1660230", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Thu 22 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1568285", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Thu 22 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5411810", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Thu 22 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1318075", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Sat 24 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8270632", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Sat 24 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ4260038", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Sat 24 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ6145280", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Sun 25 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2267773", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Sun 25 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2428415", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Sun 25 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1102782", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Tue 27 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5885147", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Tue 27 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3102560", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Tue 27 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7100218", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Thu 29 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2446216", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Thu 29 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3086312", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Thu 29 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -852,1771 +812,1597 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>SQ0818501, SQ7647904, SQ9436105, SQ1204772, SQ9290465, SQ7375084, SQ0264308, SQ9938663, SQ0693365, SQ3442432, SQ8197555, SQ9853668, SQ0732756, SQ6382131, SQ4533936, SQ4668363, SQ5203247, SQ1249736</t>
+          <t>SQ8599409, SQ7560082, SQ7443277, SQ1660230, SQ1568285, SQ5411810, SQ1318075, SQ8270632, SQ4260038, SQ6145280, SQ2267773, SQ2428415, SQ1102782, SQ5885147, SQ3102560, SQ7100218, SQ2446216, SQ3086312</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>SQ0818501</t>
+          <t>SQ8599409</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>event</t>
         </is>
-      </c>
-      <c r="M7" t="b">
-        <v>0</v>
-      </c>
-      <c r="N7" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Monthly Pick N Mix Subscription | Interest Free Payment Plan</t>
+          <t>Professional Digital DSLR Camera Sensor Clean | Coventry</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Monthly Pick N Mix Subscription Package. 10% Discount on events/services for one year | Interest Free Payment Plan | Take events or lessons immediately |</t>
+          <t>Get a camera sensor clean in Coventry . Sensor checked and cleaned using professional equipment, swabs | Full Frame and Cropped Sensors | 24hr Turnaround</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/7c76925a-43b0-425c-995e-4f4e0190221c/Photography+Payment+Plan.png</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1522495201980-KD6BKH54J01HJR93XXR6/photography-support-Services-1.png</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/monthly-pick-n-mix-subscription</t>
+          <t>https://www.alanranger.com/photography-services-near-me/camera-sensor-clean</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>photography-classes, photography-courses, photography-workshops</t>
+          <t>photography-services</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ3248242", "price": "42.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "12 x £42 = £500"}, {"@type": "Offer", "sku": "SQ3113323", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "12 x £50 = £600"}, {"@type": "Offer", "sku": "SQ4824271", "price": "60.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "12 x £60 = £720"}, {"@type": "Offer", "sku": "SQ5162846", "price": "65.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "12 x £65 = £780"}, {"@type": "Offer", "sku": "SQ0960457", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "12 x £75 = £900"}, {"@type": "Offer", "sku": "SQ6021981", "price": "85.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "12 x £85 = £1020"}, {"@type": "Offer", "sku": "SQ3596605", "price": "100.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "12 x £100 = £1200"}, {"@type": "Offer", "sku": "SQ2188035", "price": "120.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "12 x £120 = £1440"}, {"@type": "Offer", "sku": "SQ5970824", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "12 x £150 = £1800"}, {"@type": "Offer", "sku": "SQ0439157", "price": "175.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "12 x £175 = £2100"}, {"@type": "Offer", "sku": "SQ9583245", "price": "200.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "12 x £200 = £2400"}, {"@type": "Offer", "sku": "SQ9424558", "price": "250.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "12 x £250 = £3000"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ5650040", "price": "30.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12"}]</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="I8" t="n">
-        <v>250</v>
+        <v>30</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>SQ3248242, SQ3113323, SQ4824271, SQ5162846, SQ0960457, SQ6021981, SQ3596605, SQ2188035, SQ5970824, SQ0439157, SQ9583245, SQ9424558</t>
+          <t>SQ5650040</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>SQ3248242</t>
+          <t>SQ5650040</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>product</t>
         </is>
-      </c>
-      <c r="M8" t="b">
-        <v>0</v>
-      </c>
-      <c r="N8" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BLUEBELL WOODLANDS Photography - Warks - 20 Apr - 30 Apr</t>
+          <t>DARTMOOR Photography Workshop - Landscapes - 3 days</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Bluebell woodlands photography workshop - Choose a sunrise or mid-morning 4hr bluebell photography shoot or both sessions at this private bluebell woodland with exclusive accessSummaryLocation: Warwickshire (Near Stratford Upon Avon)Dates (are subject to the timing of the bluebell flowering and their peek display - you will be contacted nearer the time to consider alt-dates, please pick your initial first date choice but be flexible if nearer the time it needs to change)Tue-20-Apr-27Wed-21-Apr-27Thu-22-Apr-27Fri-23-Apr-27Sat-24-Apr-27Sun-25-Apr-27Mon-26-Apr-27Tue-27-Apr-27Wed-28-Apr-27Thu-29-Apr-27Fri-30-Apr-274hrs - 5:45 am to 9:45 am or 10:30 am to 2:30 pmOR 1 day - 5:45 am to 2:30 pmBrunch between 9:45-10:30 (not included)Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details Bluebell WoodsDescription: This Bluebell Woodlands photography workshop gives you exclusive access to a private Warwickshire bluebell wood near Stratford-upon-Avon, open to all levels and any camera. For a few short weeks each spring the woodland floor turns into a sea of blue — and unlike the well-known public bluebell spots, this one is yours to photograph without the crowds, so you can slow right down and work the scene properly in soft woodland light, rather than grabbing the same shot everyone else takes.You choose how you shoot it. Pick a four-hour half-day session — sunrise (5:45am–9:45am) for soft, warm early light, or mid-morning (10:30am–2:30pm) for brighter colour — or book the full day (5:45am–2:30pm) to shoot both, with a brunch break in between (9:45–10:30, not included). Whichever you choose, the technical craft is the floor we build on — composition, depth of field, the settings that hold a carpet of blue in focus — but the real work is learning to see. Woodland is a beautifully chaotic subject, so we'll work on simplifying it into a frame with order and intention, on finding the intimate, close-up detail as readily as the wide woodland view, and on reading the soft spring light and the blue-and-green as a quiet harmony rather than chasing a loud, over-saturated bluebell cliché.It's a small group of no more than six, taught personally and pitched at exactly your level, with easy walks along the bluebell trails and one-to-one guidance throughout. Because bluebells wait for no one, dates flex to the flowering — you'll pick a first-choice date and I'll confirm the peak display nearer the time. You'll come away with a portfolio of atmospheric spring woodland images that feel like the place — and a calmer, more intentional way of seeing colour, light and detail that you can take anywhere.</t>
+          <t>Join me on this Landscape Dartmoor Photography Workshop - in the iconic woodlands, and landscape of Dartmoor TorsSummaryLocation: Dartmoor - South DevonDates: Fri 2nd - Sun 4th Apr 2027Participants: Max 4 (1 Car, transport between locations included)Fitness: 3. HardExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details DartmoorDescription: This is a 3-day, 2-night residential landscape photography workshop based around Dartmoor National Park in South Devon, open to all levels from beginner to advanced. Dartmoor is one of England's most atmospheric wild landscapes — a vast sweep of rugged open moor, dramatic granite tors, ancient stunted woodland and serene rivers running through hidden valleys — and across a weekend you'll learn to read and photograph this dramatic terrain in its ever-changing light.Over three days we range across the moor and its woodlands, working a variety of locations as the conditions dictate — from the sculptural granite tors and big moorland vistas to the mossy, otherworldly ancient woods and tumbling rivers. The focus is on three things that make a strong landscape image here: composing order from a wild, expansive scene, controlling exposure and depth of field across big tonal ranges, and timing your shoot to the moods of Dartmoor light, with optional sunrise and sunset shoots and evening picture reviews. Throughout, the emphasis isn't just on the grand vista but on learning to see it — composing with intention, working intimate detail as readily as the wide view, and reading light and weather as a harmony rather than chasing the obvious shot. Be prepared for some longer walks over rougher ground — this is a more demanding workshop that takes you to the moor's most rewarding spots.With a maximum of just four photographers, this is genuinely personal tuition — Alan plans each day around the season and the forecast, and sends a detailed location itinerary a few days ahead. Accommodation, breakfast and evening meals are included, so all you have to think about is your photography, and you'll come away with a varied portfolio of dramatic Dartmoor landscapes — moors, tors and ancient woodland — and the field craft to capture wild country anywhere. An extra night's accommodation is available the day before if required — please request in advance, subject to hotel availability.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707309659883-DPISYTNT0T584VPXCK39/bluebell+photography+workshops.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707237329064-99H533NMXCONH5J276LM/dartmoor+photography+workshop.jpg</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/bluebell-woodlands-photography-workshops</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/dartmoor-photography-landscape-workshop</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>'- half-day photo work..., - one day photo workshops, Landscape, Woodlands, Flowering</t>
+          <t>All Photography Workshops, - weekend residential photo workshops, Landscape</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8599409", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Tue 20 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7560082", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Tue 20 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7443277", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Tue 20 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8437523", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Wed 21 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8685603", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Wed 21 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1561078", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Wed 21 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1660230", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Thu 22 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1568285", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Thu 22 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5411810", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Thu 22 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5831738", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Fri 23 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3014350", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Fri 23 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5312475", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Fri 23 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1318075", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Sat 24 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8270632", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Sat 24 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ4260038", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Sat 24 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ6145280", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Sun 25 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2267773", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Sun 25 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2428415", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Sun 25 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ6117337", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Mon 26 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8500857", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Mon 26 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1516510", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Mon 26 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1102782", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Tue 27 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5885147", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Tue 27 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3102560", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Tue 27 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1465142", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Wed 28 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1264314", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Wed 28 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8706845", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Wed 28 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7100218", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Thu 29 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2446216", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Thu 29 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3086312", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Thu 29 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1353684", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Fri 30 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0574386", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Fri 30 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2004510", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Fri 30 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ5540434", "price": "875.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12"}]</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>99</v>
+        <v>875</v>
       </c>
       <c r="I9" t="n">
-        <v>150</v>
+        <v>875</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>SQ8599409, SQ7560082, SQ7443277, SQ8437523, SQ8685603, SQ1561078, SQ1660230, SQ1568285, SQ5411810, SQ5831738, SQ3014350, SQ5312475, SQ1318075, SQ8270632, SQ4260038, SQ6145280, SQ2267773, SQ2428415, SQ6117337, SQ8500857, SQ1516510, SQ1102782, SQ5885147, SQ3102560, SQ1465142, SQ1264314, SQ8706845, SQ7100218, SQ2446216, SQ3086312, SQ1353684, SQ0574386, SQ2004510</t>
+          <t>SQ5540434</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>SQ8599409</t>
+          <t>SQ5540434</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>event</t>
         </is>
-      </c>
-      <c r="M9" t="b">
-        <v>0</v>
-      </c>
-      <c r="N9" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Annual Pick N Mix Subscription | Interest Free Payment Plan</t>
+          <t>DORSET Landscape Photography Workshop Purbeck 3 days</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Make a one-off payment by bank transfer or through this to get 20% discount on events booked for 12 Months | Tailored Pick N Mix photography training plan</t>
+          <t>Join me on this 3-day/2-night fantastic Dorset Photography workshop along the Jurassic coastline of Dorset - PurbeckSummary - Dorset Landscape PhotographyLocation: DorsetDates: Fri 9th - Sun 11th Apr 2027 3 Days/2 Nights(Price includes B&amp;B and evening meal - Half Board)Participants: Max 4 (1 Car, transport between locations included)Fitness: 3. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details DorsetDescription: This is a 3-day, 2-night residential landscape photography workshop along the Jurassic Coast of Dorset, open to all levels from beginner to advanced. Dorset's Purbeck coastline is one of the UK's great seascape locations — a prehistoric, World Heritage shore of sculpted arches, sea stacks and folded cliffs, with the iconic Durdle Door and Lulworth Cove at its heart — and across a weekend you'll learn to photograph it in its best light.Based on the Purbeck coast, we work the area's finest locations — from Durdle Door, Man O'War and Lulworth Cove to Kimmeridge, Dancing Ledge, Mupe Bay and the ghost village of Tyneham. The focus is on three things that make a strong coastal image: composing rock, sea and sky into a balanced frame, using long exposure to turn the moving water into mood, and timing your shoot to the light and the tide. It's never prescriptive though — this varied coastline lends itself to any style, so whether you're drawn to classic seascapes, black and white or abstract, there's scope to follow your own creative vision; throughout, the emphasis is on learning to see, composing with intention and reading light and tone as a harmony rather than chasing the obvious shot. There are optional sunrise and sunset shoots and evenings for relaxed picture reviews.With a maximum of just four photographers, this is genuinely personal tuition — Alan plans each day around the tides, the season and the forecast, and sends a detailed location itinerary a few days ahead. B&amp;B accommodation and an evening meal are included, so all you have to think about for three days is your photography, and you'll come away with a portfolio of dramatic Jurassic Coast images and a real command of seascape and long-exposure technique. An extra night's accommodation is available the day before if required — please request in advance, subject to hotel availability.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/4c6bb1a6-8752-4aea-a250-484fb1acdf75/Photography+Payment+Plan.png</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714681245814-0QW8DK4XQ18FM0JLBXYN/Harry+Rocks+%2301+-+Mar+2024.jpg</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/annual-pick-n-mix-subscription</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/dorset-landscape-photography-workshop</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>photography-classes, photography-courses, photography-workshops</t>
+          <t>coastal, All Photography Workshops, - weekend residential photo workshops</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ0754560", "price": "1200.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "1 x £1200 = £1200"}, {"@type": "Offer", "sku": "SQ7502565", "price": "1500.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "1 x £1500 = £1500"}, {"@type": "Offer", "sku": "SQ1485137", "price": "2000.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "1 x £2000 = £2000"}, {"@type": "Offer", "sku": "SQ7001156", "price": "2500.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "1 x £2500 = £2500"}, {"@type": "Offer", "sku": "SQ2612014", "price": "3000.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "1 x £3000 = £3000"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ2754105", "price": "925.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12"}]</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>1200</v>
+        <v>925</v>
       </c>
       <c r="I10" t="n">
-        <v>3000</v>
+        <v>925</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>SQ0754560, SQ7502565, SQ1485137, SQ7001156, SQ2612014</t>
+          <t>SQ2754105</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>SQ0754560</t>
+          <t>SQ2754105</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="M10" t="b">
-        <v>0</v>
-      </c>
-      <c r="N10" t="b">
-        <v>0</v>
+          <t>event</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Quarterly Pick N Mix Subscription | Interest Free Payments</t>
+          <t>Fine Art Photography Prints - Canvas wrap-round - Multi Size</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Quarterly Pick N Mix Subscription Package. 15% Discount on events/services for one year | Interest Free Payment Plan | Take events or lessons immediately |</t>
+          <t>Fine Art Photography Prints - Canvas wrap-round creates a contemporary finish to your photo- available in seven sizes. Include in the image title when ordering</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/fbab50ee-2fe8-4fe9-8804-e691b883cf4b/Photography+Payment+Plan.png</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1572426141642-UH9GBUDOUFH8QMTUA0KA/cavas%2Bsizes.jpg</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/quarterly-pick-n-mix-subscription</t>
+          <t>https://www.alanranger.com/photography-services-near-me/fine-art-photography-prints-canvas</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>photography-classes, photography-courses, photography-workshops</t>
+          <t>print</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ4217445", "price": "250.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "4 x £250 = £1000"}, {"@type": "Offer", "sku": "SQ6277577", "price": "300.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "4 x £300 = £1200"}, {"@type": "Offer", "sku": "SQ7788516", "price": "350.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "4 x £350 = £1400"}, {"@type": "Offer", "sku": "SQ5124608", "price": "400.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "4 x 400 = £1600"}, {"@type": "Offer", "sku": "SQ2657628", "price": "500.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "4 x £500 = £2000"}, {"@type": "Offer", "sku": "SQ2267503", "price": "750.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "4 x £750 = £3000"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ0105911", "price": "135.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "16x12 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ4206024", "price": "177.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "24x16 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ0781804", "price": "219.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "30x20 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ3982814", "price": "306.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "36x24 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ8209269", "price": "336.65", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "40x30 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ7901040", "price": "414.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "48x36 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ7260825", "price": "459.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "60x40 Canvas Wrap Round"}]</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H11" t="n">
-        <v>250</v>
+        <v>135.95</v>
       </c>
       <c r="I11" t="n">
-        <v>750</v>
+        <v>459.95</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>SQ4217445, SQ6277577, SQ7788516, SQ5124608, SQ2657628, SQ2267503</t>
+          <t>SQ0105911, SQ4206024, SQ0781804, SQ3982814, SQ8209269, SQ7901040, SQ7260825</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>SQ4217445</t>
+          <t>SQ0105911</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>product</t>
         </is>
-      </c>
-      <c r="M11" t="b">
-        <v>0</v>
-      </c>
-      <c r="N11" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Beginners Photography Course | 3 Weekly Evening Classes</t>
+          <t>Fine Art Photography Prints - Unframed Prints - Multi Sizes</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Beginners Photography Course CoventrySummary - Camera Courses For Beginners - Key InformationLocation: 45 Hathaway Road, Coventry, CV4 9HWDuration: 3 × 2hr evening classes (19:00–21:00)Participants: Max 4Start Dates: Beginners Photography Course3wks Mondays - Oct 12 - Oct 26 Coventry3wks Wednesdays - Oct 14 - Oct 28 Coventry3wks Mondays - Nov 9 - Nov 23 Coventry3wks Tuesdays - Dec 1 - Dec 15 Coventry3wks Wednesdays - Jan 13 - Jan 27 Coventry3wks Thursdays - Jan 28 - Feb 11 Coventry3wks Tuesdays - Mar 2 - Mar 16 Coventry3wks Thursdays Apr 1 - Apr 15 Coventry3wks Wednesdays May 12 - May 26 Coventry3wks Mondays - Jun 7 - Jun 21 CoventryLevel: Beginner and NoviceDescription:A practical three-week evening course that takes you from Auto to confident manual control, built around your own camera.Week 1 is about getting off Auto for good — the exposure modes, then aperture, shutter speed and ISO, and how they work together as the exposure triangle, with practical assignments to put it into practice.Week 2 goes deeper into getting the exposure right: manual exposure, metering, reading the histogram, exposure compensation, stops and dynamic range, and bracketing — followed by a review of your assignment work.Week 3 moves on to focusing and depth of field, white balance, JPEG vs RAW, and the foundations of composition, finishing with a final assignment review.With a maximum of four people, you get genuine attention and plenty of room to ask questions, and you'll leave with a printed course book covering every topic to revisit at home. Beginner and novice friendly — just bring a DSLR or mirrorless camera with manual modes.What You'll Learn: How to get off Auto and use manual exposure, aperture, shutter speed and ISO; how focus works; and the foundations of composition to make stronger, more deliberate photos.Includes: A printed course book covering every topic, so you can revisit it all afterwards.Equipment: A DSLR or mirrorless camera with manual exposure modes.</t>
+          <t>Fine Art Photography Prints available in seven sizes. Giclee print on archival paper. Please include in the image title when ordering | Pro-Lab Printing</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/773443e9-940a-440b-9faa-14e22b8c4236/beginners+photography+classes+coventry.png</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707240002916-MMJ7CA3MX9HLO60532BO/fine+art+photography+prints.jpg</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/beginners-photography-course</t>
+          <t>https://www.alanranger.com/photography-services-near-me/fine-art-photography-prints-unframed</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>photography-classes, photography-courses</t>
+          <t>print</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ6875626", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "3wks Mondays - Oct 12 - Oct 26 Coventry"}, {"@type": "Offer", "sku": "SQ8844762", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "3wks Wednesdays - Oct 14 - Oct 28 Coventry"}, {"@type": "Offer", "sku": "SQ5616379", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "3wks Mondays - Nov 9 - Nov 23 Coventry"}, {"@type": "Offer", "sku": "SQ3231903", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "3wks Tuesdays - Dec 1 - Dec 15 Coventry"}, {"@type": "Offer", "sku": "SQ5559634", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "3wks Wednesdays - Jan 13 - Jan 27 Coventry"}, {"@type": "Offer", "sku": "SQ0659870", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "3wks Thursdays - Jan 28 - Feb 11 Coventry"}, {"@type": "Offer", "sku": "SQ0358019", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "3wks Tuesdays - Mar 2 - Mar 16 Coventry"}, {"@type": "Offer", "sku": "SQ0618983", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "3wks Thursdays  Apr 1 - Apr 15 Coventry"}, {"@type": "Offer", "sku": "SQ5714218", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "3wks Wednesdays May 12 - May 26 Coventry"}, {"@type": "Offer", "sku": "SQ7630533", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "3wks Mondays  - Jun 7  - Jun 21 Coventry"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ4872440", "price": "50.57", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "16x12 Print"}, {"@type": "Offer", "sku": "SQ0453600", "price": "95.78", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "24x16 Print"}, {"@type": "Offer", "sku": "SQ7485354", "price": "138.86", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "30x20 Print"}, {"@type": "Offer", "sku": "SQ0167262", "price": "161.38", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "36x24 Print"}, {"@type": "Offer", "sku": "SQ1664775", "price": "217.23", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "40x30 Print"}, {"@type": "Offer", "sku": "SQ0377820", "price": "305.05", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "48x36 Print"}, {"@type": "Offer", "sku": "SQ8780582", "price": "416.85", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "60x40 Print"}]</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H12" t="n">
-        <v>150</v>
+        <v>50.57</v>
       </c>
       <c r="I12" t="n">
-        <v>150</v>
+        <v>416.85</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>SQ6875626, SQ8844762, SQ5616379, SQ3231903, SQ5559634, SQ0659870, SQ0358019, SQ0618983, SQ5714218, SQ7630533</t>
+          <t>SQ4872440, SQ0453600, SQ7485354, SQ0167262, SQ1664775, SQ0377820, SQ8780582</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>SQ6875626</t>
+          <t>SQ4872440</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>course</t>
-        </is>
-      </c>
-      <c r="M12" t="b">
-        <v>0</v>
-      </c>
-      <c r="N12" t="b">
-        <v>0</v>
+          <t>product</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Intermediates Intentions Photography Project Course</t>
+          <t>4 x 2hr Private Photography Classes - Face to Face Coventry</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Six-month photography project and showcase your images in a public exhibition in WarwickshireLocation: 45 Hathaway Road, Tile Hill Village, Coventry, CV4 9HWDuration: 6-month project, 6 classesParticipants: Max 4Level: IntermediateDescription: Embark on a six-month photography project and showcase your images in a public exhibition in Warwickshire — a course designed to develop your intentions, vision and a coherent body of work.Equipment: A DSLR or mirrorless camera with manual exposure modes.</t>
+          <t>4 × 2hr Private Photography Classes (Face to Face, Coventry)Summary - Private Photography Classes (Face to Face) - Key InformationLocation: Coventry (face to face)Format: Private 1-2-1 tuition, in personSessions: 4 × 2hr classes, scheduled to suit youAvailability: Mon–Fri, 9am–5pmValidity: Pay now, book dates later — you'll be sent a code to book your datesLevel: All levels, beginner to advancedDescription: A package of four private, face-to-face photography classes in Coventry — two hours each, tailored entirely to you and what you want to learn or improve.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707220703945-94B0SK8PWUMOS78FTJMO/photography+project+-+intentions+photography+course.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/17054018-4804-4c2d-ad29-c57cba809028/face+to+face+private+photography+classes.png</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/intermediates-intentions-photography-project-course</t>
+          <t>https://www.alanranger.com/photography-services-near-me/four-private-photography-classes</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>photography-classes, photography-courses</t>
+          <t>1-2-1-private-lessons, photography-tuition</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9898707", "price": "400.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "priceSpecification": {"price": "400.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ6583676", "price": "360.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "4 x 2hr sessions - weekday daytime", "priceSpecification": {"price": "360.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>400</v>
+        <v>360</v>
       </c>
       <c r="I13" t="n">
-        <v>400</v>
+        <v>360</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>SQ9898707</t>
+          <t>SQ6583676</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>SQ9898707</t>
+          <t>SQ6583676</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>course</t>
-        </is>
-      </c>
-      <c r="M13" t="b">
-        <v>0</v>
-      </c>
-      <c r="N13" t="b">
-        <v>0</v>
+          <t>product</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DEVON Landscape Photography  Workshops - Various Dates</t>
+          <t>Framed Fine Art Photography Prints - Multiple Sizes</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Hartland Quay - Landscape Photography Devon Workshop - Join me for this photo workshop to the best coastal and dramatic parts of Devon.SummaryLocation: North Devon - Hartland QuayDates:Thu 25th 12:30 - Sun 28th 12:30 Feb 2027 - 4 Days/3 NightsFri 3rd Sep - Sun 5th Sep 2027 - 3 Days/2 NightsParticipants: Max 4Fitness: 2. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera, Tripod and ND Filters (tripod and filters can be provided)Photography Workshop Event Details DevonDescription: This is a multi-day residential landscape photography workshop based at Hartland Quay on the dramatic North Devon coast, open to all levels from beginner to advanced. Hartland Quay is one of the UK's most spectacular seascape locations — long slithers of rock formations running out into a fierce Atlantic tide — and it's the perfect base for learning seascape photography on a coastline that rewards drama, patience and timing.Across the workshop you'll photograph the classic Hartland Quay views and range out along some of the finest coast in the South West — from Bude and Clovelly to Welcombe Bay, Saunton Sands and Woolacombe. The focus is on the craft of seascape photography: composing a strong coastal frame, mastering long exposure to turn moving water and sky into mood, and timing your shoot to the light and the tide. But the technical side is only the floor — the real work is learning to see, composing with intention and reading light and tide as a harmony rather than chasing the obvious shot, working the intimate detail as readily as the grand vista. Each day follows that rhythm — optional sunrise and sunset shoots when the light is best, full days in the field with tuition, and evening photo reviews and editing sessions to sharpen your eye.With a maximum of just four photographers, this is genuinely personal tuition, and because the whole coast is tide- and light-dependent, Alan plans each day around the forecast and sends a detailed location itinerary a few days ahead. Tripods and ND filters can be lent if you don't yet own them, accommodation and breakfast are included, and you'll come away with a portfolio of dramatic Devon seascapes and a real command of long-exposure coastal technique. An extra night's accommodation is available the day before if required — please request in advance, subject to hotel availability.</t>
+          <t>Fine Art Photography Prints - Giclee Framed Prints available in four sizes. Black frame with white mount. Please include in the image title when ordering</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714299365471-K36RWNIKFNGJ4C70UEXB/Atlantic+Force.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707240165500-DB965TUR2FYMNEFPXS90/fine+art+photography+prints+-+framed.jpg</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/landscape-photography-devon-hartland-quay</t>
+          <t>https://www.alanranger.com/photography-services-near-me/framed-fine-art-photography-prints</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>coastal, All Photography Workshops, - weekend residential photo workshops</t>
+          <t>print</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ3856406", "price": "950.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Thu 25th 12:30 - Sun 28th 12:30 Feb 2027 - 4 Days/3 Nights"}, {"@type": "Offer", "sku": "SQ2516659", "price": "775.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Fri 3rd Sep - Sun 5th Sep 2027 - 3 Days/2 Nights"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ6825544", "price": "133.85", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "16x12 Print (with Frame 20x16)"}, {"@type": "Offer", "sku": "SQ3786581", "price": "191.50", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "24x16 Print (with Frame 30x20)"}, {"@type": "Offer", "sku": "SQ1355351", "price": "267.43", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "30x20 Print (with Frame 40x30)"}, {"@type": "Offer", "sku": "SQ0156134", "price": "356.90", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "36x24 Print (with Frame 48x36)"}]</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H14" t="n">
-        <v>775</v>
+        <v>133.85</v>
       </c>
       <c r="I14" t="n">
-        <v>950</v>
+        <v>356.9</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>SQ3856406, SQ2516659</t>
+          <t>SQ6825544, SQ3786581, SQ1355351, SQ0156134</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>SQ3856406</t>
+          <t>SQ6825544</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>event</t>
-        </is>
-      </c>
-      <c r="M14" t="b">
-        <v>0</v>
-      </c>
-      <c r="N14" t="b">
-        <v>0</v>
+          <t>product</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CHESTERTON WINDMILL Photography Workshops - Warwickshire</t>
+          <t>The Art of GARDEN PHOTOGRAPHY  - Coventry -  May and July</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Chesterton windmill is one of Warwickshire's most famous landmarks. Join me in a sunset landscape photography workshop and learn about composition and lightSummaryLocation: Warwickshire - ChestertonDates:Mon 5th Oct 2026 - 17:30 - 19:45Tue 13th May 2027 - 18:15 - 20:15Mon 10th May 2027 - 18:30 - 20:30Mon 6th Sep 2027 - 18:00 - 20:00Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details ChestertonDescription: This sunset landscape photography workshop is an evening shoot at Chesterton Windmill, one of Warwickshire's most iconic landmarks, open to all levels and any camera. A striking 17th-century tower windmill on its arched stone legs, standing alone on a hilltop for nearly 350 years, it's one of the most photogenic structures in the county — and this workshop is built around capturing it in the golden light of sunset and the long-exposure drama of the hour that follows, in a way that's genuinely your own rather than the postcard everyone already has.The technical craft is the floor we build on — exposure, depth of field, and setting up long exposures to draw movement out of cloud and sky as dusk falls. But the real work is learning to see this familiar landmark freshly: composing the windmill with intention against the sky and the rolling countryside, finding the unexpected angle and the intimate detail as readily as the wide hilltop vista, and reading the warm, directional light of sunset as a harmony to compose with rather than just a pretty backdrop to point at. As the colour builds and fades, you'll learn to design a frame where the light, the land and the windmill all work together.It's a small group of no more than six, taught personally and pitched at exactly your level, so whether you're new to landscape photography or refining your technique, you get real one-to-one guidance in the field. You'll come away with a set of atmospheric images of this famous Warwickshire landmark — golden-hour silhouettes and long-exposure skies — and a sharper, more intentional way of seeing light and composition that lets you photograph any landmark at its best.</t>
+          <t>Join us for an unforgettable journey into macro and abstract on this garden photography workshop. Secure your spot today and embark on a transformative learning experience in garden photography.SummaryLocation: Coventry - CV4Dates:Sun May 23rd 2027 - 15:00 - 17:00Sun Jul 11th 2027 - 15:00 - 17:00Participants: Max 4Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details Garden PhotographyDescription: This Garden Photography Workshop is an intimate afternoon in Alan's own private garden in Coventry — his personal creative studio, a space he knows intimately and tends with a photographer's eye — open to all levels and any camera. A garden is one of the richest and most overlooked subjects there is: get close and the flowers, foliage, structures and borders reveal endless macro, close-up and abstract images, and this relaxed half-day is all about learning to see them, then photograph them with intention.The technical craft is the floor we build on — getting sharp focus, using your lens for macro and close-up detail, and controlling exposure and depth of field — but the real work is learning to look. You'll be given four photography assignments with guidance notes that push you to experiment and vary your approach, from intimate macro to wider garden portraits, training your eye to find the abstract within the planting and to compose with real intention. Throughout, the emphasis is on reading colour, light and texture as a harmony — letting the flowers sing without tipping into the loud, over-saturated shot — so your images feel considered and your own, not the obvious bloom-in-the-middle snap. Image reviews and feedback on a large screen in the gazebo help you see what's working and why.Places are limited to just four, so this is genuinely personal tuition, with Alan on hand for settings, composition and one-to-one guidance the whole time — and tea, coffee and cake served throughout. You'll come away with your own portfolio of garden images, and a sharper, more intentional way of seeing detail, colour and light that changes how you photograph flowers and nature everywhere.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714682519866-NVMB6B7Q4F93DGOGPQIK/Moonlit+Chesterton.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1709974516534-UJBRDOK5RXR4QNLPTECD/_-677.jpg</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/photography-workshops-chesterton-windmill</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/garden-photography-workshop</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - half-day photo workshops, Landscape</t>
+          <t>All Photography Workshops, - half-day photo workshops, Flowering, Macro &amp; Abstract</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ0796814", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Mon 5th Oct 2026 - 17:30 - 19:45", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9554270", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Tue 13th Apr 2027 - 18:15 - 20:15", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5307067", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Mon 10th May 2027 - 18:30 - 20:30", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3572999", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Mon 6th Sep 2027 - 18:00 - 20:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ0939451", "price": "45.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Sun May 23rd 2027 - 15:00 - 17:00"}, {"@type": "Offer", "sku": "SQ3644687", "price": "45.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Sun Jul 11th 2027 - 15:00 - 17:00"}]</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H15" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="I15" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>SQ0796814, SQ9554270, SQ5307067, SQ3572999</t>
+          <t>SQ0939451, SQ3644687</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>SQ0796814</t>
+          <t>SQ0939451</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>event</t>
         </is>
-      </c>
-      <c r="M15" t="b">
-        <v>0</v>
-      </c>
-      <c r="N15" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>FAIRY GLEN and Fairy Falls Long Exposure Photography</t>
+          <t>Intermediates Intentions Photography Project Course</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>A magical gorge on the River Conwy at Betws-y-Coed. Fairy Glen and Fairy Falls provide an opportunity to practise long exposure photography on the magic of this river. Fairy Glen Betws-y-Coed Long Exposure Photography WorkshopSummaryLocation: Wales - Betws-y-CoedDates:Sat 6th Mar 2027 - 10:00 - 13:30Fri 14th May 2027 - 10:00 - 13:30 + Option for Anglesey Weekend WorkshopSat 9th Oct 2027 - 10:00 - 13:30Participants: Max 4Fitness: 2. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details Fairy GlenDescription: This Fairy Glen long exposure photography workshop takes you into one of Wales' most magical locations — a serene, secluded gorge where the River Conwy tumbles through the woods at Betws-y-Coed — and is open to all levels and any camera. Flowing water through a wooded gorge is the perfect subject for long exposure, and this half-day workshop is about more than the silky-water effect: it's about learning to see this enchanting place and make images of it that are calm, considered and your own, rather than the same shot everyone takes.The long-exposure craft is the floor we build on — setting up your tripod and filters, and calculating the right exposure time for the effect you want — but the real work is composition and seeing. Working two great locations within a couple of miles of each other, you'll learn to find order among the rocks, water and woodland, to compose the intimate detail as readily as the wider gorge, and to read the soft, dappled light and the natural greens and browns of the glen as a quiet harmony rather than chasing a loud, over-processed look. The aim is a photograph with mood and restraint — moving water that feels like the place actually feels.With a maximum of just four photographers, this is genuinely personal tuition, with Alan guiding each person through observation, shot design, shooting and image reviews at both locations. You'll come away with a set of atmospheric long-exposure images of one of Snowdonia's hidden gems — and a stronger, more intentional way of seeing moving water and woodland that you can take anywhere.</t>
+          <t>Six-month photography project and showcase your images in a public exhibition in WarwickshireLocation: 45 Hathaway Road, Tile Hill Village, Coventry, CV4 9HWDuration: 6-month project, 6 classesParticipants: Max 4Level: IntermediateDescription: Embark on a six-month photography project and showcase your images in a public exhibition in Warwickshire — a course designed to develop your intentions, vision and a coherent body of work.Equipment: A DSLR or mirrorless camera with manual exposure modes.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707214813724-6QPD5O2XJNRQNOEIRBXO/Fairy+Glen+Betws-y-Coed+Photography+Workshop.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707220703945-94B0SK8PWUMOS78FTJMO/photography+project+-+intentions+photography+course.jpg</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/long-exposure-photography-workshop-fairy-glen</t>
+          <t>https://www.alanranger.com/photography-services-near-me/intermediates-intentions-photography-project-course</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - half-day photo workshops, Landscape</t>
+          <t>photography-classes, photography-courses</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9080164", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Sat 6th Mar 2027 - 10:00 - 13:30"}, {"@type": "Offer", "sku": "SQ6636860", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Fri 14th May 2027 - 10:00 - 13:30"}, {"@type": "Offer", "sku": "SQ8778402", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Sat 9th Oct 2027 - 10:00 - 13:30"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9898707", "price": "400.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "priceSpecification": {"price": "400.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>125</v>
+        <v>400</v>
       </c>
       <c r="I16" t="n">
-        <v>125</v>
+        <v>400</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>SQ9080164, SQ6636860, SQ8778402</t>
+          <t>SQ9898707</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>SQ9080164</t>
+          <t>SQ9898707</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>event</t>
-        </is>
-      </c>
-      <c r="M16" t="b">
-        <v>0</v>
-      </c>
-      <c r="N16" t="b">
-        <v>0</v>
+          <t>course</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>LAVENDER FIELD Photography Workshop - Glouc or Warks July</t>
+          <t>LAKE DISTRICT Photography Workshops - 3 Days in Cumbria</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Join me in the Cotswolds, or Warwickshire for a spectacular lavender field landscape workshop . Photograph in the evening hours by arrangement of owners (date is subject to change or weather on the day) Price includes entry fee of £30 for either of the lavender farmsSummaryLocation: Snowshill - Gloucestershire or Bubbenhall · Warwickshire, Lavender FarmsDates:Sat 3rd Jul 2027 - 18:00 20:45Sat 10th Jul 2027 - 18:00 20:45Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and Tripod (tripod available to borrow)Photography Workshop Event Details LavenderDescription: This Lavender Photography Workshop is a magical evening among the lavender rows of the Cotswolds at Snowshill in Gloucestershire or depending on arrangements at Warwickshire Lavender Farm, Bubbenhall — open to all levels and any camera. Best of all, you'll photograph the fields after the farm has closed to the general public, so instead of working around coachloads of day-trippers you have the spectacular sea of purple and the wildflower areas largely to yourselves — making it far easier to slow down, see properly and compose clean shots as the light softens towards sunset and the colour comes alive.A field of lavender is seductive but deceptively hard — it's all too easy to come home with the loud, over-saturated purple shot everyone takes. The real work here is learning to see past that. The technical craft is the floor we build on — focusing and exposing accurately in fading light, and holding both shadow and highlight as the sun drops — but the focus is on composing with intention: finding order and a lead-in through the endless rows, working the intimate, abstract close-up of colour and texture as readily as the sweeping vista, and treating the purple, the green and the warm evening light as a harmony to balance rather than a colour to crank. The aim is a photograph with mood and restraint — one that feels like that quiet evening in the field.It's a small group of no more than six, taught personally and pitched at exactly your level, with one-to-one guidance throughout. With the crowds gone and the fields quiet, you'll have the space and time to really work your compositions — and you'll come away with a portfolio of vivid lavender images at their most atmospheric, plus a sharper, more intentional way of seeing colour, light and detail that you can take anywhere. This is a special after-hours session: the farm opens to us beyond its normal public hours so we can shoot from 5p/6pmm into the early sunset light 9/9:30pm, and your workshop fee includes that commercial after-hours access. Please note the dates and finish times are set by the lavender farm rather than by Alan, and may be subject to change with the season, flowering and weather as they do not extend the hours if rain is forecast on the day, so you need to be flexible and be able to swap to an alternative Saturday evening that the farm has extended hours. Usually the first 3 Saturdays of July.</t>
+          <t>An exciting 3 day/2 night residential lake district photography workshop visiting some gorgeous spots around Cumbria. Runs every Jan, Mar, Sep, NovSummaryLocation: Cumbria - Lake DistrictDates:Fri 13 Nov - Sun 15 Nov - 3 Days/2 Nights 2026Fri 22 Jan - Sun 24 Jan - 3 Days/2 Nights 2027Fri 24 Sep - Sun 26 Sep - 3 Days/2 Nights 2027Extra night B&amp;B available for Thu - Contact me for details and booking separatelyParticipants: Max 4 (1 Car, transport between locations included)Fitness: 2. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details Lake DistrictDescription: This is a 3-day, 2-night residential Lake District photography workshop, based in the north lakes and open to all levels from beginner to advanced. The Lake District has been a favourite of landscape photographers for decades, and for good reason: nowhere else in England packs in such variety — mountains, tarns, ancient woodland, waterfalls and reflective lakes — and the changeable Cumbrian weather means it's never the same place twice. Misty mornings, atmospheric light, stormy skies and quiet reflections can all arrive within a single weekend.Over three days we shoot the iconic scenes at their best, basing ourselves in the north lakes and working two to three carefully chosen locations a day — from Derwent Water, Castlerigg and Ashness Bridge to the tarns and valleys of Langdale, Coniston and Buttermere. The rhythm follows the light: optional sunrise shoots, full days on location with tuition in the field, and optional sunset sessions, with evenings for relaxed picture reviews over a meal. Throughout, the emphasis isn't just on being at the famous viewpoint but on learning to see it — composing with intention, working intimate detail as readily as the grand vista, and reading light and weather as a harmony rather than chasing the obvious shot. You'll come away with a portfolio of dramatic Lakeland images and the field craft to read light and weather anywhere.With a maximum of just four photographers, this is genuinely personal tuition — Alan plans each day around the group, the season and the forecast, sends a detailed location itinerary a few days ahead, and adapts on the ground to chase the best conditions. Accommodation and breakfast are included, so you can switch off from the logistics and focus entirely on your photography for three days. Extra night B&amp;B available for Thursday — contact me for details and booking separately.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714572933715-EIVNF6O80HEJCSEU5D4U/lavender+sprint.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714301696717-TME057MTL131H9UHU82H/Bassenthwaite+Rise.jpg</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/photography-workshops-lavender-fields</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/lake-district-photography-workshop</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - half-day photo workshops, Flowering, Landscape</t>
+          <t>All Photography Workshops, - weekend residential photo workshops, Landscape</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ6748367", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Sat 3rd Jul 2027 - 18:00 20:45"}, {"@type": "Offer", "sku": "SQ7542811", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Sat 10th Jul 2027 - 18:00 20:45"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ5158309", "price": "1075.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Fri 13 Nov - 15 Nov - 3 Days 2026", "priceSpecification": {"price": "1075.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9016326", "price": "1075.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Fri 22 Jan - 24 Jan - 3 Days 2027"}, {"@type": "Offer", "sku": "SQ9100538", "price": "1075.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Fri 24 Sep - 26 Sep - 3 Days 2027", "priceSpecification": {"price": "1075.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H17" t="n">
-        <v>150</v>
+        <v>1075</v>
       </c>
       <c r="I17" t="n">
-        <v>150</v>
+        <v>1075</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>SQ6748367, SQ7542811</t>
+          <t>SQ5158309, SQ9016326, SQ9100538</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>SQ6748367</t>
+          <t>SQ5158309</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>event</t>
         </is>
-      </c>
-      <c r="M17" t="b">
-        <v>0</v>
-      </c>
-      <c r="N17" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Poppy Fields Photography Workshops | Worcestershire</t>
+          <t>PEAK DISTRICT Photography Workshops - 1 Day Padley Gorge</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Poppy fields photography workshop - Choose a sunrise or sunset 2.5hrs photo workshop at amazing poppy fields in Worcestershire | Seasonal DependantSummaryLocation: WorcestershireDates: (dates are subject to change based on when the poppy fields flower in June)8th Jun 19:15 - 21:459th Jun 05:00 - 07:30Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: PoppiesDescription: There are few sights in the English summer to beat rolling Worcestershire hills washed red with wild poppies, and this Poppy Fields Photography Workshop is built to catch them at their fleeting best. Open to all levels and any camera, it runs as short, focused sessions at the golden hours of sunset and sunrise — the two times of day when low, warm light makes a field of poppies truly glow.A field of red is more seductive than it is easy, and the work is learning to turn it into a photograph rather than a snapshot. The focus is on three things: composing with intention to find order and a lead-in through a busy, repeating scene, controlling exposure and depth of field to decide what's sharp and what dissolves into colour, and reading light, texture and colour as a harmony — letting the reds sing without tipping into the over-saturated cliché. You'll work both the intimate, single-stem detail and the sweeping vista, and learn to see past the obvious shot everyone else takes.It's a small group of no more than six, taught personally and pitched at exactly your level, with one-to-one guidance in the field throughout. Whether you join the sunset session, the dawn one, or both, you'll come away with a portfolio of poppy-field images at their most atmospheric — and a stronger way of seeing colour, light and composition that carries into everything you photograph next. Please note that poppies bloom briefly and unpredictably each June, so both the exact dates and the field we use are confirmed at short notice once the flowering is at its best. A flexible approach is essential — but it's exactly what lets us photograph the poppies at their absolute peak.</t>
+          <t>Join me in the Peak District in Hope Valley. Padley Gorge and Bolehill Quarry throughout the year on Peak District photography workshops | All levels welcomeSummaryLocation: Peak District - DerbyshireDates: Sat 17th Oct 2026 - 09:30 - 16:00Sun 1st Nov 2026 - 09:30 - 16:00Sat 7th Nov 2026 - 09:30 - 16:00Sat 22nd May 2027 - 09:30 - 16:00Participants: Max 6Fitness: 3. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Padley Gorge And Bolehill QuarryDescription: This Peak District photography workshop is a full day in the heart of Derbyshire's Hope Valley, open to all levels from beginner to advanced. It's built around two of the area's most rewarding and contrasting locations — the wooded, water-filled drama of Padley Gorge in the morning and the rugged, sculptural landscape of Bolehill Quarry in the afternoon — so in a single day you photograph two completely different faces of the Peak District, and learn to read each one rather than just point a camera at it.The morning at Padley Gorge — a deep, tree-lined valley with the Burbage Brook tumbling through it — is all about slowing down and seeing: simplifying a busy woodland scene into intimate close-ups of rock, moss and water, finding the quiet order in the chaos, and using long exposure to draw movement out of the brook. The afternoon at Bolehill Quarry opens out to the heights of Millstone Edge and silver birch woodland, where the work shifts to composing the bigger landscape. Across both, the technical craft is the floor we build on — exposure, depth of field, the settings that give you control — but the real lesson is learning to see: composing with intention, working close-up detail as readily as the wide vista, and reading light, texture and colour as a harmony rather than chasing the loud, obvious shot.We meet at the Grindleford Railway Café, where you can grab an optional pre-shoot breakfast before we head into the gorge. Lunch is back at the café halfway through — buy on the day or bring your own — before a short drive over to Bolehill for the afternoon session. Taught personally in a small group, this is hands-on, on-location tuition pitched at exactly your level, with Alan beside you in the field throughout; a detailed itinerary is sent a few days ahead, adjusted for the season and forecast, so you'll come away with a varied portfolio of Peak District images and a sharper, more intentional way of seeing landscape anywhere.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714575407530-MBS3PUSXD9GGHA68754C/poppy+dawn.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1709626967694-M4DJSC9GYR1R1LZFYBUF/Padley+Gorge+%2304+-+Mar+2024.jpg</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/poppy-fields-photography-workshops</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/landscape-peak-district-photography-workshops-derbyshire</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - half-day photo workshops</t>
+          <t>All Photography Workshops, - one day photo workshops, Landscape, Woodlands</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8740143", "price": "95.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Sat 8 Jun 19:15-21:45"}, {"@type": "Offer", "sku": "SQ7189877", "price": "95.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Sun 9 Jun 05:00-07:30"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ3794821", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Padley and Bolehill Sat 17th Oct  2026 09:30am - 4:00pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8457424", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Padley and Bolehill Sun 1st Nov  2026 09:30am - 4:00pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9037810", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Padley and Bolehill Sat 7th Nov  2026 09:30am - 4:00pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2363666", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Padley and Bolehill Sat 22nd May 2027 - 09:30 - 16:00", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H18" t="n">
-        <v>95</v>
+        <v>150</v>
       </c>
       <c r="I18" t="n">
-        <v>95</v>
+        <v>150</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>SQ8740143, SQ7189877</t>
+          <t>SQ3794821, SQ8457424, SQ9037810, SQ2363666</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>SQ8740143</t>
+          <t>SQ3794821</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>event</t>
         </is>
-      </c>
-      <c r="M18" t="b">
-        <v>0</v>
-      </c>
-      <c r="N18" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BURNHAM ON SEA Long Exposure Photography Workshop 8 May</t>
+          <t>DEVON Landscape Photography Workshop - 4 Days Hartland Quay</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Seascape and Long Exposure Photography workshop at this iconic location in Somerset with the lighthouse at Burnham on SeaSummaryLocation: Somerset - Burnham On SeaDates: Sat 8th May 2027 - 18:30 - 21:00Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details BurnhamDescription: This Burnham on Sea long exposure photography workshop is an evening on the Somerset coast built around one of the most photogenic subjects in the country — the town's iconic nine-legged lighthouse, standing on stilts on the open beach. Open to all levels and any camera, it's about the art of long exposure: not just the silky-water effect, but learning to see this minimalist coast and make images of it that are calm, considered and your own, rather than the same shot everyone takes.The long-exposure craft is the floor we build on, and we'll cover it properly — setting up, calculating shutter times and using filters — before heading onto the beach to shoot on an incoming tide as the sun sets. But the real work is composition and seeing. As the light builds you'll learn to place the lighthouse with real intention in a clean, minimalist frame, to work the intimate detail of stilts, reflections and wet sand as readily as the wide seascape, and to read the soft, shifting colour of a coastal sunset as a harmony rather than chasing a loud, over-saturated sky. The aim is mood and restraint — an image that feels like the quiet of that beach at dusk.It's a small group of no more than six, taught personally and pitched at exactly your level, with Alan on hand throughout for settings, composition and one-to-one guidance in the field. Whether long exposure is new to you or you're refining your technique, you'll come away with a set of atmospheric sunset images of this famous Somerset landmark — and a sharper, more intentional way of seeing light, movement and mood that you can take to any coast.</t>
+          <t>Hartland Quay - Landscape Photography Devon Workshop - Join me for this photo workshop to the best coastal and dramatic parts of Devon.SummaryLocation: North Devon - Hartland QuayDates:Thu 25th 12:30 - Sun 28th 12:30 Feb 2027 - 4 Days/3 NightsParticipants: Max 4 (1 Car, transport between locations included)Fitness: 2. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera, Tripod and ND Filters (tripod and filters can be provided)Photography Workshop Event Details DevonDescription: This is a multi-day residential landscape photography workshop based at Hartland Quay on the dramatic North Devon coast, open to all levels from beginner to advanced. Hartland Quay is one of the UK's most spectacular seascape locations — long slithers of rock formations running out into a fierce Atlantic tide — and it's the perfect base for learning seascape photography on a coastline that rewards drama, patience and timing.Across the workshop you'll photograph the classic Hartland Quay views and range out along some of the finest coast in the South West — from Bude and Clovelly to Welcombe Bay, Saunton Sands and Woolacombe. The focus is on the craft of seascape photography: composing a strong coastal frame, mastering long exposure to turn moving water and sky into mood, and timing your shoot to the light and the tide. But the technical side is only the floor — the real work is learning to see, composing with intention and reading light and tide as a harmony rather than chasing the obvious shot, working the intimate detail as readily as the grand vista. Each day follows that rhythm — optional sunrise and sunset shoots when the light is best, full days in the field with tuition, and evening photo reviews and editing sessions to sharpen your eye.With a maximum of just four photographers, this is genuinely personal tuition, and because the whole coast is tide- and light-dependent, Alan plans each day around the forecast and sends a detailed location itinerary a few days ahead. Tripods and ND filters can be lent if you don't yet own them, accommodation and breakfast are included, and you'll come away with a portfolio of dramatic Devon seascapes and a real command of long-exposure coastal technique. An extra night's accommodation is available the day before if required — please request in advance, subject to hotel availability.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714573609279-RSKP2ELI51B1VY87SOCS/Burnham+Still.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714299365471-K36RWNIKFNGJ4C70UEXB/Atlantic+Force.jpg</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/long-exposure-photography-workshops-burnham</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/landscape-photography-devon-hartland-quay</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>coastal, All Photography Workshops, - half-day photo workshops</t>
+          <t>coastal, All Photography Workshops, - weekend residential photo workshops</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9466277", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ3856406", "price": "950.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12"}]</t>
         </is>
       </c>
       <c r="G19" t="n">
         <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>99</v>
+        <v>950</v>
       </c>
       <c r="I19" t="n">
-        <v>99</v>
+        <v>950</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>SQ9466277</t>
+          <t>SQ3856406</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>SQ9466277</t>
+          <t>SQ3856406</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>event</t>
         </is>
-      </c>
-      <c r="M19" t="b">
-        <v>0</v>
-      </c>
-      <c r="N19" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>LAKE DISTRICT Photography Workshops - Jan - Mar - Sep - Nov</t>
+          <t>NORFOLK Landscape Photography Workshop - 3 Days near Cromer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>An exciting 3 day/2 night residential lake district photography workshop visiting some gorgeous spots around Cumbria. Runs every Jan, Mar, Sep, NovSummaryLocation: Cumbria - Lake DistrictDates:Fri 13 Nov - Sun 15 Nov - 3 Days/2 Nights 2026Fri 22 Jan - Sun 24 Jan - 3 Days/2 Nights 2027Fri 12 Mar - Sun 14 Mar - 3 Days/2 Nights 2027Fri 24 Sep - Sun 26 Sep - 3 Days/2 Nights 2027Extra night B&amp;B available for Thu - Contact me for details and booking separatelyParticipants: Max 4Fitness: 2. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details Lake DistrictDescription: This is a 3-day, 2-night residential Lake District photography workshop, based in the north lakes and open to all levels from beginner to advanced. The Lake District has been a favourite of landscape photographers for decades, and for good reason: nowhere else in England packs in such variety — mountains, tarns, ancient woodland, waterfalls and reflective lakes — and the changeable Cumbrian weather means it's never the same place twice. Misty mornings, atmospheric light, stormy skies and quiet reflections can all arrive within a single weekend.Over three days we shoot the iconic scenes at their best, basing ourselves in the north lakes and working two to three carefully chosen locations a day — from Derwent Water, Castlerigg and Ashness Bridge to the tarns and valleys of Langdale, Coniston and Buttermere. The rhythm follows the light: optional sunrise shoots, full days on location with tuition in the field, and optional sunset sessions, with evenings for relaxed picture reviews over a meal. Throughout, the emphasis isn't just on being at the famous viewpoint but on learning to see it — composing with intention, working intimate detail as readily as the grand vista, and reading light and weather as a harmony rather than chasing the obvious shot. You'll come away with a portfolio of dramatic Lakeland images and the field craft to read light and weather anywhere.With a maximum of just four photographers, this is genuinely personal tuition — Alan plans each day around the group, the season and the forecast, sends a detailed location itinerary a few days ahead, and adapts on the ground to chase the best conditions. Accommodation and breakfast are included, so you can switch off from the logistics and focus entirely on your photography for three days. Extra night B&amp;B available for Thursday — contact me for details and booking separately.</t>
+          <t>Landscape Photography Workshop Norfolk - Coastal Photography Based Nr CromerSummary - Norfolk Photography WorkshopLocation: North Norfolk Coast - Cromer AreaDates: Fri 20th, 09:30am - Sun 22nd Nov 2026, 14:00 - 3 Days/2 NightsParticipants: Max 4 (1 Car, transport between locations included)Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: NorfolkDescription: This is a 3-day, 2-night residential landscape photography workshop on the beautiful North Norfolk coast, based near Cromer — open to all levels from beginner to advanced. North Norfolk is one of the most varied and atmospheric stretches of coastline in England, and across a long weekend you'll photograph everything from classic seafronts and groynes to wild estuaries, windmills and big skies, learning to read and capture this ever-changing coastal landscape in its best light.There really is something for everyone here, and over three days we work a rich variety of locations as the light and tides allow — the seafronts and groynes at Overstrand and Cromer, the atmospheric estuaries of Morston Quay and Blakeney Harbour with their abandoned boats and twisting creeks, and the beach huts, windmills, sand dunes and flint-cottage charm of Blakeney village. The focus is on three things that make a strong coastal image: composing order from busy, expansive scenes, mastering long exposure to draw movement out of sea, sky and water, and timing each shoot to the tides and the soft coastal light. There's even an optional boat trip to see the seals along the way.With a maximum of just four photographers, this is genuinely personal tuition — Alan plans each day around the season, the forecast and the tide times, and sends a detailed location itinerary a few days ahead. Accommodation and breakfast are included, so all you have to think about is your photography, and you'll come away with a varied portfolio of the North Norfolk coast — seascapes, estuaries, windmills and beach huts — and the field craft to read light, tide and weather on any shore. An extra night's accommodation is available the day before if required — please request in advance, subject to hotel availability.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714301696717-TME057MTL131H9UHU82H/Bassenthwaite+Rise.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/e301c931-8fdc-4ff0-bc78-618aea6241a1/Norfolk+Nov+2024+-+%2303.jpg</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/lake-district-photography-workshop</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/landscape-photography-workshop-norfolk</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - weekend residential photo workshops, Landscape</t>
+          <t>coastal, All Photography Workshops, - weekend residential photo workshops</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ5158309", "price": "1075.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Fri 13 Nov - 15 Nov - 3 Days 2026", "priceSpecification": {"price": "1075.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9016326", "price": "1075.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Fri 22 Jan - 24 Jan - 3 Days 2027"}, {"@type": "Offer", "sku": "SQ0142956", "price": "1125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Fri 12 Mar - 14 Mar - 3 Days 2027", "priceSpecification": {"price": "1125.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9100538", "price": "1075.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Fri 24 Sep - 26 Sep - 3 Days 2027", "priceSpecification": {"price": "1075.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8747213", "price": "1075.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12"}]</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
         <v>1075</v>
       </c>
       <c r="I20" t="n">
-        <v>1125</v>
+        <v>1075</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>SQ5158309, SQ9016326, SQ0142956, SQ9100538</t>
+          <t>SQ8747213</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>SQ5158309</t>
+          <t>SQ8747213</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>event</t>
         </is>
-      </c>
-      <c r="M20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N20" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Fine Art Photography Prints - Canvas wrap-round - Multi Size</t>
+          <t>ANGLESEY Landscape Photography Workshop -  3 days</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Fine Art Photography Prints - Canvas wrap-round creates a contemporary finish to your photo- available in seven sizes. Include in the image title when ordering</t>
+          <t>Join me for this exciting Anglesey landscape photography workshop, where we will shoot along the stunning coastline features to capture breathtaking vistas that showcase the natural beauty surrounding the shorelines and iconic lighthouses.Summary - Anglesey Photography WorkshopLocation: Wales - Anglesey IslandDates: Fri 14th May 15:00 - Sun 16th May 14:00, 2027Duration: 3 Days/2 NightsParticipants: Max 4 (1 Car, transport between locations included)Fitness: 2. Moderate (15-30 min walks)Experience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details Anglesey PhotographyDescription: This is a 3-day, 2-night residential landscape photography workshop on the iconic island of Anglesey, off the north-west coast of Wales, open to all levels from beginner to advanced. Anglesey's coastline is a photographer's dream — over 200 square miles ringed by sandy coves, working harbours, rocky headlands and three iconic lighthouses — and across a weekend you'll shoot it in the golden hours when its colour, light and sea views are at their most spectacular.We work the island's finest coastal locations — from Penmon Point's Trwyn Du Lighthouse and the Church in the Sea to South Stack, Llanddwyn Island and the strange, Martian-coloured landscape of Parys Mountain, once the world's largest copper mine. The focus is on three things that make a strong coastal landscape: composing sea, shore and sky into a balanced frame, working the golden-hour light at sunrise and sunset, and using long exposure to capture the movement of the Welsh sea. Throughout, the emphasis isn't just on the iconic view but on learning to see it — composing with intention, working intimate detail as readily as the wide vista, and reading colour and light as a harmony rather than chasing the obvious shot. The days follow the light — optional sunrise and sunset shoots, full days on location with tuition, and evenings for relaxed picture reviews.With a maximum of just four photographers and transport between locations included, this is genuinely personal, hassle-free tuition — Alan plans each day around the tides, the season and the forecast, and sends a detailed location itinerary a few days ahead. Accommodation and breakfast are included, so all you have to think about for three days is your photography, and you'll come away with a portfolio of dramatic Anglesey coastal images and the field craft to read light and sea anywhere. An extra night's accommodation is available the day before if required — please request in advance, subject to hotel availability.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1572426141642-UH9GBUDOUFH8QMTUA0KA/cavas%2Bsizes.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707225841274-TEMCPAEP5DHDVCBJP2RD/anglesey+photography+workshop.jpg</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/fine-art-photography-prints-canvas</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/landscape-photography-workshops-anglesey</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>print</t>
+          <t>coastal, Landscape, - weekend residential photo workshops</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ0105911", "price": "135.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "16x12 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ4206024", "price": "177.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "24x16 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ0781804", "price": "219.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "30x20 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ3982814", "price": "306.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "36x24 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ8209269", "price": "336.65", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "40x30 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ7901040", "price": "414.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "48x36 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ7260825", "price": "459.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "60x40 Canvas Wrap Round"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8503376", "price": "975.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12"}]</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>135.95</v>
+        <v>975</v>
       </c>
       <c r="I21" t="n">
-        <v>459.95</v>
+        <v>975</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>SQ0105911, SQ4206024, SQ0781804, SQ3982814, SQ8209269, SQ7901040, SQ7260825</t>
+          <t>SQ8503376</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>SQ0105911</t>
+          <t>SQ8503376</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="M21" t="b">
-        <v>0</v>
-      </c>
-      <c r="N21" t="b">
-        <v>0</v>
+          <t>event</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Fine Art Photography Prints - Unframed Prints - Multi Sizes</t>
+          <t>Lightroom Courses for Beginners Photo Editing - Coventry</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Fine Art Photography Prints available in seven sizes. Giclee print on archival paper. Please include in the image title when ordering | Pro-Lab Printing</t>
+          <t>For those who want to implement the best workflow for image management and all the dos and don'ts of post-production with these Photo Editing Classes with LightroomAdobe Lightroom Classic Courses for Beginners - CoventryLocation: 45 Hathaway Road, Coventry, CV4 9HWDuration: 3 × 2hr evening classes (19:00–21:00)Participants: Max 3Start Dates:Lightroom Editing CourseCoventry 3 wks - Mon 7 Sep - 21 Sep 2026Coventry 3 wks - Thu 12 Nov - 26 Nov 2026Coventry 3 wks - Tue 12 Jan - 26 Jan 2027Coventry 3 wks - Thu 6 May - 20 May 2027Level: BeginnersDescription: A practical three-week evening course that takes you from a messy photo library and untouched RAW files to a finished, repeatable Lightroom Classic workflow — working on your own laptop throughout.Week 1 is about getting organised: catalogues, importing, collections, keywords and star ratings, so you can find and manage your photos for good rather than losing them across folders.Week 2 moves on to global adjustments — reading the histogram, then exposure, white balance, contrast, tone curves and sharpening — the core develop tools that do most of the work on any image.Week 3 covers local adjustments — graduated and radial filters, adjustment brushes and spot removal — and pulling it together into a consistent, repeatable style across your photos.With a maximum of three people, you get real hands-on help on your own screen whenever you hit a problem, plus course notes for each module and practical assignments to work on between sessions. Beginners welcome — no editing experience needed; just bring a laptop with Adobe Lightroom Classic installed and an active subscription.Equipment: You will need a laptop with Adobe Lightroom Classic subscription and the App installed. Alan will provide you with a training Lightroom Library with images and use that to explain and then demonstrate the various tools.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707240002916-MMJ7CA3MX9HLO60532BO/fine+art+photography+prints.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/fe40a5e1-7fa2-4057-982e-555479b97022/Lightroom+courses+-+photo+editing+course.png</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/fine-art-photography-prints-unframed</t>
+          <t>https://www.alanranger.com/photography-services-near-me/lightroom-courses-for-beginners-coventry</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>print</t>
+          <t>photography-classes, photography-courses, photo editing, lightroom</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ4872440", "price": "50.57", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "16x12 Print"}, {"@type": "Offer", "sku": "SQ0453600", "price": "95.78", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "24x16 Print"}, {"@type": "Offer", "sku": "SQ7485354", "price": "138.86", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "30x20 Print"}, {"@type": "Offer", "sku": "SQ0167262", "price": "161.38", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "36x24 Print"}, {"@type": "Offer", "sku": "SQ1664775", "price": "217.23", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "40x30 Print"}, {"@type": "Offer", "sku": "SQ0377820", "price": "305.05", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "48x36 Print"}, {"@type": "Offer", "sku": "SQ8780582", "price": "416.85", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "60x40 Print"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ7526725", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Coventry 3 wks - Mon 7 Sep - 21 Sep 2026"}, {"@type": "Offer", "sku": "SQ6831161", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Coventry 3 wks - Thu 12 Nov - 26 Nov 2026"}, {"@type": "Offer", "sku": "SQ1021857", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Coventry 3 wks - Tue 12 Jan - 26 Jan 2027"}, {"@type": "Offer", "sku": "SQ3349262", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Coventry 3 wks - Thu 6 May - 20 May 2027"}]</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H22" t="n">
-        <v>50.57</v>
+        <v>150</v>
       </c>
       <c r="I22" t="n">
-        <v>416.85</v>
+        <v>150</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>SQ4872440, SQ0453600, SQ7485354, SQ0167262, SQ1664775, SQ0377820, SQ8780582</t>
+          <t>SQ7526725, SQ6831161, SQ1021857, SQ3349262</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>SQ4872440</t>
+          <t>SQ7526725</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="M22" t="b">
-        <v>0</v>
-      </c>
-      <c r="N22" t="b">
-        <v>0</v>
+          <t>course</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>PEAK DISTRICT Photography Workshops - May, Oct and Nov</t>
+          <t>KENILWORTH Sunset Long Exposure Photography Workshop</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Join me in the Peak District in Hope Valley. Padley Gorge and Bolehill Quarry throughout the year on Peak District photography workshops | All levels welcomeSummaryLocation: Peak District - DerbyshireDates: Sat 17th Oct 2026 - 09:30 - 16:00Sun 1st Nov 2026 - 09:30 - 16:00Sat 7th Nov 2026 - 09:30 - 16:00Sat 22nd May 2027 - 09:30 - 16:00Participants: Max 6Fitness: 3. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Padley Gorge And Bolehill QuarryDescription: This Peak District photography workshop is a full day in the heart of Derbyshire's Hope Valley, open to all levels from beginner to advanced. It's built around two of the area's most rewarding and contrasting locations — the wooded, water-filled drama of Padley Gorge in the morning and the rugged, sculptural landscape of Bolehill Quarry in the afternoon — so in a single day you photograph two completely different faces of the Peak District, and learn to read each one rather than just point a camera at it.The morning at Padley Gorge — a deep, tree-lined valley with the Burbage Brook tumbling through it — is all about slowing down and seeing: simplifying a busy woodland scene into intimate close-ups of rock, moss and water, finding the quiet order in the chaos, and using long exposure to draw movement out of the brook. The afternoon at Bolehill Quarry opens out to the heights of Millstone Edge and silver birch woodland, where the work shifts to composing the bigger landscape. Across both, the technical craft is the floor we build on — exposure, depth of field, the settings that give you control — but the real lesson is learning to see: composing with intention, working close-up detail as readily as the wide vista, and reading light, texture and colour as a harmony rather than chasing the loud, obvious shot.We meet at the Grindleford Railway Café, where you can grab an optional pre-shoot breakfast before we head into the gorge. Lunch is back at the café halfway through — buy on the day or bring your own — before a short drive over to Bolehill for the afternoon session. Taught personally in a small group, this is hands-on, on-location tuition pitched at exactly your level, with Alan beside you in the field throughout; a detailed itinerary is sent a few days ahead, adjusted for the season and forecast, so you'll come away with a varied portfolio of Peak District images and a sharper, more intentional way of seeing landscape anywhere.</t>
+          <t>Sunset landscape long exposure photography workshop shoots around Kenilworth Castle - Warwickshire - Various Dates | Long Exposures | Open to all levels| Book TodaySummaryLocation: Warwickshire - KenilworthDates:Mon 22 Mar 2027 - 18:00 - 20:00Wed 14 Apr 2027 - 18:30 - 20:30Wed 5 May 2027 - 18:00 - 20:00Wed 22 Sep 2027 - 17:45 - 19:45Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: KenilworthDescription: This Long Exposure Photography Workshop is an evening shoot around the floodlit ruins of Kenilworth Castle in Warwickshire, open to all levels and any camera. Once one of England's mightiest fortresses and Robert Dudley's Elizabethan palace, the castle makes a dramatic subject against a darkening sky — and this workshop is built around the magic of long exposure at dusk, when the fading light, the castle's silhouette and a slow shutter combine to create atmospheric images that capture a sense of place, not just a record of a building.The long-exposure craft is the floor we build on, and we'll cover it properly: calculating exposure times for the movement and mood you want, focusing and exposing confidently in low light, and balancing ISO, shutter and aperture as the light drops. But the real work is learning to see. As the sky changes you'll compose the castle with intention — finding the frame beyond the obvious silhouette, working detail and texture as readily as the grand wide view, and reading the interplay of fading light, floodlight and deep shadow as a harmony rather than a problem to fight. The aim is an image with mood and restraint, where every element earns its place.It's a small group of no more than six, taught personally and pitched at exactly your level, so whether long exposure is new to you or you're refining your technique, you get real one-to-one guidance in the field. You'll come away with a set of atmospheric long-exposure images of one of England's most romantic castles — and a sharper, more intentional way of seeing light, movement and mood after dark anywhere.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1709626967694-M4DJSC9GYR1R1LZFYBUF/Padley+Gorge+%2304+-+Mar+2024.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1712472502735-OHOKCDKMCP1BAMQ0JQUA/kenilworth+defenses.jpg</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/landscape-peak-district-photography-workshops-derbyshire</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/long-exposure-photography-kenilworth</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - one day photo workshops, Landscape, Woodlands</t>
+          <t>All Photography Workshops, - half-day photo workshops, Landscape</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ3794821", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Padley and Bolehill Sat 17th Oct  2026 09:30am - 4:00pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8457424", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Padley and Bolehill Sun 1st Nov  2026 09:30am - 4:00pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9037810", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Padley and Bolehill Sat 7th Nov  2026 09:30am - 4:00pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2363666", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Padley and Bolehill Sat 22nd May 2027 - 09:30 - 16:00", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ0932604", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Mon 22 Mar 2027 - 18:00 - 20:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1178418", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Wed 14 Apr 2027 - 18:30 - 20:30", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9140400", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Wed 5 May 2027 - 18:00 - 20:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8220723", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Wed 22 Sep 2027 - 17:45 - 19:45", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G23" t="n">
         <v>4</v>
       </c>
       <c r="H23" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="I23" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>SQ3794821, SQ8457424, SQ9037810, SQ2363666</t>
+          <t>SQ0932604, SQ1178418, SQ9140400, SQ8220723</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>SQ3794821</t>
+          <t>SQ0932604</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>event</t>
         </is>
-      </c>
-      <c r="M23" t="b">
-        <v>0</v>
-      </c>
-      <c r="N23" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Framed Fine Art Photography Prints - Multiple Sizes</t>
+          <t>FAIRY GLEN and Fairy Falls Long Exposure Photography</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Fine Art Photography Prints - Giclee Framed Prints available in four sizes. Black frame with white mount. Please include in the image title when ordering</t>
+          <t>A magical gorge on the River Conwy at Betws-y-Coed. Fairy Glen and Fairy Falls provide an opportunity to practise long exposure photography on the magic of this river. Fairy Glen Betws-y-Coed Long Exposure Photography WorkshopSummaryLocation: Wales - Betws-y-CoedDates:Sat 6th Mar 2027 - 10:00 - 13:30Fri 14th May 2027 - 10:00 - 13:30 + Option for Anglesey Weekend WorkshopSat 9th Oct 2027 - 10:00 - 13:30Participants: Max 4Fitness: 2. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details Fairy GlenDescription: This Fairy Glen long exposure photography workshop takes you into one of Wales' most magical locations — a serene, secluded gorge where the River Conwy tumbles through the woods at Betws-y-Coed — and is open to all levels and any camera. Flowing water through a wooded gorge is the perfect subject for long exposure, and this half-day workshop is about more than the silky-water effect: it's about learning to see this enchanting place and make images of it that are calm, considered and your own, rather than the same shot everyone takes.The long-exposure craft is the floor we build on — setting up your tripod and filters, and calculating the right exposure time for the effect you want — but the real work is composition and seeing. Working two great locations within a couple of miles of each other, you'll learn to find order among the rocks, water and woodland, to compose the intimate detail as readily as the wider gorge, and to read the soft, dappled light and the natural greens and browns of the glen as a quiet harmony rather than chasing a loud, over-processed look. The aim is a photograph with mood and restraint — moving water that feels like the place actually feels.With a maximum of just four photographers, this is genuinely personal tuition, with Alan guiding each person through observation, shot design, shooting and image reviews at both locations. You'll come away with a set of atmospheric long-exposure images of one of Snowdonia's hidden gems — and a stronger, more intentional way of seeing moving water and woodland that you can take anywhere.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707240165500-DB965TUR2FYMNEFPXS90/fine+art+photography+prints+-+framed.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707214813724-6QPD5O2XJNRQNOEIRBXO/Fairy+Glen+Betws-y-Coed+Photography+Workshop.jpg</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/framed-fine-art-photography-prints</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/long-exposure-photography-workshop-fairy-glen</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>print</t>
+          <t>All Photography Workshops, - half-day photo workshops, Landscape</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ6825544", "price": "133.85", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "16x12 Print (with Frame 20x16)"}, {"@type": "Offer", "sku": "SQ3786581", "price": "191.50", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "24x16 Print (with Frame 30x20)"}, {"@type": "Offer", "sku": "SQ1355351", "price": "267.43", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "30x20 Print (with Frame 40x30)"}, {"@type": "Offer", "sku": "SQ0156134", "price": "356.90", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "36x24 Print (with Frame 48x36)"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9080164", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Sat 6th Mar 2027 - 10:00 - 13:30"}, {"@type": "Offer", "sku": "SQ6636860", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Fri 14th May 2027 - 10:00 - 13:30"}, {"@type": "Offer", "sku": "SQ8778402", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Sat 9th Oct 2027 - 10:00 - 13:30"}]</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H24" t="n">
-        <v>133.85</v>
+        <v>125</v>
       </c>
       <c r="I24" t="n">
-        <v>356.9</v>
+        <v>125</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>SQ6825544, SQ3786581, SQ1355351, SQ0156134</t>
+          <t>SQ9080164, SQ6636860, SQ8778402</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>SQ6825544</t>
+          <t>SQ9080164</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="M24" t="b">
-        <v>0</v>
-      </c>
-      <c r="N24" t="b">
-        <v>0</v>
+          <t>event</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>NORTHUMBERLAND Photography Workshops - Mar 18 - 21</t>
+          <t>BURNHAM ON SEA Long Exposure Photography Workshop 8 May</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Exciting 4 day residential Northumberland Landscape Photography Workshops - Coastline Photography visiting the iconic spots on the Northumbrian coastSummaryLocation: Northumberland, LowickDates:Thu 18 Mar, 13:00 - Sun 21st Mar, 13:00 2027 - 4 Days/3 NightsParticipants: Max 4Fitness: 2. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodNorthumberland Photography Workshops Event Details NorthumberlandDescription: This is a 4-day, 3-night residential Northumberland photography workshop along one of the most dramatic coastlines in Britain, open to all levels from beginner to advanced. Northumberland has more castles than any English county — over seventy — and on this coast the great ones meet the sea: Bamburgh rising from its rocky outcrop, Lindisfarne silhouetted against the North Sea, Dunstanburgh ringed by the black boulders of Embleton Beach. It's a coastline made for photographers who want history, drama and big coastal light in one trip.Based on the Northumberland coast, we spend four days chasing the best conditions across its finest locations — Bamburgh, Dunstanburgh, Lindisfarne, Beadnell, Craster and more — and because it's the east coast, you can shoot both sunrise and sunset from the same stretch of shore. The focus is on three things that define great coastal photography here: composing castles and shoreline into a strong frame, mastering long exposure to turn tide and sky into mood, and working the magical light of sunrise and sunset over the Farne Islands and empty beaches. Throughout, the emphasis isn't just on the famous castle view but on learning to see it — composing with intention, working intimate detail as readily as the grand vista, and reading light and weather as a harmony rather than chasing the obvious shot.With a maximum of just four photographers, this is genuinely personal tuition, planned each day around the tides, the light and the forecast, with a detailed location itinerary sent a few days ahead. Across four days you'll shoot empty beaches at first light, iconic castles and long-exposure seascapes — and come away with a portfolio of dramatic Northumbrian coastal images and a real command of long-exposure and coastal technique. An extra night's accommodation is available the day before if required — please request in advance, subject to hotel availability.</t>
+          <t>Seascape and Long Exposure Photography workshop at this iconic location in Somerset with the lighthouse at Burnham on SeaSummaryLocation: Somerset - Burnham On SeaDates: Sat 8th May 2027 - 18:30 - 21:00Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details BurnhamDescription: This Burnham on Sea long exposure photography workshop is an evening on the Somerset coast built around one of the most photogenic subjects in the country — the town's iconic nine-legged lighthouse, standing on stilts on the open beach. Open to all levels and any camera, it's about the art of long exposure: not just the silky-water effect, but learning to see this minimalist coast and make images of it that are calm, considered and your own, rather than the same shot everyone takes.The long-exposure craft is the floor we build on, and we'll cover it properly — setting up, calculating shutter times and using filters — before heading onto the beach to shoot on an incoming tide as the sun sets. But the real work is composition and seeing. As the light builds you'll learn to place the lighthouse with real intention in a clean, minimalist frame, to work the intimate detail of stilts, reflections and wet sand as readily as the wide seascape, and to read the soft, shifting colour of a coastal sunset as a harmony rather than chasing a loud, over-saturated sky. The aim is mood and restraint — an image that feels like the quiet of that beach at dusk.It's a small group of no more than six, taught personally and pitched at exactly your level, with Alan on hand throughout for settings, composition and one-to-one guidance in the field. Whether long exposure is new to you or you're refining your technique, you'll come away with a set of atmospheric sunset images of this famous Somerset landmark — and a sharper, more intentional way of seeing light, movement and mood that you can take to any coast.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/eb76126f-7580-40f0-ac80-39b29897cdc7/Northumberland+-+March+2025+-+%2302.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714573609279-RSKP2ELI51B1VY87SOCS/Burnham+Still.jpg</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/coastal-northumberland-photography-workshops</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/long-exposure-photography-workshops-burnham</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>coastal, All Photography Workshops, - weekend residential photo workshops</t>
+          <t>coastal, All Photography Workshops, - half-day photo workshops</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8540187", "price": "1095.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "priceSpecification": {"price": "1095.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9466277", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12"}]</t>
         </is>
       </c>
       <c r="G25" t="n">
         <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>1095</v>
+        <v>99</v>
       </c>
       <c r="I25" t="n">
-        <v>1095</v>
+        <v>99</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>SQ8540187</t>
+          <t>SQ9466277</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>SQ8540187</t>
+          <t>SQ9466277</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>event</t>
         </is>
-      </c>
-      <c r="M25" t="b">
-        <v>0</v>
-      </c>
-      <c r="N25" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ANGLESEY Landscape Photography Workshop -  May 2027</t>
+          <t>Monthly Pick N Mix Subscription | £50 a Month, Interest-Free</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Join me for this exciting Anglesey landscape photography workshop, where we will shoot along the stunning coastline features to capture breathtaking vistas that showcase the natural beauty surrounding the shorelines and iconic lighthouses.Summary - Anglesey Photography WorkshopLocation: Wales - Anglesey IslandDates: Fri 14th May 15:00 - Sun 16th May 14:00, 2027Duration: 3 Days/2 NightsParticipants: Max 4 (1 Car, transport between locations included)Fitness: 2. Moderate (15-30 min walks)Experience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details Anglesey PhotographyDescription: This is a 3-day, 2-night residential landscape photography workshop on the iconic island of Anglesey, off the north-west coast of Wales, open to all levels from beginner to advanced. Anglesey's coastline is a photographer's dream — over 200 square miles ringed by sandy coves, working harbours, rocky headlands and three iconic lighthouses — and across a weekend you'll shoot it in the golden hours when its colour, light and sea views are at their most spectacular.We work the island's finest coastal locations — from Penmon Point's Trwyn Du Lighthouse and the Church in the Sea to South Stack, Llanddwyn Island and the strange, Martian-coloured landscape of Parys Mountain, once the world's largest copper mine. The focus is on three things that make a strong coastal landscape: composing sea, shore and sky into a balanced frame, working the golden-hour light at sunrise and sunset, and using long exposure to capture the movement of the Welsh sea. Throughout, the emphasis isn't just on the iconic view but on learning to see it — composing with intention, working intimate detail as readily as the wide vista, and reading colour and light as a harmony rather than chasing the obvious shot. The days follow the light — optional sunrise and sunset shoots, full days on location with tuition, and evenings for relaxed picture reviews.With a maximum of just four photographers and transport between locations included, this is genuinely personal, hassle-free tuition — Alan plans each day around the tides, the season and the forecast, and sends a detailed location itinerary a few days ahead. Accommodation and breakfast are included, so all you have to think about for three days is your photography, and you'll come away with a portfolio of dramatic Anglesey coastal images and the field craft to read light and sea anywhere. An extra night's accommodation is available the day before if required — please request in advance, subject to hotel availability.</t>
+          <t>Monthly Pick N Mix Subscription: your first year of photography development from £50 a month (£600 plan). 10% off courses, workshops and 1-to-1s, 4 quarterly 1-2-1 reviews and free Photography Academy membership for 12 months. Interest-free</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707225841274-TEMCPAEP5DHDVCBJP2RD/anglesey+photography+workshop.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/7c76925a-43b0-425c-995e-4f4e0190221c/Photography+Payment+Plan.png</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/landscape-photography-workshops-anglesey</t>
+          <t>https://www.alanranger.com/photography-services-near-me/monthly-pick-n-mix-subscription</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>coastal, Landscape, - weekend residential photo workshops</t>
+          <t>photography-classes, photography-courses, photography-workshops</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8503376", "price": "975.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ3113323", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "12 x £50 = £600"}, {"@type": "Offer", "sku": "SQ4824271", "price": "60.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "12 x £60 = £720"}, {"@type": "Offer", "sku": "SQ5162846", "price": "65.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "12 x £65 = £780"}, {"@type": "Offer", "sku": "SQ0960457", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "12 x £75 = £900"}, {"@type": "Offer", "sku": "SQ6021981", "price": "85.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "12 x £85 = £1020"}, {"@type": "Offer", "sku": "SQ3596605", "price": "100.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "12 x £100 = £1200"}]</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H26" t="n">
-        <v>975</v>
+        <v>50</v>
       </c>
       <c r="I26" t="n">
-        <v>975</v>
+        <v>100</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>SQ8503376</t>
+          <t>SQ3113323, SQ4824271, SQ5162846, SQ0960457, SQ6021981, SQ3596605</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>SQ8503376</t>
+          <t>SQ3113323</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>event</t>
-        </is>
-      </c>
-      <c r="M26" t="b">
-        <v>0</v>
-      </c>
-      <c r="N26" t="b">
-        <v>0</v>
+          <t>product</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>NANT MILL Woodlands and Waterfalls Photo Workshop 7 Jun</t>
+          <t>PEAK DISTRICT HEATHER Photography Workshops - 14-15 Aug</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Long exposures photography on the river and waterfalls that run through this enchanting woodland, secluded Welsh valley at Nant MillSummaryLocation: Wales - Wrexham - Nant MillDates: Sat 7th June 202510:30 am to 2 pmParticipants: Max 6Fitness: 2. Easy-ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Nant MillDescription: This Nant Mill long exposure photography workshop takes you into a secluded Welsh valley near Wrexham, where a river and its waterfalls tumble through enchanting ancient woodland — open to all levels and any camera. Flowing water in a quiet, leafy gorge is the perfect subject for long exposure, and this half-day workshop is about more than the silky-water effect: it's about learning to see this beautiful, tucked-away place and make images of it that are calm, considered and your own, rather than the same shot everyone takes.The long-exposure craft is the floor we build on — setting up your tripod and filters, and calculating the right exposure time for the effect you want — but the real work is composition and seeing. Working the river, falls and woodland together, you'll learn to find order among the rocks, water and trees, to compose the intimate, close-up detail as readily as the wider valley view, and to read the soft, dappled light and the natural greens and browns of this ancient wood as a quiet harmony rather than chasing a loud, over-processed look. The aim is a photograph with mood and restraint — moving water that feels the way the place actually feels.It's a small group of no more than six, taught personally and pitched at exactly your level, so whether long exposure is new to you or you're refining your technique you get real one-to-one guidance in the field. You'll come away with a set of atmospheric long-exposure images of one of North Wales' hidden gems — and a stronger, more intentional way of seeing moving water and woodland that you can take anywhere.</t>
+          <t>Join me for the Peak District heather displays over this iconic landscape in August - 4hr Heather Peak District Photography Workshops | All levels welcomeSummaryLocation: Peak District - Derbyshire/Staffordshire2027 - Sat 14th Aug 18:15 21:15 - Derbyshire Surprise View2027 - Sun 15th Aug 05:45 08:45 - Staffordshire - The RoachesParticipants: Max 6Fitness: 3. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details HeathersDescription: Every August the moors of the Peak District turn a spectacular purple as the heather comes into bloom, and this Peak District Heather Photography Workshop is your chance to capture that fleeting display at its very best — open to all levels and any camera. Run as short, focused sessions at the magic hours of sunrise and sunset, it pairs one of Britain's most iconic landscapes with its richest seasonal colour, and the low golden light that makes heather and gritstone glow.You can join either of two sessions, or both: a sunset shoot at Surprise View above Hathersage in Derbyshire — one of the finest viewpoints in the Peak, with sweeping heather foregrounds, the Mother Cap stone and famously dark skies — or a sunrise shoot among the dramatic gritstone of The Roaches, Hen Cloud and Ramshaw Rocks in Staffordshire, weathered into extraordinary shapes above a sea of purple moorland.A blaze of purple is more seductive than it is easy, and the real work is learning to see past the obvious. The technical craft is the floor we build on — controlling exposure to hold rich colour and a dramatic sky, and working quickly in the brief light of dawn and dusk — but the focus is on composing with intention: balancing the heather and the gritstone rock forms into a frame with order, working the intimate detail of bloom and weathered stone as readily as the wide moorland vista, and treating the purple, the gold and the low light as a harmony rather than a colour to crank. We shoot two to three locations each session as conditions allow, and the aim throughout is an image with mood and restraint — one that feels like that moor at first or last light.It's a small group of no more than six, taught personally and pitched at exactly your level, with one-to-one guidance in the field throughout. Whether you take the sunset, the sunrise or make a weekend of both, you'll come away with a portfolio of the Peak District's heather at its peak — and a sharper, more intentional way of seeing colour, light and landscape that you can take anywhere. If you're booking both sessions, please arrange your own overnight accommodation near The Roaches for the early sunrise shoot. Please also note this is a seasonal workshop tied to the heather bloom, so exact dates may shift slightly with the season.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/83fecb77-55e2-4a1b-b532-efa4213e832a/limbs.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1685361335026-KNDKR6D00CTPUASRDWDV/Surprise%2BView%2B2.jpg</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/landscape-photography-workshops-nant-mill</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/peak-district-heather-photography-workshop</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - half-day photo workshops, Landscape, Woodlands</t>
+          <t>All Photography Workshops, - half-day photo workshops, Landscape, Flowering</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ4568959", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ7900435", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "2027 - Sat 14th Aug 18:15 21:15 - Derbyshire Surprise View"}, {"@type": "Offer", "sku": "SQ4225053", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "2027 - Sun 15 Aug - The Roaches &amp; Ramshaw 05:45 - 08:45"}, {"@type": "Offer", "sku": "SQ8702063", "price": "200.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Both sessions - 14 and 15 Aug - sunset and sunrise"}]</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H27" t="n">
         <v>125</v>
       </c>
       <c r="I27" t="n">
-        <v>125</v>
+        <v>200</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>SQ4568959</t>
+          <t>SQ7900435, SQ4225053, SQ8702063</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>SQ4568959</t>
+          <t>SQ7900435</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>event</t>
         </is>
-      </c>
-      <c r="M27" t="b">
-        <v>0</v>
-      </c>
-      <c r="N27" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>KERRY - Southern Ireland Photography Workshop - Mar 2026</t>
+          <t>CHESTERTON WINDMILL Photography Workshops - Warwickshire</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Photograph amazing areas in South Kerry, Dingle, and Killarney National Park on this 5-day Ireland photography workshopSummaryLocation: Dingle and Killarney - Kerry Southern IrelandDates: Thu 5th - Mon 10th Mar 2026 - 5 Days/4 NightsParticipants: Max 4Fitness: 2. Easy-ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: DingleDescription: This is a 5-day, 4-night residential photography workshop in the south-west of Ireland — the longest and most immersive trip I run, based around Dingle and exploring some of the most beautiful country in Europe. Open to all levels and any camera, it takes in three extraordinary areas of County Kerry: the wild, sea-battered Dingle Peninsula, the dramatic coastline of South Kerry along the Skellig Ring, and the mountains, lakes and ancient woodland of Killarney National Park.The variety here is the gift and the challenge — mountains, lakes, waterfalls, woodland, coastline and rock formations, often within a single day — and five days gives us the time to do it justice. We'll cover the technical control you need, but the real focus is on learning to see: composing order and intention out of these vast, busy scenes, working close-up and intimate detail as readily as the grand vista, and reading light, weather and tide as a harmony rather than chasing the obvious postcard shot. Some stops are quick laybys to catch a fleeting moment; others we'll work slowly, waiting for the light and water to come good.With a maximum of just four photographers and five full days on the ground, this is genuinely personal tuition with the time to slow down and work properly — Alan plans each day around the season, the forecast and the tides, and sends a detailed itinerary ahead. You'll come away not just with a portfolio from one of Europe's great landscapes, but with a stronger way of seeing — light, composition and restraint — that will change how you photograph wherever you go next. An extra night's accommodation is available the day before if required — please request in advance, subject to hotel availability.</t>
+          <t>Chesterton windmill is one of Warwickshire's most famous landmarks. Join me in a sunset landscape photography workshop and learn about composition and lightSummaryLocation: Warwickshire - ChestertonDates:Mon 5th Oct 2026 - 17:30 - 19:45Tue 13th May 2027 - 18:15 - 20:15Mon 10th May 2027 - 18:30 - 20:30Mon 6th Sep 2027 - 18:00 - 20:00Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details ChestertonDescription: This sunset landscape photography workshop is an evening shoot at Chesterton Windmill, one of Warwickshire's most iconic landmarks, open to all levels and any camera. A striking 17th-century tower windmill on its arched stone legs, standing alone on a hilltop for nearly 350 years, it's one of the most photogenic structures in the county — and this workshop is built around capturing it in the golden light of sunset and the long-exposure drama of the hour that follows, in a way that's genuinely your own rather than the postcard everyone already has.The technical craft is the floor we build on — exposure, depth of field, and setting up long exposures to draw movement out of cloud and sky as dusk falls. But the real work is learning to see this familiar landmark freshly: composing the windmill with intention against the sky and the rolling countryside, finding the unexpected angle and the intimate detail as readily as the wide hilltop vista, and reading the warm, directional light of sunset as a harmony to compose with rather than just a pretty backdrop to point at. As the colour builds and fades, you'll learn to design a frame where the light, the land and the windmill all work together.It's a small group of no more than six, taught personally and pitched at exactly your level, so whether you're new to landscape photography or refining your technique, you get real one-to-one guidance in the field. You'll come away with a set of atmospheric images of this famous Warwickshire landmark — golden-hour silhouettes and long-exposure skies — and a sharper, more intentional way of seeing light and composition that lets you photograph any landmark at its best.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1710060195646-WLFJL2H358FJD4GKV1CP/Coumeenoole+Strand+2.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714682519866-NVMB6B7Q4F93DGOGPQIK/Moonlit+Chesterton.jpg</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/ireland-photography-workshops-dingle</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/photography-workshops-chesterton-windmill</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>coastal, All Photography Workshops, - weekend residential photo workshops</t>
+          <t>All Photography Workshops, - half-day photo workshops, Landscape</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ7419716", "price": "1595.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ0796814", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Mon 5th Oct 2026 - 17:30 - 19:45", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9554270", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Tue 13th Apr 2027 - 18:15 - 20:15", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5307067", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Mon 10th May 2027 - 18:30 - 20:30", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3572999", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Mon 6th Sep 2027 - 18:00 - 20:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H28" t="n">
-        <v>1595</v>
+        <v>50</v>
       </c>
       <c r="I28" t="n">
-        <v>1595</v>
+        <v>50</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>SQ7419716</t>
+          <t>SQ0796814, SQ9554270, SQ5307067, SQ3572999</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>SQ7419716</t>
+          <t>SQ0796814</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>event</t>
         </is>
-      </c>
-      <c r="M28" t="b">
-        <v>0</v>
-      </c>
-      <c r="N28" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>NORFOLK Landscape Photography Workshop  - Coastal 20 - 22 Nov</t>
+          <t>LAVENDER FIELD Photography Workshop - Glouc or Warks July</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Landscape Photography Workshop Norfolk - Coastal Photography Based Nr CromerSummary - Norfolk Photography WorkshopLocation: North Norfolk Coast - Cromer AreaDates: Fri 20th, 09:30am - Sun 22nd Nov 2026, 14:00 - 3 Days/2 NightsParticipants: Max 4Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: NorfolkDescription: This is a 3-day, 2-night residential landscape photography workshop on the beautiful North Norfolk coast, based near Cromer — open to all levels from beginner to advanced. North Norfolk is one of the most varied and atmospheric stretches of coastline in England, and across a long weekend you'll photograph everything from classic seafronts and groynes to wild estuaries, windmills and big skies, learning to read and capture this ever-changing coastal landscape in its best light.There really is something for everyone here, and over three days we work a rich variety of locations as the light and tides allow — the seafronts and groynes at Overstrand and Cromer, the atmospheric estuaries of Morston Quay and Blakeney Harbour with their abandoned boats and twisting creeks, and the beach huts, windmills, sand dunes and flint-cottage charm of Blakeney village. The focus is on three things that make a strong coastal image: composing order from busy, expansive scenes, mastering long exposure to draw movement out of sea, sky and water, and timing each shoot to the tides and the soft coastal light. There's even an optional boat trip to see the seals along the way.With a maximum of just four photographers, this is genuinely personal tuition — Alan plans each day around the season, the forecast and the tide times, and sends a detailed location itinerary a few days ahead. Accommodation and breakfast are included, so all you have to think about is your photography, and you'll come away with a varied portfolio of the North Norfolk coast — seascapes, estuaries, windmills and beach huts — and the field craft to read light, tide and weather on any shore. An extra night's accommodation is available the day before if required — please request in advance, subject to hotel availability.</t>
+          <t>Join me in the Cotswolds, or Warwickshire for a spectacular lavender field landscape workshop . Photograph in the evening hours by arrangement of owners (date is subject to change or weather on the day) Price includes entry fee of £30 for either of the lavender farmsSummaryLocation: Snowshill - Gloucestershire or Bubbenhall · Warwickshire, Lavender FarmsDates:Sat 3rd Jul 2027 - 18:00 20:45Sat 10th Jul 2027 - 18:00 20:45Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and Tripod (tripod available to borrow)Photography Workshop Event Details LavenderDescription: This Lavender Photography Workshop is a magical evening among the lavender rows of the Cotswolds at Snowshill in Gloucestershire or depending on arrangements at Warwickshire Lavender Farm, Bubbenhall — open to all levels and any camera. Best of all, you'll photograph the fields after the farm has closed to the general public, so instead of working around coachloads of day-trippers you have the spectacular sea of purple and the wildflower areas largely to yourselves — making it far easier to slow down, see properly and compose clean shots as the light softens towards sunset and the colour comes alive.A field of lavender is seductive but deceptively hard — it's all too easy to come home with the loud, over-saturated purple shot everyone takes. The real work here is learning to see past that. The technical craft is the floor we build on — focusing and exposing accurately in fading light, and holding both shadow and highlight as the sun drops — but the focus is on composing with intention: finding order and a lead-in through the endless rows, working the intimate, abstract close-up of colour and texture as readily as the sweeping vista, and treating the purple, the green and the warm evening light as a harmony to balance rather than a colour to crank. The aim is a photograph with mood and restraint — one that feels like that quiet evening in the field.It's a small group of no more than six, taught personally and pitched at exactly your level, with one-to-one guidance throughout. With the crowds gone and the fields quiet, you'll have the space and time to really work your compositions — and you'll come away with a portfolio of vivid lavender images at their most atmospheric, plus a sharper, more intentional way of seeing colour, light and detail that you can take anywhere. This is a special after-hours session: the farm opens to us beyond its normal public hours so we can shoot from 5p/6pmm into the early sunset light 9/9:30pm, and your workshop fee includes that commercial after-hours access. Please note the dates and finish times are set by the lavender farm rather than by Alan, and may be subject to change with the season, flowering and weather as they do not extend the hours if rain is forecast on the day, so you need to be flexible and be able to swap to an alternative Saturday evening that the farm has extended hours. Usually the first 3 Saturdays of July.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/e301c931-8fdc-4ff0-bc78-618aea6241a1/Norfolk+Nov+2024+-+%2303.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714572933715-EIVNF6O80HEJCSEU5D4U/lavender+sprint.jpg</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/landscape-photography-workshop-norfolk</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/photography-workshops-lavender-fields</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>coastal, All Photography Workshops, - weekend residential photo workshops</t>
+          <t>All Photography Workshops, - half-day photo workshops, Flowering, Landscape</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8747213", "price": "1025.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "priceSpecification": {"price": "1025.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ6748367", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Sat 3rd Jul 2027 - 18:00 20:45"}, {"@type": "Offer", "sku": "SQ7542811", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Sat 10th Jul 2027 - 18:00 20:45"}]</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H29" t="n">
-        <v>1025</v>
+        <v>150</v>
       </c>
       <c r="I29" t="n">
-        <v>1025</v>
+        <v>150</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>SQ8747213</t>
+          <t>SQ6748367, SQ7542811</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>SQ8747213</t>
+          <t>SQ6748367</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>event</t>
         </is>
-      </c>
-      <c r="M29" t="b">
-        <v>0</v>
-      </c>
-      <c r="N29" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Beginners Portrait Photography Course - Coventry 11 Oct -25</t>
+          <t>Online Photography Classes 121 - Zoom - Package Options</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Beginners Portrait Photography Course Location: 17A Spon Street, Coventry, CV1 3BA (Pay &amp; Display, or Skydome Multi-Storey, 15 Croft Rd, CV1 3LD)Duration: 1-day course, 9am–5pm (approx 1hr lunch)Participants: Max 4Start Dates: Portrait Photography CourseSaturday 11 Oct 2025 - CoventryLevel: BeginnerDescription: A 1-day portrait photography course suitable for any amateur who wants to learn the fundamentals — lighting, exposure, camera settings and composition.Equipment: A DSLR or mirrorless camera with manual exposure modes, and a good understanding of the basics of exposure, aperture, shutter speed and ISO. Ideally a zoom lens (50mm+) or a 50mm prime.</t>
+          <t>Private Online Photography Classes (Zoom)Summary - Private Online Photography Classes - Key InformationFormat: Online 1-2-1 via Zoom (free to use)Sessions: Single 1hr lesson, or discounted packages of 4, 6, 8 or 12 hoursAvailability: Standard Mon–Fri, 9am–5pm or Premium - Mon-Sun 9am -9pmValidity: Pay now, book dates later — use within 12 months of purchaseLevel: All levels, beginner to advancedDescription: Private online photography classes tailored to your needs — tuition and support on any aspect of photography, with no other students, so the time you pay for is dedicated entirely to your own style and pace.Equipment: Anything you want to learn or improve on. Sessions run over Zoom, with notes provided; submit images for detailed feedback between lessons.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/7d4f9092-b44c-4d74-b858-cc2bcf675b8b/portraits+class.png</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/4ac49e77-bfdc-435d-bf46-d82bda3bec91/online+photography+lessons.png</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/beginners-portrait-photography-course</t>
+          <t>https://www.alanranger.com/photography-services-near-me/private-online-photography-classes-zoom</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>photography-classes, photography-courses</t>
+          <t>1-2-1-private-lessons, photography-tuition</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ2592535", "price": "195.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ1461156", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Zoom Standard (Weekdays 9-5) - 1 x 1hr - Pay as you go    £50"}, {"@type": "Offer", "sku": "SQ5568703", "price": "170.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Zoom Standard (Weekdays 9-5) - 4 x 1hr (15% Off)          £170"}, {"@type": "Offer", "sku": "SQ6341100", "price": "240.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Zoom Standard (Weekdays 9-5) - 6 x 1hr (20% Off)          £240"}, {"@type": "Offer", "sku": "SQ2281758", "price": "300.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Zoom Standard (Weekdays 9-5) - 8 x 1hr (25% Off)          £300"}, {"@type": "Offer", "sku": "SQ2043258", "price": "450.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Zoom Standard (Weekdays 9-5) - 12 x 1hr (25% Off)         £450"}, {"@type": "Offer", "sku": "SQ6476466", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Zoom Premium (Eve/Weekend 9-9) - 1 x 1hr - Pay as you go  £75"}, {"@type": "Offer", "sku": "SQ4036849", "price": "255.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Zoom Premium (Eve/Weekend 9-9) - 4 x 1hr (15% Off)        £255"}, {"@type": "Offer", "sku": "SQ6369047", "price": "360.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Zoom Premium (Eve/Weekend 9-9) - 6 x 1hr (20% Off)        £360"}, {"@type": "Offer", "sku": "SQ7040572", "price": "450.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Zoom Premium (Eve/Weekend 9-9) - 8 x 1hr (25% Off)        £450"}, {"@type": "Offer", "sku": "SQ6714463", "price": "675.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Zoom Premium (Eve/Weekend 9-9) - 12 x 1hr (25% Off)       £675"}]</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H30" t="n">
-        <v>195</v>
+        <v>50</v>
       </c>
       <c r="I30" t="n">
-        <v>195</v>
+        <v>675</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>SQ2592535</t>
+          <t>SQ1461156, SQ5568703, SQ6341100, SQ2281758, SQ2043258, SQ6476466, SQ4036849, SQ6369047, SQ7040572, SQ6714463</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>SQ2592535</t>
+          <t>SQ1461156</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>course</t>
-        </is>
-      </c>
-      <c r="M30" t="b">
-        <v>0</v>
-      </c>
-      <c r="N30" t="b">
-        <v>0</v>
+          <t>product</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SUFFOLK Landscape Photography Workshops - 5th-7th Feb</t>
+          <t>Quarterly Pick N Mix Subscription | From £250 a Quarter</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Join us for an inspiring Suffolk landscape photography workshop, where you'll have the opportunity to create stunning long exposures during breathtaking sunrises and vibrant sunsets. We will explore picturesque quays, serene estuaries, intriguing piers, and tranquil marshes, all while capturing the beauty of charming beach huts and ancient woodlands. Emphasising artistic expression, we'll also delve into the world of black and white photography, allowing you to bring a classic touch to your coastal images.SummaryLocation: Suffolk - East Anglia / Southwold/Aldeburgh AreaDates: Fri 5th 09:30 - Sun 7th 14:30 Feb 2027 - 3 Days/2 NightsParticipants: Max 4 (1 Car, transport between locations included)Fitness: 2. Moderate (15-30 min walks)Experience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details SuffolkDescription: This is a 3-day, 2-night residential Suffolk landscape photography workshop based on the Southwold and Aldeburgh coast, open to all levels from beginner to advanced. The Suffolk coastline is one of England's most photogenic and most varied — wide shoreline vistas, big skies, and a wealth of subjects most coastlines can't match: weathered piers, painted beach huts, iconic sea-defence structures and the traditional sails of Herringfleet Windmill. It's a landscape that rewards photographers who slow down and learn to see it.The focus is on long exposure and the art of black and white photography — learning to compose a strong coastal frame, to use long exposures to smooth water and sky into mood, and to recognise when a scene works better in mono. It's about more than the technical craft, though: the real work is learning to see — composing with intention, working intimate detail as readily as the wide vista, and reading light and tone as a harmony rather than chasing the obvious shot. It's never prescriptive either: over three days and two to three locations a day — from Southwold and Walberswick to Dunwich, Orford and Aldeburgh — we work with whatever light and conditions the coast gives us, with early sunrise shoots, full days in the field with tuition, and evenings for relaxed picture reviews.With a maximum of just four photographers and transport between locations included, this is genuinely personal, hassle-free tuition — Alan plans each day around the group, the season, the tides and the forecast, and sends a detailed location itinerary a few days ahead. En-suite accommodation and breakfast are included, so all you have to think about for three days is your photography. You'll come away with a portfolio of atmospheric Suffolk coastal images and a real grasp of long exposure and black and white technique. An extra night is available the day before on request, ideal for those travelling from a distance — contact me to arrange.</t>
+          <t>Quarterly Pick N Mix Subscription: your first year of photography development from £250 a quarter (£1,000 plan). 12.5% off courses, workshops and 1-to-1s, 4 one-hour quarterly 1-2-1 reviews and free Photography Academy membership for 12 months. Interest-free</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714667523305-2SEM1T5WD278HHO4HJIV/Southwold+Sunrise.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/fbab50ee-2fe8-4fe9-8804-e691b883cf4b/Photography+Payment+Plan.png</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/suffolk-landscape-photography-workshops</t>
+          <t>https://www.alanranger.com/photography-services-near-me/quarterly-pick-n-mix-subscription</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>coastal, - weekend residential photo workshops</t>
+          <t>photography-classes, photography-courses, photography-workshops</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ2176971", "price": "995.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "priceSpecification": {"price": "995.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ4217445", "price": "250.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "4 x £250 = £1000"}, {"@type": "Offer", "sku": "SQ6277577", "price": "300.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "4 x £300 = £1200"}, {"@type": "Offer", "sku": "SQ7788516", "price": "350.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "4 x £350 = £1400"}, {"@type": "Offer", "sku": "SQ5124608", "price": "400.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "4 x 400 = £1600"}, {"@type": "Offer", "sku": "SQ2657628", "price": "500.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "4 x £500 = £2000"}]</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H31" t="n">
-        <v>995</v>
+        <v>250</v>
       </c>
       <c r="I31" t="n">
-        <v>995</v>
+        <v>500</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>SQ2176971</t>
+          <t>SQ4217445, SQ6277577, SQ7788516, SQ5124608, SQ2657628</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>SQ2176971</t>
+          <t>SQ4217445</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>event</t>
-        </is>
-      </c>
-      <c r="M31" t="b">
-        <v>0</v>
-      </c>
-      <c r="N31" t="b">
-        <v>0</v>
+          <t>product</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MACRO Photography Workshops Warwickshire - Various</t>
+          <t>RPS Courses - Independent RPS Mentoring for RPS Distinctions</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Abstract and Macro Photography Workshop . Learn about camera settings, lens use, controlling DoF and composition. Various Dates in Warwickshire | Half DaySummaryLocation: WarwickshireDates: Macro Photography WorkshopsMacro Photography - Sun Nov 28th 2026 - 10:30am - 12:30pmMacro Photography - Sat May 1st 2027 - 11am - 1pmMacro Photography - Sun Sep 29th 2027 - 4:00pm - 6:00pmParticipants: Max 4Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: Digital Camera and Tripod, Zoom or Macro LensMacro Photography Workshop Event Details: Macro Photography and AbstractDescription: This Abstract and Macro Photography Workshop takes place at a Warwickshire location and is open to all levels and any camera. Macro is where ordinary surroundings become extraordinary — get close and a tree trunk, a piece of weathered stone or a patch of water reveals shapes, colours, tones and patterns most people walk straight past. The whole session is about learning to see them, and then photograph them with intention.The technical craft matters here — and we'll cover it properly — but it's the floor, not the point. Working around the area together, Alan guides you through the settings that give you control: getting sharp focus and using a macro lens or zoom, controlling depth of field to isolate your subject, and building a composition with real intention. From there the real work begins — training your eye to find the abstract within the ordinary, to read tone, shadow and highlight, and to treat colour as a harmony to compose with rather than a loud effect to chase. The aim is never the obvious close-up everyone takes, but an image that's considered and your own.It's a small group of no more than four, taught personally by an award-winning professional photographer, so every person gets real one-to-one guidance in the field — briefing and set-up, then shooting with reviews and tuition as you go. You'll leave with your own macro and abstract images, and a sharper, more intentional way of seeing detail, colour and light that changes how you photograph everything afterwards.</t>
+          <t>RPS Courses - Independant RPS Mentoring for RPS Distinctions - Start anytime, you select a package of Zoom sessions within twelve months at intervals to suit youDescription: Independent one-to-one RPS mentoring for your Licentiate (LRPS) or Associate (ARPS) distinction — online via Zoom, with a mentor who holds both distinctions himself and has a 100% pass rate to date. Most photographers who fall short don't fail on technique — they submit a collection of strong individual images rather than a planned, cohesive panel, and a panel is judged as a whole. That judgement — image selection, sequencing, the hanging plan and your Statement of Intent — is exactly what mentoring brings. We work in three stages: plan the panel, build and refine it, then test readiness before you submit. Sessions are flexible 1-hour Zoom slots — buy only what you need and book your dates later, across up to twelve months. Start fresh, or revise a panel that didn't pass first time.Format: One-to-one, online via Zoom — private and personal to you and your panel.Equipment Needed: Zoom App; free Dropbox account for sharing portfolios and updated images.Terms: A package of Zoom sessions must be used within 12 months of purchase or it is forfeited. You can extend the timeline or purchase additional sessions if needed.Method: Honest technical and creative critique with suggestions for improvement; advice on image selection, sequencing, the hanging plan and your Statement of Intent.Package Options: Choose Mon–Fri 9am–5pm daytime rates, or Mon–Sun 9am–9pm for evening and weekend flexibility.1 × 1hr — single session (fact-find &amp; review)4 × 1hr — 15% off (reset a failed panel)6 × 1hr — 20% off (from scratch, recommended)8 × 1hr — 25% off (extended panel build)12 × 1hr — 25% off (best value, full programme)More Details: about the RPS Mentoring Course</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/25c550a3-a242-4303-a11b-367dd7055dbe/Abstract%2Band%2BMacro%2BPhotography%2BWorkshops%2B%25282%2529.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707307452323-G3C2AIXAHRLLVB36VASA/RPS+Courses.jpg</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/abstract-and-macro-photography-workshops</t>
+          <t>https://www.alanranger.com/photography-services-near-me/rps-mentoring-photography-course</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - half-day photo workshops, Macro &amp; Abstract</t>
+          <t>1-2-1-private-lessons, photography-classes, photography-courses, photography-tuition, rps</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9970442", "price": "65.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Sun Nov 28th 2026 - 10:30am - 12:30pm"}, {"@type": "Offer", "sku": "SQ2051466", "price": "65.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Sat May 1st 2027 - 11am - 1pm"}, {"@type": "Offer", "sku": "SQ8660736", "price": "65.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Sun Sep 29th 2027 - 4:00pm - 6:00pm"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ7839038", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Mon- Fri 9am-5pm 1 x 1hr"}, {"@type": "Offer", "sku": "SQ3867813", "price": "170.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Mon- Fri 9am-5pm 4 x 1hr"}, {"@type": "Offer", "sku": "SQ8903198", "price": "240.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Mon- Fri 9am-5pm 6 x 1hr"}, {"@type": "Offer", "sku": "SQ4831915", "price": "300.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Mon- Fri 9am-5pm  8x 1hr"}, {"@type": "Offer", "sku": "SQ1077689", "price": "450.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Mon- Fri 9am-5pm 12 x 1hr"}, {"@type": "Offer", "sku": "SQ8233730", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Mon- Sun 9am-9pm 1 x 1hr"}, {"@type": "Offer", "sku": "SQ9139531", "price": "255.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Mon- Sun 9am-9pm 4 x 1hr"}, {"@type": "Offer", "sku": "SQ0776423", "price": "360.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Mon- Sun 9am-9pm 6 x 1hr"}, {"@type": "Offer", "sku": "SQ2385997", "price": "450.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Mon- Sun 9am-9pm 8 x 1hr"}, {"@type": "Offer", "sku": "SQ9440259", "price": "675.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Mon- Sun 9am-9pm 12 x 1hr"}]</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H32" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="I32" t="n">
-        <v>65</v>
+        <v>675</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>SQ9970442, SQ2051466, SQ8660736</t>
+          <t>SQ7839038, SQ3867813, SQ8903198, SQ4831915, SQ1077689, SQ8233730, SQ9139531, SQ0776423, SQ2385997, SQ9440259</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>SQ9970442</t>
+          <t>SQ7839038</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>event</t>
-        </is>
-      </c>
-      <c r="M32" t="b">
-        <v>0</v>
-      </c>
-      <c r="N32" t="b">
-        <v>0</v>
+          <t>course</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>NORTH YORKSHIRE Landscape Photography Workshop - Jun 2027</t>
+          <t>The Secret of WOODLAND PHOTOGRAPHY- 1-Day Jan, Apr, Aug, Oct</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>An exciting 4-day residential Yorkshire Landscape Photography Workshop - visiting some of the iconic spots around the North Yorkshire Coast and MoorsSummary - Photography Workshops YorkshireLocation: North YorkshireDates:Thu 3 Jun - Sun 6 Jun 2027 - 4 Days/3 NightsParticipants: Max 3Fitness: 2. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event DetailsNorth YorkshireDescription: This is a 4-day, 3-night residential landscape photography workshop on the dramatic northeast coast of England, exploring the iconic coastline and moors of North Yorkshire — open to all levels from beginner to advanced. Based on the coast, you'll photograph some of the most atmospheric scenery in the country, from the tumbling fishing village of Staithes and the sweeping bay at Runswick to the harbour and abbey town of Whitby, with the wild North York Moors as a backdrop.Over four full days we work from sunrise to sunset to make the most of the best light, tides and empty beaches — far more time on location than a short workshop allows. The focus is on three things that make a strong coastal image: composing the rocks, headlands and shoreline into a balanced frame, mastering long exposure to draw out movement in the sea and sky, and timing each shoot to the tides and the golden light of dawn and dusk. Throughout, the emphasis isn't just on the postcard view but on learning to see it — composing with intention, working intimate detail as readily as the wide vista, and reading light and tide as a harmony rather than chasing the obvious shot. Across the four days you'll build a real working rhythm for coastal photography, returning to locations in different conditions to capture them at their very best.With a maximum of just three photographers, this is exceptionally personal tuition — Alan plans each day around the season, the forecast and the tide times, and sends a detailed location itinerary a few days ahead. Accommodation and breakfast are included, so all you have to think about is your photography, and you'll come away with a varied portfolio of iconic Yorkshire coast and moorland images — and the field craft to read light, tide and weather on any coastline. An extra night's accommodation is available the day before if required — please request in advance, subject to hotel availability.</t>
+          <t>Simplifying Woodland Photography | Unlocking the Secrets to Capturing the Beauty of woods | Three sessions - Theory - Practical - Editing in one daySummaryLocation: Coventry - CV4 9HWDates: - 10:00 - 16:00Sun 18th Oct - AutumnSun 10th Jan - Winter 2027Sun 2nd May - Spring 2027Sun 1st Aug - Summer 2027Participants: Max 3Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: Digital Camera and TripodPhotography Workshop Event Details: Woodland Photography MasterclassDescription: The Secrets of Woodland Photography is a 1-Day Masterclass in Coventry, open to all levels and any camera. Woodland is the hardest subject there is — chaotic, cluttered, endlessly busy — which is exactly why it's the best place to learn to see. Most people come away with the tangled, cliché shot; this day is about learning to find the order, the light and the quiet beauty hidden within the chaos, and to make woodland images that are calm, intentional and your own.The technical setup matters, but it's only the floor we build on. Rather than a typical walk-and-shoot, the day runs as three connected sessions — theory, practical and editing — so we can go deeper than settings. We start with the thinking behind a strong woodland image and the craft that delivers it: simplifying a busy scene, using light and shadow, choosing what to include and what to leave out. Then you put it into practice on a woodland walk, working the close-up, the macro detail and the abstract as readily as the wider view — reading texture and colour as a harmony, not chasing the loud, over-saturated shot. Finally we review your images together and finish on the editing that brings the quiet colours of the forest to life without shouting.The day runs from Alan's home, which offers three things most workshops can't: instant access to woodland straight from the garden, a comfortable covered and heated space for the presentations and image reviews, and a large screen to study your shots on — so the day works whatever the weather. You'll leave not just with a set of woodland images, but with a way of seeing — light, simplicity and restraint — that changes how you photograph trees, nature and detail wherever you go next.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714649253879-9IH9C2DQR5W69WW1JK5P/Saltwick+Bay.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714646680135-9EB3PR57B78W9NMZ09JI/Plant+Hill+Woods+%2310+-+Jan+2022.jpg</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/north-yorkshire-landscape-photography</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/secrets-of-woodland-photography-workshop</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>coastal, All Photography Workshops, - weekend residential photo workshops</t>
+          <t>All Photography Workshops, - one day photo workshops, Macro &amp; Abstract, Woodlands</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9283225", "price": "1450.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "priceSpecification": {"price": "1450.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ4894934", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Sun 18th Oct 2026 - 10am - 4pm"}, {"@type": "Offer", "sku": "SQ2827052", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Sun 10 Jan 2027 - 10am - 4pm"}, {"@type": "Offer", "sku": "SQ0512761", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Sun 2nd May 2027 - 10am - 4pm"}, {"@type": "Offer", "sku": "SQ4914997", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Sun 1st Aug 2027 - 10am - 4pm"}]</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H33" t="n">
-        <v>1450</v>
+        <v>150</v>
       </c>
       <c r="I33" t="n">
-        <v>1450</v>
+        <v>150</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>SQ9283225</t>
+          <t>SQ4894934, SQ2827052, SQ0512761, SQ4914997</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>SQ9283225</t>
+          <t>SQ4894934</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>event</t>
         </is>
-      </c>
-      <c r="M33" t="b">
-        <v>0</v>
-      </c>
-      <c r="N33" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Christmas Photography Seasonal Workshops - Warwickshire UK</t>
+          <t>SUFFOLK Landscape Photography Workshops - 3 days</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Christmas photography workshops. A Leisurely Christmas photography walk and photograph the countryside - Lapworth or the Christmas lights Stratford Upon Avon photography- Warwickshire - Expert Advice GivenSummaryLocation: WarwickshireDates: 2026 DatesThu 10 December 2026 - 18:45 - 20:30 - Stratford Upon Avon Evening ShootTue, 29 December 2026 - 1 day Christmas Photo Walk 09:00 15:00Break for pub lunch around 12:45 - Not includedParticipants: Max 6Fitness: 2. Easy-ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodChristmas Photography Workshop Event Details Christmas PhotowalkDescription: This Christmas Photography Workshop is the perfect way to escape the heat and fuss of the festive season — swap the wrapping paper for your camera, walk off a little of the overindulgence, and rediscover how much there is to photograph at the most atmospheric time of year. Open to all levels and any camera, it's a relaxed, sociable outing in Warwickshire with expert guidance throughout, and there's a choice of two very different sessions.Stratford-upon-Avon, evening: an after-dark shoot in the heart of the town, photographing the Christmas lights and festive atmosphere. It's a chance to work long exposure, reflections and the warm glow of the season — learning to control exposure in low light and compose a strong frame out of a busy, sparkling scene rather than settling for the obvious snapshot.Lapworth, daytime: the antidote to Christmas. Once the presents are unwrapped, the family politics have peaked and you've eaten your bodyweight in turkey, this leisurely day in the winter countryside is the tonic — a chance to breathe, clear your head and lose yourself in your photography for a few hours. We'll amble through frosty fields, bare woodland and quiet lanes reading the soft, low winter light, with a relaxed lunch in the middle of the day. The whole walk is under five miles at an easy, unhurried pace — gentle enough that the photography, the fresh air and the company are the whole point. The focus stays on seeing: composing with intention, working both intimate detail and wider vista, and reading light, texture and mood to make a picture that's truly yours.It's a small group of no more than six, taught personally and pitched at exactly your level, with one-to-one guidance in the field throughout. Whether you choose the festive lights of Stratford, the crisp countryside of Lapworth, or both, you'll come away with a set of atmospheric seasonal images — and a stronger eye for light, composition and winter colour that carries through long after the decorations come down. For the Lapworth day, a table is reserved in advance at a welcoming country pub, with a festive menu offering both lighter and full festive-meal options to suit every appetite. The lunch itself isn't included in the workshop fee, so you simply pay for what you choose on the day.</t>
+          <t>Join us for an inspiring Suffolk landscape photography workshop, where you'll have the opportunity to create stunning long exposures during breathtaking sunrises and vibrant sunsets. We will explore picturesque quays, serene estuaries, intriguing piers, and tranquil marshes, all while capturing the beauty of charming beach huts and ancient woodlands. Emphasising artistic expression, we'll also delve into the world of black and white photography, allowing you to bring a classic touch to your coastal images.SummaryLocation: Suffolk - East Anglia / Southwold/Aldeburgh AreaDates: Fri 5th 09:30 - Sun 7th 14:30 Feb 2027 - 3 Days/2 NightsParticipants: Max 4 (1 Car, transport between locations included)Fitness: 2. Moderate (15-30 min walks)Experience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details SuffolkDescription: This is a 3-day, 2-night residential Suffolk landscape photography workshop based on the Southwold and Aldeburgh coast, open to all levels from beginner to advanced. The Suffolk coastline is one of England's most photogenic and most varied — wide shoreline vistas, big skies, and a wealth of subjects most coastlines can't match: weathered piers, painted beach huts, iconic sea-defence structures and the traditional sails of Herringfleet Windmill. It's a landscape that rewards photographers who slow down and learn to see it.The focus is on long exposure and the art of black and white photography — learning to compose a strong coastal frame, to use long exposures to smooth water and sky into mood, and to recognise when a scene works better in mono. It's about more than the technical craft, though: the real work is learning to see — composing with intention, working intimate detail as readily as the wide vista, and reading light and tone as a harmony rather than chasing the obvious shot. It's never prescriptive either: over three days and two to three locations a day — from Southwold and Walberswick to Dunwich, Orford and Aldeburgh — we work with whatever light and conditions the coast gives us, with early sunrise shoots, full days in the field with tuition, and evenings for relaxed picture reviews.With a maximum of just four photographers and transport between locations included, this is genuinely personal, hassle-free tuition — Alan plans each day around the group, the season, the tides and the forecast, and sends a detailed location itinerary a few days ahead. En-suite accommodation and breakfast are included, so all you have to think about for three days is your photography. You'll come away with a portfolio of atmospheric Suffolk coastal images and a real grasp of long exposure and black and white technique. An extra night is available the day before on request, ideal for those travelling from a distance — contact me to arrange.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1573822266360-1I7REB8B91RNZXW2PNKP/christmas-sparkle-photography-workshop.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714667523305-2SEM1T5WD278HHO4HJIV/Southwold+Sunrise.jpg</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/christmas-photography-workshops</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/suffolk-landscape-photography-workshops</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - half-day photo workshops, Landscape, Urban</t>
+          <t>coastal, - weekend residential photo workshops</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8119747", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Thu 10 Dec 18:45- 20:30 - Stratford Upon Avon"}, {"@type": "Offer", "sku": "SQ6178610", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Tue 29 Dec 09:00 - 15:00 - Lapworth"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ2176971", "price": "995.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "priceSpecification": {"price": "995.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H34" t="n">
-        <v>50</v>
+        <v>995</v>
       </c>
       <c r="I34" t="n">
-        <v>125</v>
+        <v>995</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>SQ8119747, SQ6178610</t>
+          <t>SQ2176971</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>SQ8119747</t>
+          <t>SQ2176971</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>event</t>
         </is>
-      </c>
-      <c r="M34" t="b">
-        <v>0</v>
-      </c>
-      <c r="N34" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>YORKSHIRE DALES Landscape  Photography Workshop - 16 - 18 Apr</t>
+          <t>URBAN ARCHITECTURE Photography Workshops - Coventry Sep</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Yorkshire Dales Photography Workshop - Join me for this fantastic landscape workshop on limestone pavements and waterfalls.SummaryLocation: Yorkshire DalesDates: Fri 16th - Sun 18th Apr 2027 - 3 Days/2 NightsParticipants: Max 4Fitness: 3. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details Yorkshire DalesDescription: This is a 3-day, 2-night residential landscape photography workshop in the Yorkshire Dales — one of England's most iconic and varied landscapes, open to all levels from beginner to advanced. From dramatic limestone pavements and amphitheatre cliffs to tumbling waterfalls, soaring viaducts and lone, wind-sculpted trees, the Dales pack an extraordinary range of subjects into one area, and over a long weekend you'll learn to read and photograph this moody, dramatic country in its best light.Across three days we work some of the Dales' most rewarding locations as the conditions and season allow — the natural amphitheatre of Malham Cove and the ravine at Gordale Scar, the waterfalls of Ingleton, Aysgarth and Janet's Foss, the sweeping arches of Ribblehead Viaduct, and the famous lone tree set on its bare limestone pavement. The focus is on three things that make a strong Dales image: composing rock, water and vista into a balanced frame, mastering long exposure to bring waterfalls and rivers to life, and timing each shoot — including early morning starts — to the dramatic light and weather these hills are known for. Throughout, the emphasis isn't just on the grand vista but on learning to see it — composing with intention, working intimate detail as readily as the wide view, and reading light and colour as a harmony rather than chasing the obvious shot.With a maximum of just four photographers, this is genuinely personal tuition — Alan plans each day around the season and the forecast, and sends a detailed location itinerary a few days ahead. Accommodation and breakfast are included, so all you have to think about is your photography, and you'll come away with a varied portfolio of the Yorkshire Dales — waterfalls, limestone pavements, viaducts and classic vistas — and the field craft to capture dramatic upland landscape anywhere. An extra night's accommodation is available the day before if required — please request in advance, subject to hotel availability.</t>
+          <t>We will walk around several historic parts of Coventry in this 2.5hr Urban Architecture Photography Workshop, photographing buildings and ruins.SummaryLocation: Coventry City CentreDates: Mon 13 Sep 2027 - 18:15-20:15Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Street PhotographyDescription: This Urban Architecture Photography workshop is an evening walk through the historic heart of Coventry — once UK City of Culture — open to all levels and any camera. Cities transform after dark: artificial light, deep shadow and the last colour in the sky turn ordinary buildings and ruins into something dramatic, and this 2.5-hour workshop is built around learning to see and design photographs at night, in the tricky low light most people find hardest to shoot.Confident technique in the dark is the floor we build on — and we'll cover it: focusing and exposing accurately in low light, and setting up long exposures to capture movement and mood. But the real work is learning to see the city as a photographer. Walking together through old and new architectural corners — including the cathedral area and its ruins — you'll learn to compose with form, line, texture and contrast, to read the interplay of artificial light and shadow as a harmony rather than a problem, and to find the considered, intentional frame instead of the obvious postcard of a landmark. Old against new, light against dark, detail against sweep — it's about designing an image, not just recording a building.It's a small group of no more than six, taught personally and pitched at exactly your level, so whether you're new to night photography or refining your eye you get real one-to-one guidance in the field. You'll come away with a set of atmospheric urban and architectural images — long exposures, abstracts, dramatic skies — and a sharper, more intentional way of seeing that lets you photograph any city after dark.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714659095505-TB874TXCA6ADNDFC82FX/Muker+%2302+-+July+2021.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1658913526628-KD8S5Y2CTOHVVBBJMAYJ/Coventry+3.jpg</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/yorkshire-dales-photography-workshops</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/urban-architecture-photography-workshops-coventry</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - weekend residential photo workshops, Landscape</t>
+          <t>All Photography Workshops, - half-day photo workshops, Urban</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9211910", "price": "895.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ4066377", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G35" t="n">
         <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>895</v>
+        <v>50</v>
       </c>
       <c r="I35" t="n">
-        <v>895</v>
+        <v>50</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>SQ9211910</t>
+          <t>SQ4066377</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>SQ9211910</t>
+          <t>SQ4066377</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>event</t>
         </is>
-      </c>
-      <c r="M35" t="b">
-        <v>0</v>
-      </c>
-      <c r="N35" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>WALES Photography Workshop | Lake Vyrnwy 10-11 Oct</t>
+          <t>WALES Landscape Photography Workshop - 2 Days Lake Vyrnwy</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Join me for this fantastic Wales photography workshop of woodlands, lakes and waterfalls in Mid-WalesLocation: Wales - Dee ValleyDates: Sat 10th - Sun 11th Oct 2026 - 2 Days/1 NightParticipants: Max 4Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodWales Photography Workshop Event Details Lake VyrnwyDescription: This is a 2-day, 1-night residential Wales photography workshop based in the valleys of Mid-Wales, open to all levels from beginner to advanced. It's built around two of the country's most rewarding landscape locations — Pistyll Rhaeadr, an enchanting waterfall in the Berwyn Mountains and, at 240ft, Britain's tallest single-drop fall, and the tranquil 11-mile shoreline of Lake Vyrnwy — giving you woodlands, water, mountains and one of the seven wonders of Wales in a single weekend.Over two days we work both locations at their best. At Pistyll Rhaeadr you'll photograph the three-stage falls from the viewing platform and bridge, then drop down to water level among the slate beds and mini-falls for intimate compositions; around Lake Vyrnwy we take a leisurely circuit of the reservoir, stopping at quiet bays and outlets and walking the river to the waterfall at the valley head. The focus is on three things that make moving water and big Welsh landscape work: composing a strong frame from a busy natural scene, mastering long exposure to turn falling water into silk, and reading the light and weather that give these valleys their mood. Throughout, the emphasis isn't just on the famous waterfall but on learning to see it — working intimate detail as readily as the wide vista, and treating light and colour as a harmony rather than chasing the obvious shot.With a maximum of just four photographers, this is genuinely personal tuition — Alan plans each day around the season and the forecast, and sends a detailed location itinerary a few days ahead. Accommodation and breakfast are included, so all you have to think about is your photography, and you'll come away with a varied portfolio of Welsh waterfalls, lakes and valleys — and a real command of long-exposure water technique. An extra night's accommodation is available the day before if required — please request in advance, subject to hotel availability.</t>
+          <t>Join me for this fantastic Wales photography workshop of woodlands, lakes and waterfalls in Mid-WalesLocation: Wales - Lake Vyrnwy &amp; Pistyll Rhaeadr, PowysDates: Sat 13th - Sun 14th Mar 2027 - 2 Days/1 NightParticipants: Max 4 (1 Car, transport between locations included)Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodWales Photography Workshop Event Details Lake VyrnwyDescription: This is a 2-day, 1-night residential Wales photography workshop based in the valleys of Mid-Wales, open to all levels from beginner to advanced. It's built around two of the country's most rewarding landscape locations — Pistyll Rhaeadr, an enchanting waterfall in the Berwyn Mountains and, at 240ft, Britain's tallest single-drop fall, and the tranquil 11-mile shoreline of Lake Vyrnwy — giving you woodlands, water, mountains and one of the seven wonders of Wales in a single weekend.Over two days we work both locations at their best. At Pistyll Rhaeadr you'll photograph the three-stage falls from the viewing platform and bridge, then drop down to water level among the slate beds and mini-falls for intimate compositions; around Lake Vyrnwy we take a leisurely circuit of the reservoir, stopping at quiet bays and outlets and walking the river to the waterfall at the valley head. The focus is on three things that make moving water and big Welsh landscape work: composing a strong frame from a busy natural scene, mastering long exposure to turn falling water into silk, and reading the light and weather that give these valleys their mood. Throughout, the emphasis isn't just on the famous waterfall but on learning to see it — working intimate detail as readily as the wide vista, and treating light and colour as a harmony rather than chasing the obvious shot.With a maximum of just four photographers, this is genuinely personal tuition — Alan plans each day around the season and the forecast, and sends a detailed location itinerary a few days ahead. Accommodation and breakfast are included, so all you have to think about is your photography, and you'll come away with a varied portfolio of Welsh waterfalls, lakes and valleys — and a real command of long-exposure water technique. An extra night's accommodation is available the day before if required — please request in advance, subject to hotel availability.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2636,7 +2422,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ5697158", "price": "695.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ5697158", "price": "695.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12"}]</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -2663,1189 +2449,117 @@
           <t>event</t>
         </is>
       </c>
-      <c r="M36" t="b">
-        <v>0</v>
-      </c>
-      <c r="N36" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>DORSET Landscape Photography Workshop Purbeck 9 Apr</t>
+          <t>WARWICKSHIRE Woodland PHOTOGRAPHY WALKS - Monthly - 2hrs</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Join me on this 3-day/2-night fantastic Dorset Photography workshop along the Jurassic coastline of Dorset - PurbeckSummary - Dorset Landscape PhotographyLocation: DorsetDates: Fri 9th - Sun 11th Apr 2027 3 Days/2 Nights(Price includes B&amp;B and evening meal - Half Board)Participants: Max 4Fitness: 3. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details DorsetDescription: This is a 3-day, 2-night residential landscape photography workshop along the Jurassic Coast of Dorset, open to all levels from beginner to advanced. Dorset's Purbeck coastline is one of the UK's great seascape locations — a prehistoric, World Heritage shore of sculpted arches, sea stacks and folded cliffs, with the iconic Durdle Door and Lulworth Cove at its heart — and across a weekend you'll learn to photograph it in its best light.Based on the Purbeck coast, we work the area's finest locations — from Durdle Door, Man O'War and Lulworth Cove to Kimmeridge, Dancing Ledge, Mupe Bay and the ghost village of Tyneham. The focus is on three things that make a strong coastal image: composing rock, sea and sky into a balanced frame, using long exposure to turn the moving water into mood, and timing your shoot to the light and the tide. It's never prescriptive though — this varied coastline lends itself to any style, so whether you're drawn to classic seascapes, black and white or abstract, there's scope to follow your own creative vision; throughout, the emphasis is on learning to see, composing with intention and reading light and tone as a harmony rather than chasing the obvious shot. There are optional sunrise and sunset shoots and evenings for relaxed picture reviews.With a maximum of just four photographers, this is genuinely personal tuition — Alan plans each day around the tides, the season and the forecast, and sends a detailed location itinerary a few days ahead. B&amp;B accommodation and an evening meal are included, so all you have to think about for three days is your photography, and you'll come away with a portfolio of dramatic Jurassic Coast images and a real command of seascape and long-exposure technique. An extra night's accommodation is available the day before if required — please request in advance, subject to hotel availability.</t>
+          <t>Informal woodland photography walks in and around Warwickshire Woodlands - All Levels and types of camera welcome - Length 2hrs. 9:30 am-11:30 amSummaryLocation: Various Warwickshire Woodlands2026 - 09:30 - 11:30Hay Woods - Solihull Fri Jan 2Tile Hill Nature Reserve Mon Feb 2Millisons Wood, Meriden -Sun May 3Piles Coppice, Coventry - Fri Oct 16Crackley Wood, Kenilworth - Fri Nov 6Hay Woods - Solihull Fri Dec 4Participants: Max 6Fitness: 1. EasyExperience Level: Novice to BeginnerEquipment Needed: Phone or Digital CameraPhotography Workshop Event Details: Woodland WalksDescription: This is a relaxed, informal woodland photography walk through the beautiful woodlands in and around Warwickshire — a regular monthly outing open to all levels and any camera. It's a gentle two hours among the trees with camera in hand, and it's as much about slowing down and reconnecting with nature as it is about photography: we walk, we observe, we take in the wood around us, and we make a photograph when something moves us to — or simply enjoy being there.My aim isn't to tell you what to shoot. It's to help you develop your own visual awareness, your photographic eye and your personal interpretation of what's in front of you. Woodland is one of the hardest subjects there is — chaotic, cluttered, endlessly busy — so the real work is learning to see: to simplify the scene, to find the quiet order and the light within the tangle, and to photograph the close-up, the intimate detail and the abstract as readily as the wider woodland view. I'm always on hand for the "how to" — the settings and the craft — but in service of what you feel drawn to express, not a shot list.The walks rotate through a lovely variety of local woodlands across the seasons — among them Crackley Wood, Hay Wood, Tile Hill Nature Reserve, Millisons Wood and Piles Coppice — so there's always something new to see. With no more than six of us it stays personal and unhurried, with one-to-one guidance whenever you want it. You'll come away with images that are genuinely your own — and a calmer, more intentional way of seeing that stays with you long after the walk.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714681245814-0QW8DK4XQ18FM0JLBXYN/Harry+Rocks+%2301+-+Mar+2024.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707217364251-99ITJH38DI58S3G3YA47/Woodland+Photography+Walk.jpg</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/dorset-landscape-photography-workshop</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/woodland-photography-walk-warwickshire</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>coastal, All Photography Workshops, - weekend residential photo workshops</t>
+          <t>All Photography Workshops, - half-day photo workshops, Woodlands</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ2754105", "price": "925.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ1654264", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Fri Jan 2 Hay Woods - Solihull"}, {"@type": "Offer", "sku": "SQ1288994", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Mon Feb 2 - Tile Hill Nature Reserve - Coventry"}, {"@type": "Offer", "sku": "SQ0063623", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Sun May 3 - Millisons Wood, Meriden"}, {"@type": "Offer", "sku": "SQ6524101", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Fri Oct 16 - Piles Coppice, Coventry"}, {"@type": "Offer", "sku": "SQ7078023", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Fri Nov 6 - Crackley Wood, Kenilworth"}, {"@type": "Offer", "sku": "SQ3819844", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Fri Dec 4 - Hay Wood - Lapworth"}]</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H37" t="n">
-        <v>925</v>
+        <v>15</v>
       </c>
       <c r="I37" t="n">
-        <v>925</v>
+        <v>15</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>SQ2754105</t>
+          <t>SQ1654264, SQ1288994, SQ0063623, SQ6524101, SQ7078023, SQ3819844</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>SQ2754105</t>
+          <t>SQ1654264</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>event</t>
         </is>
-      </c>
-      <c r="M37" t="b">
-        <v>0</v>
-      </c>
-      <c r="N37" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>URBAN ARCHITECTURE Photography Workshops - Coventry 9 Sep</t>
+          <t>YORKSHIRE DALES Landscape  Photography Workshop - 3 Days</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>We will walk around several historic parts of Coventry in this 2.5hr Urban Architecture Photography Workshop, photographing buildings and ruins.SummaryLocation: Coventry City CentreDates: Mon 13 Sep 2027 - 18:15-20:15Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Street PhotographyDescription: This Urban Architecture Photography workshop is an evening walk through the historic heart of Coventry — once UK City of Culture — open to all levels and any camera. Cities transform after dark: artificial light, deep shadow and the last colour in the sky turn ordinary buildings and ruins into something dramatic, and this 2.5-hour workshop is built around learning to see and design photographs at night, in the tricky low light most people find hardest to shoot.Confident technique in the dark is the floor we build on — and we'll cover it: focusing and exposing accurately in low light, and setting up long exposures to capture movement and mood. But the real work is learning to see the city as a photographer. Walking together through old and new architectural corners — including the cathedral area and its ruins — you'll learn to compose with form, line, texture and contrast, to read the interplay of artificial light and shadow as a harmony rather than a problem, and to find the considered, intentional frame instead of the obvious postcard of a landmark. Old against new, light against dark, detail against sweep — it's about designing an image, not just recording a building.It's a small group of no more than six, taught personally and pitched at exactly your level, so whether you're new to night photography or refining your eye you get real one-to-one guidance in the field. You'll come away with a set of atmospheric urban and architectural images — long exposures, abstracts, dramatic skies — and a sharper, more intentional way of seeing that lets you photograph any city after dark.</t>
+          <t>Yorkshire Dales Photography Workshop - Join me for this fantastic landscape workshop on limestone pavements and waterfalls.SummaryLocation: Yorkshire DalesDates: Fri 16th - Sun 18th Apr 2027 - 3 Days/2 NightsParticipants: Max 4 (1 Car, transport between locations included)Fitness: 3. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details Yorkshire DalesDescription: This is a 3-day, 2-night residential landscape photography workshop in the Yorkshire Dales — one of England's most iconic and varied landscapes, open to all levels from beginner to advanced. From dramatic limestone pavements and amphitheatre cliffs to tumbling waterfalls, soaring viaducts and lone, wind-sculpted trees, the Dales pack an extraordinary range of subjects into one area, and over a long weekend you'll learn to read and photograph this moody, dramatic country in its best light.Across three days we work some of the Dales' most rewarding locations as the conditions and season allow — the natural amphitheatre of Malham Cove and the ravine at Gordale Scar, the waterfalls of Ingleton, Aysgarth and Janet's Foss, the sweeping arches of Ribblehead Viaduct, and the famous lone tree set on its bare limestone pavement. The focus is on three things that make a strong Dales image: composing rock, water and vista into a balanced frame, mastering long exposure to bring waterfalls and rivers to life, and timing each shoot — including early morning starts — to the dramatic light and weather these hills are known for. Throughout, the emphasis isn't just on the grand vista but on learning to see it — composing with intention, working intimate detail as readily as the wide view, and reading light and colour as a harmony rather than chasing the obvious shot.With a maximum of just four photographers, this is genuinely personal tuition — Alan plans each day around the season and the forecast, and sends a detailed location itinerary a few days ahead. Accommodation and breakfast are included, so all you have to think about is your photography, and you'll come away with a varied portfolio of the Yorkshire Dales — waterfalls, limestone pavements, viaducts and classic vistas — and the field craft to capture dramatic upland landscape anywhere. An extra night's accommodation is available the day before if required — please request in advance, subject to hotel availability.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1658913526628-KD8S5Y2CTOHVVBBJMAYJ/Coventry+3.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714659095505-TB874TXCA6ADNDFC82FX/Muker+%2302+-+July+2021.jpg</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/urban-architecture-photography-workshops-coventry</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/yorkshire-dales-photography-workshops</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - half-day photo workshops, Urban</t>
+          <t>All Photography Workshops, - weekend residential photo workshops, Landscape</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ4066377", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9211910", "price": "895.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12"}]</t>
         </is>
       </c>
       <c r="G38" t="n">
         <v>1</v>
       </c>
       <c r="H38" t="n">
-        <v>50</v>
+        <v>895</v>
       </c>
       <c r="I38" t="n">
-        <v>50</v>
+        <v>895</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>SQ4066377</t>
+          <t>SQ9211910</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>SQ4066377</t>
+          <t>SQ9211910</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>event</t>
         </is>
-      </c>
-      <c r="M38" t="b">
-        <v>0</v>
-      </c>
-      <c r="N38" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>KENILWORTH Sunset Long Exposure Photography Workshop</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Sunset landscape long exposure photography workshop shoots around Kenilworth Castle - Warwickshire - Various Dates | Long Exposures | Open to all levels| Book TodaySummaryLocation: Warwickshire - KenilworthDates:Mon 22 Mar 2027 - 18:00 - 20:00Wed 14 Apr 2027 - 18:30 - 20:30Wed 5 May 2027 - 18:00 - 20:00Wed 22 Sep 2027 - 17:45 - 19:45Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: KenilworthDescription: This Long Exposure Photography Workshop is an evening shoot around the floodlit ruins of Kenilworth Castle in Warwickshire, open to all levels and any camera. Once one of England's mightiest fortresses and Robert Dudley's Elizabethan palace, the castle makes a dramatic subject against a darkening sky — and this workshop is built around the magic of long exposure at dusk, when the fading light, the castle's silhouette and a slow shutter combine to create atmospheric images that capture a sense of place, not just a record of a building.The long-exposure craft is the floor we build on, and we'll cover it properly: calculating exposure times for the movement and mood you want, focusing and exposing confidently in low light, and balancing ISO, shutter and aperture as the light drops. But the real work is learning to see. As the sky changes you'll compose the castle with intention — finding the frame beyond the obvious silhouette, working detail and texture as readily as the grand wide view, and reading the interplay of fading light, floodlight and deep shadow as a harmony rather than a problem to fight. The aim is an image with mood and restraint, where every element earns its place.It's a small group of no more than six, taught personally and pitched at exactly your level, so whether long exposure is new to you or you're refining your technique, you get real one-to-one guidance in the field. You'll come away with a set of atmospheric long-exposure images of one of England's most romantic castles — and a sharper, more intentional way of seeing light, movement and mood after dark anywhere.</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1712472502735-OHOKCDKMCP1BAMQ0JQUA/kenilworth+defenses.jpg</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/long-exposure-photography-kenilworth</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>All Photography Workshops, - half-day photo workshops, Landscape</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>[{"@type": "Offer", "sku": "SQ0932604", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Mon 22 Mar 2027 - 18:00 - 20:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1178418", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Wed 14 Apr 2027 - 18:30 - 20:30", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9140400", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Wed 5 May 2027 - 18:00 - 20:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8220723", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Wed 22 Sep 2027 - 17:45 - 19:45", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
-        </is>
-      </c>
-      <c r="G39" t="n">
-        <v>4</v>
-      </c>
-      <c r="H39" t="n">
-        <v>50</v>
-      </c>
-      <c r="I39" t="n">
-        <v>50</v>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>SQ0932604, SQ1178418, SQ9140400, SQ8220723</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>SQ0932604</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>event</t>
-        </is>
-      </c>
-      <c r="M39" t="b">
-        <v>0</v>
-      </c>
-      <c r="N39" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>SNOWDONIA Landscape Photography  - Sat 6 - Sun 7 Mar 2027</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Join me on this landscape photography Snowdonia workshop in the iconic mountains, quarries and landscape of Snowdonia national park.Summary - Snowdonia Landscape photography workshopLocation:Wales - Snowdonia National ParkDates: Sat 6th - Sun 7th Mar 2027 - 2 Days/1 NightParticipants: Max 4 (1 Car, transport between locations included)Fitness: 2. Moderate (15-30 min walks)Experience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details SnowdoniaDescription: This is a 2-day, 1-night residential landscape photography workshop in Snowdonia National Park, North Wales — open to all levels from beginner to advanced. Home to the highest mountain ranges in England and Wales, Snowdonia is a landscape that will both inspire and challenge any photographer: rugged peaks and flowing rivers, serene lakes and ancient slate quarries, all within a compact corner of Wales that you'll learn to read and photograph in its ever-changing light.What makes Snowdonia so rewarding is its variety, and over two days we work three very different faces of it: the waterfalls and rivers that are perfect for long exposure, turning moving water to silk; the starker, striking world of the historic slate quarries and mining relics, where industry and mountain meet; and the majestic lakes, where still water mirrors the peaks for compelling, reflective compositions. Across all of it the focus stays on the same craft — composing order from a vast scene, controlling exposure across big tonal ranges, and timing your shoot to the light and weather that shift the mood from rugged to serene and back. And throughout, the emphasis isn't just on the grand vista but on learning to see it — working intimate detail as readily as the wide view, and reading light and colour as a harmony rather than chasing the obvious shot.With a maximum of just four photographers and transport between locations included, this is genuinely personal tuition — Alan plans each day around the season and the forecast, and sends a detailed location itinerary a few days ahead. Likely locations include the reflective waters of Llynnau Mymbyr beneath the Snowdon massif, the Capel Curig pinnacles, Swallow Falls and the hidden lake of Llyn Craftnant. Accommodation and breakfast are included, so all you have to think about is your photography — and you'll leave with a varied portfolio that captures both the drama and the stillness of this remarkable landscape. An extra night's accommodation is available the day before if required — please request in advance, subject to hotel availability.</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1711625824431-22D7V1RNKR8H2LBRW4Z9/Snowdonia+%2301+-+Oct+2023.jpg</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/landscape-photography-snowdonia-workshops</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Landscape, - weekend residential photo workshops</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>[{"@type": "Offer", "sku": "SQ0548499", "price": "595.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29"}]</t>
-        </is>
-      </c>
-      <c r="G40" t="n">
-        <v>1</v>
-      </c>
-      <c r="H40" t="n">
-        <v>595</v>
-      </c>
-      <c r="I40" t="n">
-        <v>595</v>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>SQ0548499</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>SQ0548499</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>event</t>
-        </is>
-      </c>
-      <c r="M40" t="b">
-        <v>0</v>
-      </c>
-      <c r="N40" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>The Art of GARDEN PHOTOGRAPHY  - Coventry -  May and July</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Join us for an unforgettable journey into macro and abstract on this garden photography workshop. Secure your spot today and embark on a transformative learning experience in garden photography.SummaryLocation: Coventry - CV4Dates:Sun May 23rd 2027 - 15:00 - 17:00Sun Jul 11th 2027 - 15:00 - 17:00Participants: Max 4Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details Garden PhotographyDescription: This Garden Photography Workshop is an intimate afternoon in Alan's own private garden in Coventry — his personal creative studio, a space he knows intimately and tends with a photographer's eye — open to all levels and any camera. A garden is one of the richest and most overlooked subjects there is: get close and the flowers, foliage, structures and borders reveal endless macro, close-up and abstract images, and this relaxed half-day is all about learning to see them, then photograph them with intention.The technical craft is the floor we build on — getting sharp focus, using your lens for macro and close-up detail, and controlling exposure and depth of field — but the real work is learning to look. You'll be given four photography assignments with guidance notes that push you to experiment and vary your approach, from intimate macro to wider garden portraits, training your eye to find the abstract within the planting and to compose with real intention. Throughout, the emphasis is on reading colour, light and texture as a harmony — letting the flowers sing without tipping into the loud, over-saturated shot — so your images feel considered and your own, not the obvious bloom-in-the-middle snap. Image reviews and feedback on a large screen in the gazebo help you see what's working and why.Places are limited to just four, so this is genuinely personal tuition, with Alan on hand for settings, composition and one-to-one guidance the whole time — and tea, coffee and cake served throughout. You'll come away with your own portfolio of garden images, and a sharper, more intentional way of seeing detail, colour and light that changes how you photograph flowers and nature everywhere.</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1709974516534-UJBRDOK5RXR4QNLPTECD/_-677.jpg</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/garden-photography-workshop</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>All Photography Workshops, - half-day photo workshops, Flowering, Macro &amp; Abstract</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>[{"@type": "Offer", "sku": "SQ0939451", "price": "45.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Sun May 23rd 2027 - 15:00 - 17:00"}, {"@type": "Offer", "sku": "SQ3644687", "price": "45.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Sun Jul 11th 2027 - 15:00 - 17:00"}]</t>
-        </is>
-      </c>
-      <c r="G41" t="n">
-        <v>2</v>
-      </c>
-      <c r="H41" t="n">
-        <v>45</v>
-      </c>
-      <c r="I41" t="n">
-        <v>45</v>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>SQ0939451, SQ3644687</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>SQ0939451</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>event</t>
-        </is>
-      </c>
-      <c r="M41" t="b">
-        <v>0</v>
-      </c>
-      <c r="N41" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>GOWER Landscape Photography Wales - 28 May - 30 May 2027</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Stunning shorelines and beauty of South Wales and the Gower Peninsular. Max 3 places for this residential photography workshop - landscape photography walesSummaryLocation: South Wales - Gower PeninsularDates:Fri 28th May - Sun 30th May 2027 - 3 Days/2 NightsParticipants: Max 4Fitness: 3. HardExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodLandscape photography Wales Photography Workshop Event Details GowerDescription: This is a 3-day, 2-night residential landscape photography workshop on the Gower Peninsula in South Wales — the UK's very first Area of Outstanding Natural Beauty, and one of the finest stretches of coast for landscape photography in Wales. Open to all levels from beginner to advanced, it takes you along 19 miles of dramatic shoreline west of Swansea, where lofty limestone cliffs, golden sandy beaches and jagged rocky shores meet wild moorland, dunes and tranquil salt marshes.Over three days we work the peninsula's most iconic locations as the light and tides allow — from the sweeping expanse of Rhossili Bay and the dramatic outline of Worms Head to the wreck of the Helvetia and the snug cove of Pwll Du. The focus is on three things that make a strong coastal image: composing cliffs, beaches and rock forms into a balanced frame, mastering long exposure to draw movement out of sea and sky, and timing each shoot from dawn to dusk to catch the best light and tide. Throughout, the emphasis isn't just on the famous viewpoint but on learning to see it — composing with intention, working intimate detail as readily as the wide vista, and reading light and colour as a harmony rather than chasing the obvious shot. You'll photograph at sunrise and sunset, the richest hours on this coast, and return to locations in changing conditions to capture them at their best.With a small group taught personally, this is genuinely one-to-one tuition — Alan plans each day around the season, the forecast and the tide times, and sends a detailed location itinerary a few days ahead. Be prepared for some longer walks over cliff paths and rougher coastal ground to reach the best viewpoints. Accommodation and breakfast are included, so all you have to think about is your photography, and you'll come away with a varied portfolio of the Gower's iconic Welsh coastline — and the field craft to read light, tide and weather on any shore. An extra night's accommodation is available the day before if required — please request in advance, subject to hotel availability.</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1715702409761-590M3MJ45KYXBDH1KSM0/Gower+%2305+-+May+2024.jpg</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/landscape-photography-wales-photo-workshop</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>coastal, All Photography Workshops, - weekend residential photo workshops</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>[{"@type": "Offer", "sku": "SQ5141863", "price": "825.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29"}]</t>
-        </is>
-      </c>
-      <c r="G42" t="n">
-        <v>1</v>
-      </c>
-      <c r="H42" t="n">
-        <v>825</v>
-      </c>
-      <c r="I42" t="n">
-        <v>825</v>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>SQ5141863</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>SQ5141863</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>event</t>
-        </is>
-      </c>
-      <c r="M42" t="b">
-        <v>0</v>
-      </c>
-      <c r="N42" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Fireworks Photography Workshop | Long Exposure | Kenilworth</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Fireworks Photography Workshop - Long exposure and fireworks. Learn about camera settings, exposure use and composition.SummaryLocation: KenilworthDates: TBCParticipants: Max 4Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: FireworksDescription: This Fireworks Photography Workshop is a one-off evening capturing one of the most exciting subjects in photography — a full fireworks display bursting over the floodlit ruins of Kenilworth Castle. Open to all levels and any camera, it's built around the Round Table's spectacular annual display, and the magical, fleeting moment when long exposure turns streaking light and exploding colour into a single dramatic image with the castle as its backdrop.Fireworks look chaotic but reward a calm, technical approach, and that's exactly what we'll work on. The focus is on three things that make the difference between a lucky snap and a controlled image: setting up for long exposure — shutter, aperture and the timing that lets you build a burst on the sensor — composing the frame so the castle and the sky work together rather than fighting, and reading the rhythm of the display to know when to open and close the shutter. You'll learn to anticipate rather than react, and to keep shooting cleanly when the sky is at its busiest.It's a small group of no more than four, taught personally and right beside you in the dark, so you get real one-to-one guidance exactly when the action is happening. Better still, we photograph from outside the castle walls, so there's no admission ticket to buy for the display. You'll come away with a set of dramatic fireworks images over a historic castle — and the long-exposure and timing skills to photograph fireworks, light trails and night scenes anywhere. (Please note this is an annual event with the date set by the organisers, so timing is confirmed each year nearer the display.)</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1713518270092-GJSBASA0ZLL4NBMCK355/Kenilworth+Fireworks+2017+-+2.jpg</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/fireworks-photography-workshop-kenilworth</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>All Photography Workshops, - half-day photo workshops</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>[{"@type": "Offer", "sku": "SQ1182401", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29"}]</t>
-        </is>
-      </c>
-      <c r="G43" t="n">
-        <v>1</v>
-      </c>
-      <c r="H43" t="n">
-        <v>75</v>
-      </c>
-      <c r="I43" t="n">
-        <v>75</v>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>SQ1182401</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>SQ1182401</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>event</t>
-        </is>
-      </c>
-      <c r="M43" t="b">
-        <v>0</v>
-      </c>
-      <c r="N43" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>EXMOOR Photography Workshop - Sat 12 - Sun 13 Jun 2027</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Lynmouth - Exmoor Photography Workshop - Join me for this exciting and inspiring trip to explore and capture the stunning coastal landscapes and breathtaking natural beauty of North Devon.SummaryLocation: Lynmouth - ExmoorDates: Sat 12 10:30 - Sun 13 Jun 14:00 2027 2 Days/1 NightParticipants:Max 4 (1 Car, transport between locations included)Fitness: 1. Easy (5-15 min walks)Experience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodExmoor Photography Workshop Event DetailsLynmouthDescription: This is a 2-day, 1-night residential seascape photography workshop based at Lynmouth on the dramatic Exmoor coast of North Devon, open to all levels from beginner to advanced. Lynmouth is a photographer's paradise — where the East and West Lyn rivers meet the sea beneath towering cliffs, fringed by secluded bays, weathered rock formations and the quaint harbour village with its iconic Rhenish Tower. It's a compact, richly varied coastline that rewards a focused weekend of shooting.Over two days we work the area's finest coastal locations — from the secluded bays and rock formations around Lynmouth and the sweeping Valley of Rocks to Watersmeet, Heddon's Mouth and Porlock Weir. The focus is on three things that make a strong seascape: composing rock, water and sky into a balanced frame, using long exposure to turn the moving sea into mood, and timing your shoot to the light and the tide. Throughout, the emphasis isn't just on the grand view but on learning to see it — composing with intention, working intimate detail as readily as the wide vista, and reading light and tide as a harmony rather than chasing the obvious shot. The days follow the conditions — full days on location with tuition, an optional sunset shoot, and an optional sunrise, with evenings for relaxed picture reviews.With a maximum of just four photographers and transport between locations included, this is genuinely personal, hassle-free tuition — Alan plans each day around the tides, the season and the forecast, and sends a detailed location itinerary a few days ahead. Accommodation and breakfast are included, so all you have to think about is your photography, and you'll come away with a portfolio of dramatic Exmoor seascapes and the field craft to read light and tide on any coast. An extra night's accommodation is available the day before if required — please request in advance, subject to hotel availability.</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714638630127-79B9OMJPFF60L8Q9VLJL/Timeless+Memories.jpg</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/exmoor-photography-workshops-lynmouth</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>coastal, All Photography Workshops, - weekend residential photo workshops</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>[{"@type": "Offer", "sku": "SQ8057321", "price": "575.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29"}]</t>
-        </is>
-      </c>
-      <c r="G44" t="n">
-        <v>1</v>
-      </c>
-      <c r="H44" t="n">
-        <v>575</v>
-      </c>
-      <c r="I44" t="n">
-        <v>575</v>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>SQ8057321</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>SQ8057321</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>event</t>
-        </is>
-      </c>
-      <c r="M44" t="b">
-        <v>0</v>
-      </c>
-      <c r="N44" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>SEZINCOTE Garden Photography Workshop - Gloucs 29 May</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Macro and abstract Garden photography workshop. Camera settings, controlling DoF and composition at this Mughal Indian palace in the Cotswolds.SummaryLocation: Moreton on Marsh (Sezincote) - GloucestershireDates: Thu 29th May 2026 - 11:00 - 13:30Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details Garden PhotographyDescription: This Sezincote Garden Photography Workshop takes you into one of the most extraordinary gardens in the Cotswolds — the grounds of a Mughal Indian palace, complete with copper dome and minarets, set in the gentle hills of Gloucestershire and open to all levels and any camera. Few gardens offer a photographer this much: a water garden of seven pools, waterfalls and a grotto, a temple to the Hindu sun god Surya, and a curving Orangery framing a Persian Garden of Paradise — all waiting to be explored through your lens.A setting this rich is a wonderful place to slow down and learn to see. The technical craft is the floor we build on — sharp focus, controlling depth of field to isolate a subject, the settings that give you control — but the real work is composition and intention. Working through the estate's grounds together, you'll learn to find a strong frame within a busy, ornate scene, to work the intimate macro and close-up detail as readily as the wide views of pools, temple and dome, and to read the light and the colour as a harmony rather than chasing the loud, obvious shot. The aim is always an image that's considered and your own, not just a record of a remarkable place.It's a small group of no more than six, taught personally and pitched at exactly your level, with Alan on hand throughout for camera settings, composition and one-to-one guidance, plus image reviews to spark ideas and inspiration on the day. You'll come away with a portfolio of images from one of England's most unusual gardens — and a sharper, more intentional way of seeing detail, composition and light in any garden you photograph. Please note the workshop fee does not include the entrance fee to Sezincote garden and house, which is payable separately on the day.</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1715077805264-XJYPE427XFHYBMW7L4TL/_.jpg</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/sezincote-garden-photography-workshop</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>All Photography Workshops, - half-day photo workshops, Flowering, Macro &amp; Abstract</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>[{"@type": "Offer", "sku": "SQ9859986", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
-        </is>
-      </c>
-      <c r="G45" t="n">
-        <v>1</v>
-      </c>
-      <c r="H45" t="n">
-        <v>50</v>
-      </c>
-      <c r="I45" t="n">
-        <v>50</v>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>SQ9859986</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>SQ9859986</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>event</t>
-        </is>
-      </c>
-      <c r="M45" t="b">
-        <v>0</v>
-      </c>
-      <c r="N45" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>PEAK DISTRICT HEATHER Photography Workshops - 14-15 Aug</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Join me for the Peak District heather displays over this iconic landscape in August - 4hr Heather Peak District Photography Workshops | All levels welcomeSummaryLocation: Peak District - Derbyshire/Staffordshire2026 - Sat 15th Aug 18:15 21:15 - Derbyshire Surprise View2026 - Sun 16th Aug 05:45 08:45 - Staffordshire - The Roaches2027 - Sat 14th Aug 18:15 21:15 - Derbyshire Surprise View2027 - Sun 15th Aug 05:45 08:45 - Staffordshire - The RoachesParticipants: Max 6Fitness: 3. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details HeathersDescription: Every August the moors of the Peak District turn a spectacular purple as the heather comes into bloom, and this Peak District Heather Photography Workshop is your chance to capture that fleeting display at its very best — open to all levels and any camera. Run as short, focused sessions at the magic hours of sunrise and sunset, it pairs one of Britain's most iconic landscapes with its richest seasonal colour, and the low golden light that makes heather and gritstone glow.You can join either of two sessions, or both: a sunset shoot at Surprise View above Hathersage in Derbyshire — one of the finest viewpoints in the Peak, with sweeping heather foregrounds, the Mother Cap stone and famously dark skies — or a sunrise shoot among the dramatic gritstone of The Roaches, Hen Cloud and Ramshaw Rocks in Staffordshire, weathered into extraordinary shapes above a sea of purple moorland.A blaze of purple is more seductive than it is easy, and the real work is learning to see past the obvious. The technical craft is the floor we build on — controlling exposure to hold rich colour and a dramatic sky, and working quickly in the brief light of dawn and dusk — but the focus is on composing with intention: balancing the heather and the gritstone rock forms into a frame with order, working the intimate detail of bloom and weathered stone as readily as the wide moorland vista, and treating the purple, the gold and the low light as a harmony rather than a colour to crank. We shoot two to three locations each session as conditions allow, and the aim throughout is an image with mood and restraint — one that feels like that moor at first or last light.It's a small group of no more than six, taught personally and pitched at exactly your level, with one-to-one guidance in the field throughout. Whether you take the sunset, the sunrise or make a weekend of both, you'll come away with a portfolio of the Peak District's heather at its peak — and a sharper, more intentional way of seeing colour, light and landscape that you can take anywhere. If you're booking both sessions, please arrange your own overnight accommodation near The Roaches for the early sunrise shoot. Please also note this is a seasonal workshop tied to the heather bloom, so exact dates may shift slightly with the season.</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1685361335026-KNDKR6D00CTPUASRDWDV/Surprise%2BView%2B2.jpg</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/peak-district-heather-photography-workshop</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>All Photography Workshops, - half-day photo workshops, Landscape, Flowering</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>[{"@type": "Offer", "sku": "SQ1994489", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Sat 15 Aug 2026 - Hathersage 18:15 - 21:15", "priceSpecification": {"price": "125.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1389945", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Sun 16 Aug 2026 - The Roaches &amp; Ramshaw 05:45 - 08:45", "priceSpecification": {"price": "125.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5395624", "price": "200.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Both sessions - 15 and 16 Aug - sunset and sunrise"}, {"@type": "Offer", "sku": "SQ7900435", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "2027 - Sat 14th Aug 18:15 21:15 - Derbyshire Surprise View"}, {"@type": "Offer", "sku": "SQ4225053", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "2027 - Sun 15 Aug - The Roaches &amp; Ramshaw 05:45 - 08:45"}, {"@type": "Offer", "sku": "SQ8702063", "price": "200.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Both sessions - 14 and 15 Aug - sunset and sunrise"}]</t>
-        </is>
-      </c>
-      <c r="G46" t="n">
-        <v>6</v>
-      </c>
-      <c r="H46" t="n">
-        <v>125</v>
-      </c>
-      <c r="I46" t="n">
-        <v>200</v>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>SQ1994489, SQ1389945, SQ5395624, SQ7900435, SQ4225053, SQ8702063</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>SQ1994489</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>event</t>
-        </is>
-      </c>
-      <c r="M46" t="b">
-        <v>0</v>
-      </c>
-      <c r="N46" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>The Secret of WOODLAND PHOTOGRAPHY- 1-Day Jan, Apr, Aug, Oct</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Simplifying Woodland Photography | Unlocking the Secrets to Capturing the Beauty of woods | Three sessions - Theory - Practical - Editing in one daySummaryLocation: Coventry - CV4 9HWDates: - 10:00 - 16:00Sun 18th Oct - AutumnSun 10th Jan - Winter 2027Sun 2nd May - Spring 2027Sun 1st Aug - Summer 2027Participants: Max 3Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: Digital Camera and TripodPhotography Workshop Event Details: Woodland Photography MasterclassDescription: The Secrets of Woodland Photography is a 1-Day Masterclass in Coventry, open to all levels and any camera. Woodland is the hardest subject there is — chaotic, cluttered, endlessly busy — which is exactly why it's the best place to learn to see. Most people come away with the tangled, cliché shot; this day is about learning to find the order, the light and the quiet beauty hidden within the chaos, and to make woodland images that are calm, intentional and your own.The technical setup matters, but it's only the floor we build on. Rather than a typical walk-and-shoot, the day runs as three connected sessions — theory, practical and editing — so we can go deeper than settings. We start with the thinking behind a strong woodland image and the craft that delivers it: simplifying a busy scene, using light and shadow, choosing what to include and what to leave out. Then you put it into practice on a woodland walk, working the close-up, the macro detail and the abstract as readily as the wider view — reading texture and colour as a harmony, not chasing the loud, over-saturated shot. Finally we review your images together and finish on the editing that brings the quiet colours of the forest to life without shouting.The day runs from Alan's home, which offers three things most workshops can't: instant access to woodland straight from the garden, a comfortable covered and heated space for the presentations and image reviews, and a large screen to study your shots on — so the day works whatever the weather. You'll leave not just with a set of woodland images, but with a way of seeing — light, simplicity and restraint — that changes how you photograph trees, nature and detail wherever you go next.</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714646680135-9EB3PR57B78W9NMZ09JI/Plant+Hill+Woods+%2310+-+Jan+2022.jpg</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/secrets-of-woodland-photography-workshop</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>All Photography Workshops, - one day photo workshops, Macro &amp; Abstract, Woodlands</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>[{"@type": "Offer", "sku": "SQ4894934", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Sun 18th Oct 2026 - 10am - 4pm"}, {"@type": "Offer", "sku": "SQ2827052", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Sun 10 Jan 2027 - 10am - 4pm"}, {"@type": "Offer", "sku": "SQ0512761", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Sun 2nd May 2027 - 10am - 4pm"}, {"@type": "Offer", "sku": "SQ4914997", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Sun 1st Aug 2027 - 10am - 4pm"}]</t>
-        </is>
-      </c>
-      <c r="G47" t="n">
-        <v>4</v>
-      </c>
-      <c r="H47" t="n">
-        <v>150</v>
-      </c>
-      <c r="I47" t="n">
-        <v>150</v>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>SQ4894934, SQ2827052, SQ0512761, SQ4914997</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>SQ4894934</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>event</t>
-        </is>
-      </c>
-      <c r="M47" t="b">
-        <v>0</v>
-      </c>
-      <c r="N47" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>DARTMOOR Photography Workshop - Landscapes - 2nd - 4th Apr</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Join me on this Landscape Dartmoor Photography Workshop - in the iconic woodlands, and landscape of Dartmoor TorsSummaryLocation: Dartmoor - South DevonDates: Fri 2nd - Sun 4th Apr 2027Participants: Max 4Fitness: 3. HardExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details DartmoorDescription: This is a 3-day, 2-night residential landscape photography workshop based around Dartmoor National Park in South Devon, open to all levels from beginner to advanced. Dartmoor is one of England's most atmospheric wild landscapes — a vast sweep of rugged open moor, dramatic granite tors, ancient stunted woodland and serene rivers running through hidden valleys — and across a weekend you'll learn to read and photograph this dramatic terrain in its ever-changing light.Over three days we range across the moor and its woodlands, working a variety of locations as the conditions dictate — from the sculptural granite tors and big moorland vistas to the mossy, otherworldly ancient woods and tumbling rivers. The focus is on three things that make a strong landscape image here: composing order from a wild, expansive scene, controlling exposure and depth of field across big tonal ranges, and timing your shoot to the moods of Dartmoor light, with optional sunrise and sunset shoots and evening picture reviews. Throughout, the emphasis isn't just on the grand vista but on learning to see it — composing with intention, working intimate detail as readily as the wide view, and reading light and weather as a harmony rather than chasing the obvious shot. Be prepared for some longer walks over rougher ground — this is a more demanding workshop that takes you to the moor's most rewarding spots.With a maximum of just four photographers, this is genuinely personal tuition — Alan plans each day around the season and the forecast, and sends a detailed location itinerary a few days ahead. Accommodation, breakfast and evening meals are included, so all you have to think about is your photography, and you'll come away with a varied portfolio of dramatic Dartmoor landscapes — moors, tors and ancient woodland — and the field craft to capture wild country anywhere. An extra night's accommodation is available the day before if required — please request in advance, subject to hotel availability.</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707237329064-99H533NMXCONH5J276LM/dartmoor+photography+workshop.jpg</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/dartmoor-photography-landscape-workshop</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>All Photography Workshops, - weekend residential photo workshops, Landscape</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>[{"@type": "Offer", "sku": "SQ5540434", "price": "875.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29"}]</t>
-        </is>
-      </c>
-      <c r="G48" t="n">
-        <v>1</v>
-      </c>
-      <c r="H48" t="n">
-        <v>875</v>
-      </c>
-      <c r="I48" t="n">
-        <v>875</v>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>SQ5540434</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>SQ5540434</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>event</t>
-        </is>
-      </c>
-      <c r="M48" t="b">
-        <v>0</v>
-      </c>
-      <c r="N48" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Online Photography Classes 121 - Zoom - Package Options</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Private Online Photography Classes (Zoom)Summary - Private Online Photography Classes - Key InformationFormat: Online 1-2-1 via Zoom (free to use)Sessions: Single 1hr lesson, or discounted packages of 4, 6, 8 or 12 hoursAvailability: Standard Mon–Fri, 9am–5pm or Premium - Mon-Sun 9am -9pmValidity: Pay now, book dates later — use within 12 months of purchaseLevel: All levels, beginner to advancedDescription: Private online photography classes tailored to your needs — tuition and support on any aspect of photography, with no other students, so the time you pay for is dedicated entirely to your own style and pace.Equipment: Anything you want to learn or improve on. Sessions run over Zoom, with notes provided; submit images for detailed feedback between lessons.</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/4ac49e77-bfdc-435d-bf46-d82bda3bec91/online+photography+lessons.png</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>https://www.alanranger.com/photography-services-near-me/private-online-photography-classes-zoom</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>1-2-1-private-lessons, photography-tuition</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>[{"@type": "Offer", "sku": "SQ1461156", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Zoom Standard (Weekdays 9-5) - 1 x 1hr - Pay as you go    £50"}, {"@type": "Offer", "sku": "SQ5568703", "price": "170.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Zoom Standard (Weekdays 9-5) - 4 x 1hr (15% Off)          £170"}, {"@type": "Offer", "sku": "SQ6341100", "price": "240.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Zoom Standard (Weekdays 9-5) - 6 x 1hr (20% Off)          £240"}, {"@type": "Offer", "sku": "SQ2281758", "price": "300.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Zoom Standard (Weekdays 9-5) - 8 x 1hr (25% Off)          £300"}, {"@type": "Offer", "sku": "SQ2043258", "price": "450.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Zoom Standard (Weekdays 9-5) - 12 x 1hr (25% Off)         £450"}, {"@type": "Offer", "sku": "SQ6476466", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Zoom Premium (Eve/Weekend 9-9) - 1 x 1hr - Pay as you go  £75"}, {"@type": "Offer", "sku": "SQ4036849", "price": "255.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Zoom Premium (Eve/Weekend 9-9) - 4 x 1hr (15% Off)        £255"}, {"@type": "Offer", "sku": "SQ6369047", "price": "360.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Zoom Premium (Eve/Weekend 9-9) - 6 x 1hr (20% Off)        £360"}, {"@type": "Offer", "sku": "SQ7040572", "price": "450.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Zoom Premium (Eve/Weekend 9-9) - 8 x 1hr (25% Off)        £450"}, {"@type": "Offer", "sku": "SQ6714463", "price": "675.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Zoom Premium (Eve/Weekend 9-9) - 12 x 1hr (25% Off)       £675"}]</t>
-        </is>
-      </c>
-      <c r="G49" t="n">
-        <v>10</v>
-      </c>
-      <c r="H49" t="n">
-        <v>50</v>
-      </c>
-      <c r="I49" t="n">
-        <v>675</v>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>SQ1461156, SQ5568703, SQ6341100, SQ2281758, SQ2043258, SQ6476466, SQ4036849, SQ6369047, SQ7040572, SQ6714463</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>SQ1461156</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="M49" t="b">
-        <v>0</v>
-      </c>
-      <c r="N49" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>1 x 2hr Private Photography Classes - Face to Face Coventry</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>1 × 2hr Private Photography Classes (Face to Face, Coventry)Summary - Private Photography Classes (Face to Face) - Key InformationLocation: Coventry (face to face)Format: Private 1-2-1 tuition, in personSessions: 1 × 2hr classes, scheduled to suit youAvailability: Mon–Fri, 9am–5pmValidity: Pay now, book dates later — you'll be sent a code to book your datesLevel: All levels, beginner to advancedDescription: A package of four private, face-to-face photography classes in Coventry — two hours each, tailored entirely to you and what you want to learn or improve.</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/17054018-4804-4c2d-ad29-c57cba809028/face+to+face+private+photography+classes.png</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>https://www.alanranger.com/photography-services-near-me/2hr-private-photography-classes-2hr</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>1-2-1-private-lessons, photography-classes, photography-tuition, photography-courses</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>[{"@type": "Offer", "sku": "SQ5440373", "price": "120.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29"}]</t>
-        </is>
-      </c>
-      <c r="G50" t="n">
-        <v>1</v>
-      </c>
-      <c r="H50" t="n">
-        <v>120</v>
-      </c>
-      <c r="I50" t="n">
-        <v>120</v>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>SQ5440373</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>SQ5440373</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="M50" t="b">
-        <v>1</v>
-      </c>
-      <c r="N50" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Photography Gift Vouchers | Digital eCard | Email Delivery</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Photography Gift Vouchers | Digital eCard | Email Delivery</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1556527290185-GZJ3ZPC3M7AU34BFFVOE/photography-gift-vouchers.png</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>https://www.alanranger.com/photography-services-near-me/photography-gift-vouchers</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>online;1-2-1-private-lessons;gift-voucher;photography-services;photography-tuition, photography-gift-vouchers;photography-presents</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>[{"@type": "Offer", "sku": "SUP-PHOTOGRAPHY-GIFT-VOUCHERS-DIGITA", "price": "5.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Photography Gift Vouchers | Digital eCard | Email Delivery"}]</t>
-        </is>
-      </c>
-      <c r="G51" t="n">
-        <v>1</v>
-      </c>
-      <c r="H51" t="n">
-        <v>5</v>
-      </c>
-      <c r="I51" t="n">
-        <v>5</v>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>SUP-PHOTOGRAPHY-GIFT-VOUCHERS-DIGITA</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>SUP-PHOTOGRAPHY-GIFT-VOUCHERS-DIGITA</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="M51" t="b">
-        <v>0</v>
-      </c>
-      <c r="N51" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Professional Black and White Photography Course | Coventry</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Professional Black and White Photography Course | Coventry</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1721724334692-7KPD0E90A6E4YZMAR324/black+and+white+photography+course+.jpg</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>https://www.alanranger.com/photography-services-near-me/black-and-white-photography-course</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>photography-courses, beginners-photography-course</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>[{"@type": "Offer", "sku": "SUP-PROFESSIONAL-BLACK-AND-WHITE-PHO", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Professional Black and White Photography Course | Coventry"}]</t>
-        </is>
-      </c>
-      <c r="G52" t="n">
-        <v>1</v>
-      </c>
-      <c r="H52" t="n">
-        <v>150</v>
-      </c>
-      <c r="I52" t="n">
-        <v>150</v>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>SUP-PROFESSIONAL-BLACK-AND-WHITE-PHO</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>SUP-PROFESSIONAL-BLACK-AND-WHITE-PHO</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>course</t>
-        </is>
-      </c>
-      <c r="M52" t="b">
-        <v>0</v>
-      </c>
-      <c r="N52" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Photography Masterclasses-Learn and improve your photography</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Photography Masterclasses-Learn and improve your photography</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1675588273356-8MVS4YXJTH3Y5PRQ36N7/photography-tuition-Package-2.jpg</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>https://www.alanranger.com/photography-services-near-me/photography-masterclasses-coventry</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>photography-classes;photography-courses;photography-tuition, coventry</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>[{"@type": "Offer", "sku": "SUP-PHOTOGRAPHY-MASTERCLASSES-LEARN-", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-09-29", "priceValidUntil": "2027-09-29", "name": "Photography Masterclasses-Learn and improve your photography"}]</t>
-        </is>
-      </c>
-      <c r="G53" t="n">
-        <v>1</v>
-      </c>
-      <c r="H53" t="n">
-        <v>150</v>
-      </c>
-      <c r="I53" t="n">
-        <v>150</v>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>SUP-PHOTOGRAPHY-MASTERCLASSES-LEARN-</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>SUP-PHOTOGRAPHY-MASTERCLASSES-LEARN-</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="M53" t="b">
-        <v>0</v>
-      </c>
-      <c r="N53" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Photography Mentor Online — Monthly Mentoring</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Online photography mentoring with monthly assignments, a personal Lightroom review of your images and 30 practice packs. £20/month, cancel anytime.</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/0ddfe780-871c-4d90-a207-82f053d68ce0/monthly+mentoring+assigments.png</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>https://www.alanranger.com/photography-mentoring-online-assignments</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>photography-mentoring, online-mentoring</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>[{"@type": "Offer", "sku": "SQ-MENTOR-MONTHLY", "price": "20.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-06", "priceValidUntil": "2027-10-06", "name": "Foundation Plus \u2014 Monthly Mentoring \u00a320/mo"}]</t>
-        </is>
-      </c>
-      <c r="G54" t="n">
-        <v>1</v>
-      </c>
-      <c r="H54" t="n">
-        <v>20</v>
-      </c>
-      <c r="I54" t="n">
-        <v>20</v>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>SQ-MENTOR-MONTHLY</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>SQ-MENTOR-MONTHLY</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="M54" t="b">
-        <v>1</v>
-      </c>
-      <c r="N54" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Free Online Photography Course</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Free online photography course from the Alan Ranger photography academy. 60 modules covering camera settings, gear, composition, genres and practical exercises. 14-day free trial; £79/year membership.</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/72b72191-5a88-45c1-85cc-db9f7e0032b7/FREE+online+photography+course</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>https://www.alanranger.com/free-online-photography-course</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>photography-academy, online-course</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>[{"@type": "Offer", "sku": "SQ-ACADEMY-ANNUAL", "price": "79.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-06", "priceValidUntil": "2027-10-06", "name": "Alan Ranger Academy \u2014 Annual Membership \u00a379/yr"}]</t>
-        </is>
-      </c>
-      <c r="G55" t="n">
-        <v>1</v>
-      </c>
-      <c r="H55" t="n">
-        <v>79</v>
-      </c>
-      <c r="I55" t="n">
-        <v>79</v>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>SQ-ACADEMY-ANNUAL</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>SQ-ACADEMY-ANNUAL</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="M55" t="b">
-        <v>0</v>
-      </c>
-      <c r="N55" t="b">
-        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/csv processed/02 – products_cleaned.xlsx
+++ b/csv processed/02 – products_cleaned.xlsx
@@ -498,7 +498,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Abstract and Macro Photography Workshop . Learn about camera settings, lens use, controlling DoF and composition. Various Dates in Warwickshire | Half DaySummaryLocation: WarwickshireDates: Macro Photography WorkshopsMacro Photography - Sun Nov 28th 2026 - 10:30am - 12:30pmMacro Photography - Sat May 1st 2027 - 11am - 1pmMacro Photography - Sun Sep 29th 2027 - 4:00pm - 6:00pmParticipants: Max 4Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: Digital Camera and Tripod, Zoom or Macro LensMacro Photography Workshop Event Details: Macro Photography and AbstractDescription: This Abstract and Macro Photography Workshop takes place at a Warwickshire location and is open to all levels and any camera. Macro is where ordinary surroundings become extraordinary — get close and a tree trunk, a piece of weathered stone or a patch of water reveals shapes, colours, tones and patterns most people walk straight past. The whole session is about learning to see them, and then photograph them with intention.The technical craft matters here — and we'll cover it properly — but it's the floor, not the point. Working around the area together, Alan guides you through the settings that give you control: getting sharp focus and using a macro lens or zoom, controlling depth of field to isolate your subject, and building a composition with real intention. From there the real work begins — training your eye to find the abstract within the ordinary, to read tone, shadow and highlight, and to treat colour as a harmony to compose with rather than a loud effect to chase. The aim is never the obvious close-up everyone takes, but an image that's considered and your own.It's a small group of no more than four, taught personally by an award-winning professional photographer, so every person gets real one-to-one guidance in the field — briefing and set-up, then shooting with reviews and tuition as you go. You'll leave with your own macro and abstract images, and a sharper, more intentional way of seeing detail, colour and light that changes how you photograph everything afterwards.</t>
+          <t>Abstract and Macro Photography Workshop . Learn about camera settings, lens use, controlling DoF and composition. Various Dates in Warwickshire | Half DaySummaryLocation: WarwickshireDates: Macro Photography WorkshopsMacro Photography - Sun Nov 28th 2026 - 10:30am - 1:30pmMacro Photography - Sat May 1st 2027 - 11am - 2pmMacro Photography - Sun Sep 29th 2027 - 2:00pm - 5:00pmParticipants: Max 4Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: Digital Camera and Tripod, Zoom or Macro LensMacro Photography Workshop Event Details: Macro Photography and AbstractDescription: This Abstract and Macro Photography Workshop takes place at a Warwickshire location and is open to all levels and any camera. Macro is where ordinary surroundings become extraordinary — get close and a tree trunk, a piece of weathered stone or a patch of water reveals shapes, colours, tones and patterns most people walk straight past. The whole session is about learning to see them, and then photograph them with intention.The technical craft matters here — and we'll cover it properly — but it's the floor, not the point. Working around the area together, Alan guides you through the settings that give you control: getting sharp focus and using a macro lens or zoom, controlling depth of field to isolate your subject, and building a composition with real intention. From there the real work begins — training your eye to find the abstract within the ordinary, to read tone, shadow and highlight, and to treat colour as a harmony to compose with rather than a loud effect to chase. The aim is never the obvious close-up everyone takes, but an image that's considered and your own.It's a small group of no more than four, taught personally by an award-winning professional photographer, so every person gets real one-to-one guidance in the field — briefing and set-up, then shooting with reviews and tuition as you go. You'll leave with your own macro and abstract images, and a sharper, more intentional way of seeing detail, colour and light that changes how you photograph everything afterwards.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -518,17 +518,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9970442", "price": "65.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Sun Nov 28th 2026 - 10:30am - 12:30pm"}, {"@type": "Offer", "sku": "SQ2051466", "price": "65.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Sat May 1st 2027 - 11am - 1pm"}, {"@type": "Offer", "sku": "SQ8660736", "price": "65.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Sun Sep 29th 2027 - 4:00pm - 6:00pm"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9970442", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Sun Nov 28th 2026 - 10:30am - 1:30pm"}, {"@type": "Offer", "sku": "SQ2051466", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Sat May 1st 2027 - 11am - 2pm"}, {"@type": "Offer", "sku": "SQ8660736", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Sun Sep 29th 2027 - 2:00pm - 5:00pm"}]</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>3</v>
       </c>
       <c r="H2" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="I2" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Annual Pick N Mix Subscription: pay once up-front, from £1,200, for your first year of photography development. 15% off courses, workshops and 1-to-1s, 4 one-hour quarterly 1-2-1 reviews and free Photography Academy membership for 12 months</t>
+          <t>Annual Picknmix: pay once, from £1,200, for your photography development. 15% off courses, workshops and 1-to-1s, 4 x1 hour reviews and free Academy membership</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -574,7 +574,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ0754560", "price": "1200.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "1 x £1200 = £1200"}, {"@type": "Offer", "sku": "SQ7502565", "price": "1500.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "1 x £1500 = £1500"}, {"@type": "Offer", "sku": "SQ1485137", "price": "2000.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "1 x £2000 = £2000"}, {"@type": "Offer", "sku": "SQ7001156", "price": "2500.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "1 x £2500 = £2500"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ0754560", "price": "1200.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "1 x £1200 = £1200"}, {"@type": "Offer", "sku": "SQ7502565", "price": "1500.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "1 x £1500 = £1500"}, {"@type": "Offer", "sku": "SQ1485137", "price": "2000.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "1 x £2000 = £2000"}, {"@type": "Offer", "sku": "SQ7001156", "price": "2500.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "1 x £2500 = £2500"}]</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -605,12 +605,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BATSFORD Arboretum Autumn Photography Workshops 23 - 29 Oct</t>
+          <t>BATSFORD Arboretum Autumn Photography Workshops 23 - 31 Oct</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Batsford Arboretum Photography Workshops in autumn. Enjoy the colour and expert photographic guidance | Half or One Day Sessions | Any Level and CameraSummaryLocation: Batsford Arboretum - GloucestershireDates: Fri 23 Oct –Thu 29 2026Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless CameraPhotography Workshop Event Batsford ArboretumDescription: For nearly fifteen years I've returned to Batsford Arboretum each autumn, and in that time I've come to know every corner of it — which spot works at which hour, where the light falls and the angles that turn one of Britain's finest tree collections into a photograph rather than a snapshot. This workshop is built on that knowledge. Open to all levels and any camera, it's a chance to photograph Batsford's autumn colour with someone who can put you in the right place at the right time, so you can spend your energy on the thing that actually matters: seeing.Because that's where this workshop really lives. We'll cover the technical setup — exposure, depth of field, the settings that give you control — but that's only the floor. The real work is learning to look: to compose with intention and move beyond the cliché shot everyone else comes home with, to find the close-up, the macro detail and the quiet abstract as readily as the wide vista, and above all to read light, texture and colour as a harmony rather than chasing the over-saturated "look how vivid this is" image. Colour handled with restraint and relationship will always outlast colour shouted.With small numbers and genuine one-to-one attention throughout, you'll have the time and space to slow down and work properly — and you can choose a half-day morning or afternoon session, or a full day in the colour. You'll leave not just with a set of strong autumn images, but with a way of seeing — light, texture and composition — that changes how you photograph colour, woodland and the natural world wherever you go next.Good to know: the workshop price includes entrance to the Arboretum. On the early morning session we have exclusive access before the gardens open to the public — the quiet best light of the day, with the place to ourselves. A grab-and-go breakfast is available from around 9:30am, and the café and outdoor snack bar are open through the day for lunch and refreshments, with toilets on site by the reception area.</t>
+          <t>Batsford Arboretum photography workshops in autumn: a guided day, 9:30am-3pm, in 60 acres of colour with Alan Ranger. £150 incl. entrance. Max 6, any level.SummaryLocation: Batsford Arboretum - GloucestershireDates: Sat 23 Oct and Sun 24 Oct 2027Sat 30 Oct and Sun 31 Oct 2027Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless CameraPhotography Workshop Event Batsford ArboretumDescription: For fifteen autumns I’ve guided photographers through Batsford Arboretum’s 60 acres — more than 300 of them — and I know almost every inch of it: which tree, which shrub, which corner comes alive at which hour, and exactly where the light falls as the day moves round. This workshop is built on that knowledge. Open to all levels and any camera, it’s a chance to photograph Batsford’s autumn colour with a seasoned professional who puts you in the right place at the right time, so you can spend your energy on the thing that actually matters: seeing.Because that's where this workshop really lives. We'll cover the technical setup — exposure, depth of field, the settings that give you control — but that's only the floor. The real work is learning to look: to compose with intention and move beyond the cliché shot everyone else comes home with, to find the close-up, the macro detail and the quiet abstract as readily as the wide vista, and above all to read light, texture and colour as a harmony rather than chasing the over-saturated "look how vivid this is" image. Colour handled with restraint and relationship will always outlast colour shouted.With a group of no more than six and genuine one-to-one attention throughout, you’ll have the time and space to slow down and work properly across a guided day paced around the light. You’ll leave not just with a set of strong autumn images, but with a way of seeing — light, texture and composition — that changes how you photograph colour, woodland and the natural world wherever you go next.Good to know: the £150 workshop price includes entrance to the Arboretum. We meet at 9:30am in the Batsford café for a breakfast briefing (breakfast and drinks at your own cost), head into the arboretum at 10am, break for lunch at 12:30, then photograph a different part of the arboretum in the afternoon light, aiming to be back at the café by 3pm. The café and outdoor snack bar are open through the day, with toilets on site by the reception area.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -625,26 +625,26 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - half-day photo workshops, - one day photo workshops, Landscape, Woodlands, autumn</t>
+          <t>All Photography Workshops, - one day photo workshops, Landscape, Woodlands, autumn</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ0818501", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Fri 23  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7647904", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Fri 23 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9436105", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Fri 23 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1204772", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Sat 24  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9290465", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Sat 24 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7375084", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Sat 24 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0264308", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Sun 25 Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9938663", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Sun 25 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0693365", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Sun 25 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3442432", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Thu 29  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8197555", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Thu 29 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9853668", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Thu 29 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ0818501", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Sat 23 Oct 2027 - 9:30 - 15:00"}, {"@type": "Offer", "sku": "SQ1204772", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Sun 24 Oct 2027 - 9:30 - 15:00"}, {"@type": "Offer", "sku": "SQ7375084", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Sat 30 Oct 2027 - 9:30 - 15:00"}, {"@type": "Offer", "sku": "SQ0264308", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Sun 31 Oct 2027 - 9:30 - 15:00"}]</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="H4" t="n">
-        <v>99</v>
+        <v>150</v>
       </c>
       <c r="I4" t="n">
         <v>150</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>SQ0818501, SQ7647904, SQ9436105, SQ1204772, SQ9290465, SQ7375084, SQ0264308, SQ9938663, SQ0693365, SQ3442432, SQ8197555, SQ9853668</t>
+          <t>SQ0818501, SQ1204772, SQ7375084, SQ0264308</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ5616379", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "3wks Mondays - Nov 9 - Nov 23 Coventry"}, {"@type": "Offer", "sku": "SQ3231903", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "3wks Tuesdays - Dec 1 - Dec 15 Coventry"}, {"@type": "Offer", "sku": "SQ5559634", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "3wks Wednesdays - Jan 13 - Jan 27 Coventry"}, {"@type": "Offer", "sku": "SQ0659870", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "3wks Thursdays - Jan 28 - Feb 11 Coventry"}, {"@type": "Offer", "sku": "SQ0358019", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "3wks Tuesdays - Mar 2 - Mar 16 Coventry"}, {"@type": "Offer", "sku": "SQ0618983", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "3wks Thursdays  Apr 1 - Apr 15 Coventry"}, {"@type": "Offer", "sku": "SQ5714218", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "3wks Wednesdays May 12 - May 26 Coventry"}, {"@type": "Offer", "sku": "SQ7630533", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "3wks Mondays  - Jun 7  - Jun 21 Coventry"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ5616379", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "3wks Mondays - Nov 9 - Nov 23 Coventry"}, {"@type": "Offer", "sku": "SQ3231903", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "3wks Tuesdays - Dec 1 - Dec 15 Coventry"}, {"@type": "Offer", "sku": "SQ5559634", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "3wks Wednesdays - Jan 13 - Jan 27 Coventry"}, {"@type": "Offer", "sku": "SQ0659870", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "3wks Thursdays - Jan 28 - Feb 11 Coventry"}, {"@type": "Offer", "sku": "SQ0358019", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "3wks Tuesdays - Mar 2 - Mar 16 Coventry"}, {"@type": "Offer", "sku": "SQ0618983", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "3wks Thursdays  Apr 1 - Apr 15 Coventry"}, {"@type": "Offer", "sku": "SQ5714218", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "3wks Wednesdays May 12 - May 26 Coventry"}, {"@type": "Offer", "sku": "SQ7630533", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "3wks Mondays  - Jun 7  - Jun 21 Coventry"}]</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -742,7 +742,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ2592535", "price": "195.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ2592535", "price": "195.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25"}]</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -798,7 +798,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8599409", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Tue 20 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7560082", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Tue 20 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7443277", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Tue 20 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1660230", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Thu 22 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1568285", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Thu 22 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5411810", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Thu 22 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1318075", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Sat 24 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8270632", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Sat 24 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ4260038", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Sat 24 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ6145280", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Sun 25 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2267773", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Sun 25 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2428415", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Sun 25 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1102782", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Tue 27 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5885147", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Tue 27 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3102560", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Tue 27 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7100218", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Thu 29 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2446216", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Thu 29 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3086312", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Thu 29 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8599409", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Tue 20 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7560082", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Tue 20 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7443277", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Tue 20 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1660230", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Thu 22 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1568285", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Thu 22 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5411810", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Thu 22 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1318075", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Sat 24 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8270632", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Sat 24 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ4260038", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Sat 24 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ6145280", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Sun 25 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2267773", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Sun 25 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2428415", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Sun 25 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1102782", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Tue 27 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5885147", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Tue 27 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3102560", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Tue 27 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7100218", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Thu 29 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2446216", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Thu 29 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3086312", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Thu 29 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -854,7 +854,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ5650040", "price": "30.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ5650040", "price": "30.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25"}]</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -910,7 +910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ5540434", "price": "875.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ5540434", "price": "875.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25"}]</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -966,7 +966,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ2754105", "price": "925.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ2754105", "price": "925.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25"}]</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ0105911", "price": "135.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "16x12 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ4206024", "price": "177.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "24x16 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ0781804", "price": "219.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "30x20 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ3982814", "price": "306.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "36x24 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ8209269", "price": "336.65", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "40x30 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ7901040", "price": "414.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "48x36 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ7260825", "price": "459.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "60x40 Canvas Wrap Round"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ0105911", "price": "135.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "16x12 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ4206024", "price": "177.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "24x16 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ0781804", "price": "219.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "30x20 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ3982814", "price": "306.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "36x24 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ8209269", "price": "336.65", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "40x30 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ7901040", "price": "414.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "48x36 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ7260825", "price": "459.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "60x40 Canvas Wrap Round"}]</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ4872440", "price": "50.57", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "16x12 Print"}, {"@type": "Offer", "sku": "SQ0453600", "price": "95.78", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "24x16 Print"}, {"@type": "Offer", "sku": "SQ7485354", "price": "138.86", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "30x20 Print"}, {"@type": "Offer", "sku": "SQ0167262", "price": "161.38", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "36x24 Print"}, {"@type": "Offer", "sku": "SQ1664775", "price": "217.23", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "40x30 Print"}, {"@type": "Offer", "sku": "SQ0377820", "price": "305.05", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "48x36 Print"}, {"@type": "Offer", "sku": "SQ8780582", "price": "416.85", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "60x40 Print"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ4872440", "price": "50.57", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "16x12 Print"}, {"@type": "Offer", "sku": "SQ0453600", "price": "95.78", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "24x16 Print"}, {"@type": "Offer", "sku": "SQ7485354", "price": "138.86", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "30x20 Print"}, {"@type": "Offer", "sku": "SQ0167262", "price": "161.38", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "36x24 Print"}, {"@type": "Offer", "sku": "SQ1664775", "price": "217.23", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "40x30 Print"}, {"@type": "Offer", "sku": "SQ0377820", "price": "305.05", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "48x36 Print"}, {"@type": "Offer", "sku": "SQ8780582", "price": "416.85", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "60x40 Print"}]</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ6583676", "price": "360.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "4 x 2hr sessions - weekday daytime", "priceSpecification": {"price": "360.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ6583676", "price": "360.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "4 x 2hr sessions - weekday daytime", "priceSpecification": {"price": "360.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ6825544", "price": "133.85", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "16x12 Print (with Frame 20x16)"}, {"@type": "Offer", "sku": "SQ3786581", "price": "191.50", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "24x16 Print (with Frame 30x20)"}, {"@type": "Offer", "sku": "SQ1355351", "price": "267.43", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "30x20 Print (with Frame 40x30)"}, {"@type": "Offer", "sku": "SQ0156134", "price": "356.90", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "36x24 Print (with Frame 48x36)"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ6825544", "price": "133.85", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "16x12 Print (with Frame 20x16)"}, {"@type": "Offer", "sku": "SQ3786581", "price": "191.50", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "24x16 Print (with Frame 30x20)"}, {"@type": "Offer", "sku": "SQ1355351", "price": "267.43", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "30x20 Print (with Frame 40x30)"}, {"@type": "Offer", "sku": "SQ0156134", "price": "356.90", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "36x24 Print (with Frame 48x36)"}]</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ0939451", "price": "45.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Sun May 23rd 2027 - 15:00 - 17:00"}, {"@type": "Offer", "sku": "SQ3644687", "price": "45.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Sun Jul 11th 2027 - 15:00 - 17:00"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ0939451", "price": "45.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Sun May 23rd 2027 - 15:00 - 17:00"}, {"@type": "Offer", "sku": "SQ3644687", "price": "45.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Sun Jul 11th 2027 - 15:00 - 17:00"}]</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9898707", "price": "400.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "priceSpecification": {"price": "400.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9898707", "price": "400.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "priceSpecification": {"price": "400.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ5158309", "price": "1075.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Fri 13 Nov - 15 Nov - 3 Days 2026", "priceSpecification": {"price": "1075.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9016326", "price": "1075.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Fri 22 Jan - 24 Jan - 3 Days 2027"}, {"@type": "Offer", "sku": "SQ9100538", "price": "1075.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Fri 24 Sep - 26 Sep - 3 Days 2027", "priceSpecification": {"price": "1075.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ5158309", "price": "1075.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Fri 13 Nov - 15 Nov - 3 Days 2026", "priceSpecification": {"price": "1075.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9016326", "price": "1075.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Fri 22 Jan - 24 Jan - 3 Days 2027"}, {"@type": "Offer", "sku": "SQ9100538", "price": "1075.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Fri 24 Sep - 26 Sep - 3 Days 2027", "priceSpecification": {"price": "1075.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1709626967694-M4DJSC9GYR1R1LZFYBUF/Padley+Gorge+%2304+-+Mar+2024.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/f6bd9c81-8d71-40ff-8af4-680c9b2b5874/Bolehill+Oct+2025+-+%2301.jpg</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ3794821", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Padley and Bolehill Sat 17th Oct  2026 09:30am - 4:00pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8457424", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Padley and Bolehill Sun 1st Nov  2026 09:30am - 4:00pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9037810", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Padley and Bolehill Sat 7th Nov  2026 09:30am - 4:00pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2363666", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Padley and Bolehill Sat 22nd May 2027 - 09:30 - 16:00", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8457424", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Padley and Bolehill Sun 1st Nov  2026 09:30am - 4:00pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9037810", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Padley and Bolehill Sat 7th Nov  2026 09:30am - 4:00pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2363666", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Padley and Bolehill Sat 22nd May 2027 - 09:30 - 16:00", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3794821", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Padley and Bolehill Sat 16th Oct  2027 09:30am - 4:00pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>SQ3794821, SQ8457424, SQ9037810, SQ2363666</t>
+          <t>SQ8457424, SQ9037810, SQ2363666, SQ3794821</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>SQ3794821</t>
+          <t>SQ8457424</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ3856406", "price": "950.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ3856406", "price": "950.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25"}]</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8747213", "price": "1075.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8747213", "price": "1075.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25"}]</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8503376", "price": "975.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8503376", "price": "975.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25"}]</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ7526725", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Coventry 3 wks - Mon 7 Sep - 21 Sep 2026"}, {"@type": "Offer", "sku": "SQ6831161", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Coventry 3 wks - Thu 12 Nov - 26 Nov 2026"}, {"@type": "Offer", "sku": "SQ1021857", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Coventry 3 wks - Tue 12 Jan - 26 Jan 2027"}, {"@type": "Offer", "sku": "SQ3349262", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Coventry 3 wks - Thu 6 May - 20 May 2027"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ7526725", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Coventry 3 wks - Mon 7 Sep - 21 Sep 2026"}, {"@type": "Offer", "sku": "SQ6831161", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Coventry 3 wks - Thu 12 Nov - 26 Nov 2026"}, {"@type": "Offer", "sku": "SQ1021857", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Coventry 3 wks - Tue 12 Jan - 26 Jan 2027"}, {"@type": "Offer", "sku": "SQ3349262", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Coventry 3 wks - Thu 6 May - 20 May 2027"}]</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ0932604", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Mon 22 Mar 2027 - 18:00 - 20:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1178418", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Wed 14 Apr 2027 - 18:30 - 20:30", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9140400", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Wed 5 May 2027 - 18:00 - 20:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8220723", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Wed 22 Sep 2027 - 17:45 - 19:45", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ0932604", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Mon 22 Mar 2027 - 18:00 - 20:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1178418", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Wed 14 Apr 2027 - 18:30 - 20:30", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9140400", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Wed 5 May 2027 - 18:00 - 20:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8220723", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Wed 22 Sep 2027 - 17:45 - 19:45", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9080164", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Sat 6th Mar 2027 - 10:00 - 13:30"}, {"@type": "Offer", "sku": "SQ6636860", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Fri 14th May 2027 - 10:00 - 13:30"}, {"@type": "Offer", "sku": "SQ8778402", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Sat 9th Oct 2027 - 10:00 - 13:30"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9080164", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Sat 6th Mar 2027 - 10:00 - 13:30"}, {"@type": "Offer", "sku": "SQ6636860", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Fri 14th May 2027 - 10:00 - 13:30"}, {"@type": "Offer", "sku": "SQ8778402", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Sat 9th Oct 2027 - 10:00 - 13:30"}]</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9466277", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9466277", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25"}]</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Monthly Pick N Mix Subscription: your first year of photography development from £50 a month (£600 plan). 10% off courses, workshops and 1-to-1s, 4 quarterly 1-2-1 reviews and free Photography Academy membership for 12 months. Interest-free</t>
+          <t>Monthly PicknMix from £50 a month. 10% off courses, workshops and 1-to-1s, 4 quarterly 1-2-1 reviews and free Academy membership for 12 months. Interest-free</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ3113323", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "12 x £50 = £600"}, {"@type": "Offer", "sku": "SQ4824271", "price": "60.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "12 x £60 = £720"}, {"@type": "Offer", "sku": "SQ5162846", "price": "65.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "12 x £65 = £780"}, {"@type": "Offer", "sku": "SQ0960457", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "12 x £75 = £900"}, {"@type": "Offer", "sku": "SQ6021981", "price": "85.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "12 x £85 = £1020"}, {"@type": "Offer", "sku": "SQ3596605", "price": "100.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "12 x £100 = £1200"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ3113323", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "12 x £50 = £600"}, {"@type": "Offer", "sku": "SQ4824271", "price": "60.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "12 x £60 = £720"}, {"@type": "Offer", "sku": "SQ5162846", "price": "65.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "12 x £65 = £780"}, {"@type": "Offer", "sku": "SQ0960457", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "12 x £75 = £900"}, {"@type": "Offer", "sku": "SQ6021981", "price": "85.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "12 x £85 = £1020"}, {"@type": "Offer", "sku": "SQ3596605", "price": "100.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "12 x £100 = £1200"}]</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ7900435", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "2027 - Sat 14th Aug 18:15 21:15 - Derbyshire Surprise View"}, {"@type": "Offer", "sku": "SQ4225053", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "2027 - Sun 15 Aug - The Roaches &amp; Ramshaw 05:45 - 08:45"}, {"@type": "Offer", "sku": "SQ8702063", "price": "200.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Both sessions - 14 and 15 Aug - sunset and sunrise"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ7900435", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "2027 - Sat 14th Aug 18:15 21:15 - Derbyshire Surprise View"}, {"@type": "Offer", "sku": "SQ4225053", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "2027 - Sun 15 Aug - The Roaches &amp; Ramshaw 05:45 - 08:45"}, {"@type": "Offer", "sku": "SQ8702063", "price": "200.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Both sessions - 14 and 15 Aug - sunset and sunrise"}]</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ0796814", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Mon 5th Oct 2026 - 17:30 - 19:45", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9554270", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Tue 13th Apr 2027 - 18:15 - 20:15", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5307067", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Mon 10th May 2027 - 18:30 - 20:30", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3572999", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Mon 6th Sep 2027 - 18:00 - 20:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ0796814", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Mon 5th Oct 2026 - 17:30 - 19:45", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9554270", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Tue 13th Apr 2027 - 18:15 - 20:15", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5307067", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Mon 10th May 2027 - 18:30 - 20:30", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3572999", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Mon 6th Sep 2027 - 18:00 - 20:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ6748367", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Sat 3rd Jul 2027 - 18:00 20:45"}, {"@type": "Offer", "sku": "SQ7542811", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Sat 10th Jul 2027 - 18:00 20:45"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ6748367", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Sat 3rd Jul 2027 - 18:00 20:45"}, {"@type": "Offer", "sku": "SQ7542811", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Sat 10th Jul 2027 - 18:00 20:45"}]</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ1461156", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Zoom Standard (Weekdays 9-5) - 1 x 1hr - Pay as you go    £50"}, {"@type": "Offer", "sku": "SQ5568703", "price": "170.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Zoom Standard (Weekdays 9-5) - 4 x 1hr (15% Off)          £170"}, {"@type": "Offer", "sku": "SQ6341100", "price": "240.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Zoom Standard (Weekdays 9-5) - 6 x 1hr (20% Off)          £240"}, {"@type": "Offer", "sku": "SQ2281758", "price": "300.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Zoom Standard (Weekdays 9-5) - 8 x 1hr (25% Off)          £300"}, {"@type": "Offer", "sku": "SQ2043258", "price": "450.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Zoom Standard (Weekdays 9-5) - 12 x 1hr (25% Off)         £450"}, {"@type": "Offer", "sku": "SQ6476466", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Zoom Premium (Eve/Weekend 9-9) - 1 x 1hr - Pay as you go  £75"}, {"@type": "Offer", "sku": "SQ4036849", "price": "255.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Zoom Premium (Eve/Weekend 9-9) - 4 x 1hr (15% Off)        £255"}, {"@type": "Offer", "sku": "SQ6369047", "price": "360.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Zoom Premium (Eve/Weekend 9-9) - 6 x 1hr (20% Off)        £360"}, {"@type": "Offer", "sku": "SQ7040572", "price": "450.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Zoom Premium (Eve/Weekend 9-9) - 8 x 1hr (25% Off)        £450"}, {"@type": "Offer", "sku": "SQ6714463", "price": "675.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Zoom Premium (Eve/Weekend 9-9) - 12 x 1hr (25% Off)       £675"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ1461156", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Zoom Standard (Weekdays 9-5) - 1 x 1hr - Pay as you go    £50"}, {"@type": "Offer", "sku": "SQ5568703", "price": "170.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Zoom Standard (Weekdays 9-5) - 4 x 1hr (15% Off)          £170"}, {"@type": "Offer", "sku": "SQ6341100", "price": "240.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Zoom Standard (Weekdays 9-5) - 6 x 1hr (20% Off)          £240"}, {"@type": "Offer", "sku": "SQ2281758", "price": "300.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Zoom Standard (Weekdays 9-5) - 8 x 1hr (25% Off)          £300"}, {"@type": "Offer", "sku": "SQ2043258", "price": "450.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Zoom Standard (Weekdays 9-5) - 12 x 1hr (25% Off)         £450"}, {"@type": "Offer", "sku": "SQ6476466", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Zoom Premium (Eve/Weekend 9-9) - 1 x 1hr - Pay as you go  £75"}, {"@type": "Offer", "sku": "SQ4036849", "price": "255.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Zoom Premium (Eve/Weekend 9-9) - 4 x 1hr (15% Off)        £255"}, {"@type": "Offer", "sku": "SQ6369047", "price": "360.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Zoom Premium (Eve/Weekend 9-9) - 6 x 1hr (20% Off)        £360"}, {"@type": "Offer", "sku": "SQ7040572", "price": "450.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Zoom Premium (Eve/Weekend 9-9) - 8 x 1hr (25% Off)        £450"}, {"@type": "Offer", "sku": "SQ6714463", "price": "675.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Zoom Premium (Eve/Weekend 9-9) - 12 x 1hr (25% Off)       £675"}]</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Quarterly Pick N Mix Subscription: your first year of photography development from £250 a quarter (£1,000 plan). 12.5% off courses, workshops and 1-to-1s, 4 one-hour quarterly 1-2-1 reviews and free Photography Academy membership for 12 months. Interest-free</t>
+          <t>Qtrly PicknMix: photography development from £250 a QTR 12.5% off courses, workshops and 1-to-1s, 4 1hr quarterly 1-2-1 reviews and free Academy membership</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ4217445", "price": "250.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "4 x £250 = £1000"}, {"@type": "Offer", "sku": "SQ6277577", "price": "300.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "4 x £300 = £1200"}, {"@type": "Offer", "sku": "SQ7788516", "price": "350.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "4 x £350 = £1400"}, {"@type": "Offer", "sku": "SQ5124608", "price": "400.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "4 x 400 = £1600"}, {"@type": "Offer", "sku": "SQ2657628", "price": "500.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "4 x £500 = £2000"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ4217445", "price": "250.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "4 x £250 = £1000"}, {"@type": "Offer", "sku": "SQ6277577", "price": "300.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "4 x £300 = £1200"}, {"@type": "Offer", "sku": "SQ7788516", "price": "350.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "4 x £350 = £1400"}, {"@type": "Offer", "sku": "SQ5124608", "price": "400.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "4 x 400 = £1600"}, {"@type": "Offer", "sku": "SQ2657628", "price": "500.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "4 x £500 = £2000"}]</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ7839038", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Mon- Fri 9am-5pm 1 x 1hr"}, {"@type": "Offer", "sku": "SQ3867813", "price": "170.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Mon- Fri 9am-5pm 4 x 1hr"}, {"@type": "Offer", "sku": "SQ8903198", "price": "240.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Mon- Fri 9am-5pm 6 x 1hr"}, {"@type": "Offer", "sku": "SQ4831915", "price": "300.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Mon- Fri 9am-5pm  8x 1hr"}, {"@type": "Offer", "sku": "SQ1077689", "price": "450.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Mon- Fri 9am-5pm 12 x 1hr"}, {"@type": "Offer", "sku": "SQ8233730", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Mon- Sun 9am-9pm 1 x 1hr"}, {"@type": "Offer", "sku": "SQ9139531", "price": "255.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Mon- Sun 9am-9pm 4 x 1hr"}, {"@type": "Offer", "sku": "SQ0776423", "price": "360.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Mon- Sun 9am-9pm 6 x 1hr"}, {"@type": "Offer", "sku": "SQ2385997", "price": "450.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Mon- Sun 9am-9pm 8 x 1hr"}, {"@type": "Offer", "sku": "SQ9440259", "price": "675.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Mon- Sun 9am-9pm 12 x 1hr"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ7839038", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Mon- Fri 9am-5pm 1 x 1hr"}, {"@type": "Offer", "sku": "SQ3867813", "price": "170.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Mon- Fri 9am-5pm 4 x 1hr"}, {"@type": "Offer", "sku": "SQ8903198", "price": "240.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Mon- Fri 9am-5pm 6 x 1hr"}, {"@type": "Offer", "sku": "SQ4831915", "price": "300.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Mon- Fri 9am-5pm  8x 1hr"}, {"@type": "Offer", "sku": "SQ1077689", "price": "450.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Mon- Fri 9am-5pm 12 x 1hr"}, {"@type": "Offer", "sku": "SQ8233730", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Mon- Sun 9am-9pm 1 x 1hr"}, {"@type": "Offer", "sku": "SQ9139531", "price": "255.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Mon- Sun 9am-9pm 4 x 1hr"}, {"@type": "Offer", "sku": "SQ0776423", "price": "360.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Mon- Sun 9am-9pm 6 x 1hr"}, {"@type": "Offer", "sku": "SQ2385997", "price": "450.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Mon- Sun 9am-9pm 8 x 1hr"}, {"@type": "Offer", "sku": "SQ9440259", "price": "675.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Mon- Sun 9am-9pm 12 x 1hr"}]</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ4894934", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Sun 18th Oct 2026 - 10am - 4pm"}, {"@type": "Offer", "sku": "SQ2827052", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Sun 10 Jan 2027 - 10am - 4pm"}, {"@type": "Offer", "sku": "SQ0512761", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Sun 2nd May 2027 - 10am - 4pm"}, {"@type": "Offer", "sku": "SQ4914997", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Sun 1st Aug 2027 - 10am - 4pm"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ2827052", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Sun 10 Jan 2027 - 10am - 4pm"}, {"@type": "Offer", "sku": "SQ0512761", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Sun 2nd May 2027 - 10am - 4pm"}, {"@type": "Offer", "sku": "SQ4914997", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Sun 1st Aug 2027 - 10am - 4pm"}, {"@type": "Offer", "sku": "SQ4894934", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Sun 17th Oct 2027 - 10am - 4pm"}]</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>SQ4894934, SQ2827052, SQ0512761, SQ4914997</t>
+          <t>SQ2827052, SQ0512761, SQ4914997, SQ4894934</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>SQ4894934</t>
+          <t>SQ2827052</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ2176971", "price": "995.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "priceSpecification": {"price": "995.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ2176971", "price": "995.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "priceSpecification": {"price": "995.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ4066377", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ4066377", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -2422,7 +2422,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ5697158", "price": "695.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ5697158", "price": "695.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25"}]</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ1654264", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Fri Jan 2 Hay Woods - Solihull"}, {"@type": "Offer", "sku": "SQ1288994", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Mon Feb 2 - Tile Hill Nature Reserve - Coventry"}, {"@type": "Offer", "sku": "SQ0063623", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Sun May 3 - Millisons Wood, Meriden"}, {"@type": "Offer", "sku": "SQ6524101", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Fri Oct 16 - Piles Coppice, Coventry"}, {"@type": "Offer", "sku": "SQ7078023", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Fri Nov 6 - Crackley Wood, Kenilworth"}, {"@type": "Offer", "sku": "SQ3819844", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12", "name": "Fri Dec 4 - Hay Wood - Lapworth"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ1654264", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Fri Jan 2 Hay Woods - Solihull"}, {"@type": "Offer", "sku": "SQ1288994", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Mon Feb 2 - Tile Hill Nature Reserve - Coventry"}, {"@type": "Offer", "sku": "SQ0063623", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Sun May 3 - Millisons Wood, Meriden"}, {"@type": "Offer", "sku": "SQ6524101", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Fri Oct 16 - Piles Coppice, Coventry"}, {"@type": "Offer", "sku": "SQ7078023", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Fri Nov 6 - Crackley Wood, Kenilworth"}, {"@type": "Offer", "sku": "SQ3819844", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Fri Dec 4 - Hay Wood - Lapworth"}]</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9211910", "price": "895.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-12", "priceValidUntil": "2027-10-12"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9211910", "price": "895.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25"}]</t>
         </is>
       </c>
       <c r="G38" t="n">

--- a/csv processed/02 – products_cleaned.xlsx
+++ b/csv processed/02 – products_cleaned.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L38"/>
+  <dimension ref="A1:L39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,7 +518,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9970442", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Sun Nov 28th 2026 - 10:30am - 1:30pm"}, {"@type": "Offer", "sku": "SQ2051466", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Sat May 1st 2027 - 11am - 2pm"}, {"@type": "Offer", "sku": "SQ8660736", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Sun Sep 29th 2027 - 2:00pm - 5:00pm"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9970442", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "Sun Nov 28th 2026 - 10:30am - 1:30pm"}, {"@type": "Offer", "sku": "SQ2051466", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "Sat May 1st 2027 - 11am - 2pm"}, {"@type": "Offer", "sku": "SQ8660736", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "Sun Sep 29th 2027 - 2:00pm - 5:00pm"}]</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -574,7 +574,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ0754560", "price": "1200.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "1 x £1200 = £1200"}, {"@type": "Offer", "sku": "SQ7502565", "price": "1500.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "1 x £1500 = £1500"}, {"@type": "Offer", "sku": "SQ1485137", "price": "2000.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "1 x £2000 = £2000"}, {"@type": "Offer", "sku": "SQ7001156", "price": "2500.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "1 x £2500 = £2500"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ0754560", "price": "1200.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "1 x £1200 = £1200"}, {"@type": "Offer", "sku": "SQ7502565", "price": "1500.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "1 x £1500 = £1500"}, {"@type": "Offer", "sku": "SQ1485137", "price": "2000.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "1 x £2000 = £2000"}, {"@type": "Offer", "sku": "SQ7001156", "price": "2500.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "1 x £2500 = £2500"}]</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -630,7 +630,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ0818501", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Sat 23 Oct 2027 - 9:30 - 15:00"}, {"@type": "Offer", "sku": "SQ1204772", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Sun 24 Oct 2027 - 9:30 - 15:00"}, {"@type": "Offer", "sku": "SQ7375084", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Sat 30 Oct 2027 - 9:30 - 15:00"}, {"@type": "Offer", "sku": "SQ0264308", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Sun 31 Oct 2027 - 9:30 - 15:00"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ0818501", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "Sat 23 Oct 2027 - 9:30 - 15:00"}, {"@type": "Offer", "sku": "SQ1204772", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "Sun 24 Oct 2027 - 9:30 - 15:00"}, {"@type": "Offer", "sku": "SQ7375084", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "Sat 30 Oct 2027 - 9:30 - 15:00"}, {"@type": "Offer", "sku": "SQ0264308", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "Sun 31 Oct 2027 - 9:30 - 15:00"}]</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -686,7 +686,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ5616379", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "3wks Mondays - Nov 9 - Nov 23 Coventry"}, {"@type": "Offer", "sku": "SQ3231903", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "3wks Tuesdays - Dec 1 - Dec 15 Coventry"}, {"@type": "Offer", "sku": "SQ5559634", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "3wks Wednesdays - Jan 13 - Jan 27 Coventry"}, {"@type": "Offer", "sku": "SQ0659870", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "3wks Thursdays - Jan 28 - Feb 11 Coventry"}, {"@type": "Offer", "sku": "SQ0358019", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "3wks Tuesdays - Mar 2 - Mar 16 Coventry"}, {"@type": "Offer", "sku": "SQ0618983", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "3wks Thursdays  Apr 1 - Apr 15 Coventry"}, {"@type": "Offer", "sku": "SQ5714218", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "3wks Wednesdays May 12 - May 26 Coventry"}, {"@type": "Offer", "sku": "SQ7630533", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "3wks Mondays  - Jun 7  - Jun 21 Coventry"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ5616379", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "3wks Mondays - Nov 9 - Nov 23 Coventry"}, {"@type": "Offer", "sku": "SQ3231903", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "3wks Tuesdays - Dec 1 - Dec 15 Coventry"}, {"@type": "Offer", "sku": "SQ5559634", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "3wks Wednesdays - Jan 13 - Jan 27 Coventry"}, {"@type": "Offer", "sku": "SQ0659870", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "3wks Thursdays - Jan 28 - Feb 11 Coventry"}, {"@type": "Offer", "sku": "SQ0358019", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "3wks Tuesdays - Mar 2 - Mar 16 Coventry"}, {"@type": "Offer", "sku": "SQ0618983", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "3wks Thursdays  Apr 1 - Apr 15 Coventry"}, {"@type": "Offer", "sku": "SQ5714218", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "3wks Wednesdays May 12 - May 26 Coventry"}, {"@type": "Offer", "sku": "SQ7630533", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "3wks Mondays  - Jun 7  - Jun 21 Coventry"}]</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -742,7 +742,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ2592535", "price": "195.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ2592535", "price": "195.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31"}]</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -798,7 +798,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8599409", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Tue 20 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7560082", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Tue 20 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7443277", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Tue 20 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1660230", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Thu 22 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1568285", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Thu 22 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5411810", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Thu 22 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1318075", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Sat 24 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8270632", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Sat 24 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ4260038", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Sat 24 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ6145280", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Sun 25 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2267773", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Sun 25 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2428415", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Sun 25 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1102782", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Tue 27 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5885147", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Tue 27 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3102560", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Tue 27 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7100218", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Thu 29 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2446216", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Thu 29 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3086312", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Thu 29 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8599409", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "Tue 20 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7560082", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "Tue 20 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7443277", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "Tue 20 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1660230", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "Thu 22 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1568285", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "Thu 22 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5411810", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "Thu 22 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1318075", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "Sat 24 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8270632", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "Sat 24 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ4260038", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "Sat 24 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ6145280", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "Sun 25 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2267773", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "Sun 25 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2428415", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "Sun 25 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1102782", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "Tue 27 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5885147", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "Tue 27 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3102560", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "Tue 27 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7100218", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "Thu 29 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2446216", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "Thu 29 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3086312", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "Thu 29 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -854,7 +854,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ5650040", "price": "30.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ5650040", "price": "30.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31"}]</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -910,7 +910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ5540434", "price": "875.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ5540434", "price": "875.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31"}]</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -966,7 +966,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ2754105", "price": "925.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ2754105", "price": "925.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31"}]</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ0105911", "price": "135.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "16x12 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ4206024", "price": "177.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "24x16 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ0781804", "price": "219.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "30x20 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ3982814", "price": "306.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "36x24 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ8209269", "price": "336.65", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "40x30 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ7901040", "price": "414.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "48x36 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ7260825", "price": "459.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "60x40 Canvas Wrap Round"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ0105911", "price": "135.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "16x12 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ4206024", "price": "177.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "24x16 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ0781804", "price": "219.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "30x20 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ3982814", "price": "306.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "36x24 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ8209269", "price": "336.65", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "40x30 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ7901040", "price": "414.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "48x36 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ7260825", "price": "459.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "60x40 Canvas Wrap Round"}]</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ4872440", "price": "50.57", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "16x12 Print"}, {"@type": "Offer", "sku": "SQ0453600", "price": "95.78", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "24x16 Print"}, {"@type": "Offer", "sku": "SQ7485354", "price": "138.86", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "30x20 Print"}, {"@type": "Offer", "sku": "SQ0167262", "price": "161.38", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "36x24 Print"}, {"@type": "Offer", "sku": "SQ1664775", "price": "217.23", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "40x30 Print"}, {"@type": "Offer", "sku": "SQ0377820", "price": "305.05", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "48x36 Print"}, {"@type": "Offer", "sku": "SQ8780582", "price": "416.85", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "60x40 Print"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ4872440", "price": "50.57", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "16x12 Print"}, {"@type": "Offer", "sku": "SQ0453600", "price": "95.78", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "24x16 Print"}, {"@type": "Offer", "sku": "SQ7485354", "price": "138.86", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "30x20 Print"}, {"@type": "Offer", "sku": "SQ0167262", "price": "161.38", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "36x24 Print"}, {"@type": "Offer", "sku": "SQ1664775", "price": "217.23", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "40x30 Print"}, {"@type": "Offer", "sku": "SQ0377820", "price": "305.05", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "48x36 Print"}, {"@type": "Offer", "sku": "SQ8780582", "price": "416.85", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "60x40 Print"}]</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ6583676", "price": "360.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "4 x 2hr sessions - weekday daytime", "priceSpecification": {"price": "360.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ6583676", "price": "360.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "4 x 2hr sessions - weekday daytime", "priceSpecification": {"price": "360.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ6825544", "price": "133.85", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "16x12 Print (with Frame 20x16)"}, {"@type": "Offer", "sku": "SQ3786581", "price": "191.50", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "24x16 Print (with Frame 30x20)"}, {"@type": "Offer", "sku": "SQ1355351", "price": "267.43", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "30x20 Print (with Frame 40x30)"}, {"@type": "Offer", "sku": "SQ0156134", "price": "356.90", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "36x24 Print (with Frame 48x36)"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ6825544", "price": "133.85", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "16x12 Print (with Frame 20x16)"}, {"@type": "Offer", "sku": "SQ3786581", "price": "191.50", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "24x16 Print (with Frame 30x20)"}, {"@type": "Offer", "sku": "SQ1355351", "price": "267.43", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "30x20 Print (with Frame 40x30)"}, {"@type": "Offer", "sku": "SQ0156134", "price": "356.90", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "36x24 Print (with Frame 48x36)"}]</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ0939451", "price": "45.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Sun May 23rd 2027 - 15:00 - 17:00"}, {"@type": "Offer", "sku": "SQ3644687", "price": "45.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Sun Jul 11th 2027 - 15:00 - 17:00"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ0939451", "price": "45.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "Sun May 23rd 2027 - 15:00 - 17:00"}, {"@type": "Offer", "sku": "SQ3644687", "price": "45.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "Sun Jul 11th 2027 - 15:00 - 17:00"}]</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9898707", "price": "400.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "priceSpecification": {"price": "400.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9898707", "price": "400.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "priceSpecification": {"price": "400.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ5158309", "price": "1075.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Fri 13 Nov - 15 Nov - 3 Days 2026", "priceSpecification": {"price": "1075.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9016326", "price": "1075.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Fri 22 Jan - 24 Jan - 3 Days 2027"}, {"@type": "Offer", "sku": "SQ9100538", "price": "1075.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Fri 24 Sep - 26 Sep - 3 Days 2027", "priceSpecification": {"price": "1075.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ5158309", "price": "1075.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "Fri 13 Nov - 15 Nov - 3 Days 2026", "priceSpecification": {"price": "1075.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9016326", "price": "1075.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "Fri 22 Jan - 24 Jan - 3 Days 2027"}, {"@type": "Offer", "sku": "SQ9100538", "price": "1075.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "Fri 24 Sep - 26 Sep - 3 Days 2027", "priceSpecification": {"price": "1075.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8457424", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Padley and Bolehill Sun 1st Nov  2026 09:30am - 4:00pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9037810", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Padley and Bolehill Sat 7th Nov  2026 09:30am - 4:00pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2363666", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Padley and Bolehill Sat 22nd May 2027 - 09:30 - 16:00", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3794821", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Padley and Bolehill Sat 16th Oct  2027 09:30am - 4:00pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8457424", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "Padley and Bolehill Sun 1st Nov  2026 09:30am - 4:00pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9037810", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "Padley and Bolehill Sat 7th Nov  2026 09:30am - 4:00pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2363666", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "Padley and Bolehill Sat 22nd May 2027 - 09:30 - 16:00", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3794821", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "Padley and Bolehill Sat 16th Oct  2027 09:30am - 4:00pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ3856406", "price": "950.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ3856406", "price": "950.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31"}]</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8747213", "price": "1075.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8747213", "price": "1075.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31"}]</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8503376", "price": "975.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8503376", "price": "975.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31"}]</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ7526725", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Coventry 3 wks - Mon 7 Sep - 21 Sep 2026"}, {"@type": "Offer", "sku": "SQ6831161", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Coventry 3 wks - Thu 12 Nov - 26 Nov 2026"}, {"@type": "Offer", "sku": "SQ1021857", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Coventry 3 wks - Tue 12 Jan - 26 Jan 2027"}, {"@type": "Offer", "sku": "SQ3349262", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Coventry 3 wks - Thu 6 May - 20 May 2027"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ7526725", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "Coventry 3 wks - Mon 7 Sep - 21 Sep 2026"}, {"@type": "Offer", "sku": "SQ6831161", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "Coventry 3 wks - Thu 12 Nov - 26 Nov 2026"}, {"@type": "Offer", "sku": "SQ1021857", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "Coventry 3 wks - Tue 12 Jan - 26 Jan 2027"}, {"@type": "Offer", "sku": "SQ3349262", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "Coventry 3 wks - Thu 6 May - 20 May 2027"}]</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ0932604", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Mon 22 Mar 2027 - 18:00 - 20:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1178418", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Wed 14 Apr 2027 - 18:30 - 20:30", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9140400", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Wed 5 May 2027 - 18:00 - 20:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8220723", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Wed 22 Sep 2027 - 17:45 - 19:45", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ0932604", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "Mon 22 Mar 2027 - 18:00 - 20:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1178418", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "Wed 14 Apr 2027 - 18:30 - 20:30", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9140400", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "Wed 5 May 2027 - 18:00 - 20:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8220723", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "Wed 22 Sep 2027 - 17:45 - 19:45", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9080164", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Sat 6th Mar 2027 - 10:00 - 13:30"}, {"@type": "Offer", "sku": "SQ6636860", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Fri 14th May 2027 - 10:00 - 13:30"}, {"@type": "Offer", "sku": "SQ8778402", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Sat 9th Oct 2027 - 10:00 - 13:30"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9080164", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "Sat 6th Mar 2027 - 10:00 - 13:30"}, {"@type": "Offer", "sku": "SQ6636860", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "Fri 14th May 2027 - 10:00 - 13:30"}, {"@type": "Offer", "sku": "SQ8778402", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "Sat 9th Oct 2027 - 10:00 - 13:30"}]</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9466277", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9466277", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31"}]</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ3113323", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "12 x £50 = £600"}, {"@type": "Offer", "sku": "SQ4824271", "price": "60.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "12 x £60 = £720"}, {"@type": "Offer", "sku": "SQ5162846", "price": "65.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "12 x £65 = £780"}, {"@type": "Offer", "sku": "SQ0960457", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "12 x £75 = £900"}, {"@type": "Offer", "sku": "SQ6021981", "price": "85.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "12 x £85 = £1020"}, {"@type": "Offer", "sku": "SQ3596605", "price": "100.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "12 x £100 = £1200"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ3113323", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "12 x £50 = £600"}, {"@type": "Offer", "sku": "SQ4824271", "price": "60.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "12 x £60 = £720"}, {"@type": "Offer", "sku": "SQ5162846", "price": "65.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "12 x £65 = £780"}, {"@type": "Offer", "sku": "SQ0960457", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "12 x £75 = £900"}, {"@type": "Offer", "sku": "SQ6021981", "price": "85.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "12 x £85 = £1020"}, {"@type": "Offer", "sku": "SQ3596605", "price": "100.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "12 x £100 = £1200"}]</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ7900435", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "2027 - Sat 14th Aug 18:15 21:15 - Derbyshire Surprise View"}, {"@type": "Offer", "sku": "SQ4225053", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "2027 - Sun 15 Aug - The Roaches &amp; Ramshaw 05:45 - 08:45"}, {"@type": "Offer", "sku": "SQ8702063", "price": "200.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Both sessions - 14 and 15 Aug - sunset and sunrise"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ7900435", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "2027 - Sat 14th Aug 18:15 21:15 - Derbyshire Surprise View"}, {"@type": "Offer", "sku": "SQ4225053", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "2027 - Sun 15 Aug - The Roaches &amp; Ramshaw 05:45 - 08:45"}, {"@type": "Offer", "sku": "SQ8702063", "price": "200.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "Both sessions - 14 and 15 Aug - sunset and sunrise"}]</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ0796814", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Mon 5th Oct 2026 - 17:30 - 19:45", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9554270", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Tue 13th Apr 2027 - 18:15 - 20:15", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5307067", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Mon 10th May 2027 - 18:30 - 20:30", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3572999", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Mon 6th Sep 2027 - 18:00 - 20:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ0796814", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "Mon 5th Oct 2026 - 17:30 - 19:45", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9554270", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "Tue 13th Apr 2027 - 18:15 - 20:15", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5307067", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "Mon 10th May 2027 - 18:30 - 20:30", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3572999", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "Mon 6th Sep 2027 - 18:00 - 20:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ6748367", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Sat 3rd Jul 2027 - 18:00 20:45"}, {"@type": "Offer", "sku": "SQ7542811", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Sat 10th Jul 2027 - 18:00 20:45"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ6748367", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "Sat 3rd Jul 2027 - 18:00 20:45"}, {"@type": "Offer", "sku": "SQ7542811", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "Sat 10th Jul 2027 - 18:00 20:45"}]</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ1461156", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Zoom Standard (Weekdays 9-5) - 1 x 1hr - Pay as you go    £50"}, {"@type": "Offer", "sku": "SQ5568703", "price": "170.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Zoom Standard (Weekdays 9-5) - 4 x 1hr (15% Off)          £170"}, {"@type": "Offer", "sku": "SQ6341100", "price": "240.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Zoom Standard (Weekdays 9-5) - 6 x 1hr (20% Off)          £240"}, {"@type": "Offer", "sku": "SQ2281758", "price": "300.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Zoom Standard (Weekdays 9-5) - 8 x 1hr (25% Off)          £300"}, {"@type": "Offer", "sku": "SQ2043258", "price": "450.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Zoom Standard (Weekdays 9-5) - 12 x 1hr (25% Off)         £450"}, {"@type": "Offer", "sku": "SQ6476466", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Zoom Premium (Eve/Weekend 9-9) - 1 x 1hr - Pay as you go  £75"}, {"@type": "Offer", "sku": "SQ4036849", "price": "255.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Zoom Premium (Eve/Weekend 9-9) - 4 x 1hr (15% Off)        £255"}, {"@type": "Offer", "sku": "SQ6369047", "price": "360.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Zoom Premium (Eve/Weekend 9-9) - 6 x 1hr (20% Off)        £360"}, {"@type": "Offer", "sku": "SQ7040572", "price": "450.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Zoom Premium (Eve/Weekend 9-9) - 8 x 1hr (25% Off)        £450"}, {"@type": "Offer", "sku": "SQ6714463", "price": "675.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Zoom Premium (Eve/Weekend 9-9) - 12 x 1hr (25% Off)       £675"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ1461156", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "Zoom Standard (Weekdays 9-5) - 1 x 1hr - Pay as you go    £50"}, {"@type": "Offer", "sku": "SQ5568703", "price": "170.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "Zoom Standard (Weekdays 9-5) - 4 x 1hr (15% Off)          £170"}, {"@type": "Offer", "sku": "SQ6341100", "price": "240.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "Zoom Standard (Weekdays 9-5) - 6 x 1hr (20% Off)          £240"}, {"@type": "Offer", "sku": "SQ2281758", "price": "300.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "Zoom Standard (Weekdays 9-5) - 8 x 1hr (25% Off)          £300"}, {"@type": "Offer", "sku": "SQ2043258", "price": "450.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "Zoom Standard (Weekdays 9-5) - 12 x 1hr (25% Off)         £450"}, {"@type": "Offer", "sku": "SQ6476466", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "Zoom Premium (Eve/Weekend 9-9) - 1 x 1hr - Pay as you go  £75"}, {"@type": "Offer", "sku": "SQ4036849", "price": "255.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "Zoom Premium (Eve/Weekend 9-9) - 4 x 1hr (15% Off)        £255"}, {"@type": "Offer", "sku": "SQ6369047", "price": "360.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "Zoom Premium (Eve/Weekend 9-9) - 6 x 1hr (20% Off)        £360"}, {"@type": "Offer", "sku": "SQ7040572", "price": "450.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "Zoom Premium (Eve/Weekend 9-9) - 8 x 1hr (25% Off)        £450"}, {"@type": "Offer", "sku": "SQ6714463", "price": "675.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "Zoom Premium (Eve/Weekend 9-9) - 12 x 1hr (25% Off)       £675"}]</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ4217445", "price": "250.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "4 x £250 = £1000"}, {"@type": "Offer", "sku": "SQ6277577", "price": "300.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "4 x £300 = £1200"}, {"@type": "Offer", "sku": "SQ7788516", "price": "350.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "4 x £350 = £1400"}, {"@type": "Offer", "sku": "SQ5124608", "price": "400.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "4 x 400 = £1600"}, {"@type": "Offer", "sku": "SQ2657628", "price": "500.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "4 x £500 = £2000"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ4217445", "price": "250.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "4 x £250 = £1000"}, {"@type": "Offer", "sku": "SQ6277577", "price": "300.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "4 x £300 = £1200"}, {"@type": "Offer", "sku": "SQ7788516", "price": "350.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "4 x £350 = £1400"}, {"@type": "Offer", "sku": "SQ5124608", "price": "400.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "4 x 400 = £1600"}, {"@type": "Offer", "sku": "SQ2657628", "price": "500.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "4 x £500 = £2000"}]</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ7839038", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Mon- Fri 9am-5pm 1 x 1hr"}, {"@type": "Offer", "sku": "SQ3867813", "price": "170.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Mon- Fri 9am-5pm 4 x 1hr"}, {"@type": "Offer", "sku": "SQ8903198", "price": "240.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Mon- Fri 9am-5pm 6 x 1hr"}, {"@type": "Offer", "sku": "SQ4831915", "price": "300.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Mon- Fri 9am-5pm  8x 1hr"}, {"@type": "Offer", "sku": "SQ1077689", "price": "450.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Mon- Fri 9am-5pm 12 x 1hr"}, {"@type": "Offer", "sku": "SQ8233730", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Mon- Sun 9am-9pm 1 x 1hr"}, {"@type": "Offer", "sku": "SQ9139531", "price": "255.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Mon- Sun 9am-9pm 4 x 1hr"}, {"@type": "Offer", "sku": "SQ0776423", "price": "360.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Mon- Sun 9am-9pm 6 x 1hr"}, {"@type": "Offer", "sku": "SQ2385997", "price": "450.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Mon- Sun 9am-9pm 8 x 1hr"}, {"@type": "Offer", "sku": "SQ9440259", "price": "675.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Mon- Sun 9am-9pm 12 x 1hr"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ7839038", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "Mon- Fri 9am-5pm 1 x 1hr"}, {"@type": "Offer", "sku": "SQ3867813", "price": "170.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "Mon- Fri 9am-5pm 4 x 1hr"}, {"@type": "Offer", "sku": "SQ8903198", "price": "240.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "Mon- Fri 9am-5pm 6 x 1hr"}, {"@type": "Offer", "sku": "SQ4831915", "price": "300.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "Mon- Fri 9am-5pm  8x 1hr"}, {"@type": "Offer", "sku": "SQ1077689", "price": "450.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "Mon- Fri 9am-5pm 12 x 1hr"}, {"@type": "Offer", "sku": "SQ8233730", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "Mon- Sun 9am-9pm 1 x 1hr"}, {"@type": "Offer", "sku": "SQ9139531", "price": "255.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "Mon- Sun 9am-9pm 4 x 1hr"}, {"@type": "Offer", "sku": "SQ0776423", "price": "360.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "Mon- Sun 9am-9pm 6 x 1hr"}, {"@type": "Offer", "sku": "SQ2385997", "price": "450.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "Mon- Sun 9am-9pm 8 x 1hr"}, {"@type": "Offer", "sku": "SQ9440259", "price": "675.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "Mon- Sun 9am-9pm 12 x 1hr"}]</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ2827052", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Sun 10 Jan 2027 - 10am - 4pm"}, {"@type": "Offer", "sku": "SQ0512761", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Sun 2nd May 2027 - 10am - 4pm"}, {"@type": "Offer", "sku": "SQ4914997", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Sun 1st Aug 2027 - 10am - 4pm"}, {"@type": "Offer", "sku": "SQ4894934", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Sun 17th Oct 2027 - 10am - 4pm"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ2827052", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "Sun 10 Jan 2027 - 10am - 4pm"}, {"@type": "Offer", "sku": "SQ0512761", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "Sun 2nd May 2027 - 10am - 4pm"}, {"@type": "Offer", "sku": "SQ4914997", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "Sun 1st Aug 2027 - 10am - 4pm"}, {"@type": "Offer", "sku": "SQ4894934", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "Sun 17th Oct 2027 - 10am - 4pm"}]</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ2176971", "price": "995.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "priceSpecification": {"price": "995.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ2176971", "price": "995.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "priceSpecification": {"price": "995.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ4066377", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ4066377", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -2422,7 +2422,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ5697158", "price": "695.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ5697158", "price": "695.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31"}]</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ1654264", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Fri Jan 2 Hay Woods - Solihull"}, {"@type": "Offer", "sku": "SQ1288994", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Mon Feb 2 - Tile Hill Nature Reserve - Coventry"}, {"@type": "Offer", "sku": "SQ0063623", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Sun May 3 - Millisons Wood, Meriden"}, {"@type": "Offer", "sku": "SQ6524101", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Fri Oct 16 - Piles Coppice, Coventry"}, {"@type": "Offer", "sku": "SQ7078023", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Fri Nov 6 - Crackley Wood, Kenilworth"}, {"@type": "Offer", "sku": "SQ3819844", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25", "name": "Fri Dec 4 - Hay Wood - Lapworth"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ1654264", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "Fri Jan 2 Hay Woods - Solihull"}, {"@type": "Offer", "sku": "SQ1288994", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "Mon Feb 2 - Tile Hill Nature Reserve - Coventry"}, {"@type": "Offer", "sku": "SQ0063623", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "Sun May 3 - Millisons Wood, Meriden"}, {"@type": "Offer", "sku": "SQ6524101", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "Fri Oct 16 - Piles Coppice, Coventry"}, {"@type": "Offer", "sku": "SQ7078023", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "Fri Nov 6 - Crackley Wood, Kenilworth"}, {"@type": "Offer", "sku": "SQ3819844", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "Fri Dec 4 - Hay Wood - Lapworth"}]</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9211910", "price": "895.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-25", "priceValidUntil": "2027-10-25"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9211910", "price": "895.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31"}]</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -2559,6 +2559,62 @@
       <c r="L38" t="inlineStr">
         <is>
           <t>event</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Photography Gift Vouchers | Digital eCard | Email Delivery</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Photography Gift Vouchers | Digital eCard | Email Delivery</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1556527290185-GZJ3ZPC3M7AU34BFFVOE/photography-gift-vouchers.png</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>https://www.alanranger.com/photography-services-near-me/photography-gift-vouchers</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>online;1-2-1-private-lessons;gift-voucher;photography-services;photography-tuition, photography-gift-vouchers;photography-presents</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>[{"@type": "Offer", "sku": "SUP-PHOTOGRAPHY-GIFT-VOUCHERS-DIGITA", "price": "5.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-10-31", "priceValidUntil": "2027-10-31", "name": "Photography Gift Vouchers | Digital eCard | Email Delivery"}]</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>1</v>
+      </c>
+      <c r="H39" t="n">
+        <v>5</v>
+      </c>
+      <c r="I39" t="n">
+        <v>5</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>SUP-PHOTOGRAPHY-GIFT-VOUCHERS-DIGITA</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>SUP-PHOTOGRAPHY-GIFT-VOUCHERS-DIGITA</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>product</t>
         </is>
       </c>
     </row>
